--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>McGee Lake Mo, Co, U Cu Prospect</t>
+          <t>Mountain Top Cu Mine</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A15-024</t>
+          <t>K10-004</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mo, Co, U, Cu, Ag</t>
+          <t>Cu, As, Ag, Au</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I35" t="b">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>U 2.4%, Ag 314.00 g/t, Co 0.599%, Mo 0.285%, Cu 0.0554%</t>
+          <t>Cu 2%, Au 1.73 g/t, Ag 50.00 g/t, Te 0.0014%, Bi 0.017%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3136,23 +3136,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>44</v>
       </c>
       <c r="V35" t="n">
-        <v>44.99925</v>
+        <v>46.60502</v>
       </c>
       <c r="W35" t="n">
-        <v>-64.56028000000001</v>
+        <v>-60.92288</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A15-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-004</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coxheath Cu, Mo, Co, Au, Ag Deposit</t>
+          <t>McGee Lake Mo, Co, U Cu Prospect</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>K01-001</t>
+          <t>A15-024</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cu, Mo, Ag, Au, Co, As, Bi, Hg, Sb</t>
+          <t>Mo, Co, U, Cu, Ag</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I36" t="b">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Cu 2%, Co 0.365%, Au 0.51 g/t, Ag 15.80 g/t, Mo 0.0347%</t>
+          <t>U 2.4%, Ag 314.00 g/t, Co 0.599%, Mo 0.285%, Cu 0.0554%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3212,23 +3212,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U36" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V36" t="n">
-        <v>46.0864</v>
+        <v>44.99925</v>
       </c>
       <c r="W36" t="n">
-        <v>-60.35439</v>
+        <v>-64.56028000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A15-024</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mountain Top Cu Mine</t>
+          <t>Coxheath Cu, Mo, Co, Au, Ag Deposit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>K10-004</t>
+          <t>K01-001</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cu, As, Ag, Au</t>
+          <t>Cu, Mo, Ag, Au, Co, As, Bi, Hg, Sb</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cu 2%, Au 1.73 g/t, Ag 50.00 g/t, Te 0.0014%, Bi 0.017%</t>
+          <t>Cu 2%, Co 0.365%, Au 0.51 g/t, Ag 15.80 g/t, Mo 0.0347%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3525,14 +3525,14 @@
         <v>43</v>
       </c>
       <c r="V40" t="n">
-        <v>46.60502</v>
+        <v>46.0864</v>
       </c>
       <c r="W40" t="n">
-        <v>-60.92288</v>
+        <v>-60.35439</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-001</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -22234,12 +22234,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Grand Lake Au, Ag Prospect</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>D13-006</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -22251,12 +22251,12 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Au, Ag</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I297" t="b">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>Au 0.80 g/t, Ag 6.00 g/t, W 0.0004%, Zn 0.0054%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M297" t="inlineStr"/>
@@ -22293,14 +22293,14 @@
         <v>28</v>
       </c>
       <c r="V297" t="n">
-        <v>44.87004</v>
+        <v>45.66247</v>
       </c>
       <c r="W297" t="n">
-        <v>-63.63384</v>
+        <v>-60.50348</v>
       </c>
       <c r="X297" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -22310,12 +22310,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -22327,7 +22327,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M298" t="inlineStr"/>
@@ -22366,17 +22366,17 @@
         <v>325</v>
       </c>
       <c r="U298" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V298" t="n">
-        <v>46.44885</v>
+        <v>45.66068</v>
       </c>
       <c r="W298" t="n">
-        <v>-60.58676</v>
+        <v>-60.49983</v>
       </c>
       <c r="X298" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -22386,12 +22386,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Grand Lake Au, Ag Prospect</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>D13-006</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -22403,12 +22403,12 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Au, Ag</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I299" t="b">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Au 0.80 g/t, Ag 6.00 g/t, W 0.0004%, Zn 0.0054%</t>
         </is>
       </c>
       <c r="M299" t="inlineStr"/>
@@ -22442,17 +22442,17 @@
         <v>325</v>
       </c>
       <c r="U299" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V299" t="n">
-        <v>46.44219</v>
+        <v>44.87004</v>
       </c>
       <c r="W299" t="n">
-        <v>-60.58706</v>
+        <v>-63.63384</v>
       </c>
       <c r="X299" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-006</t>
         </is>
       </c>
     </row>
@@ -22462,12 +22462,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>East Dalhousie Cu, Sn, Li, Zn, Ag, As Prospect</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>A10-001</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -22479,12 +22479,12 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Sn, Cu, Li, Zn, Ag, As</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I300" t="b">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>Sn 0.0732%, Cu 0.143%, Ag 5.70 g/t, Be 0.00024%, Bi 0.00317%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr"/>
@@ -22518,17 +22518,17 @@
         <v>325</v>
       </c>
       <c r="U300" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V300" t="n">
-        <v>44.71912</v>
+        <v>45.66139</v>
       </c>
       <c r="W300" t="n">
-        <v>-64.79982</v>
+        <v>-60.50763</v>
       </c>
       <c r="X300" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -23222,12 +23222,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -23239,12 +23239,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I310" t="b">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M310" t="inlineStr"/>
@@ -23281,14 +23281,14 @@
         <v>27</v>
       </c>
       <c r="V310" t="n">
-        <v>45.66068</v>
+        <v>45.25896</v>
       </c>
       <c r="W310" t="n">
-        <v>-60.49983</v>
+        <v>-62.86207</v>
       </c>
       <c r="X310" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -23298,12 +23298,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -23315,12 +23315,12 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I311" t="b">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M311" t="inlineStr"/>
@@ -23357,14 +23357,14 @@
         <v>27</v>
       </c>
       <c r="V311" t="n">
-        <v>45.66139</v>
+        <v>45.29028</v>
       </c>
       <c r="W311" t="n">
-        <v>-60.50763</v>
+        <v>-62.75575</v>
       </c>
       <c r="X311" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -23374,12 +23374,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>East Dalhousie Cu, Sn, Li, Zn, Ag, As Prospect</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>A10-001</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Sn, Cu, Li, Zn, Ag, As</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Sn 0.0732%, Cu 0.143%, Ag 5.70 g/t, Be 0.00024%, Bi 0.00317%</t>
         </is>
       </c>
       <c r="M312" t="inlineStr"/>
@@ -23433,14 +23433,14 @@
         <v>27</v>
       </c>
       <c r="V312" t="n">
-        <v>45.29028</v>
+        <v>44.71912</v>
       </c>
       <c r="W312" t="n">
-        <v>-62.75575</v>
+        <v>-64.79982</v>
       </c>
       <c r="X312" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-001</t>
         </is>
       </c>
     </row>
@@ -23450,12 +23450,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -23467,12 +23467,12 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I313" t="b">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M313" t="inlineStr"/>
@@ -23509,14 +23509,14 @@
         <v>27</v>
       </c>
       <c r="V313" t="n">
-        <v>45.26433</v>
+        <v>46.44219</v>
       </c>
       <c r="W313" t="n">
-        <v>-62.84191</v>
+        <v>-60.58706</v>
       </c>
       <c r="X313" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -23526,12 +23526,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -23543,12 +23543,12 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I314" t="b">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M314" t="inlineStr"/>
@@ -23585,14 +23585,14 @@
         <v>27</v>
       </c>
       <c r="V314" t="n">
-        <v>45.25896</v>
+        <v>46.44885</v>
       </c>
       <c r="W314" t="n">
-        <v>-62.86207</v>
+        <v>-60.58676</v>
       </c>
       <c r="X314" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -23754,12 +23754,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I317" t="b">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M317" t="inlineStr"/>
@@ -23813,14 +23813,14 @@
         <v>27</v>
       </c>
       <c r="V317" t="n">
-        <v>45.66247</v>
+        <v>45.26433</v>
       </c>
       <c r="W317" t="n">
-        <v>-60.50348</v>
+        <v>-62.84191</v>
       </c>
       <c r="X317" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -24818,12 +24818,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Morleys Pegmatite</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>A09-014</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -24835,12 +24835,12 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>W, Sn, Jasper, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I331" t="b">
@@ -24856,7 +24856,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>W 0.1%, Be 0.00032%, Bi 0.0009%, Cu 0.0051%, Li 0.0132%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M331" t="inlineStr"/>
@@ -24877,14 +24877,14 @@
         <v>26</v>
       </c>
       <c r="V331" t="n">
-        <v>44.73955</v>
+        <v>45.39942</v>
       </c>
       <c r="W331" t="n">
-        <v>-64.4462</v>
+        <v>-61.45755</v>
       </c>
       <c r="X331" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -24894,12 +24894,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Morleys Pegmatite</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A09-014</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>W, Sn, Jasper, F</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I332" t="b">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>W 0.1%, Be 0.00032%, Bi 0.0009%, Cu 0.0051%, Li 0.0132%</t>
         </is>
       </c>
       <c r="M332" t="inlineStr"/>
@@ -24953,14 +24953,14 @@
         <v>26</v>
       </c>
       <c r="V332" t="n">
-        <v>46.51529</v>
+        <v>44.73955</v>
       </c>
       <c r="W332" t="n">
-        <v>-60.64417</v>
+        <v>-64.4462</v>
       </c>
       <c r="X332" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-014</t>
         </is>
       </c>
     </row>
@@ -25029,10 +25029,10 @@
         <v>26</v>
       </c>
       <c r="V333" t="n">
-        <v>46.51478</v>
+        <v>46.51529</v>
       </c>
       <c r="W333" t="n">
-        <v>-60.64575</v>
+        <v>-60.64417</v>
       </c>
       <c r="X333" t="inlineStr">
         <is>
@@ -25105,10 +25105,10 @@
         <v>26</v>
       </c>
       <c r="V334" t="n">
-        <v>46.51814</v>
+        <v>46.51478</v>
       </c>
       <c r="W334" t="n">
-        <v>-60.655</v>
+        <v>-60.64575</v>
       </c>
       <c r="X334" t="inlineStr">
         <is>
@@ -25181,10 +25181,10 @@
         <v>26</v>
       </c>
       <c r="V335" t="n">
-        <v>46.51553</v>
+        <v>46.51814</v>
       </c>
       <c r="W335" t="n">
-        <v>-60.64503</v>
+        <v>-60.655</v>
       </c>
       <c r="X335" t="inlineStr">
         <is>
@@ -25198,12 +25198,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -25215,12 +25215,12 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I336" t="b">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M336" t="inlineStr"/>
@@ -25257,14 +25257,14 @@
         <v>26</v>
       </c>
       <c r="V336" t="n">
-        <v>45.40126</v>
+        <v>46.51553</v>
       </c>
       <c r="W336" t="n">
-        <v>-61.45511</v>
+        <v>-60.64503</v>
       </c>
       <c r="X336" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -25274,12 +25274,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>K03-010</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -25291,12 +25291,12 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I337" t="b">
@@ -25312,7 +25312,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M337" t="inlineStr"/>
@@ -25333,14 +25333,14 @@
         <v>26</v>
       </c>
       <c r="V337" t="n">
-        <v>46.12968</v>
+        <v>45.40126</v>
       </c>
       <c r="W337" t="n">
-        <v>-61.12853</v>
+        <v>-61.45511</v>
       </c>
       <c r="X337" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -25350,12 +25350,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K03-010</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -25367,7 +25367,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -25388,7 +25388,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
         </is>
       </c>
       <c r="M338" t="inlineStr"/>
@@ -25409,14 +25409,14 @@
         <v>26</v>
       </c>
       <c r="V338" t="n">
-        <v>46.58857</v>
+        <v>46.12968</v>
       </c>
       <c r="W338" t="n">
-        <v>-60.8649</v>
+        <v>-61.12853</v>
       </c>
       <c r="X338" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
         </is>
       </c>
     </row>
@@ -25426,12 +25426,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>K03-010</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -25443,7 +25443,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M339" t="inlineStr"/>
@@ -25485,14 +25485,14 @@
         <v>26</v>
       </c>
       <c r="V339" t="n">
-        <v>46.12375</v>
+        <v>46.58857</v>
       </c>
       <c r="W339" t="n">
-        <v>-61.13508</v>
+        <v>-60.8649</v>
       </c>
       <c r="X339" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -25502,12 +25502,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K03-010</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -25519,7 +25519,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
         </is>
       </c>
       <c r="M340" t="inlineStr"/>
@@ -25561,14 +25561,14 @@
         <v>26</v>
       </c>
       <c r="V340" t="n">
-        <v>46.59758</v>
+        <v>46.12375</v>
       </c>
       <c r="W340" t="n">
-        <v>-60.88034</v>
+        <v>-61.13508</v>
       </c>
       <c r="X340" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
         </is>
       </c>
     </row>
@@ -25578,12 +25578,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -25595,12 +25595,12 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I341" t="b">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M341" t="inlineStr"/>
@@ -25637,14 +25637,14 @@
         <v>26</v>
       </c>
       <c r="V341" t="n">
-        <v>44.6087</v>
+        <v>46.59758</v>
       </c>
       <c r="W341" t="n">
-        <v>-65.6011</v>
+        <v>-60.88034</v>
       </c>
       <c r="X341" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -25713,10 +25713,10 @@
         <v>26</v>
       </c>
       <c r="V342" t="n">
-        <v>44.6151</v>
+        <v>44.6087</v>
       </c>
       <c r="W342" t="n">
-        <v>-65.58083999999999</v>
+        <v>-65.6011</v>
       </c>
       <c r="X342" t="inlineStr">
         <is>
@@ -25730,12 +25730,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>K03-010</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -25747,12 +25747,12 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I343" t="b">
@@ -25768,7 +25768,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M343" t="inlineStr"/>
@@ -25789,14 +25789,14 @@
         <v>26</v>
       </c>
       <c r="V343" t="n">
-        <v>46.12952</v>
+        <v>44.6151</v>
       </c>
       <c r="W343" t="n">
-        <v>-61.13022</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X343" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -25806,12 +25806,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K03-010</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -25823,12 +25823,12 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I344" t="b">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
         </is>
       </c>
       <c r="M344" t="inlineStr"/>
@@ -25865,14 +25865,14 @@
         <v>26</v>
       </c>
       <c r="V344" t="n">
-        <v>44.62709</v>
+        <v>46.12952</v>
       </c>
       <c r="W344" t="n">
-        <v>-65.56032</v>
+        <v>-61.13022</v>
       </c>
       <c r="X344" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
         </is>
       </c>
     </row>
@@ -25882,12 +25882,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -25920,7 +25920,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M345" t="inlineStr"/>
@@ -25941,14 +25941,14 @@
         <v>26</v>
       </c>
       <c r="V345" t="n">
-        <v>45.39942</v>
+        <v>44.62709</v>
       </c>
       <c r="W345" t="n">
-        <v>-61.45755</v>
+        <v>-65.56032</v>
       </c>
       <c r="X345" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -26017,10 +26017,10 @@
         <v>25</v>
       </c>
       <c r="V346" t="n">
-        <v>44.68634</v>
+        <v>44.69007</v>
       </c>
       <c r="W346" t="n">
-        <v>-63.97235</v>
+        <v>-63.97154</v>
       </c>
       <c r="X346" t="inlineStr">
         <is>
@@ -26093,10 +26093,10 @@
         <v>25</v>
       </c>
       <c r="V347" t="n">
-        <v>44.69007</v>
+        <v>44.68634</v>
       </c>
       <c r="W347" t="n">
-        <v>-63.97154</v>
+        <v>-63.97235</v>
       </c>
       <c r="X347" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -7670,12 +7670,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Whycocomagh Cu, Fe, W Occurrence</t>
+          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>F14-003</t>
+          <t>K10-066</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7687,12 +7687,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cu, W, Mo, Fe</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>W 0.0742%, Cu 0.959%, Ag 1.40 g/t, Au 0.11 g/t, Co 0.0044%</t>
+          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7720,23 +7720,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T96" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U96" t="n">
         <v>33</v>
       </c>
       <c r="V96" t="n">
-        <v>45.99025</v>
+        <v>46.52503</v>
       </c>
       <c r="W96" t="n">
-        <v>-61.10637</v>
+        <v>-60.71296</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lime Hill Zn and Wollastonite Deposit</t>
+          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>F14-012</t>
+          <t>K10-066</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Zn, Cu, W, Wollastonite</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
+          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7805,14 +7805,14 @@
         <v>33</v>
       </c>
       <c r="V97" t="n">
-        <v>45.77777</v>
+        <v>46.52383</v>
       </c>
       <c r="W97" t="n">
-        <v>-61.15731</v>
+        <v>-60.71507</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
         </is>
       </c>
     </row>
@@ -7822,12 +7822,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lime Hill Zn and Wollastonite Deposit</t>
+          <t>Whycocomagh Cu, Fe, W Occurrence</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>F14-012</t>
+          <t>F14-003</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zn, Cu, W, Wollastonite</t>
+          <t>Cu, W, Mo, Fe</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
+          <t>W 0.0742%, Cu 0.959%, Ag 1.40 g/t, Au 0.11 g/t, Co 0.0044%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -7872,23 +7872,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T98" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U98" t="n">
         <v>33</v>
       </c>
       <c r="V98" t="n">
-        <v>45.77684</v>
+        <v>45.99025</v>
       </c>
       <c r="W98" t="n">
-        <v>-61.1495</v>
+        <v>-61.10637</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-003</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
+          <t>Lime Hill Zn and Wollastonite Deposit</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>K10-066</t>
+          <t>F14-012</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -7915,12 +7915,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Zn, Cu, W, Wollastonite</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I99" t="b">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
+          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -7954,17 +7954,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V99" t="n">
-        <v>46.52383</v>
+        <v>45.77777</v>
       </c>
       <c r="W99" t="n">
-        <v>-60.71507</v>
+        <v>-61.15731</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
         </is>
       </c>
     </row>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
+          <t>Lime Hill Zn and Wollastonite Deposit</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>K10-066</t>
+          <t>F14-012</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7991,12 +7991,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Zn, Cu, W, Wollastonite</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
+          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -8030,17 +8030,17 @@
         <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V100" t="n">
-        <v>46.52503</v>
+        <v>45.77684</v>
       </c>
       <c r="W100" t="n">
-        <v>-60.71296</v>
+        <v>-61.1495</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gegogan Au District</t>
+          <t>Cochrane Hill Au District</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>F04-001</t>
+          <t>E01-007</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Pb, Zn</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8248,23 +8248,23 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U103" t="n">
         <v>30</v>
       </c>
       <c r="V103" t="n">
-        <v>45.04598</v>
+        <v>45.24893</v>
       </c>
       <c r="W103" t="n">
-        <v>-61.95574</v>
+        <v>-62.013</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Moose River Tungsten Deposit</t>
+          <t>Cochrane Hill Au District</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>D15-012</t>
+          <t>E01-007</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>W, Pt</t>
+          <t>Au, As, Pb, Zn</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8320,23 +8320,23 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T104" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U104" t="n">
         <v>30</v>
       </c>
       <c r="V104" t="n">
-        <v>44.97314</v>
+        <v>45.24892</v>
       </c>
       <c r="W104" t="n">
-        <v>-62.9798</v>
+        <v>-62.01122</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>A16-007</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Mn, Fe, Clay</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>30</v>
       </c>
       <c r="V105" t="n">
-        <v>44.84593</v>
+        <v>45.0448</v>
       </c>
       <c r="W105" t="n">
-        <v>-64.45107</v>
+        <v>-62.16418</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Indian Path Au-W Mine</t>
+          <t>North Star Au Mine</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>A08-018</t>
+          <t>F04-018</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Au, W</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>30</v>
       </c>
       <c r="V106" t="n">
-        <v>44.32606</v>
+        <v>45.16836</v>
       </c>
       <c r="W106" t="n">
-        <v>-64.34589</v>
+        <v>-61.65632</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Voglers Cove Au District</t>
+          <t>Indian Path Au-W Mine</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>A02-006</t>
+          <t>A08-018</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, W</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>30</v>
       </c>
       <c r="V107" t="n">
-        <v>44.20946</v>
+        <v>44.32356</v>
       </c>
       <c r="W107" t="n">
-        <v>-64.51952</v>
+        <v>-64.35141</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Indian Path Au-W Mine</t>
+          <t>Voglers Cove Au District</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>A08-018</t>
+          <t>A02-006</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Au, W</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>30</v>
       </c>
       <c r="V109" t="n">
-        <v>44.32356</v>
+        <v>44.20946</v>
       </c>
       <c r="W109" t="n">
-        <v>-64.35141</v>
+        <v>-64.51952</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-006</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Indian Path Au-W Mine</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>A08-018</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Au, W</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8761,14 +8761,14 @@
         <v>30</v>
       </c>
       <c r="V110" t="n">
-        <v>45.0448</v>
+        <v>44.32606</v>
       </c>
       <c r="W110" t="n">
-        <v>-62.16418</v>
+        <v>-64.34589</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
         </is>
       </c>
     </row>
@@ -8778,12 +8778,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cochrane Hill Au District</t>
+          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>E01-007</t>
+          <t>A16-007</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Au, As, Pb, Zn</t>
+          <t>Mn, Fe, Clay</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8824,23 +8824,23 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T111" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U111" t="n">
         <v>30</v>
       </c>
       <c r="V111" t="n">
-        <v>45.24892</v>
+        <v>44.84593</v>
       </c>
       <c r="W111" t="n">
-        <v>-62.01122</v>
+        <v>-64.45107</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cochrane Hill Au District</t>
+          <t>Moose River Tungsten Deposit</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>E01-007</t>
+          <t>D15-012</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Au, As, Pb, Zn</t>
+          <t>W, Pt</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8896,23 +8896,23 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T112" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U112" t="n">
         <v>30</v>
       </c>
       <c r="V112" t="n">
-        <v>45.24893</v>
+        <v>44.97314</v>
       </c>
       <c r="W112" t="n">
-        <v>-62.013</v>
+        <v>-62.9798</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-012</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>North Star Au Mine</t>
+          <t>Gegogan Au District</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>F04-018</t>
+          <t>F04-001</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8977,14 +8977,14 @@
         <v>30</v>
       </c>
       <c r="V113" t="n">
-        <v>45.16836</v>
+        <v>45.04598</v>
       </c>
       <c r="W113" t="n">
-        <v>-61.65632</v>
+        <v>-61.95574</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-001</t>
         </is>
       </c>
     </row>
@@ -22462,12 +22462,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -22479,12 +22479,12 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I300" t="b">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr"/>
@@ -22521,14 +22521,14 @@
         <v>27</v>
       </c>
       <c r="V300" t="n">
-        <v>46.60665</v>
+        <v>46.44885</v>
       </c>
       <c r="W300" t="n">
-        <v>-60.92386</v>
+        <v>-60.58676</v>
       </c>
       <c r="X300" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -22538,12 +22538,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -22555,12 +22555,12 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I301" t="b">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M301" t="inlineStr"/>
@@ -22597,14 +22597,14 @@
         <v>27</v>
       </c>
       <c r="V301" t="n">
-        <v>45.25896</v>
+        <v>46.44956</v>
       </c>
       <c r="W301" t="n">
-        <v>-62.86207</v>
+        <v>-60.57775</v>
       </c>
       <c r="X301" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -22614,12 +22614,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -22631,7 +22631,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -22652,7 +22652,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M302" t="inlineStr"/>
@@ -22673,14 +22673,14 @@
         <v>27</v>
       </c>
       <c r="V302" t="n">
-        <v>45.66247</v>
+        <v>46.44219</v>
       </c>
       <c r="W302" t="n">
-        <v>-60.50348</v>
+        <v>-60.58706</v>
       </c>
       <c r="X302" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -22690,12 +22690,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M303" t="inlineStr"/>
@@ -22749,14 +22749,14 @@
         <v>27</v>
       </c>
       <c r="V303" t="n">
-        <v>45.66068</v>
+        <v>46.44638</v>
       </c>
       <c r="W303" t="n">
-        <v>-60.49983</v>
+        <v>-60.57242</v>
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -22766,12 +22766,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -22783,12 +22783,12 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I304" t="b">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr"/>
@@ -22825,14 +22825,14 @@
         <v>27</v>
       </c>
       <c r="V304" t="n">
-        <v>46.60854</v>
+        <v>46.45026</v>
       </c>
       <c r="W304" t="n">
-        <v>-60.92379</v>
+        <v>-60.5768</v>
       </c>
       <c r="X304" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -22842,12 +22842,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -22859,12 +22859,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I305" t="b">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr"/>
@@ -22901,14 +22901,14 @@
         <v>27</v>
       </c>
       <c r="V305" t="n">
-        <v>46.60835</v>
+        <v>46.44952</v>
       </c>
       <c r="W305" t="n">
-        <v>-60.92328</v>
+        <v>-60.57801</v>
       </c>
       <c r="X305" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -22918,12 +22918,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -22935,12 +22935,12 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I306" t="b">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr"/>
@@ -22977,14 +22977,14 @@
         <v>27</v>
       </c>
       <c r="V306" t="n">
-        <v>45.26433</v>
+        <v>46.4638</v>
       </c>
       <c r="W306" t="n">
-        <v>-62.84191</v>
+        <v>-60.57034</v>
       </c>
       <c r="X306" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -23146,12 +23146,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M309" t="inlineStr"/>
@@ -23205,14 +23205,14 @@
         <v>27</v>
       </c>
       <c r="V309" t="n">
-        <v>46.60547</v>
+        <v>45.25896</v>
       </c>
       <c r="W309" t="n">
-        <v>-60.92313</v>
+        <v>-62.86207</v>
       </c>
       <c r="X309" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -23222,12 +23222,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -23239,12 +23239,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I310" t="b">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M310" t="inlineStr"/>
@@ -23281,14 +23281,14 @@
         <v>27</v>
       </c>
       <c r="V310" t="n">
-        <v>46.60942</v>
+        <v>45.66247</v>
       </c>
       <c r="W310" t="n">
-        <v>-60.91762</v>
+        <v>-60.50348</v>
       </c>
       <c r="X310" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -23298,12 +23298,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -23315,12 +23315,12 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I311" t="b">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M311" t="inlineStr"/>
@@ -23354,17 +23354,17 @@
         <v>325</v>
       </c>
       <c r="U311" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V311" t="n">
-        <v>46.2982</v>
+        <v>45.66068</v>
       </c>
       <c r="W311" t="n">
-        <v>-60.94257</v>
+        <v>-60.49983</v>
       </c>
       <c r="X311" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -23374,12 +23374,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M312" t="inlineStr"/>
@@ -23430,17 +23430,17 @@
         <v>325</v>
       </c>
       <c r="U312" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V312" t="n">
-        <v>46.59758</v>
+        <v>46.60854</v>
       </c>
       <c r="W312" t="n">
-        <v>-60.88034</v>
+        <v>-60.92379</v>
       </c>
       <c r="X312" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23450,12 +23450,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -23467,7 +23467,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M313" t="inlineStr"/>
@@ -23506,17 +23506,17 @@
         <v>325</v>
       </c>
       <c r="U313" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V313" t="n">
-        <v>46.58857</v>
+        <v>46.60835</v>
       </c>
       <c r="W313" t="n">
-        <v>-60.8649</v>
+        <v>-60.92328</v>
       </c>
       <c r="X313" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23526,12 +23526,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -23543,7 +23543,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M314" t="inlineStr"/>
@@ -23582,17 +23582,17 @@
         <v>325</v>
       </c>
       <c r="U314" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V314" t="n">
-        <v>46.29595</v>
+        <v>46.60665</v>
       </c>
       <c r="W314" t="n">
-        <v>-60.9372</v>
+        <v>-60.92386</v>
       </c>
       <c r="X314" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23602,12 +23602,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -23619,12 +23619,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I315" t="b">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M315" t="inlineStr"/>
@@ -23658,17 +23658,17 @@
         <v>325</v>
       </c>
       <c r="U315" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V315" t="n">
-        <v>46.44219</v>
+        <v>46.60547</v>
       </c>
       <c r="W315" t="n">
-        <v>-60.58706</v>
+        <v>-60.92313</v>
       </c>
       <c r="X315" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23678,12 +23678,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Morleys Pegmatite</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>A09-014</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -23695,12 +23695,12 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>W, Sn, Jasper, F</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I316" t="b">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>W 0.1%, Be 0.00032%, Bi 0.0009%, Cu 0.0051%, Li 0.0132%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M316" t="inlineStr"/>
@@ -23734,17 +23734,17 @@
         <v>325</v>
       </c>
       <c r="U316" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V316" t="n">
-        <v>44.73955</v>
+        <v>46.60942</v>
       </c>
       <c r="W316" t="n">
-        <v>-64.4462</v>
+        <v>-60.91762</v>
       </c>
       <c r="X316" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23754,12 +23754,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -23771,7 +23771,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M317" t="inlineStr"/>
@@ -23810,17 +23810,17 @@
         <v>325</v>
       </c>
       <c r="U317" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V317" t="n">
-        <v>46.51529</v>
+        <v>45.26433</v>
       </c>
       <c r="W317" t="n">
-        <v>-60.64417</v>
+        <v>-62.84191</v>
       </c>
       <c r="X317" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -23889,10 +23889,10 @@
         <v>26</v>
       </c>
       <c r="V318" t="n">
-        <v>46.51553</v>
+        <v>46.51529</v>
       </c>
       <c r="W318" t="n">
-        <v>-60.64503</v>
+        <v>-60.64417</v>
       </c>
       <c r="X318" t="inlineStr">
         <is>
@@ -24134,12 +24134,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -24151,12 +24151,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I322" t="b">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M322" t="inlineStr"/>
@@ -24193,14 +24193,14 @@
         <v>26</v>
       </c>
       <c r="V322" t="n">
-        <v>44.6151</v>
+        <v>46.51553</v>
       </c>
       <c r="W322" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.64503</v>
       </c>
       <c r="X322" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -24894,12 +24894,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I332" t="b">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M332" t="inlineStr"/>
@@ -24953,14 +24953,14 @@
         <v>26</v>
       </c>
       <c r="V332" t="n">
-        <v>46.58794</v>
+        <v>44.6151</v>
       </c>
       <c r="W332" t="n">
-        <v>-60.86479</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X332" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -24970,12 +24970,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M333" t="inlineStr"/>
@@ -25029,14 +25029,14 @@
         <v>26</v>
       </c>
       <c r="V333" t="n">
-        <v>46.51873</v>
+        <v>46.29966</v>
       </c>
       <c r="W333" t="n">
-        <v>-60.64496</v>
+        <v>-60.94836</v>
       </c>
       <c r="X333" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -25046,12 +25046,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -25063,7 +25063,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M334" t="inlineStr"/>
@@ -25105,14 +25105,14 @@
         <v>26</v>
       </c>
       <c r="V334" t="n">
-        <v>46.29966</v>
+        <v>46.51873</v>
       </c>
       <c r="W334" t="n">
-        <v>-60.94836</v>
+        <v>-60.64496</v>
       </c>
       <c r="X334" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -25122,12 +25122,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -25139,12 +25139,12 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I335" t="b">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M335" t="inlineStr"/>
@@ -25181,14 +25181,14 @@
         <v>26</v>
       </c>
       <c r="V335" t="n">
-        <v>46.44885</v>
+        <v>46.29595</v>
       </c>
       <c r="W335" t="n">
-        <v>-60.58676</v>
+        <v>-60.9372</v>
       </c>
       <c r="X335" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -25198,12 +25198,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -25215,12 +25215,12 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I336" t="b">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M336" t="inlineStr"/>
@@ -25257,14 +25257,14 @@
         <v>26</v>
       </c>
       <c r="V336" t="n">
-        <v>46.44956</v>
+        <v>46.2982</v>
       </c>
       <c r="W336" t="n">
-        <v>-60.57775</v>
+        <v>-60.94257</v>
       </c>
       <c r="X336" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -25426,12 +25426,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -25443,12 +25443,12 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I339" t="b">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M339" t="inlineStr"/>
@@ -25485,14 +25485,14 @@
         <v>26</v>
       </c>
       <c r="V339" t="n">
-        <v>46.44952</v>
+        <v>46.58857</v>
       </c>
       <c r="W339" t="n">
-        <v>-60.57801</v>
+        <v>-60.8649</v>
       </c>
       <c r="X339" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -25502,12 +25502,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -25519,12 +25519,12 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I340" t="b">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M340" t="inlineStr"/>
@@ -25561,14 +25561,14 @@
         <v>26</v>
       </c>
       <c r="V340" t="n">
-        <v>46.4638</v>
+        <v>46.58794</v>
       </c>
       <c r="W340" t="n">
-        <v>-60.57034</v>
+        <v>-60.86479</v>
       </c>
       <c r="X340" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -25578,12 +25578,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Morleys Pegmatite</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A09-014</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -25595,7 +25595,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>W, Sn, Jasper, F</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>W 0.1%, Be 0.00032%, Bi 0.0009%, Cu 0.0051%, Li 0.0132%</t>
         </is>
       </c>
       <c r="M341" t="inlineStr"/>
@@ -25637,14 +25637,14 @@
         <v>26</v>
       </c>
       <c r="V341" t="n">
-        <v>46.44638</v>
+        <v>44.73955</v>
       </c>
       <c r="W341" t="n">
-        <v>-60.57242</v>
+        <v>-64.4462</v>
       </c>
       <c r="X341" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-014</t>
         </is>
       </c>
     </row>
@@ -25654,12 +25654,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -25671,12 +25671,12 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I342" t="b">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M342" t="inlineStr"/>
@@ -25713,14 +25713,14 @@
         <v>26</v>
       </c>
       <c r="V342" t="n">
-        <v>46.45026</v>
+        <v>46.59758</v>
       </c>
       <c r="W342" t="n">
-        <v>-60.5768</v>
+        <v>-60.88034</v>
       </c>
       <c r="X342" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -22462,12 +22462,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -22479,12 +22479,12 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I300" t="b">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr"/>
@@ -22521,14 +22521,14 @@
         <v>27</v>
       </c>
       <c r="V300" t="n">
-        <v>46.44885</v>
+        <v>46.60665</v>
       </c>
       <c r="W300" t="n">
-        <v>-60.58676</v>
+        <v>-60.92386</v>
       </c>
       <c r="X300" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -22538,12 +22538,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -22555,12 +22555,12 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I301" t="b">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M301" t="inlineStr"/>
@@ -22597,14 +22597,14 @@
         <v>27</v>
       </c>
       <c r="V301" t="n">
-        <v>46.44956</v>
+        <v>45.25896</v>
       </c>
       <c r="W301" t="n">
-        <v>-60.57775</v>
+        <v>-62.86207</v>
       </c>
       <c r="X301" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -22614,12 +22614,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -22631,7 +22631,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -22652,7 +22652,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M302" t="inlineStr"/>
@@ -22673,14 +22673,14 @@
         <v>27</v>
       </c>
       <c r="V302" t="n">
-        <v>46.44219</v>
+        <v>45.66247</v>
       </c>
       <c r="W302" t="n">
-        <v>-60.58706</v>
+        <v>-60.50348</v>
       </c>
       <c r="X302" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -22690,12 +22690,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M303" t="inlineStr"/>
@@ -22749,14 +22749,14 @@
         <v>27</v>
       </c>
       <c r="V303" t="n">
-        <v>46.44638</v>
+        <v>45.66068</v>
       </c>
       <c r="W303" t="n">
-        <v>-60.57242</v>
+        <v>-60.49983</v>
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -22766,12 +22766,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -22783,12 +22783,12 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I304" t="b">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr"/>
@@ -22825,14 +22825,14 @@
         <v>27</v>
       </c>
       <c r="V304" t="n">
-        <v>46.45026</v>
+        <v>46.60854</v>
       </c>
       <c r="W304" t="n">
-        <v>-60.5768</v>
+        <v>-60.92379</v>
       </c>
       <c r="X304" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -22842,12 +22842,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -22859,12 +22859,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I305" t="b">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr"/>
@@ -22901,14 +22901,14 @@
         <v>27</v>
       </c>
       <c r="V305" t="n">
-        <v>46.44952</v>
+        <v>46.60835</v>
       </c>
       <c r="W305" t="n">
-        <v>-60.57801</v>
+        <v>-60.92328</v>
       </c>
       <c r="X305" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -22918,12 +22918,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -22935,12 +22935,12 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I306" t="b">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr"/>
@@ -22977,14 +22977,14 @@
         <v>27</v>
       </c>
       <c r="V306" t="n">
-        <v>46.4638</v>
+        <v>45.26433</v>
       </c>
       <c r="W306" t="n">
-        <v>-60.57034</v>
+        <v>-62.84191</v>
       </c>
       <c r="X306" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -23146,12 +23146,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M309" t="inlineStr"/>
@@ -23205,14 +23205,14 @@
         <v>27</v>
       </c>
       <c r="V309" t="n">
-        <v>45.25896</v>
+        <v>46.60547</v>
       </c>
       <c r="W309" t="n">
-        <v>-62.86207</v>
+        <v>-60.92313</v>
       </c>
       <c r="X309" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23222,12 +23222,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -23239,12 +23239,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I310" t="b">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M310" t="inlineStr"/>
@@ -23281,14 +23281,14 @@
         <v>27</v>
       </c>
       <c r="V310" t="n">
-        <v>45.66247</v>
+        <v>46.60942</v>
       </c>
       <c r="W310" t="n">
-        <v>-60.50348</v>
+        <v>-60.91762</v>
       </c>
       <c r="X310" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23298,12 +23298,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -23315,12 +23315,12 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I311" t="b">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M311" t="inlineStr"/>
@@ -23354,17 +23354,17 @@
         <v>325</v>
       </c>
       <c r="U311" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V311" t="n">
-        <v>45.66068</v>
+        <v>46.2982</v>
       </c>
       <c r="W311" t="n">
-        <v>-60.49983</v>
+        <v>-60.94257</v>
       </c>
       <c r="X311" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -23374,12 +23374,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M312" t="inlineStr"/>
@@ -23430,17 +23430,17 @@
         <v>325</v>
       </c>
       <c r="U312" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V312" t="n">
-        <v>46.60854</v>
+        <v>46.59758</v>
       </c>
       <c r="W312" t="n">
-        <v>-60.92379</v>
+        <v>-60.88034</v>
       </c>
       <c r="X312" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -23450,12 +23450,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -23467,7 +23467,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M313" t="inlineStr"/>
@@ -23506,17 +23506,17 @@
         <v>325</v>
       </c>
       <c r="U313" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V313" t="n">
-        <v>46.60835</v>
+        <v>46.58857</v>
       </c>
       <c r="W313" t="n">
-        <v>-60.92328</v>
+        <v>-60.8649</v>
       </c>
       <c r="X313" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -23526,12 +23526,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -23543,7 +23543,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M314" t="inlineStr"/>
@@ -23582,17 +23582,17 @@
         <v>325</v>
       </c>
       <c r="U314" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V314" t="n">
-        <v>46.60665</v>
+        <v>46.29595</v>
       </c>
       <c r="W314" t="n">
-        <v>-60.92386</v>
+        <v>-60.9372</v>
       </c>
       <c r="X314" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -23602,12 +23602,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -23619,12 +23619,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I315" t="b">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M315" t="inlineStr"/>
@@ -23658,17 +23658,17 @@
         <v>325</v>
       </c>
       <c r="U315" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V315" t="n">
-        <v>46.60547</v>
+        <v>46.44219</v>
       </c>
       <c r="W315" t="n">
-        <v>-60.92313</v>
+        <v>-60.58706</v>
       </c>
       <c r="X315" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -23678,12 +23678,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Morleys Pegmatite</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>A09-014</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -23695,12 +23695,12 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>W, Sn, Jasper, F</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I316" t="b">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>W 0.1%, Be 0.00032%, Bi 0.0009%, Cu 0.0051%, Li 0.0132%</t>
         </is>
       </c>
       <c r="M316" t="inlineStr"/>
@@ -23734,17 +23734,17 @@
         <v>325</v>
       </c>
       <c r="U316" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V316" t="n">
-        <v>46.60942</v>
+        <v>44.73955</v>
       </c>
       <c r="W316" t="n">
-        <v>-60.91762</v>
+        <v>-64.4462</v>
       </c>
       <c r="X316" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-014</t>
         </is>
       </c>
     </row>
@@ -23754,12 +23754,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -23771,7 +23771,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M317" t="inlineStr"/>
@@ -23810,17 +23810,17 @@
         <v>325</v>
       </c>
       <c r="U317" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V317" t="n">
-        <v>45.26433</v>
+        <v>46.51529</v>
       </c>
       <c r="W317" t="n">
-        <v>-62.84191</v>
+        <v>-60.64417</v>
       </c>
       <c r="X317" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -23889,10 +23889,10 @@
         <v>26</v>
       </c>
       <c r="V318" t="n">
-        <v>46.51529</v>
+        <v>46.51553</v>
       </c>
       <c r="W318" t="n">
-        <v>-60.64417</v>
+        <v>-60.64503</v>
       </c>
       <c r="X318" t="inlineStr">
         <is>
@@ -24134,12 +24134,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -24151,12 +24151,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I322" t="b">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M322" t="inlineStr"/>
@@ -24193,14 +24193,14 @@
         <v>26</v>
       </c>
       <c r="V322" t="n">
-        <v>46.51553</v>
+        <v>44.6151</v>
       </c>
       <c r="W322" t="n">
-        <v>-60.64503</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X322" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -24894,12 +24894,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -24911,12 +24911,12 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I332" t="b">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M332" t="inlineStr"/>
@@ -24953,14 +24953,14 @@
         <v>26</v>
       </c>
       <c r="V332" t="n">
-        <v>44.6151</v>
+        <v>46.58794</v>
       </c>
       <c r="W332" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.86479</v>
       </c>
       <c r="X332" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -24970,12 +24970,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M333" t="inlineStr"/>
@@ -25029,14 +25029,14 @@
         <v>26</v>
       </c>
       <c r="V333" t="n">
-        <v>46.29966</v>
+        <v>46.51873</v>
       </c>
       <c r="W333" t="n">
-        <v>-60.94836</v>
+        <v>-60.64496</v>
       </c>
       <c r="X333" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -25046,12 +25046,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -25063,7 +25063,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M334" t="inlineStr"/>
@@ -25105,14 +25105,14 @@
         <v>26</v>
       </c>
       <c r="V334" t="n">
-        <v>46.51873</v>
+        <v>46.29966</v>
       </c>
       <c r="W334" t="n">
-        <v>-60.64496</v>
+        <v>-60.94836</v>
       </c>
       <c r="X334" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -25122,12 +25122,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -25139,12 +25139,12 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I335" t="b">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M335" t="inlineStr"/>
@@ -25181,14 +25181,14 @@
         <v>26</v>
       </c>
       <c r="V335" t="n">
-        <v>46.29595</v>
+        <v>46.44885</v>
       </c>
       <c r="W335" t="n">
-        <v>-60.9372</v>
+        <v>-60.58676</v>
       </c>
       <c r="X335" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25198,12 +25198,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -25215,12 +25215,12 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I336" t="b">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M336" t="inlineStr"/>
@@ -25257,14 +25257,14 @@
         <v>26</v>
       </c>
       <c r="V336" t="n">
-        <v>46.2982</v>
+        <v>46.44956</v>
       </c>
       <c r="W336" t="n">
-        <v>-60.94257</v>
+        <v>-60.57775</v>
       </c>
       <c r="X336" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25426,12 +25426,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -25443,12 +25443,12 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I339" t="b">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M339" t="inlineStr"/>
@@ -25485,14 +25485,14 @@
         <v>26</v>
       </c>
       <c r="V339" t="n">
-        <v>46.58857</v>
+        <v>46.44952</v>
       </c>
       <c r="W339" t="n">
-        <v>-60.8649</v>
+        <v>-60.57801</v>
       </c>
       <c r="X339" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25502,12 +25502,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -25519,12 +25519,12 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I340" t="b">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M340" t="inlineStr"/>
@@ -25561,14 +25561,14 @@
         <v>26</v>
       </c>
       <c r="V340" t="n">
-        <v>46.58794</v>
+        <v>46.4638</v>
       </c>
       <c r="W340" t="n">
-        <v>-60.86479</v>
+        <v>-60.57034</v>
       </c>
       <c r="X340" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25578,12 +25578,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Morleys Pegmatite</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>A09-014</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -25595,7 +25595,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>W, Sn, Jasper, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>W 0.1%, Be 0.00032%, Bi 0.0009%, Cu 0.0051%, Li 0.0132%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M341" t="inlineStr"/>
@@ -25637,14 +25637,14 @@
         <v>26</v>
       </c>
       <c r="V341" t="n">
-        <v>44.73955</v>
+        <v>46.44638</v>
       </c>
       <c r="W341" t="n">
-        <v>-64.4462</v>
+        <v>-60.57242</v>
       </c>
       <c r="X341" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25654,12 +25654,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -25671,12 +25671,12 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I342" t="b">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M342" t="inlineStr"/>
@@ -25713,14 +25713,14 @@
         <v>26</v>
       </c>
       <c r="V342" t="n">
-        <v>46.59758</v>
+        <v>46.45026</v>
       </c>
       <c r="W342" t="n">
-        <v>-60.88034</v>
+        <v>-60.5768</v>
       </c>
       <c r="X342" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -26093,10 +26093,10 @@
         <v>25</v>
       </c>
       <c r="V347" t="n">
-        <v>44.69021</v>
+        <v>44.68634</v>
       </c>
       <c r="W347" t="n">
-        <v>-63.97107</v>
+        <v>-63.97235</v>
       </c>
       <c r="X347" t="inlineStr">
         <is>
@@ -26169,10 +26169,10 @@
         <v>25</v>
       </c>
       <c r="V348" t="n">
-        <v>44.68634</v>
+        <v>44.69021</v>
       </c>
       <c r="W348" t="n">
-        <v>-63.97235</v>
+        <v>-63.97107</v>
       </c>
       <c r="X348" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -7822,12 +7822,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lime Hill Zn and Wollastonite Deposit</t>
+          <t>Whycocomagh Cu, Fe, W Occurrence</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>F14-012</t>
+          <t>F14-003</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zn, Cu, W, Wollastonite</t>
+          <t>Cu, W, Mo, Fe</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
+          <t>W 0.0742%, Cu 0.959%, Ag 1.40 g/t, Au 0.11 g/t, Co 0.0044%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -7872,23 +7872,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T98" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U98" t="n">
         <v>33</v>
       </c>
       <c r="V98" t="n">
-        <v>45.77684</v>
+        <v>45.99025</v>
       </c>
       <c r="W98" t="n">
-        <v>-61.1495</v>
+        <v>-61.10637</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-003</t>
         </is>
       </c>
     </row>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Whycocomagh Cu, Fe, W Occurrence</t>
+          <t>Lime Hill Zn and Wollastonite Deposit</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>F14-003</t>
+          <t>F14-012</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7991,12 +7991,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cu, W, Mo, Fe</t>
+          <t>Zn, Cu, W, Wollastonite</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>W 0.0742%, Cu 0.959%, Ag 1.40 g/t, Au 0.11 g/t, Co 0.0044%</t>
+          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -8024,23 +8024,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T100" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U100" t="n">
         <v>33</v>
       </c>
       <c r="V100" t="n">
-        <v>45.99025</v>
+        <v>45.77684</v>
       </c>
       <c r="W100" t="n">
-        <v>-61.10637</v>
+        <v>-61.1495</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
         </is>
       </c>
     </row>
@@ -8109,10 +8109,10 @@
         <v>32</v>
       </c>
       <c r="V101" t="n">
-        <v>46.5638</v>
+        <v>46.56345</v>
       </c>
       <c r="W101" t="n">
-        <v>-60.93777</v>
+        <v>-60.9383</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -8185,10 +8185,10 @@
         <v>32</v>
       </c>
       <c r="V102" t="n">
-        <v>46.56345</v>
+        <v>46.5638</v>
       </c>
       <c r="W102" t="n">
-        <v>-60.9383</v>
+        <v>-60.93777</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Cochrane Hill Au District</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>E01-007</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au, As, Pb, Zn</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I103" t="b">
@@ -8238,11 +8238,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
@@ -8252,23 +8248,23 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U103" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V103" t="n">
-        <v>45.91475</v>
+        <v>45.24893</v>
       </c>
       <c r="W103" t="n">
-        <v>-61.23041</v>
+        <v>-62.013</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
         </is>
       </c>
     </row>
@@ -8278,12 +8274,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>North Star Au Mine</t>
+          <t>Cochrane Hill Au District</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>F04-018</t>
+          <t>E01-007</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -8295,7 +8291,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Pb, Zn</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8324,23 +8320,23 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T104" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U104" t="n">
         <v>30</v>
       </c>
       <c r="V104" t="n">
-        <v>45.16836</v>
+        <v>45.24892</v>
       </c>
       <c r="W104" t="n">
-        <v>-61.65632</v>
+        <v>-62.01122</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
         </is>
       </c>
     </row>
@@ -8422,12 +8418,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cochrane Hill Au District</t>
+          <t>North Star Au Mine</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>E01-007</t>
+          <t>F04-018</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8439,7 +8435,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Au, As, Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8468,23 +8464,23 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T106" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U106" t="n">
         <v>30</v>
       </c>
       <c r="V106" t="n">
-        <v>45.24892</v>
+        <v>45.16836</v>
       </c>
       <c r="W106" t="n">
-        <v>-62.01122</v>
+        <v>-61.65632</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
         </is>
       </c>
     </row>
@@ -8566,12 +8562,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cochrane Hill Au District</t>
+          <t>Indian Path Au-W Mine</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>E01-007</t>
+          <t>A08-018</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8583,7 +8579,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Au, As, Pb, Zn</t>
+          <t>Au, W</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8612,23 +8608,23 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T108" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U108" t="n">
         <v>30</v>
       </c>
       <c r="V108" t="n">
-        <v>45.24893</v>
+        <v>44.32518</v>
       </c>
       <c r="W108" t="n">
-        <v>-62.013</v>
+        <v>-64.34795</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8761,10 @@
         <v>30</v>
       </c>
       <c r="V110" t="n">
-        <v>44.32518</v>
+        <v>44.32606</v>
       </c>
       <c r="W110" t="n">
-        <v>-64.34795</v>
+        <v>-64.34589</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
@@ -8782,12 +8778,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Indian Path Au-W Mine</t>
+          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>A08-018</t>
+          <t>A16-007</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8799,7 +8795,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Au, W</t>
+          <t>Mn, Fe, Clay</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8837,14 +8833,14 @@
         <v>30</v>
       </c>
       <c r="V111" t="n">
-        <v>44.32606</v>
+        <v>44.84593</v>
       </c>
       <c r="W111" t="n">
-        <v>-64.34589</v>
+        <v>-64.45107</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
         </is>
       </c>
     </row>
@@ -8854,12 +8850,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
+          <t>Moose River Tungsten Deposit</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>A16-007</t>
+          <t>D15-012</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8871,7 +8867,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Mn, Fe, Clay</t>
+          <t>W, Pt</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8909,14 +8905,14 @@
         <v>30</v>
       </c>
       <c r="V112" t="n">
-        <v>44.84593</v>
+        <v>44.97314</v>
       </c>
       <c r="W112" t="n">
-        <v>-64.45107</v>
+        <v>-62.9798</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-012</t>
         </is>
       </c>
     </row>
@@ -8926,12 +8922,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Moose River Tungsten Deposit</t>
+          <t>Gegogan Au District</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>D15-012</t>
+          <t>F04-001</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8943,7 +8939,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>W, Pt</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8981,14 +8977,14 @@
         <v>30</v>
       </c>
       <c r="V113" t="n">
-        <v>44.97314</v>
+        <v>45.04598</v>
       </c>
       <c r="W113" t="n">
-        <v>-62.9798</v>
+        <v>-61.95574</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-001</t>
         </is>
       </c>
     </row>
@@ -8998,12 +8994,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Gegogan Au District</t>
+          <t>Lake Catcha Au District</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>F04-001</t>
+          <t>D11-004</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -9015,7 +9011,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, Pb</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9053,14 +9049,14 @@
         <v>30</v>
       </c>
       <c r="V114" t="n">
-        <v>45.04598</v>
+        <v>44.73873</v>
       </c>
       <c r="W114" t="n">
-        <v>-61.95574</v>
+        <v>-63.19466</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-004</t>
         </is>
       </c>
     </row>
@@ -9125,10 +9121,10 @@
         <v>30</v>
       </c>
       <c r="V115" t="n">
-        <v>44.72139</v>
+        <v>44.71411</v>
       </c>
       <c r="W115" t="n">
-        <v>-63.5068</v>
+        <v>-63.52504</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
@@ -9142,12 +9138,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Montague Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>D12-001</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9159,7 +9155,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Au, Pb, Cu, Fe, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9197,14 +9193,14 @@
         <v>30</v>
       </c>
       <c r="V116" t="n">
-        <v>44.71411</v>
+        <v>44.73589</v>
       </c>
       <c r="W116" t="n">
-        <v>-63.52504</v>
+        <v>-62.91248</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -9269,10 +9265,10 @@
         <v>30</v>
       </c>
       <c r="V117" t="n">
-        <v>44.73589</v>
+        <v>44.73624</v>
       </c>
       <c r="W117" t="n">
-        <v>-62.91248</v>
+        <v>-62.91259</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
@@ -9341,10 +9337,10 @@
         <v>30</v>
       </c>
       <c r="V118" t="n">
-        <v>44.73624</v>
+        <v>44.73608</v>
       </c>
       <c r="W118" t="n">
-        <v>-62.91259</v>
+        <v>-62.91488</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
@@ -9413,10 +9409,10 @@
         <v>30</v>
       </c>
       <c r="V119" t="n">
-        <v>44.73608</v>
+        <v>44.73395</v>
       </c>
       <c r="W119" t="n">
-        <v>-62.91488</v>
+        <v>-62.91588</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
@@ -9430,12 +9426,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9447,7 +9443,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9485,14 +9481,14 @@
         <v>30</v>
       </c>
       <c r="V120" t="n">
-        <v>44.73395</v>
+        <v>44.64923</v>
       </c>
       <c r="W120" t="n">
-        <v>-62.91588</v>
+        <v>-64.65634</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9498,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Pleasantfield (Fifteen Mile Brook) Gold Deposit</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>A02-012</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9519,7 +9515,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9557,14 +9553,14 @@
         <v>30</v>
       </c>
       <c r="V121" t="n">
-        <v>44.64923</v>
+        <v>44.23654</v>
       </c>
       <c r="W121" t="n">
-        <v>-64.65634</v>
+        <v>-64.9011</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-012</t>
         </is>
       </c>
     </row>
@@ -9574,12 +9570,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Pleasantfield (Fifteen Mile Brook) Gold Deposit</t>
+          <t>Voglers Cove Au District</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>A02-012</t>
+          <t>A02-006</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9629,14 +9625,14 @@
         <v>30</v>
       </c>
       <c r="V122" t="n">
-        <v>44.23654</v>
+        <v>44.18782</v>
       </c>
       <c r="W122" t="n">
-        <v>-64.9011</v>
+        <v>-64.52444</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-006</t>
         </is>
       </c>
     </row>
@@ -9646,12 +9642,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Voglers Cove Au District</t>
+          <t>Pleasantfield (Fifteen Mile Brook) Gold Deposit</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>A02-006</t>
+          <t>A02-012</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9701,14 +9697,14 @@
         <v>30</v>
       </c>
       <c r="V123" t="n">
-        <v>44.1851</v>
+        <v>44.23617</v>
       </c>
       <c r="W123" t="n">
-        <v>-64.52497</v>
+        <v>-64.90196</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-012</t>
         </is>
       </c>
     </row>
@@ -9773,10 +9769,10 @@
         <v>30</v>
       </c>
       <c r="V124" t="n">
-        <v>44.23617</v>
+        <v>44.23579</v>
       </c>
       <c r="W124" t="n">
-        <v>-64.90196</v>
+        <v>-64.90268</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
@@ -9790,12 +9786,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pleasantfield (Fifteen Mile Brook) Gold Deposit</t>
+          <t>Little Liscomb Lake Gold Mine</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A02-012</t>
+          <t>E01-018</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9807,7 +9803,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9845,14 +9841,14 @@
         <v>30</v>
       </c>
       <c r="V125" t="n">
-        <v>44.23579</v>
+        <v>45.24748</v>
       </c>
       <c r="W125" t="n">
-        <v>-64.90268</v>
+        <v>-62.45078</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-018</t>
         </is>
       </c>
     </row>
@@ -9862,12 +9858,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Little Liscomb Lake Gold Mine</t>
+          <t>Fifteen Mile Stream Au Mine (Pleasantfield)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>E01-018</t>
+          <t>A02-003</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9879,7 +9875,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9917,14 +9913,14 @@
         <v>30</v>
       </c>
       <c r="V126" t="n">
-        <v>45.24748</v>
+        <v>44.23654</v>
       </c>
       <c r="W126" t="n">
-        <v>-62.45078</v>
+        <v>-64.9011</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-003</t>
         </is>
       </c>
     </row>
@@ -9989,10 +9985,10 @@
         <v>30</v>
       </c>
       <c r="V127" t="n">
-        <v>44.23654</v>
+        <v>44.23617</v>
       </c>
       <c r="W127" t="n">
-        <v>-64.9011</v>
+        <v>-64.90196</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
@@ -10006,12 +10002,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fifteen Mile Stream Au Mine (Pleasantfield)</t>
+          <t>Voglers Cove Au District</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>A02-003</t>
+          <t>A02-006</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -10061,14 +10057,14 @@
         <v>30</v>
       </c>
       <c r="V128" t="n">
-        <v>44.23617</v>
+        <v>44.1851</v>
       </c>
       <c r="W128" t="n">
-        <v>-64.90196</v>
+        <v>-64.52497</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-006</t>
         </is>
       </c>
     </row>
@@ -10205,10 +10201,10 @@
         <v>30</v>
       </c>
       <c r="V130" t="n">
-        <v>44.18782</v>
+        <v>44.20137</v>
       </c>
       <c r="W130" t="n">
-        <v>-64.52444</v>
+        <v>-64.52287</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
@@ -10222,12 +10218,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Voglers Cove Au District</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>A02-006</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -10239,12 +10235,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I131" t="b">
@@ -10258,7 +10254,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="n">
@@ -10277,14 +10277,14 @@
         <v>30</v>
       </c>
       <c r="V131" t="n">
-        <v>44.20137</v>
+        <v>46.61843</v>
       </c>
       <c r="W131" t="n">
-        <v>-64.52287</v>
+        <v>-60.52086</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -10294,12 +10294,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>North Star Au Mine</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>F04-018</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -10311,12 +10311,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I132" t="b">
@@ -10330,11 +10330,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="n">
@@ -10353,14 +10349,14 @@
         <v>30</v>
       </c>
       <c r="V132" t="n">
-        <v>46.61843</v>
+        <v>45.16846</v>
       </c>
       <c r="W132" t="n">
-        <v>-60.52086</v>
+        <v>-61.65383</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
         </is>
       </c>
     </row>
@@ -10425,10 +10421,10 @@
         <v>30</v>
       </c>
       <c r="V133" t="n">
-        <v>45.16846</v>
+        <v>45.16856</v>
       </c>
       <c r="W133" t="n">
-        <v>-61.65383</v>
+        <v>-61.65448</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
@@ -10442,12 +10438,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>North Star Au Mine</t>
+          <t>Cap d'Or (Hanway Shaft)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>F04-018</t>
+          <t>H07-035</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10459,7 +10455,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Au, Ag</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10497,14 +10493,14 @@
         <v>30</v>
       </c>
       <c r="V134" t="n">
-        <v>45.16856</v>
+        <v>45.31342</v>
       </c>
       <c r="W134" t="n">
-        <v>-61.65448</v>
+        <v>-64.73712</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H07-035</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10510,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cap d'Or (Hanway Shaft)</t>
+          <t>Stephen's Manganese Mine</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>H07-035</t>
+          <t>H01-013</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -10531,7 +10527,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cu, Au, Ag</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10560,23 +10556,23 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T135" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U135" t="n">
         <v>30</v>
       </c>
       <c r="V135" t="n">
-        <v>45.31342</v>
+        <v>45.22152</v>
       </c>
       <c r="W135" t="n">
-        <v>-64.73712</v>
+        <v>-64.01091</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H07-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H01-013</t>
         </is>
       </c>
     </row>
@@ -10632,19 +10628,19 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T136" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U136" t="n">
         <v>30</v>
       </c>
       <c r="V136" t="n">
-        <v>45.22152</v>
+        <v>45.22029</v>
       </c>
       <c r="W136" t="n">
-        <v>-64.01091</v>
+        <v>-64.01739000000001</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
@@ -10713,10 +10709,10 @@
         <v>30</v>
       </c>
       <c r="V137" t="n">
-        <v>45.22029</v>
+        <v>45.22076</v>
       </c>
       <c r="W137" t="n">
-        <v>-64.01739000000001</v>
+        <v>-64.01523</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
@@ -10730,12 +10726,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Stephen's Manganese Mine</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>H01-013</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -10747,7 +10743,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10785,14 +10781,14 @@
         <v>30</v>
       </c>
       <c r="V138" t="n">
-        <v>45.22076</v>
+        <v>45.04257</v>
       </c>
       <c r="W138" t="n">
-        <v>-64.01523</v>
+        <v>-62.15494</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H01-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -10857,10 +10853,10 @@
         <v>30</v>
       </c>
       <c r="V139" t="n">
-        <v>45.04257</v>
+        <v>45.04155</v>
       </c>
       <c r="W139" t="n">
-        <v>-62.15494</v>
+        <v>-62.13832</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
@@ -10929,10 +10925,10 @@
         <v>30</v>
       </c>
       <c r="V140" t="n">
-        <v>45.04155</v>
+        <v>45.04194</v>
       </c>
       <c r="W140" t="n">
-        <v>-62.13832</v>
+        <v>-62.14309</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
@@ -11001,10 +10997,10 @@
         <v>30</v>
       </c>
       <c r="V141" t="n">
-        <v>45.04194</v>
+        <v>45.03585</v>
       </c>
       <c r="W141" t="n">
-        <v>-62.14309</v>
+        <v>-62.15331</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
@@ -11018,12 +11014,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Ecum Secum Au District</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>D16-004</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -11035,7 +11031,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -11073,14 +11069,14 @@
         <v>30</v>
       </c>
       <c r="V142" t="n">
-        <v>45.03585</v>
+        <v>44.97138</v>
       </c>
       <c r="W142" t="n">
-        <v>-62.15331</v>
+        <v>-62.17984</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-004</t>
         </is>
       </c>
     </row>
@@ -11090,12 +11086,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ecum Secum Au District</t>
+          <t>Montague Au District</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>D16-004</t>
+          <t>D12-001</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -11107,7 +11103,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, Pb, Cu, Fe, As</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11145,14 +11141,14 @@
         <v>30</v>
       </c>
       <c r="V143" t="n">
-        <v>44.97138</v>
+        <v>44.72139</v>
       </c>
       <c r="W143" t="n">
-        <v>-62.17984</v>
+        <v>-63.5068</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-001</t>
         </is>
       </c>
     </row>
@@ -11162,12 +11158,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Killag Au District</t>
+          <t>Stephen's Manganese Mine</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>E02-002</t>
+          <t>H01-013</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -11179,7 +11175,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11208,23 +11204,23 @@
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T144" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U144" t="n">
         <v>30</v>
       </c>
       <c r="V144" t="n">
-        <v>45.01883</v>
+        <v>45.22105</v>
       </c>
       <c r="W144" t="n">
-        <v>-62.62609</v>
+        <v>-64.01282</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H01-013</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11230,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Stephen's Manganese Mine</t>
+          <t>Shaw and Churchhill Manganese Mine</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>H01-013</t>
+          <t>H01-012</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -11251,7 +11247,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Mn, Sr, Ba</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11280,23 +11276,23 @@
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T145" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U145" t="n">
         <v>30</v>
       </c>
       <c r="V145" t="n">
-        <v>45.22105</v>
+        <v>45.22688</v>
       </c>
       <c r="W145" t="n">
-        <v>-64.01282</v>
+        <v>-64.00566000000001</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H01-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H01-012</t>
         </is>
       </c>
     </row>
@@ -11306,12 +11302,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Shaw and Churchhill Manganese Mine</t>
+          <t>Loch Lomond (Kaiser Celestite Mine) Celestite Deposit</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>H01-012</t>
+          <t>F15-039</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -11323,7 +11319,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Mn, Sr, Ba</t>
+          <t>Sr</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11352,23 +11348,23 @@
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T146" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U146" t="n">
         <v>30</v>
       </c>
       <c r="V146" t="n">
-        <v>45.22688</v>
+        <v>45.81128</v>
       </c>
       <c r="W146" t="n">
-        <v>-64.00566000000001</v>
+        <v>-60.53299</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-039</t>
         </is>
       </c>
     </row>
@@ -11378,12 +11374,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Loch Lomond (Kaiser Celestite Mine) Celestite Deposit</t>
+          <t>Moose River Gold Mine</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>F15-039</t>
+          <t>D15-003</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -11395,7 +11391,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sr</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11433,14 +11429,14 @@
         <v>30</v>
       </c>
       <c r="V147" t="n">
-        <v>45.81128</v>
+        <v>44.97638</v>
       </c>
       <c r="W147" t="n">
-        <v>-60.53299</v>
+        <v>-62.95849</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-039</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-003</t>
         </is>
       </c>
     </row>
@@ -11505,10 +11501,10 @@
         <v>30</v>
       </c>
       <c r="V148" t="n">
-        <v>44.97638</v>
+        <v>44.98105</v>
       </c>
       <c r="W148" t="n">
-        <v>-62.95849</v>
+        <v>-62.94542</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
@@ -11522,12 +11518,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Moose River Gold Mine</t>
+          <t>Dunbrack Pb, Cu, Zn, Ag Mine</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>D15-003</t>
+          <t>D14-009</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -11539,7 +11535,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Cu, Zn, Ag, Bi, Au</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11577,14 +11573,14 @@
         <v>30</v>
       </c>
       <c r="V149" t="n">
-        <v>44.98105</v>
+        <v>44.81842</v>
       </c>
       <c r="W149" t="n">
-        <v>-62.94542</v>
+        <v>-63.19012</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-009</t>
         </is>
       </c>
     </row>
@@ -11594,12 +11590,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dunbrack Pb, Cu, Zn, Ag Mine</t>
+          <t>Lake Charlotte Au District</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>D14-009</t>
+          <t>D14-008</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -11611,7 +11607,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pb, Cu, Zn, Ag, Bi, Au</t>
+          <t>Au, W, As, Ag</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11649,14 +11645,14 @@
         <v>30</v>
       </c>
       <c r="V150" t="n">
-        <v>44.81842</v>
+        <v>44.85396</v>
       </c>
       <c r="W150" t="n">
-        <v>-63.19012</v>
+        <v>-62.99313</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-008</t>
         </is>
       </c>
     </row>
@@ -11721,10 +11717,10 @@
         <v>30</v>
       </c>
       <c r="V151" t="n">
-        <v>44.85396</v>
+        <v>44.85447</v>
       </c>
       <c r="W151" t="n">
-        <v>-62.99313</v>
+        <v>-63.00234</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
@@ -11738,12 +11734,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lake Charlotte Au District</t>
+          <t>Fifteen Mile Stream Gold District</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>D14-008</t>
+          <t>E02-010</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -11755,7 +11751,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Au, W, As, Ag</t>
+          <t>Au, Pt</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11793,14 +11789,14 @@
         <v>30</v>
       </c>
       <c r="V152" t="n">
-        <v>44.85447</v>
+        <v>45.13818</v>
       </c>
       <c r="W152" t="n">
-        <v>-63.00234</v>
+        <v>-62.53166</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-010</t>
         </is>
       </c>
     </row>
@@ -11865,10 +11861,10 @@
         <v>30</v>
       </c>
       <c r="V153" t="n">
-        <v>45.13818</v>
+        <v>45.14102</v>
       </c>
       <c r="W153" t="n">
-        <v>-62.53166</v>
+        <v>-62.52299</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
@@ -11882,12 +11878,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Fifteen Mile Stream Gold District</t>
+          <t>Killag Au District</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>E02-010</t>
+          <t>E02-002</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11899,7 +11895,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Au, Pt</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11937,14 +11933,14 @@
         <v>30</v>
       </c>
       <c r="V154" t="n">
-        <v>45.14102</v>
+        <v>45.02035</v>
       </c>
       <c r="W154" t="n">
-        <v>-62.52299</v>
+        <v>-62.61824</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-002</t>
         </is>
       </c>
     </row>
@@ -12009,10 +12005,10 @@
         <v>30</v>
       </c>
       <c r="V155" t="n">
-        <v>45.02035</v>
+        <v>45.01869</v>
       </c>
       <c r="W155" t="n">
-        <v>-62.61824</v>
+        <v>-62.62021</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
@@ -12081,10 +12077,10 @@
         <v>30</v>
       </c>
       <c r="V156" t="n">
-        <v>45.01869</v>
+        <v>45.01836</v>
       </c>
       <c r="W156" t="n">
-        <v>-62.62021</v>
+        <v>-62.62726</v>
       </c>
       <c r="X156" t="inlineStr">
         <is>
@@ -12153,10 +12149,10 @@
         <v>30</v>
       </c>
       <c r="V157" t="n">
-        <v>45.01836</v>
+        <v>45.01883</v>
       </c>
       <c r="W157" t="n">
-        <v>-62.62726</v>
+        <v>-62.62609</v>
       </c>
       <c r="X157" t="inlineStr">
         <is>
@@ -12170,12 +12166,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lake Catcha Au District</t>
+          <t>Cochrane Hill Au District</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>D11-004</t>
+          <t>E01-007</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -12187,7 +12183,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Au, Pb</t>
+          <t>Au, As, Pb, Zn</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12216,23 +12212,23 @@
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T158" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U158" t="n">
         <v>30</v>
       </c>
       <c r="V158" t="n">
-        <v>44.73873</v>
+        <v>45.24876</v>
       </c>
       <c r="W158" t="n">
-        <v>-63.19466</v>
+        <v>-62.0144</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
         </is>
       </c>
     </row>
@@ -12242,12 +12238,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cochrane Hill Au District</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>E01-007</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -12259,7 +12255,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Au, As, Pb, Zn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12288,23 +12284,23 @@
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T159" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U159" t="n">
         <v>30</v>
       </c>
       <c r="V159" t="n">
-        <v>45.24876</v>
+        <v>44.9011</v>
       </c>
       <c r="W159" t="n">
-        <v>-62.0144</v>
+        <v>-65.00793</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -12314,12 +12310,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Lake Charlotte Au District</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>D14-008</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -12331,7 +12327,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au, W, As, Ag</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12369,14 +12365,14 @@
         <v>30</v>
       </c>
       <c r="V160" t="n">
-        <v>44.9011</v>
+        <v>44.85199</v>
       </c>
       <c r="W160" t="n">
-        <v>-65.00793</v>
+        <v>-63.00288</v>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-008</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12382,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lake Charlotte Au District</t>
+          <t>Oldham Au District</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>D14-008</t>
+          <t>D14-003</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -12403,7 +12399,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Au, W, As, Ag</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12441,14 +12437,14 @@
         <v>30</v>
       </c>
       <c r="V161" t="n">
-        <v>44.85199</v>
+        <v>44.9236</v>
       </c>
       <c r="W161" t="n">
-        <v>-63.00288</v>
+        <v>-63.48222</v>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-003</t>
         </is>
       </c>
     </row>
@@ -12458,12 +12454,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Oldham Au District</t>
+          <t>Kemptville Au District</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>D14-003</t>
+          <t>A04-003</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -12513,14 +12509,14 @@
         <v>30</v>
       </c>
       <c r="V162" t="n">
-        <v>44.9236</v>
+        <v>44.05456</v>
       </c>
       <c r="W162" t="n">
-        <v>-63.48222</v>
+        <v>-65.84322</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-003</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12526,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Kemptville Au District</t>
+          <t>Harrigan Cove Au District</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>A04-003</t>
+          <t>D16-003</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12547,7 +12543,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, Pb, As</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12585,14 +12581,14 @@
         <v>30</v>
       </c>
       <c r="V163" t="n">
-        <v>44.05456</v>
+        <v>44.93794</v>
       </c>
       <c r="W163" t="n">
-        <v>-65.84322</v>
+        <v>-62.2917</v>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-003</t>
         </is>
       </c>
     </row>
@@ -12602,12 +12598,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Wine Harbour Au District</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>F04-002</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12619,7 +12615,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12657,14 +12653,14 @@
         <v>30</v>
       </c>
       <c r="V164" t="n">
-        <v>44.631</v>
+        <v>45.07379</v>
       </c>
       <c r="W164" t="n">
-        <v>-63.44222</v>
+        <v>-61.84337</v>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-002</t>
         </is>
       </c>
     </row>
@@ -12729,10 +12725,10 @@
         <v>30</v>
       </c>
       <c r="V165" t="n">
-        <v>45.07379</v>
+        <v>45.07365</v>
       </c>
       <c r="W165" t="n">
-        <v>-61.84337</v>
+        <v>-61.83821</v>
       </c>
       <c r="X165" t="inlineStr">
         <is>
@@ -12801,10 +12797,10 @@
         <v>30</v>
       </c>
       <c r="V166" t="n">
-        <v>45.07365</v>
+        <v>45.07601</v>
       </c>
       <c r="W166" t="n">
-        <v>-61.83821</v>
+        <v>-61.85669</v>
       </c>
       <c r="X166" t="inlineStr">
         <is>
@@ -12873,10 +12869,10 @@
         <v>30</v>
       </c>
       <c r="V167" t="n">
-        <v>45.07601</v>
+        <v>45.07783</v>
       </c>
       <c r="W167" t="n">
-        <v>-61.85669</v>
+        <v>-61.83813</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
@@ -12945,10 +12941,10 @@
         <v>30</v>
       </c>
       <c r="V168" t="n">
-        <v>45.07783</v>
+        <v>45.07814</v>
       </c>
       <c r="W168" t="n">
-        <v>-61.83813</v>
+        <v>-61.82559</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -12962,12 +12958,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Wine Harbour Au District</t>
+          <t>Caribou Au District</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>F04-002</t>
+          <t>E02-004</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -13017,14 +13013,14 @@
         <v>30</v>
       </c>
       <c r="V169" t="n">
-        <v>45.07814</v>
+        <v>45.05848</v>
       </c>
       <c r="W169" t="n">
-        <v>-61.82559</v>
+        <v>-62.9415</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-004</t>
         </is>
       </c>
     </row>
@@ -13089,10 +13085,10 @@
         <v>30</v>
       </c>
       <c r="V170" t="n">
-        <v>45.05848</v>
+        <v>45.06032</v>
       </c>
       <c r="W170" t="n">
-        <v>-62.9415</v>
+        <v>-62.94358</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -13106,12 +13102,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Caribou Au District</t>
+          <t>Mount Uniacke Au District</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>E02-004</t>
+          <t>D13-004</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -13123,7 +13119,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13161,14 +13157,14 @@
         <v>30</v>
       </c>
       <c r="V171" t="n">
-        <v>45.06032</v>
+        <v>44.92688</v>
       </c>
       <c r="W171" t="n">
-        <v>-62.94358</v>
+        <v>-63.80945</v>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-004</t>
         </is>
       </c>
     </row>
@@ -13178,12 +13174,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mount Uniacke Au District</t>
+          <t>Ardoise Au Prospect</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>D13-004</t>
+          <t>D13-005</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -13233,14 +13229,14 @@
         <v>30</v>
       </c>
       <c r="V172" t="n">
-        <v>44.92688</v>
+        <v>44.96159</v>
       </c>
       <c r="W172" t="n">
-        <v>-63.80945</v>
+        <v>-63.91592</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-005</t>
         </is>
       </c>
     </row>
@@ -13305,10 +13301,10 @@
         <v>30</v>
       </c>
       <c r="V173" t="n">
-        <v>44.96159</v>
+        <v>44.96324</v>
       </c>
       <c r="W173" t="n">
-        <v>-63.91592</v>
+        <v>-63.91582</v>
       </c>
       <c r="X173" t="inlineStr">
         <is>
@@ -13377,10 +13373,10 @@
         <v>30</v>
       </c>
       <c r="V174" t="n">
-        <v>44.96324</v>
+        <v>44.95988</v>
       </c>
       <c r="W174" t="n">
-        <v>-63.91582</v>
+        <v>-63.91491</v>
       </c>
       <c r="X174" t="inlineStr">
         <is>
@@ -13394,12 +13390,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ardoise Au Prospect</t>
+          <t>Pockwock Au Prospect</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>D13-005</t>
+          <t>D13-009</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13411,12 +13407,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, Ag</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I175" t="b">
@@ -13430,7 +13426,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Au 1.16 g/t, Ag 14.30 g/t</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="n">
@@ -13449,14 +13449,14 @@
         <v>30</v>
       </c>
       <c r="V175" t="n">
-        <v>44.95988</v>
+        <v>44.75715</v>
       </c>
       <c r="W175" t="n">
-        <v>-63.91491</v>
+        <v>-63.8588</v>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-009</t>
         </is>
       </c>
     </row>
@@ -13525,10 +13525,10 @@
         <v>30</v>
       </c>
       <c r="V176" t="n">
-        <v>44.75715</v>
+        <v>44.75722</v>
       </c>
       <c r="W176" t="n">
-        <v>-63.8588</v>
+        <v>-63.85829</v>
       </c>
       <c r="X176" t="inlineStr">
         <is>
@@ -13542,12 +13542,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Pockwock Au Prospect</t>
+          <t>Caribou Au District</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>D13-009</t>
+          <t>E02-004</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Au, Ag</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I177" t="b">
@@ -13578,11 +13578,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>Au 1.16 g/t, Ag 14.30 g/t</t>
-        </is>
-      </c>
+      <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="n">
@@ -13601,14 +13597,14 @@
         <v>30</v>
       </c>
       <c r="V177" t="n">
-        <v>44.75722</v>
+        <v>45.05696</v>
       </c>
       <c r="W177" t="n">
-        <v>-63.85829</v>
+        <v>-62.93511</v>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-004</t>
         </is>
       </c>
     </row>
@@ -13618,12 +13614,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Caribou Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>E02-004</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13635,7 +13631,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13673,14 +13669,14 @@
         <v>30</v>
       </c>
       <c r="V178" t="n">
-        <v>45.05696</v>
+        <v>44.7357</v>
       </c>
       <c r="W178" t="n">
-        <v>-62.93511</v>
+        <v>-62.91338</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13686,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Mooseland Au District</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>D15-004</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -13707,7 +13703,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -13745,14 +13741,14 @@
         <v>30</v>
       </c>
       <c r="V179" t="n">
-        <v>44.7357</v>
+        <v>44.93474</v>
       </c>
       <c r="W179" t="n">
-        <v>-62.91338</v>
+        <v>-62.77464</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-004</t>
         </is>
       </c>
     </row>
@@ -13817,10 +13813,10 @@
         <v>30</v>
       </c>
       <c r="V180" t="n">
-        <v>44.93474</v>
+        <v>44.93392</v>
       </c>
       <c r="W180" t="n">
-        <v>-62.77464</v>
+        <v>-62.77429</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
@@ -13889,10 +13885,10 @@
         <v>30</v>
       </c>
       <c r="V181" t="n">
-        <v>44.93392</v>
+        <v>44.93618</v>
       </c>
       <c r="W181" t="n">
-        <v>-62.77429</v>
+        <v>-62.77165</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
@@ -13961,10 +13957,10 @@
         <v>30</v>
       </c>
       <c r="V182" t="n">
-        <v>44.93618</v>
+        <v>44.93833</v>
       </c>
       <c r="W182" t="n">
-        <v>-62.77165</v>
+        <v>-62.77055</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
@@ -13978,12 +13974,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mooseland Au District</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>D15-004</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -13995,7 +13991,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -14033,14 +14029,14 @@
         <v>30</v>
       </c>
       <c r="V183" t="n">
-        <v>44.93833</v>
+        <v>44.89232</v>
       </c>
       <c r="W183" t="n">
-        <v>-62.77055</v>
+        <v>-65.04106</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -14050,12 +14046,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Moosehead Gold Mine (Shiers Point)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>D16-002</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -14067,7 +14063,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -14105,14 +14101,14 @@
         <v>30</v>
       </c>
       <c r="V184" t="n">
-        <v>44.89232</v>
+        <v>44.94536</v>
       </c>
       <c r="W184" t="n">
-        <v>-65.04106</v>
+        <v>-62.24682</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-002</t>
         </is>
       </c>
     </row>
@@ -14177,10 +14173,10 @@
         <v>30</v>
       </c>
       <c r="V185" t="n">
-        <v>44.94536</v>
+        <v>44.94433</v>
       </c>
       <c r="W185" t="n">
-        <v>-62.24682</v>
+        <v>-62.25286</v>
       </c>
       <c r="X185" t="inlineStr">
         <is>
@@ -14194,12 +14190,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Moosehead Gold Mine (Shiers Point)</t>
+          <t>Harrigan Cove Au District</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>D16-002</t>
+          <t>D16-003</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -14211,7 +14207,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Au, Pb, As</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14249,14 +14245,14 @@
         <v>30</v>
       </c>
       <c r="V186" t="n">
-        <v>44.94433</v>
+        <v>44.93572</v>
       </c>
       <c r="W186" t="n">
-        <v>-62.25286</v>
+        <v>-62.29378</v>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-003</t>
         </is>
       </c>
     </row>
@@ -14321,10 +14317,10 @@
         <v>30</v>
       </c>
       <c r="V187" t="n">
-        <v>44.93572</v>
+        <v>44.93472</v>
       </c>
       <c r="W187" t="n">
-        <v>-62.29378</v>
+        <v>-62.2924</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
@@ -14393,10 +14389,10 @@
         <v>30</v>
       </c>
       <c r="V188" t="n">
-        <v>44.93472</v>
+        <v>44.93706</v>
       </c>
       <c r="W188" t="n">
-        <v>-62.2924</v>
+        <v>-62.29388</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
@@ -14410,12 +14406,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Harrigan Cove Au District</t>
+          <t>North Star Au Mine</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>D16-003</t>
+          <t>F04-018</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -14427,7 +14423,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Au, Pb, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14465,14 +14461,14 @@
         <v>30</v>
       </c>
       <c r="V189" t="n">
-        <v>44.93706</v>
+        <v>45.16835</v>
       </c>
       <c r="W189" t="n">
-        <v>-62.29388</v>
+        <v>-61.65325</v>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
         </is>
       </c>
     </row>
@@ -14482,12 +14478,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Harrigan Cove Au District</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>D16-003</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -14499,7 +14495,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Au, Pb, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14537,14 +14533,14 @@
         <v>30</v>
       </c>
       <c r="V190" t="n">
-        <v>44.93794</v>
+        <v>44.631</v>
       </c>
       <c r="W190" t="n">
-        <v>-62.2917</v>
+        <v>-63.44222</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -14554,12 +14550,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>North Star Au Mine</t>
+          <t>Lawerencetown Au District</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>F04-018</t>
+          <t>D11-002</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -14609,14 +14605,14 @@
         <v>30</v>
       </c>
       <c r="V191" t="n">
-        <v>45.16835</v>
+        <v>44.69621</v>
       </c>
       <c r="W191" t="n">
-        <v>-61.65325</v>
+        <v>-63.38554</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-002</t>
         </is>
       </c>
     </row>
@@ -14626,12 +14622,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lawerencetown Au District</t>
+          <t>Gold Lake Au District (Scraggy Lake Au Mine)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>D11-002</t>
+          <t>D15-005</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -14643,7 +14639,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Pb, Cu, Zn</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -14681,14 +14677,14 @@
         <v>30</v>
       </c>
       <c r="V192" t="n">
-        <v>44.69621</v>
+        <v>44.91772</v>
       </c>
       <c r="W192" t="n">
-        <v>-63.38554</v>
+        <v>-62.944</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-005</t>
         </is>
       </c>
     </row>
@@ -14698,12 +14694,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Gold Lake Au District (Scraggy Lake Au Mine)</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>D15-005</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -14715,7 +14711,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Au, As, Pb, Cu, Zn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -14753,14 +14749,14 @@
         <v>30</v>
       </c>
       <c r="V193" t="n">
-        <v>44.91772</v>
+        <v>44.89125</v>
       </c>
       <c r="W193" t="n">
-        <v>-62.944</v>
+        <v>-65.04064</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -14825,10 +14821,10 @@
         <v>30</v>
       </c>
       <c r="V194" t="n">
-        <v>44.89125</v>
+        <v>44.89109</v>
       </c>
       <c r="W194" t="n">
-        <v>-65.04064</v>
+        <v>-65.03443</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
@@ -14897,10 +14893,10 @@
         <v>30</v>
       </c>
       <c r="V195" t="n">
-        <v>44.89109</v>
+        <v>44.88953</v>
       </c>
       <c r="W195" t="n">
-        <v>-65.03443</v>
+        <v>-65.04628</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
@@ -14969,10 +14965,10 @@
         <v>30</v>
       </c>
       <c r="V196" t="n">
-        <v>44.88953</v>
+        <v>44.88409</v>
       </c>
       <c r="W196" t="n">
-        <v>-65.04628</v>
+        <v>-65.05318</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
@@ -14986,12 +14982,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>A16-007</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -15003,7 +14999,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn, Fe, Clay</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -15041,14 +15037,14 @@
         <v>30</v>
       </c>
       <c r="V197" t="n">
-        <v>44.88409</v>
+        <v>44.84479</v>
       </c>
       <c r="W197" t="n">
-        <v>-65.05318</v>
+        <v>-64.45338</v>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
         </is>
       </c>
     </row>
@@ -15058,12 +15054,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
+          <t>Cranberry Head Au Mine (Cream Pot Mine)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>A16-007</t>
+          <t>O16-002</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -15075,7 +15071,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Mn, Fe, Clay</t>
+          <t>Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15113,14 +15109,14 @@
         <v>30</v>
       </c>
       <c r="V198" t="n">
-        <v>44.84479</v>
+        <v>43.89875</v>
       </c>
       <c r="W198" t="n">
-        <v>-64.45338</v>
+        <v>-66.16804</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O16-002</t>
         </is>
       </c>
     </row>
@@ -15130,12 +15126,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Cranberry Head Au Mine (Cream Pot Mine)</t>
+          <t>Tangier Gold District</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>O16-002</t>
+          <t>D15-001</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -15147,7 +15143,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Au, Cu, Pb</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15185,14 +15181,14 @@
         <v>30</v>
       </c>
       <c r="V199" t="n">
-        <v>43.89875</v>
+        <v>44.80808</v>
       </c>
       <c r="W199" t="n">
-        <v>-66.16804</v>
+        <v>-62.69623</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O16-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-001</t>
         </is>
       </c>
     </row>
@@ -15202,12 +15198,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Tangier Gold District</t>
+          <t>Waverley Gold District</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>D15-001</t>
+          <t>D13-002</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -15219,7 +15215,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15257,14 +15253,14 @@
         <v>30</v>
       </c>
       <c r="V200" t="n">
-        <v>44.80808</v>
+        <v>44.78725</v>
       </c>
       <c r="W200" t="n">
-        <v>-62.69623</v>
+        <v>-63.59504</v>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-002</t>
         </is>
       </c>
     </row>
@@ -15329,10 +15325,10 @@
         <v>30</v>
       </c>
       <c r="V201" t="n">
-        <v>44.78725</v>
+        <v>44.78619</v>
       </c>
       <c r="W201" t="n">
-        <v>-63.59504</v>
+        <v>-63.60607</v>
       </c>
       <c r="X201" t="inlineStr">
         <is>
@@ -15346,12 +15342,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Waverley Gold District</t>
+          <t>Caribou Au District</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>D13-002</t>
+          <t>E02-004</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -15401,14 +15397,14 @@
         <v>30</v>
       </c>
       <c r="V202" t="n">
-        <v>44.78619</v>
+        <v>45.0626</v>
       </c>
       <c r="W202" t="n">
-        <v>-63.60607</v>
+        <v>-62.92085</v>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-004</t>
         </is>
       </c>
     </row>
@@ -15473,10 +15469,10 @@
         <v>30</v>
       </c>
       <c r="V203" t="n">
-        <v>45.0626</v>
+        <v>45.05304</v>
       </c>
       <c r="W203" t="n">
-        <v>-62.92085</v>
+        <v>-62.94877</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
@@ -15545,10 +15541,10 @@
         <v>30</v>
       </c>
       <c r="V204" t="n">
-        <v>45.05304</v>
+        <v>45.04586</v>
       </c>
       <c r="W204" t="n">
-        <v>-62.94877</v>
+        <v>-62.96507</v>
       </c>
       <c r="X204" t="inlineStr">
         <is>
@@ -15617,10 +15613,10 @@
         <v>30</v>
       </c>
       <c r="V205" t="n">
-        <v>45.04586</v>
+        <v>45.06151</v>
       </c>
       <c r="W205" t="n">
-        <v>-62.96507</v>
+        <v>-62.9466</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
@@ -15634,12 +15630,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Caribou Au District</t>
+          <t>Tangier Gold District</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>E02-004</t>
+          <t>D15-001</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -15651,7 +15647,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -15689,14 +15685,14 @@
         <v>30</v>
       </c>
       <c r="V206" t="n">
-        <v>45.06151</v>
+        <v>44.81273</v>
       </c>
       <c r="W206" t="n">
-        <v>-62.9466</v>
+        <v>-62.68112</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-001</t>
         </is>
       </c>
     </row>
@@ -15706,12 +15702,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Tangier Gold District</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>D15-001</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15723,7 +15719,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -15761,14 +15757,14 @@
         <v>30</v>
       </c>
       <c r="V207" t="n">
-        <v>44.81273</v>
+        <v>46.14468</v>
       </c>
       <c r="W207" t="n">
-        <v>-62.68112</v>
+        <v>-60.44769</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -15833,10 +15829,10 @@
         <v>30</v>
       </c>
       <c r="V208" t="n">
-        <v>46.14468</v>
+        <v>46.13825</v>
       </c>
       <c r="W208" t="n">
-        <v>-60.44769</v>
+        <v>-60.45019</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
@@ -15850,12 +15846,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Walton Pb, Zn, Ag, Ba Deposit</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>H01-008</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -15867,7 +15863,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Pb, Zn, Cu, Ag, Ba</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15905,14 +15901,14 @@
         <v>30</v>
       </c>
       <c r="V209" t="n">
-        <v>46.13825</v>
+        <v>45.2066</v>
       </c>
       <c r="W209" t="n">
-        <v>-60.45019</v>
+        <v>-64.04203</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H01-008</t>
         </is>
       </c>
     </row>
@@ -15922,12 +15918,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Walton Pb, Zn, Ag, Ba Deposit</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>H01-008</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -15939,12 +15935,12 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Ag, Ba</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I210" t="b">
@@ -15958,7 +15954,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="n">
@@ -15977,14 +15977,14 @@
         <v>30</v>
       </c>
       <c r="V210" t="n">
-        <v>45.2066</v>
+        <v>45.98426</v>
       </c>
       <c r="W210" t="n">
-        <v>-64.04203</v>
+        <v>-60.95151</v>
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H01-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -16011,12 +16011,12 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I211" t="b">
@@ -16030,11 +16030,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="n">
@@ -16053,14 +16049,14 @@
         <v>30</v>
       </c>
       <c r="V211" t="n">
-        <v>45.98426</v>
+        <v>44.44715</v>
       </c>
       <c r="W211" t="n">
-        <v>-60.95151</v>
+        <v>-64.78395</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -16070,12 +16066,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Black Diamond Iron Mine</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>E07-051</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -16087,7 +16083,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16125,14 +16121,14 @@
         <v>30</v>
       </c>
       <c r="V212" t="n">
-        <v>44.44715</v>
+        <v>45.43794</v>
       </c>
       <c r="W212" t="n">
-        <v>-64.78395</v>
+        <v>-62.60809</v>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-051</t>
         </is>
       </c>
     </row>
@@ -16142,12 +16138,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Black Diamond Iron Mine</t>
+          <t>McDonald Mine Iron Mine</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>E07-051</t>
+          <t>E07-052</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -16197,14 +16193,14 @@
         <v>30</v>
       </c>
       <c r="V213" t="n">
-        <v>45.43794</v>
+        <v>45.43703</v>
       </c>
       <c r="W213" t="n">
-        <v>-62.60809</v>
+        <v>-62.60298</v>
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-051</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-052</t>
         </is>
       </c>
     </row>
@@ -16214,12 +16210,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>McDonald Mine Iron Mine</t>
+          <t>Black Rock Iron Mine</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>E07-052</t>
+          <t>E07-055</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -16231,7 +16227,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16269,14 +16265,14 @@
         <v>30</v>
       </c>
       <c r="V214" t="n">
-        <v>45.43703</v>
+        <v>45.41004</v>
       </c>
       <c r="W214" t="n">
-        <v>-62.60298</v>
+        <v>-62.53634</v>
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-052</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-055</t>
         </is>
       </c>
     </row>
@@ -16286,12 +16282,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Black Rock Iron Mine</t>
+          <t>Lansdowne Cu Deposit (New Lairg)</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>E07-055</t>
+          <t>E07-002</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -16303,7 +16299,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Pb, Sb, Ag</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16341,14 +16337,14 @@
         <v>30</v>
       </c>
       <c r="V215" t="n">
-        <v>45.41004</v>
+        <v>45.45981</v>
       </c>
       <c r="W215" t="n">
-        <v>-62.53634</v>
+        <v>-62.81822</v>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-002</t>
         </is>
       </c>
     </row>
@@ -16358,12 +16354,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Lansdowne Cu Deposit (New Lairg)</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>E07-002</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -16375,12 +16371,12 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cu, Pb, Sb, Ag</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I216" t="b">
@@ -16394,7 +16390,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="n">
@@ -16413,14 +16413,14 @@
         <v>30</v>
       </c>
       <c r="V216" t="n">
-        <v>45.45981</v>
+        <v>45.9849</v>
       </c>
       <c r="W216" t="n">
-        <v>-62.81822</v>
+        <v>-60.95704</v>
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -16430,12 +16430,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Lansdowne Cu Deposit (New Lairg)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E07-002</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -16447,12 +16447,12 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Cu, Pb, Sb, Ag</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I217" t="b">
@@ -16466,11 +16466,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="n">
@@ -16489,14 +16485,14 @@
         <v>30</v>
       </c>
       <c r="V217" t="n">
-        <v>45.9849</v>
+        <v>45.46034</v>
       </c>
       <c r="W217" t="n">
-        <v>-60.95704</v>
+        <v>-62.81643</v>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-002</t>
         </is>
       </c>
     </row>
@@ -16506,12 +16502,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Lansdowne Cu Deposit (New Lairg)</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>E07-002</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -16523,7 +16519,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Cu, Pb, Sb, Ag</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -16561,14 +16557,14 @@
         <v>30</v>
       </c>
       <c r="V218" t="n">
-        <v>45.46034</v>
+        <v>45.4857</v>
       </c>
       <c r="W218" t="n">
-        <v>-62.81643</v>
+        <v>-62.52535</v>
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -16578,12 +16574,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Specular Iron Mines</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>E07-010</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -16595,7 +16591,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Fe, Co, Au</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -16633,14 +16629,14 @@
         <v>30</v>
       </c>
       <c r="V219" t="n">
-        <v>45.4857</v>
+        <v>45.39658</v>
       </c>
       <c r="W219" t="n">
-        <v>-62.52535</v>
+        <v>-62.56726</v>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-010</t>
         </is>
       </c>
     </row>
@@ -16705,10 +16701,10 @@
         <v>30</v>
       </c>
       <c r="V220" t="n">
-        <v>45.39658</v>
+        <v>45.39836</v>
       </c>
       <c r="W220" t="n">
-        <v>-62.56726</v>
+        <v>-62.56139</v>
       </c>
       <c r="X220" t="inlineStr">
         <is>
@@ -16722,12 +16718,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Specular Iron Mines</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>E07-010</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -16739,12 +16735,12 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Fe, Co, Au</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I221" t="b">
@@ -16758,7 +16754,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="n">
@@ -16777,14 +16777,14 @@
         <v>30</v>
       </c>
       <c r="V221" t="n">
-        <v>45.39836</v>
+        <v>45.9844</v>
       </c>
       <c r="W221" t="n">
-        <v>-62.56139</v>
+        <v>-60.94402</v>
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -16844,19 +16844,19 @@
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T222" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U222" t="n">
         <v>30</v>
       </c>
       <c r="V222" t="n">
-        <v>45.9844</v>
+        <v>45.99089</v>
       </c>
       <c r="W222" t="n">
-        <v>-60.94402</v>
+        <v>-60.96495</v>
       </c>
       <c r="X222" t="inlineStr">
         <is>
@@ -16870,12 +16870,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Lansdowne Cu Deposit (New Lairg)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E07-002</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -16887,12 +16887,12 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Cu, Pb, Sb, Ag</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I223" t="b">
@@ -16906,11 +16906,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="n">
@@ -16920,23 +16916,23 @@
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T223" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U223" t="n">
         <v>30</v>
       </c>
       <c r="V223" t="n">
-        <v>45.99089</v>
+        <v>45.46084</v>
       </c>
       <c r="W223" t="n">
-        <v>-60.96495</v>
+        <v>-62.81853</v>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-002</t>
         </is>
       </c>
     </row>
@@ -16946,12 +16942,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Lansdowne Cu Deposit (New Lairg)</t>
+          <t>Waverley Gold District</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>E07-002</t>
+          <t>D13-002</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -16963,7 +16959,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Cu, Pb, Sb, Ag</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17001,14 +16997,14 @@
         <v>30</v>
       </c>
       <c r="V224" t="n">
-        <v>45.46084</v>
+        <v>44.77967</v>
       </c>
       <c r="W224" t="n">
-        <v>-62.81853</v>
+        <v>-63.61055</v>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-002</t>
         </is>
       </c>
     </row>
@@ -17073,10 +17069,10 @@
         <v>30</v>
       </c>
       <c r="V225" t="n">
-        <v>44.77967</v>
+        <v>44.78536</v>
       </c>
       <c r="W225" t="n">
-        <v>-63.61055</v>
+        <v>-63.60927</v>
       </c>
       <c r="X225" t="inlineStr">
         <is>
@@ -17090,12 +17086,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Waverley Gold District</t>
+          <t>Kemptville Au District</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>D13-002</t>
+          <t>A04-003</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -17107,7 +17103,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17145,14 +17141,14 @@
         <v>30</v>
       </c>
       <c r="V226" t="n">
-        <v>44.78536</v>
+        <v>44.0512</v>
       </c>
       <c r="W226" t="n">
-        <v>-63.60927</v>
+        <v>-65.85553</v>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-003</t>
         </is>
       </c>
     </row>
@@ -17162,12 +17158,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Kemptville Au District</t>
+          <t>Country Harbour Au District</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>A04-003</t>
+          <t>F04-003</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -17217,14 +17213,14 @@
         <v>30</v>
       </c>
       <c r="V227" t="n">
-        <v>44.0512</v>
+        <v>45.25642</v>
       </c>
       <c r="W227" t="n">
-        <v>-65.85553</v>
+        <v>-61.81272</v>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-003</t>
         </is>
       </c>
     </row>
@@ -17234,12 +17230,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Country Harbour Au District</t>
+          <t>Forest Hill Gold District</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>F04-003</t>
+          <t>F05-012</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -17251,7 +17247,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -17289,14 +17285,14 @@
         <v>30</v>
       </c>
       <c r="V228" t="n">
-        <v>45.25642</v>
+        <v>45.30592</v>
       </c>
       <c r="W228" t="n">
-        <v>-61.81272</v>
+        <v>-61.7444</v>
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F05-012</t>
         </is>
       </c>
     </row>
@@ -17361,10 +17357,10 @@
         <v>30</v>
       </c>
       <c r="V229" t="n">
-        <v>45.30592</v>
+        <v>45.30925</v>
       </c>
       <c r="W229" t="n">
-        <v>-61.7444</v>
+        <v>-61.75538</v>
       </c>
       <c r="X229" t="inlineStr">
         <is>
@@ -17378,12 +17374,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Forest Hill Gold District</t>
+          <t>Stanburne</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>F05-012</t>
+          <t>A10-002</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -17395,7 +17391,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Au, W</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -17433,14 +17429,14 @@
         <v>30</v>
       </c>
       <c r="V230" t="n">
-        <v>45.30925</v>
+        <v>44.61835</v>
       </c>
       <c r="W230" t="n">
-        <v>-61.75538</v>
+        <v>-64.74563000000001</v>
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F05-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-002</t>
         </is>
       </c>
     </row>
@@ -17450,12 +17446,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Stanburne</t>
+          <t>Pockwock Au Prospect</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>A10-002</t>
+          <t>D13-009</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -17467,12 +17463,12 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Au, W</t>
+          <t>Au, Ag</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I231" t="b">
@@ -17486,7 +17482,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Au 1.16 g/t, Ag 14.30 g/t</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="n">
@@ -17505,14 +17505,14 @@
         <v>30</v>
       </c>
       <c r="V231" t="n">
-        <v>44.61835</v>
+        <v>44.75716</v>
       </c>
       <c r="W231" t="n">
-        <v>-64.74563000000001</v>
+        <v>-63.85781</v>
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-009</t>
         </is>
       </c>
     </row>
@@ -17522,12 +17522,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Pockwock Au Prospect</t>
+          <t>Wine Harbour Au District</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>D13-009</t>
+          <t>F04-002</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -17539,12 +17539,12 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Au, Ag</t>
+          <t>Au, As</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I232" t="b">
@@ -17558,11 +17558,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>Au 1.16 g/t, Ag 14.30 g/t</t>
-        </is>
-      </c>
+      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="n">
@@ -17581,14 +17577,14 @@
         <v>30</v>
       </c>
       <c r="V232" t="n">
-        <v>44.75716</v>
+        <v>45.07497</v>
       </c>
       <c r="W232" t="n">
-        <v>-63.85781</v>
+        <v>-61.8476</v>
       </c>
       <c r="X232" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-002</t>
         </is>
       </c>
     </row>
@@ -17653,10 +17649,10 @@
         <v>30</v>
       </c>
       <c r="V233" t="n">
-        <v>45.07497</v>
+        <v>45.07654</v>
       </c>
       <c r="W233" t="n">
-        <v>-61.8476</v>
+        <v>-61.84784</v>
       </c>
       <c r="X233" t="inlineStr">
         <is>
@@ -17670,12 +17666,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Wine Harbour Au District</t>
+          <t>Country Harbour Au District</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>F04-002</t>
+          <t>F04-003</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -17687,7 +17683,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Au, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -17725,14 +17721,14 @@
         <v>30</v>
       </c>
       <c r="V234" t="n">
-        <v>45.07654</v>
+        <v>45.24668</v>
       </c>
       <c r="W234" t="n">
-        <v>-61.84784</v>
+        <v>-61.80894</v>
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-003</t>
         </is>
       </c>
     </row>
@@ -17742,12 +17738,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Country Harbour Au District</t>
+          <t>Carleton Au District</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>F04-003</t>
+          <t>A04-001</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -17759,7 +17755,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Cu, Pb, Ag</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -17788,23 +17784,23 @@
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T235" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U235" t="n">
         <v>30</v>
       </c>
       <c r="V235" t="n">
-        <v>45.24668</v>
+        <v>44.00567</v>
       </c>
       <c r="W235" t="n">
-        <v>-61.80894</v>
+        <v>-65.93244</v>
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-001</t>
         </is>
       </c>
     </row>
@@ -17814,12 +17810,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Carleton Au District</t>
+          <t>Whiteburn Au District</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>A04-001</t>
+          <t>A06-001</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -17831,7 +17827,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Au, As, Cu, Pb, Ag</t>
+          <t>Au, Cu, Pb</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -17860,23 +17856,23 @@
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T236" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U236" t="n">
         <v>30</v>
       </c>
       <c r="V236" t="n">
-        <v>44.00567</v>
+        <v>44.31051</v>
       </c>
       <c r="W236" t="n">
-        <v>-65.93244</v>
+        <v>-65.07468</v>
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A06-001</t>
         </is>
       </c>
     </row>
@@ -17886,12 +17882,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Whiteburn Au District</t>
+          <t>West Caledonia Au Mine (McGinty Mine)</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>A06-001</t>
+          <t>A06-002</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -17903,7 +17899,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Au, Cu, Pb</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -17941,14 +17937,14 @@
         <v>30</v>
       </c>
       <c r="V237" t="n">
-        <v>44.31051</v>
+        <v>44.35715</v>
       </c>
       <c r="W237" t="n">
-        <v>-65.07468</v>
+        <v>-65.16668</v>
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A06-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A06-002</t>
         </is>
       </c>
     </row>
@@ -17958,12 +17954,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>West Caledonia Au Mine (McGinty Mine)</t>
+          <t>Molega  Au District</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>A06-002</t>
+          <t>A07-003</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -18013,14 +18009,14 @@
         <v>30</v>
       </c>
       <c r="V238" t="n">
-        <v>44.35715</v>
+        <v>44.3318</v>
       </c>
       <c r="W238" t="n">
-        <v>-65.16668</v>
+        <v>-64.90184000000001</v>
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A06-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-003</t>
         </is>
       </c>
     </row>
@@ -18085,10 +18081,10 @@
         <v>30</v>
       </c>
       <c r="V239" t="n">
-        <v>44.3318</v>
+        <v>44.3384</v>
       </c>
       <c r="W239" t="n">
-        <v>-64.90184000000001</v>
+        <v>-64.89478</v>
       </c>
       <c r="X239" t="inlineStr">
         <is>
@@ -18157,10 +18153,10 @@
         <v>30</v>
       </c>
       <c r="V240" t="n">
-        <v>44.3384</v>
+        <v>44.33365</v>
       </c>
       <c r="W240" t="n">
-        <v>-64.89478</v>
+        <v>-64.88785</v>
       </c>
       <c r="X240" t="inlineStr">
         <is>
@@ -18174,12 +18170,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Molega  Au District</t>
+          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>A07-003</t>
+          <t>A16-007</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -18191,7 +18187,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Mn, Fe, Clay</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18229,14 +18225,14 @@
         <v>30</v>
       </c>
       <c r="V241" t="n">
-        <v>44.33365</v>
+        <v>44.8513</v>
       </c>
       <c r="W241" t="n">
-        <v>-64.88785</v>
+        <v>-64.44418</v>
       </c>
       <c r="X241" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
         </is>
       </c>
     </row>
@@ -18246,12 +18242,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
+          <t>Blockhouse Au Mine</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>A16-007</t>
+          <t>A08-006</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -18263,7 +18259,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Mn, Fe, Clay</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18301,14 +18297,14 @@
         <v>30</v>
       </c>
       <c r="V242" t="n">
-        <v>44.8513</v>
+        <v>44.43646</v>
       </c>
       <c r="W242" t="n">
-        <v>-64.44418</v>
+        <v>-64.42234999999999</v>
       </c>
       <c r="X242" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-006</t>
         </is>
       </c>
     </row>
@@ -18318,12 +18314,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Blockhouse Au Mine</t>
+          <t>Mill Village Au District</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>A08-006</t>
+          <t>A02-004</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -18373,14 +18369,14 @@
         <v>30</v>
       </c>
       <c r="V243" t="n">
-        <v>44.43646</v>
+        <v>44.1573</v>
       </c>
       <c r="W243" t="n">
-        <v>-64.42234999999999</v>
+        <v>-64.70350999999999</v>
       </c>
       <c r="X243" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-004</t>
         </is>
       </c>
     </row>
@@ -18445,10 +18441,10 @@
         <v>30</v>
       </c>
       <c r="V244" t="n">
-        <v>44.1573</v>
+        <v>44.15977</v>
       </c>
       <c r="W244" t="n">
-        <v>-64.70350999999999</v>
+        <v>-64.70071</v>
       </c>
       <c r="X244" t="inlineStr">
         <is>
@@ -18517,10 +18513,10 @@
         <v>30</v>
       </c>
       <c r="V245" t="n">
-        <v>44.15977</v>
+        <v>44.15962</v>
       </c>
       <c r="W245" t="n">
-        <v>-64.70071</v>
+        <v>-64.6992</v>
       </c>
       <c r="X245" t="inlineStr">
         <is>
@@ -18534,12 +18530,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Mill Village Au District</t>
+          <t>Goldenville Au District</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>A02-004</t>
+          <t>E01-001</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -18551,7 +18547,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -18589,14 +18585,14 @@
         <v>30</v>
       </c>
       <c r="V246" t="n">
-        <v>44.15962</v>
+        <v>45.12504</v>
       </c>
       <c r="W246" t="n">
-        <v>-64.6992</v>
+        <v>-62.0205</v>
       </c>
       <c r="X246" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-001</t>
         </is>
       </c>
     </row>
@@ -18652,19 +18648,19 @@
       <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T247" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U247" t="n">
         <v>30</v>
       </c>
       <c r="V247" t="n">
-        <v>45.12504</v>
+        <v>45.12319</v>
       </c>
       <c r="W247" t="n">
-        <v>-62.0205</v>
+        <v>-62.01631</v>
       </c>
       <c r="X247" t="inlineStr">
         <is>
@@ -18733,10 +18729,10 @@
         <v>30</v>
       </c>
       <c r="V248" t="n">
-        <v>45.12319</v>
+        <v>45.12314</v>
       </c>
       <c r="W248" t="n">
-        <v>-62.01631</v>
+        <v>-62.01171</v>
       </c>
       <c r="X248" t="inlineStr">
         <is>
@@ -18750,12 +18746,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Goldenville Au District</t>
+          <t>Brookfield Au Mine</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>E01-001</t>
+          <t>A07-004</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -18767,7 +18763,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Au, As, Cu, Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -18796,23 +18792,23 @@
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T249" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U249" t="n">
         <v>30</v>
       </c>
       <c r="V249" t="n">
-        <v>45.12314</v>
+        <v>44.40458</v>
       </c>
       <c r="W249" t="n">
-        <v>-62.01171</v>
+        <v>-64.91835</v>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-004</t>
         </is>
       </c>
     </row>
@@ -18822,12 +18818,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Brookfield Au Mine</t>
+          <t>Stirling Zn, Pb, Cu Deposit (Mindamar Mine)</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>A07-004</t>
+          <t>F09-001</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -18839,7 +18835,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Zn, Pb, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -18877,14 +18873,14 @@
         <v>30</v>
       </c>
       <c r="V250" t="n">
-        <v>44.40458</v>
+        <v>45.72959</v>
       </c>
       <c r="W250" t="n">
-        <v>-64.91835</v>
+        <v>-60.43738</v>
       </c>
       <c r="X250" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F09-001</t>
         </is>
       </c>
     </row>
@@ -18894,12 +18890,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Stirling Zn, Pb, Cu Deposit (Mindamar Mine)</t>
+          <t>Fifteen Mile Stream Gold District</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>F09-001</t>
+          <t>E02-010</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -18911,7 +18907,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ag, Au</t>
+          <t>Au, Pt</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -18949,14 +18945,14 @@
         <v>30</v>
       </c>
       <c r="V251" t="n">
-        <v>45.72959</v>
+        <v>45.13842</v>
       </c>
       <c r="W251" t="n">
-        <v>-60.43738</v>
+        <v>-62.54832</v>
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F09-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-010</t>
         </is>
       </c>
     </row>
@@ -19021,10 +19017,10 @@
         <v>30</v>
       </c>
       <c r="V252" t="n">
-        <v>45.13842</v>
+        <v>45.14238</v>
       </c>
       <c r="W252" t="n">
-        <v>-62.54832</v>
+        <v>-62.53468</v>
       </c>
       <c r="X252" t="inlineStr">
         <is>
@@ -19038,12 +19034,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Fifteen Mile Stream Gold District</t>
+          <t>Cameron Iron Mine</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>E02-010</t>
+          <t>E07-050</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -19055,7 +19051,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Au, Pt</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -19093,14 +19089,14 @@
         <v>30</v>
       </c>
       <c r="V253" t="n">
-        <v>45.14238</v>
+        <v>45.44002</v>
       </c>
       <c r="W253" t="n">
-        <v>-62.53468</v>
+        <v>-62.60987</v>
       </c>
       <c r="X253" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-050</t>
         </is>
       </c>
     </row>
@@ -19110,12 +19106,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Cameron Iron Mine</t>
+          <t>Aureus West Gold Property (Fmr Dufferin West)</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>E07-050</t>
+          <t>D16-009</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -19127,7 +19123,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19165,14 +19161,14 @@
         <v>30</v>
       </c>
       <c r="V254" t="n">
-        <v>45.44002</v>
+        <v>44.96249</v>
       </c>
       <c r="W254" t="n">
-        <v>-62.60987</v>
+        <v>-62.39562</v>
       </c>
       <c r="X254" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-050</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-009</t>
         </is>
       </c>
     </row>
@@ -19182,12 +19178,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Aureus West Gold Property (Fmr Dufferin West)</t>
+          <t>East Kemptville Sn Deposit</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>D16-009</t>
+          <t>A04-009</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -19199,7 +19195,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Ag, Cu, Sn, Zn, In</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -19237,14 +19233,14 @@
         <v>30</v>
       </c>
       <c r="V255" t="n">
-        <v>44.96249</v>
+        <v>44.10315</v>
       </c>
       <c r="W255" t="n">
-        <v>-62.39562</v>
+        <v>-65.68088</v>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-009</t>
         </is>
       </c>
     </row>
@@ -19254,12 +19250,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>East Kemptville Sn Deposit</t>
+          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>A04-009</t>
+          <t>A16-007</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -19271,7 +19267,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Ag, Cu, Sn, Zn, In</t>
+          <t>Mn, Fe, Clay</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -19309,14 +19305,14 @@
         <v>30</v>
       </c>
       <c r="V256" t="n">
-        <v>44.10315</v>
+        <v>44.84782</v>
       </c>
       <c r="W256" t="n">
-        <v>-65.68088</v>
+        <v>-64.44878</v>
       </c>
       <c r="X256" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
         </is>
       </c>
     </row>
@@ -19326,12 +19322,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>A16-007</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -19343,7 +19339,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Mn, Fe, Clay</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -19381,14 +19377,14 @@
         <v>30</v>
       </c>
       <c r="V257" t="n">
-        <v>44.84782</v>
+        <v>44.44452</v>
       </c>
       <c r="W257" t="n">
-        <v>-64.44878</v>
+        <v>-64.79065</v>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -19453,10 +19449,10 @@
         <v>30</v>
       </c>
       <c r="V258" t="n">
-        <v>44.44452</v>
+        <v>44.43925</v>
       </c>
       <c r="W258" t="n">
-        <v>-64.79065</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X258" t="inlineStr">
         <is>
@@ -19470,12 +19466,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Gold River Au District</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>A09-003</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -19487,7 +19483,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, Cu, Fe, As</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -19525,14 +19521,14 @@
         <v>30</v>
       </c>
       <c r="V259" t="n">
-        <v>44.43925</v>
+        <v>44.57468</v>
       </c>
       <c r="W259" t="n">
-        <v>-64.78243999999999</v>
+        <v>-64.33113</v>
       </c>
       <c r="X259" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-003</t>
         </is>
       </c>
     </row>
@@ -19542,12 +19538,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Gold River Au District</t>
+          <t>Stanburne</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>A09-003</t>
+          <t>A10-002</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -19559,7 +19555,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Au, Cu, Fe, As</t>
+          <t>Au, W</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -19597,14 +19593,14 @@
         <v>30</v>
       </c>
       <c r="V260" t="n">
-        <v>44.57468</v>
+        <v>44.62095</v>
       </c>
       <c r="W260" t="n">
-        <v>-64.33113</v>
+        <v>-64.74576</v>
       </c>
       <c r="X260" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-002</t>
         </is>
       </c>
     </row>
@@ -19614,12 +19610,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Stanburne</t>
+          <t>Dean and Chapter Mn Mine (Upper Mine)</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>A10-002</t>
+          <t>A16-006</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -19631,7 +19627,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Au, W</t>
+          <t>Mn, Fe, Clay</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -19669,14 +19665,14 @@
         <v>30</v>
       </c>
       <c r="V261" t="n">
-        <v>44.62095</v>
+        <v>44.8647</v>
       </c>
       <c r="W261" t="n">
-        <v>-64.74576</v>
+        <v>-64.43781</v>
       </c>
       <c r="X261" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-006</t>
         </is>
       </c>
     </row>
@@ -19686,12 +19682,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Dean and Chapter Mn Mine (Upper Mine)</t>
+          <t>Beaver Dam Gold District</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>A16-006</t>
+          <t>E02-001</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -19703,7 +19699,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Mn, Fe, Clay</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -19741,14 +19737,14 @@
         <v>30</v>
       </c>
       <c r="V262" t="n">
-        <v>44.8647</v>
+        <v>45.06488</v>
       </c>
       <c r="W262" t="n">
-        <v>-64.43781</v>
+        <v>-62.71683</v>
       </c>
       <c r="X262" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-001</t>
         </is>
       </c>
     </row>
@@ -19758,12 +19754,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Beaver Dam Gold District</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>E02-001</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -19775,12 +19771,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I263" t="b">
@@ -19794,7 +19790,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="n">
@@ -19813,14 +19813,14 @@
         <v>30</v>
       </c>
       <c r="V263" t="n">
-        <v>45.06488</v>
+        <v>45.91475</v>
       </c>
       <c r="W263" t="n">
-        <v>-62.71683</v>
+        <v>-61.23041</v>
       </c>
       <c r="X263" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E02-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -20126,12 +20126,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Saddler Fe Mine (Monck Shaft)</t>
+          <t>Specular Iron Mines</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>E07-049</t>
+          <t>E07-010</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe, Co, Au</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -20181,14 +20181,14 @@
         <v>30</v>
       </c>
       <c r="V268" t="n">
-        <v>45.43112</v>
+        <v>45.39797</v>
       </c>
       <c r="W268" t="n">
-        <v>-62.58794</v>
+        <v>-62.55694</v>
       </c>
       <c r="X268" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-010</t>
         </is>
       </c>
     </row>
@@ -20198,12 +20198,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Grant Iron Mines</t>
+          <t>Specular Iron Mines</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>E07-048</t>
+          <t>E07-010</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -20215,7 +20215,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe, Co, Au</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -20253,14 +20253,14 @@
         <v>30</v>
       </c>
       <c r="V269" t="n">
-        <v>45.43657</v>
+        <v>45.39792</v>
       </c>
       <c r="W269" t="n">
-        <v>-62.60094</v>
+        <v>-62.53845</v>
       </c>
       <c r="X269" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-048</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-010</t>
         </is>
       </c>
     </row>
@@ -20270,12 +20270,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Grant Iron Mines</t>
+          <t>Glenbervie Pb Mine</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>E07-048</t>
+          <t>E07-018</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -20325,14 +20325,14 @@
         <v>30</v>
       </c>
       <c r="V270" t="n">
-        <v>45.43496</v>
+        <v>45.28513</v>
       </c>
       <c r="W270" t="n">
-        <v>-62.59149</v>
+        <v>-62.93781</v>
       </c>
       <c r="X270" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-048</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
         </is>
       </c>
     </row>
@@ -20342,12 +20342,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Grant Iron Mines</t>
+          <t>Bridgeville (J.S. Cameron Mine)</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>E07-048</t>
+          <t>E07-044</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -20397,14 +20397,14 @@
         <v>30</v>
       </c>
       <c r="V271" t="n">
-        <v>45.43606</v>
+        <v>45.43705</v>
       </c>
       <c r="W271" t="n">
-        <v>-62.59698</v>
+        <v>-62.6104</v>
       </c>
       <c r="X271" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-048</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-044</t>
         </is>
       </c>
     </row>
@@ -20414,12 +20414,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Bridgeville (J.S. Cameron Mine)</t>
+          <t>Grant Iron Mines</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>E07-044</t>
+          <t>E07-048</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -20469,14 +20469,14 @@
         <v>30</v>
       </c>
       <c r="V272" t="n">
-        <v>45.43705</v>
+        <v>45.43606</v>
       </c>
       <c r="W272" t="n">
-        <v>-62.6104</v>
+        <v>-62.59698</v>
       </c>
       <c r="X272" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-044</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-048</t>
         </is>
       </c>
     </row>
@@ -20486,12 +20486,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Glenbervie Pb Mine</t>
+          <t>Grant Iron Mines</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>E07-018</t>
+          <t>E07-048</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -20503,7 +20503,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -20541,14 +20541,14 @@
         <v>30</v>
       </c>
       <c r="V273" t="n">
-        <v>45.28513</v>
+        <v>45.43496</v>
       </c>
       <c r="W273" t="n">
-        <v>-62.93781</v>
+        <v>-62.59149</v>
       </c>
       <c r="X273" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-048</t>
         </is>
       </c>
     </row>
@@ -20558,12 +20558,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Specular Iron Mines</t>
+          <t>Grant Iron Mines</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>E07-010</t>
+          <t>E07-048</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -20575,7 +20575,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Fe, Co, Au</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -20613,14 +20613,14 @@
         <v>30</v>
       </c>
       <c r="V274" t="n">
-        <v>45.39792</v>
+        <v>45.43657</v>
       </c>
       <c r="W274" t="n">
-        <v>-62.53845</v>
+        <v>-62.60094</v>
       </c>
       <c r="X274" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-048</t>
         </is>
       </c>
     </row>
@@ -20630,12 +20630,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Specular Iron Mines</t>
+          <t>Saddler Fe Mine (Monck Shaft)</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>E07-010</t>
+          <t>E07-049</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Fe, Co, Au</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -20685,14 +20685,14 @@
         <v>30</v>
       </c>
       <c r="V275" t="n">
-        <v>45.39797</v>
+        <v>45.43112</v>
       </c>
       <c r="W275" t="n">
-        <v>-62.55694</v>
+        <v>-62.58794</v>
       </c>
       <c r="X275" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-049</t>
         </is>
       </c>
     </row>
@@ -21206,12 +21206,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Widow Point Au Mine</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>F04-016</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -21223,7 +21223,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -21261,14 +21261,14 @@
         <v>30</v>
       </c>
       <c r="V283" t="n">
-        <v>45.24176</v>
+        <v>45.73558</v>
       </c>
       <c r="W283" t="n">
-        <v>-61.79157</v>
+        <v>-62.16591</v>
       </c>
       <c r="X283" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -21278,12 +21278,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Erinville (Walsh and McKinnon Mines)</t>
+          <t>Widow Point Au Mine</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>F05-007</t>
+          <t>F04-016</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -21295,7 +21295,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -21333,14 +21333,14 @@
         <v>30</v>
       </c>
       <c r="V284" t="n">
-        <v>45.38392</v>
+        <v>45.23913</v>
       </c>
       <c r="W284" t="n">
-        <v>-61.74394</v>
+        <v>-61.78763</v>
       </c>
       <c r="X284" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F05-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-016</t>
         </is>
       </c>
     </row>
@@ -21405,10 +21405,10 @@
         <v>30</v>
       </c>
       <c r="V285" t="n">
-        <v>45.38255</v>
+        <v>45.38392</v>
       </c>
       <c r="W285" t="n">
-        <v>-61.75055</v>
+        <v>-61.74394</v>
       </c>
       <c r="X285" t="inlineStr">
         <is>
@@ -21422,12 +21422,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>College Grant Cu, Fe Mine</t>
+          <t>Erinville (Walsh and McKinnon Mines)</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>E08-002</t>
+          <t>F05-007</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Cu, Fe, Pb, Zn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -21477,14 +21477,14 @@
         <v>30</v>
       </c>
       <c r="V286" t="n">
-        <v>45.40028</v>
+        <v>45.38255</v>
       </c>
       <c r="W286" t="n">
-        <v>-62.05918</v>
+        <v>-61.75055</v>
       </c>
       <c r="X286" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F05-007</t>
         </is>
       </c>
     </row>
@@ -21549,10 +21549,10 @@
         <v>30</v>
       </c>
       <c r="V287" t="n">
-        <v>45.39575</v>
+        <v>45.40028</v>
       </c>
       <c r="W287" t="n">
-        <v>-62.07867</v>
+        <v>-62.05918</v>
       </c>
       <c r="X287" t="inlineStr">
         <is>
@@ -21621,10 +21621,10 @@
         <v>30</v>
       </c>
       <c r="V288" t="n">
-        <v>45.39379</v>
+        <v>45.39575</v>
       </c>
       <c r="W288" t="n">
-        <v>-62.08662</v>
+        <v>-62.07867</v>
       </c>
       <c r="X288" t="inlineStr">
         <is>
@@ -21638,12 +21638,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Cross Roads Ohio Cu-Pb-Zn Mine</t>
+          <t>College Grant Cu, Fe Mine</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>E08-005</t>
+          <t>E08-002</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -21655,7 +21655,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Cu, Fe, Pb, Zn, F</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21693,14 +21693,14 @@
         <v>30</v>
       </c>
       <c r="V289" t="n">
-        <v>45.48717</v>
+        <v>45.39379</v>
       </c>
       <c r="W289" t="n">
-        <v>-62.07373</v>
+        <v>-62.08662</v>
       </c>
       <c r="X289" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-002</t>
         </is>
       </c>
     </row>
@@ -21710,12 +21710,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Cross Roads Ohio Cu-Pb-Zn Mine</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>E08-005</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -21727,7 +21727,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -21765,14 +21765,14 @@
         <v>30</v>
       </c>
       <c r="V290" t="n">
-        <v>45.25157</v>
+        <v>45.48717</v>
       </c>
       <c r="W290" t="n">
-        <v>-62.11656</v>
+        <v>-62.07373</v>
       </c>
       <c r="X290" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-005</t>
         </is>
       </c>
     </row>
@@ -21782,12 +21782,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -21837,14 +21837,14 @@
         <v>30</v>
       </c>
       <c r="V291" t="n">
-        <v>45.73558</v>
+        <v>45.25157</v>
       </c>
       <c r="W291" t="n">
-        <v>-62.16591</v>
+        <v>-62.11656</v>
       </c>
       <c r="X291" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -21909,10 +21909,10 @@
         <v>30</v>
       </c>
       <c r="V292" t="n">
-        <v>45.23913</v>
+        <v>45.24176</v>
       </c>
       <c r="W292" t="n">
-        <v>-61.78763</v>
+        <v>-61.79157</v>
       </c>
       <c r="X292" t="inlineStr">
         <is>
@@ -22462,12 +22462,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -22479,12 +22479,12 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I300" t="b">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr"/>
@@ -22521,14 +22521,14 @@
         <v>27</v>
       </c>
       <c r="V300" t="n">
-        <v>46.44885</v>
+        <v>46.60665</v>
       </c>
       <c r="W300" t="n">
-        <v>-60.58676</v>
+        <v>-60.92386</v>
       </c>
       <c r="X300" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -22538,12 +22538,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -22555,12 +22555,12 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I301" t="b">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M301" t="inlineStr"/>
@@ -22597,14 +22597,14 @@
         <v>27</v>
       </c>
       <c r="V301" t="n">
-        <v>46.44956</v>
+        <v>45.25896</v>
       </c>
       <c r="W301" t="n">
-        <v>-60.57775</v>
+        <v>-62.86207</v>
       </c>
       <c r="X301" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -22614,12 +22614,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -22631,7 +22631,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -22652,7 +22652,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M302" t="inlineStr"/>
@@ -22673,14 +22673,14 @@
         <v>27</v>
       </c>
       <c r="V302" t="n">
-        <v>46.44219</v>
+        <v>45.66247</v>
       </c>
       <c r="W302" t="n">
-        <v>-60.58706</v>
+        <v>-60.50348</v>
       </c>
       <c r="X302" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -22690,12 +22690,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M303" t="inlineStr"/>
@@ -22749,14 +22749,14 @@
         <v>27</v>
       </c>
       <c r="V303" t="n">
-        <v>46.44638</v>
+        <v>45.66068</v>
       </c>
       <c r="W303" t="n">
-        <v>-60.57242</v>
+        <v>-60.49983</v>
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -22766,12 +22766,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -22783,12 +22783,12 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I304" t="b">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr"/>
@@ -22825,14 +22825,14 @@
         <v>27</v>
       </c>
       <c r="V304" t="n">
-        <v>46.45026</v>
+        <v>46.60854</v>
       </c>
       <c r="W304" t="n">
-        <v>-60.5768</v>
+        <v>-60.92379</v>
       </c>
       <c r="X304" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -22842,12 +22842,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -22859,12 +22859,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I305" t="b">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr"/>
@@ -22901,14 +22901,14 @@
         <v>27</v>
       </c>
       <c r="V305" t="n">
-        <v>46.44952</v>
+        <v>46.60835</v>
       </c>
       <c r="W305" t="n">
-        <v>-60.57801</v>
+        <v>-60.92328</v>
       </c>
       <c r="X305" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -22918,12 +22918,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Eastville Zn Prospect</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>E07-021</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -22935,12 +22935,12 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Zn, Pb</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I306" t="b">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Zn 1.63%, Pb 1.71%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr"/>
@@ -22977,14 +22977,14 @@
         <v>27</v>
       </c>
       <c r="V306" t="n">
-        <v>46.4638</v>
+        <v>45.26433</v>
       </c>
       <c r="W306" t="n">
-        <v>-60.57034</v>
+        <v>-62.84191</v>
       </c>
       <c r="X306" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
         </is>
       </c>
     </row>
@@ -23146,12 +23146,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M309" t="inlineStr"/>
@@ -23205,14 +23205,14 @@
         <v>27</v>
       </c>
       <c r="V309" t="n">
-        <v>45.25896</v>
+        <v>46.60547</v>
       </c>
       <c r="W309" t="n">
-        <v>-62.86207</v>
+        <v>-60.92313</v>
       </c>
       <c r="X309" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23222,12 +23222,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -23239,12 +23239,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I310" t="b">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M310" t="inlineStr"/>
@@ -23281,14 +23281,14 @@
         <v>27</v>
       </c>
       <c r="V310" t="n">
-        <v>45.66247</v>
+        <v>46.60942</v>
       </c>
       <c r="W310" t="n">
-        <v>-60.50348</v>
+        <v>-60.91762</v>
       </c>
       <c r="X310" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23298,12 +23298,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -23315,12 +23315,12 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I311" t="b">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M311" t="inlineStr"/>
@@ -23354,17 +23354,17 @@
         <v>325</v>
       </c>
       <c r="U311" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V311" t="n">
-        <v>45.66068</v>
+        <v>46.2982</v>
       </c>
       <c r="W311" t="n">
-        <v>-60.49983</v>
+        <v>-60.94257</v>
       </c>
       <c r="X311" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -23374,12 +23374,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M312" t="inlineStr"/>
@@ -23430,17 +23430,17 @@
         <v>325</v>
       </c>
       <c r="U312" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V312" t="n">
-        <v>46.60854</v>
+        <v>46.59758</v>
       </c>
       <c r="W312" t="n">
-        <v>-60.92379</v>
+        <v>-60.88034</v>
       </c>
       <c r="X312" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -23450,12 +23450,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -23467,7 +23467,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M313" t="inlineStr"/>
@@ -23506,17 +23506,17 @@
         <v>325</v>
       </c>
       <c r="U313" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V313" t="n">
-        <v>46.60835</v>
+        <v>46.58857</v>
       </c>
       <c r="W313" t="n">
-        <v>-60.92328</v>
+        <v>-60.8649</v>
       </c>
       <c r="X313" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -23526,12 +23526,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -23543,7 +23543,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M314" t="inlineStr"/>
@@ -23582,17 +23582,17 @@
         <v>325</v>
       </c>
       <c r="U314" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V314" t="n">
-        <v>46.60665</v>
+        <v>46.29595</v>
       </c>
       <c r="W314" t="n">
-        <v>-60.92386</v>
+        <v>-60.9372</v>
       </c>
       <c r="X314" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -23602,12 +23602,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -23619,12 +23619,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I315" t="b">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M315" t="inlineStr"/>
@@ -23658,17 +23658,17 @@
         <v>325</v>
       </c>
       <c r="U315" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V315" t="n">
-        <v>46.60547</v>
+        <v>46.44219</v>
       </c>
       <c r="W315" t="n">
-        <v>-60.92313</v>
+        <v>-60.58706</v>
       </c>
       <c r="X315" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -23678,12 +23678,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Morleys Pegmatite</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>A09-014</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -23695,12 +23695,12 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>W, Sn, Jasper, F</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I316" t="b">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>W 0.1%, Be 0.00032%, Bi 0.0009%, Cu 0.0051%, Li 0.0132%</t>
         </is>
       </c>
       <c r="M316" t="inlineStr"/>
@@ -23734,17 +23734,17 @@
         <v>325</v>
       </c>
       <c r="U316" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V316" t="n">
-        <v>46.60942</v>
+        <v>44.73955</v>
       </c>
       <c r="W316" t="n">
-        <v>-60.91762</v>
+        <v>-64.4462</v>
       </c>
       <c r="X316" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-014</t>
         </is>
       </c>
     </row>
@@ -23754,12 +23754,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Eastville Zn Prospect</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>E07-021</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -23771,7 +23771,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Zn, Pb</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>Zn 1.63%, Pb 1.71%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M317" t="inlineStr"/>
@@ -23810,17 +23810,17 @@
         <v>325</v>
       </c>
       <c r="U317" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V317" t="n">
-        <v>45.26433</v>
+        <v>46.51529</v>
       </c>
       <c r="W317" t="n">
-        <v>-62.84191</v>
+        <v>-60.64417</v>
       </c>
       <c r="X317" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -23889,10 +23889,10 @@
         <v>26</v>
       </c>
       <c r="V318" t="n">
-        <v>46.51529</v>
+        <v>46.51553</v>
       </c>
       <c r="W318" t="n">
-        <v>-60.64417</v>
+        <v>-60.64503</v>
       </c>
       <c r="X318" t="inlineStr">
         <is>
@@ -24134,12 +24134,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -24151,12 +24151,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I322" t="b">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M322" t="inlineStr"/>
@@ -24193,14 +24193,14 @@
         <v>26</v>
       </c>
       <c r="V322" t="n">
-        <v>46.51553</v>
+        <v>44.6151</v>
       </c>
       <c r="W322" t="n">
-        <v>-60.64503</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X322" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -24970,12 +24970,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Trout Lakes Ni, Cu, Co Prospect</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-020</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -24987,12 +24987,12 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Ni, Cu, Co, Fe</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I333" t="b">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
         </is>
       </c>
       <c r="M333" t="inlineStr"/>
@@ -25029,14 +25029,14 @@
         <v>26</v>
       </c>
       <c r="V333" t="n">
-        <v>44.6151</v>
+        <v>46.58794</v>
       </c>
       <c r="W333" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.86479</v>
       </c>
       <c r="X333" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
         </is>
       </c>
     </row>
@@ -25046,12 +25046,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -25063,7 +25063,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M334" t="inlineStr"/>
@@ -25105,14 +25105,14 @@
         <v>26</v>
       </c>
       <c r="V334" t="n">
-        <v>46.29966</v>
+        <v>46.51873</v>
       </c>
       <c r="W334" t="n">
-        <v>-60.94836</v>
+        <v>-60.64496</v>
       </c>
       <c r="X334" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -25122,12 +25122,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -25139,7 +25139,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M335" t="inlineStr"/>
@@ -25181,14 +25181,14 @@
         <v>26</v>
       </c>
       <c r="V335" t="n">
-        <v>46.51873</v>
+        <v>46.29966</v>
       </c>
       <c r="W335" t="n">
-        <v>-60.64496</v>
+        <v>-60.94836</v>
       </c>
       <c r="X335" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -25198,12 +25198,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -25215,12 +25215,12 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I336" t="b">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M336" t="inlineStr"/>
@@ -25257,14 +25257,14 @@
         <v>26</v>
       </c>
       <c r="V336" t="n">
-        <v>46.29595</v>
+        <v>46.44885</v>
       </c>
       <c r="W336" t="n">
-        <v>-60.9372</v>
+        <v>-60.58676</v>
       </c>
       <c r="X336" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25274,12 +25274,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -25291,12 +25291,12 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I337" t="b">
@@ -25312,7 +25312,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M337" t="inlineStr"/>
@@ -25333,14 +25333,14 @@
         <v>26</v>
       </c>
       <c r="V337" t="n">
-        <v>46.2982</v>
+        <v>46.44956</v>
       </c>
       <c r="W337" t="n">
-        <v>-60.94257</v>
+        <v>-60.57775</v>
       </c>
       <c r="X337" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25502,12 +25502,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -25519,12 +25519,12 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I340" t="b">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M340" t="inlineStr"/>
@@ -25561,14 +25561,14 @@
         <v>26</v>
       </c>
       <c r="V340" t="n">
-        <v>46.58857</v>
+        <v>46.44952</v>
       </c>
       <c r="W340" t="n">
-        <v>-60.8649</v>
+        <v>-60.57801</v>
       </c>
       <c r="X340" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25578,12 +25578,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -25595,12 +25595,12 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I341" t="b">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M341" t="inlineStr"/>
@@ -25637,14 +25637,14 @@
         <v>26</v>
       </c>
       <c r="V341" t="n">
-        <v>46.58794</v>
+        <v>46.4638</v>
       </c>
       <c r="W341" t="n">
-        <v>-60.86479</v>
+        <v>-60.57034</v>
       </c>
       <c r="X341" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25654,12 +25654,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Morleys Pegmatite</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>A09-014</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -25671,7 +25671,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>W, Sn, Jasper, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>W 0.1%, Be 0.00032%, Bi 0.0009%, Cu 0.0051%, Li 0.0132%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M342" t="inlineStr"/>
@@ -25713,14 +25713,14 @@
         <v>26</v>
       </c>
       <c r="V342" t="n">
-        <v>44.73955</v>
+        <v>46.44638</v>
       </c>
       <c r="W342" t="n">
-        <v>-64.4462</v>
+        <v>-60.57242</v>
       </c>
       <c r="X342" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -25730,12 +25730,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Trout Lakes Ni, Cu, Co Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>K10-020</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -25747,12 +25747,12 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Ni, Cu, Co, Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I343" t="b">
@@ -25768,7 +25768,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>Ni 0.116%, Co 0.0273%, Ag 0.40 g/t, Au 0.04 g/t, Bi 0.0009%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M343" t="inlineStr"/>
@@ -25789,14 +25789,14 @@
         <v>26</v>
       </c>
       <c r="V343" t="n">
-        <v>46.59758</v>
+        <v>46.45026</v>
       </c>
       <c r="W343" t="n">
-        <v>-60.88034</v>
+        <v>-60.5768</v>
       </c>
       <c r="X343" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -1524,7 +1524,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, W 0.0341%, Ag 40.60 g/t, Zn 2%, Cu 0.294%</t>
+          <t>Au 10.00 g/t, W 0.0341%, Zn 2%, Ag 40.60 g/t, Cu 0.294%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Whycocomagh Mountain Cu, Pb, Zn, Ag, Au Occurrence</t>
+          <t>Walker Moly Prospect</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>K03-033</t>
+          <t>A16-010</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5911,12 +5911,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, Ag, Au, W</t>
+          <t>Mo, Cu, W, Sn, U, Bi</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Cu 2.34%, Ag 69.00 g/t, Au 0.61 g/t, Pb 0.367%, Te 0.0023%</t>
+          <t>Cu 0.621%, Sn 0.0819%, Ga 0.00742%, Mo 0.0759%, Ag 10.80 g/t</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -5944,23 +5944,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T72" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U72" t="n">
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>46.00679</v>
+        <v>44.7728</v>
       </c>
       <c r="W72" t="n">
-        <v>-61.0938</v>
+        <v>-64.41518000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-033</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-010</t>
         </is>
       </c>
     </row>
@@ -5970,12 +5970,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Whycocomagh Mountain Cu, Pb, Zn, Ag, Au Occurrence</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>K03-033</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -5987,12 +5987,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, Ag, Au, W</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Cu 2.34%, Ag 69.00 g/t, Au 0.61 g/t, Pb 0.367%, Te 0.0023%</t>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -6020,23 +6020,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>46.00712</v>
+        <v>46.27323</v>
       </c>
       <c r="W73" t="n">
-        <v>-61.10322</v>
+        <v>-60.69898</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-033</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Brookdale Mn Quarry</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>H16-001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -6063,12 +6063,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I74" t="b">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+          <t>Zn 250%, Ag 3000.00 g/t, Cu 0.05%, Pb 0.05%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -6105,14 +6105,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>46.27323</v>
+        <v>45.78832</v>
       </c>
       <c r="W74" t="n">
-        <v>-60.69898</v>
+        <v>-64.14641</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H16-001</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Brookdale Mn Quarry</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>H16-001</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -6158,11 +6158,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Zn 250%, Ag 3000.00 g/t, Cu 0.05%, Pb 0.05%</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
@@ -6181,14 +6177,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>45.78832</v>
+        <v>45.92081</v>
       </c>
       <c r="W75" t="n">
-        <v>-64.14641</v>
+        <v>-61.3156</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=H16-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6194,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>McCuish Mn Mine</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>F15-009</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -6215,7 +6211,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6253,14 +6249,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>45.92081</v>
+        <v>45.80981</v>
       </c>
       <c r="W76" t="n">
-        <v>-61.3156</v>
+        <v>-60.50294</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-009</t>
         </is>
       </c>
     </row>
@@ -6270,12 +6266,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Walker Moly Prospect</t>
+          <t>McCuish Mn Mine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A16-010</t>
+          <t>F15-009</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6287,12 +6283,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Mo, Cu, W, Sn, U, Bi</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -6306,11 +6302,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Cu 0.621%, Sn 0.0819%, Ga 0.00742%, Mo 0.0759%, Ag 10.80 g/t</t>
-        </is>
-      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
@@ -6329,14 +6321,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>44.7728</v>
+        <v>45.80966</v>
       </c>
       <c r="W77" t="n">
-        <v>-64.41518000000001</v>
+        <v>-60.50423</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-009</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6338,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McCuish Mn Mine</t>
+          <t>Yava Pb Deposit (Silvermine Pb Deposit)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>F15-009</t>
+          <t>F16-025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6363,7 +6355,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6401,14 +6393,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>45.80981</v>
+        <v>45.87077</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.50294</v>
+        <v>-60.38759</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-025</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6410,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McCuish Mn Mine</t>
+          <t>Yava Pb Deposit (Silvermine Pb Deposit)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>F15-009</t>
+          <t>F16-025</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6435,7 +6427,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6473,14 +6465,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>45.80966</v>
+        <v>45.86017</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.50423</v>
+        <v>-60.4163</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-025</t>
         </is>
       </c>
     </row>
@@ -6545,10 +6537,10 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>45.87077</v>
+        <v>45.86575</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.38759</v>
+        <v>-60.40045</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -6562,12 +6554,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Yava Pb Deposit (Silvermine Pb Deposit)</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>F16-025</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6579,7 +6571,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6617,14 +6609,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>45.86017</v>
+        <v>46.11181</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.4163</v>
+        <v>-61.12443</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-025</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6626,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Yava Pb Deposit (Silvermine Pb Deposit)</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>F16-025</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6651,7 +6643,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6689,14 +6681,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>45.86575</v>
+        <v>46.09672</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.40045</v>
+        <v>-61.13017</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-025</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -6761,10 +6753,10 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>46.11181</v>
+        <v>46.18739</v>
       </c>
       <c r="W83" t="n">
-        <v>-61.12443</v>
+        <v>-61.15217</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -6833,10 +6825,10 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>46.09672</v>
+        <v>46.15321</v>
       </c>
       <c r="W84" t="n">
-        <v>-61.13017</v>
+        <v>-61.1254</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -6905,10 +6897,10 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>46.18739</v>
+        <v>46.19675</v>
       </c>
       <c r="W85" t="n">
-        <v>-61.15217</v>
+        <v>-61.17421</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -6977,10 +6969,10 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>46.15321</v>
+        <v>46.21501</v>
       </c>
       <c r="W86" t="n">
-        <v>-61.1254</v>
+        <v>-61.11267</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -6994,12 +6986,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -7011,12 +7003,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -7030,7 +7022,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="n">
@@ -7046,17 +7042,17 @@
         <v>325</v>
       </c>
       <c r="U87" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V87" t="n">
-        <v>46.19675</v>
+        <v>43.70849</v>
       </c>
       <c r="W87" t="n">
-        <v>-61.17421</v>
+        <v>-66.06631</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7062,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -7083,12 +7079,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -7102,7 +7098,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
@@ -7118,17 +7118,17 @@
         <v>325</v>
       </c>
       <c r="U88" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V88" t="n">
-        <v>46.21501</v>
+        <v>46.24968</v>
       </c>
       <c r="W88" t="n">
-        <v>-61.11267</v>
+        <v>-61.04986</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Whycocomagh Mountain Cu, Pb, Zn, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>K03-033</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>Cu, Pb, Zn, Ag, Au, W</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>Cu 2.34%, Ag 69.00 g/t, Au 0.61 g/t, Pb 0.367%, Te 0.0023%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7188,23 +7188,23 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T89" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U89" t="n">
         <v>34</v>
       </c>
       <c r="V89" t="n">
-        <v>43.70849</v>
+        <v>46.00679</v>
       </c>
       <c r="W89" t="n">
-        <v>-66.06631</v>
+        <v>-61.0938</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-033</t>
         </is>
       </c>
     </row>
@@ -7273,10 +7273,10 @@
         <v>34</v>
       </c>
       <c r="V90" t="n">
-        <v>44.60164</v>
+        <v>44.60241</v>
       </c>
       <c r="W90" t="n">
-        <v>-64.05405</v>
+        <v>-64.0553</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -7290,12 +7290,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Whycocomagh Mountain Cu, Pb, Zn, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>K03-033</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Cu, Pb, Zn, Ag, Au, W</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>Cu 2.34%, Ag 69.00 g/t, Au 0.61 g/t, Pb 0.367%, Te 0.0023%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7340,23 +7340,23 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T91" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U91" t="n">
         <v>34</v>
       </c>
       <c r="V91" t="n">
-        <v>46.24968</v>
+        <v>46.00712</v>
       </c>
       <c r="W91" t="n">
-        <v>-61.04986</v>
+        <v>-61.10322</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-033</t>
         </is>
       </c>
     </row>
@@ -7425,10 +7425,10 @@
         <v>34</v>
       </c>
       <c r="V92" t="n">
-        <v>44.60241</v>
+        <v>44.60164</v>
       </c>
       <c r="W92" t="n">
-        <v>-64.0553</v>
+        <v>-64.05405</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -7670,12 +7670,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
+          <t>Whycocomagh Cu, Fe, W Occurrence</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>K10-066</t>
+          <t>F14-003</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7687,12 +7687,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Cu, W, Mo, Fe</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
+          <t>W 0.0742%, Cu 0.959%, Ag 1.40 g/t, Au 0.11 g/t, Co 0.0044%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7720,23 +7720,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T96" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U96" t="n">
         <v>33</v>
       </c>
       <c r="V96" t="n">
-        <v>46.52503</v>
+        <v>45.99025</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.71296</v>
+        <v>-61.10637</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-003</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
+          <t>Lime Hill Zn and Wollastonite Deposit</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>K10-066</t>
+          <t>F14-012</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Zn, Cu, W, Wollastonite</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
+          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7805,14 +7805,14 @@
         <v>33</v>
       </c>
       <c r="V97" t="n">
-        <v>46.52383</v>
+        <v>45.77777</v>
       </c>
       <c r="W97" t="n">
-        <v>-60.71507</v>
+        <v>-61.15731</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
         </is>
       </c>
     </row>
@@ -7822,12 +7822,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Whycocomagh Cu, Fe, W Occurrence</t>
+          <t>Lime Hill Zn and Wollastonite Deposit</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>F14-003</t>
+          <t>F14-012</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cu, W, Mo, Fe</t>
+          <t>Zn, Cu, W, Wollastonite</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>W 0.0742%, Cu 0.959%, Ag 1.40 g/t, Au 0.11 g/t, Co 0.0044%</t>
+          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -7872,23 +7872,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T98" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U98" t="n">
         <v>33</v>
       </c>
       <c r="V98" t="n">
-        <v>45.99025</v>
+        <v>45.77684</v>
       </c>
       <c r="W98" t="n">
-        <v>-61.10637</v>
+        <v>-61.1495</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lime Hill Zn and Wollastonite Deposit</t>
+          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>F14-012</t>
+          <t>K10-066</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -7915,12 +7915,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Zn, Cu, W, Wollastonite</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I99" t="b">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
+          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -7954,17 +7954,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V99" t="n">
-        <v>45.77777</v>
+        <v>46.52383</v>
       </c>
       <c r="W99" t="n">
-        <v>-61.15731</v>
+        <v>-60.71507</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
         </is>
       </c>
     </row>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lime Hill Zn and Wollastonite Deposit</t>
+          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>F14-012</t>
+          <t>K10-066</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7991,12 +7991,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Zn, Cu, W, Wollastonite</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Zn 9%, Ag 1.90 g/t, Co 0.003%, Cr 0.033%, Cu 0.0113%</t>
+          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -8030,17 +8030,17 @@
         <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V100" t="n">
-        <v>45.77684</v>
+        <v>46.52503</v>
       </c>
       <c r="W100" t="n">
-        <v>-61.1495</v>
+        <v>-60.71296</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cochrane Hill Au District</t>
+          <t>Gegogan Au District</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>E01-007</t>
+          <t>F04-001</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Au, As, Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8248,23 +8248,23 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T103" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U103" t="n">
         <v>30</v>
       </c>
       <c r="V103" t="n">
-        <v>45.24893</v>
+        <v>45.04598</v>
       </c>
       <c r="W103" t="n">
-        <v>-62.013</v>
+        <v>-61.95574</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-001</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cochrane Hill Au District</t>
+          <t>Moose River Tungsten Deposit</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>E01-007</t>
+          <t>D15-012</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Au, As, Pb, Zn</t>
+          <t>W, Pt</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8320,23 +8320,23 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U104" t="n">
         <v>30</v>
       </c>
       <c r="V104" t="n">
-        <v>45.24892</v>
+        <v>44.97314</v>
       </c>
       <c r="W104" t="n">
-        <v>-62.01122</v>
+        <v>-62.9798</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-012</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>A16-007</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Mn, Fe, Clay</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>30</v>
       </c>
       <c r="V105" t="n">
-        <v>45.0448</v>
+        <v>44.84593</v>
       </c>
       <c r="W105" t="n">
-        <v>-62.16418</v>
+        <v>-64.45107</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>North Star Au Mine</t>
+          <t>Indian Path Au-W Mine</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>F04-018</t>
+          <t>A08-018</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, W</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>30</v>
       </c>
       <c r="V106" t="n">
-        <v>45.16836</v>
+        <v>44.32606</v>
       </c>
       <c r="W106" t="n">
-        <v>-61.65632</v>
+        <v>-64.34589</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Indian Path Au-W Mine</t>
+          <t>Voglers Cove Au District</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>A08-018</t>
+          <t>A02-006</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Au, W</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>30</v>
       </c>
       <c r="V107" t="n">
-        <v>44.32356</v>
+        <v>44.20946</v>
       </c>
       <c r="W107" t="n">
-        <v>-64.35141</v>
+        <v>-64.51952</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-006</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Voglers Cove Au District</t>
+          <t>Indian Path Au-W Mine</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>A02-006</t>
+          <t>A08-018</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, W</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>30</v>
       </c>
       <c r="V109" t="n">
-        <v>44.20946</v>
+        <v>44.32356</v>
       </c>
       <c r="W109" t="n">
-        <v>-64.51952</v>
+        <v>-64.35141</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Indian Path Au-W Mine</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>A08-018</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Au, W</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8761,14 +8761,14 @@
         <v>30</v>
       </c>
       <c r="V110" t="n">
-        <v>44.32606</v>
+        <v>45.0448</v>
       </c>
       <c r="W110" t="n">
-        <v>-64.34589</v>
+        <v>-62.16418</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A08-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -8778,12 +8778,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cain and Riddle Mn Mines and Marpic Shaft</t>
+          <t>Cochrane Hill Au District</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>A16-007</t>
+          <t>E01-007</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Mn, Fe, Clay</t>
+          <t>Au, As, Pb, Zn</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8824,23 +8824,23 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T111" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U111" t="n">
         <v>30</v>
       </c>
       <c r="V111" t="n">
-        <v>44.84593</v>
+        <v>45.24892</v>
       </c>
       <c r="W111" t="n">
-        <v>-64.45107</v>
+        <v>-62.01122</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Moose River Tungsten Deposit</t>
+          <t>Cochrane Hill Au District</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>D15-012</t>
+          <t>E01-007</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>W, Pt</t>
+          <t>Au, As, Pb, Zn</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8896,23 +8896,23 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T112" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U112" t="n">
         <v>30</v>
       </c>
       <c r="V112" t="n">
-        <v>44.97314</v>
+        <v>45.24893</v>
       </c>
       <c r="W112" t="n">
-        <v>-62.9798</v>
+        <v>-62.013</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D15-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-007</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Gegogan Au District</t>
+          <t>North Star Au Mine</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>F04-001</t>
+          <t>F04-018</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8977,14 +8977,14 @@
         <v>30</v>
       </c>
       <c r="V113" t="n">
-        <v>45.04598</v>
+        <v>45.16836</v>
       </c>
       <c r="W113" t="n">
-        <v>-61.95574</v>
+        <v>-61.65632</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F04-018</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -1524,7 +1524,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, W 0.0341%, Zn 2%, Ag 40.60 g/t, Cu 0.294%</t>
+          <t>Au 10.00 g/t, W 0.0341%, Ag 40.60 g/t, Zn 2%, Cu 0.294%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.56569</v>
+        <v>46.57026</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91812</v>
+        <v>-60.91194</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1000,19 +1000,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.56838</v>
+        <v>46.56826</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.91763</v>
+        <v>-60.90602</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1076,23 +1076,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U8" t="n">
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.56837</v>
+        <v>46.04734</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.91202</v>
+        <v>-60.45799</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.04734</v>
+        <v>46.56837</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.45799</v>
+        <v>-60.91202</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1228,23 +1228,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.57009</v>
+        <v>46.37314</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.91782</v>
+        <v>-60.59907</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1380,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U12" t="n">
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.56826</v>
+        <v>46.57009</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.90602</v>
+        <v>-60.91782</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.57026</v>
+        <v>46.56838</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91194</v>
+        <v>-60.91763</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.37494</v>
+        <v>46.56569</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.59901</v>
+        <v>-60.91812</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1617,10 +1617,10 @@
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37314</v>
+        <v>46.37494</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59907</v>
+        <v>-60.59901</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Springhaven Pb, Zn, Ag Occurrence</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P13-008</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Cd, Bi</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
+          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>43.91009</v>
+        <v>46.28</v>
       </c>
       <c r="W18" t="n">
-        <v>-65.87437</v>
+        <v>-60.56967</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Springhaven Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>P13-008</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Pb, Zn, Ag, Cd, Bi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1925,14 +1925,14 @@
         <v>39</v>
       </c>
       <c r="V19" t="n">
-        <v>46.28</v>
+        <v>43.91009</v>
       </c>
       <c r="W19" t="n">
-        <v>-60.56967</v>
+        <v>-65.87437</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00887</v>
+        <v>47.00366</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59389</v>
+        <v>-60.59004</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>38</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00366</v>
+        <v>47.00887</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59004</v>
+        <v>-60.59389</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,7 +2206,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2225,14 +2229,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>45.16925</v>
+        <v>46.27323</v>
       </c>
       <c r="W23" t="n">
-        <v>-63.38899</v>
+        <v>-60.69898</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2246,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2259,12 +2263,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2278,11 +2282,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
@@ -2301,14 +2301,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>46.27323</v>
+        <v>45.28773</v>
       </c>
       <c r="W24" t="n">
-        <v>-60.69898</v>
+        <v>-63.47906</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2364,23 +2364,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.92081</v>
+        <v>45.30934</v>
       </c>
       <c r="W25" t="n">
-        <v>-61.3156</v>
+        <v>-63.47675</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2445,14 +2445,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.3433</v>
+        <v>45.33992</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.53544</v>
+        <v>-63.48499</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2517,14 +2517,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.33992</v>
+        <v>45.24369</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.48499</v>
+        <v>-63.44116</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2580,23 +2580,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.26713</v>
+        <v>45.24778</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.45492</v>
+        <v>-63.4519</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2661,14 +2661,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.28773</v>
+        <v>45.16925</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.47906</v>
+        <v>-63.38899</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2724,23 +2724,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.30934</v>
+        <v>45.20532</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.47675</v>
+        <v>-63.41063</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.24778</v>
+        <v>45.19199</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.4519</v>
+        <v>-63.39818</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2868,23 +2868,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.24369</v>
+        <v>45.92081</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.44116</v>
+        <v>-61.3156</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2940,23 +2940,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.2282</v>
+        <v>45.26713</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.41684</v>
+        <v>-63.45492</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3012,23 +3012,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>45.20532</v>
+        <v>46.09672</v>
       </c>
       <c r="W34" t="n">
-        <v>-63.41063</v>
+        <v>-61.13017</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3084,23 +3084,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>45.19199</v>
+        <v>46.18739</v>
       </c>
       <c r="W35" t="n">
-        <v>-63.39818</v>
+        <v>-61.15217</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3156,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>46.09672</v>
+        <v>45.2282</v>
       </c>
       <c r="W36" t="n">
-        <v>-61.13017</v>
+        <v>-63.41684</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -3228,19 +3228,19 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>46.18739</v>
+        <v>46.21501</v>
       </c>
       <c r="W37" t="n">
-        <v>-61.15217</v>
+        <v>-61.11267</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3309,14 +3309,14 @@
         <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>46.21501</v>
+        <v>45.3433</v>
       </c>
       <c r="W38" t="n">
-        <v>-61.11267</v>
+        <v>-63.53544</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
         <v>34</v>
       </c>
       <c r="V39" t="n">
-        <v>43.70849</v>
+        <v>46.24968</v>
       </c>
       <c r="W39" t="n">
-        <v>-66.06631</v>
+        <v>-61.04986</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3461,14 +3461,14 @@
         <v>34</v>
       </c>
       <c r="V40" t="n">
-        <v>46.24968</v>
+        <v>43.70849</v>
       </c>
       <c r="W40" t="n">
-        <v>-61.04986</v>
+        <v>-66.06631</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -3537,10 +3537,10 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>44.60241</v>
+        <v>44.60164</v>
       </c>
       <c r="W41" t="n">
-        <v>-64.0553</v>
+        <v>-64.05405</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         <v>34</v>
       </c>
       <c r="V42" t="n">
-        <v>44.60164</v>
+        <v>44.60241</v>
       </c>
       <c r="W42" t="n">
-        <v>-64.05405</v>
+        <v>-64.0553</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77979</v>
+        <v>45.77777</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.1485</v>
+        <v>-61.15731</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77981</v>
+        <v>45.77684</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.14953</v>
+        <v>-61.1495</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77777</v>
+        <v>45.77981</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.15731</v>
+        <v>-61.14953</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77684</v>
+        <v>45.77979</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1495</v>
+        <v>-61.1485</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3980,23 +3980,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>45.0448</v>
+        <v>44.64923</v>
       </c>
       <c r="W47" t="n">
-        <v>-62.16418</v>
+        <v>-64.65634</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73589</v>
+        <v>44.73395</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91248</v>
+        <v>-62.91588</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4124,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T49" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.73395</v>
+        <v>44.43925</v>
       </c>
       <c r="W49" t="n">
-        <v>-62.91588</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4196,23 +4196,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.64923</v>
+        <v>44.73589</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.65634</v>
+        <v>-62.91248</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4258,11 +4258,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4272,23 +4268,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>46.61843</v>
+        <v>44.7357</v>
       </c>
       <c r="W51" t="n">
-        <v>-60.52086</v>
+        <v>-62.91338</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4294,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4315,7 +4311,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4344,23 +4340,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>44.9011</v>
+        <v>45.2409</v>
       </c>
       <c r="W52" t="n">
-        <v>-65.00793</v>
+        <v>-63.99801</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4387,12 +4383,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4406,7 +4402,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>45.26005</v>
+        <v>46.61843</v>
       </c>
       <c r="W53" t="n">
-        <v>-63.93614</v>
+        <v>-60.52086</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4478,7 +4478,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4488,23 +4492,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.27248</v>
+        <v>45.9844</v>
       </c>
       <c r="W54" t="n">
-        <v>-63.87936</v>
+        <v>-60.94402</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4531,7 +4535,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4560,23 +4564,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T55" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>44.7357</v>
+        <v>45.0448</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.91338</v>
+        <v>-62.16418</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4590,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4603,12 +4607,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4622,8 +4626,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4641,14 +4653,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.89232</v>
+        <v>44.83208</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.04106</v>
+        <v>-65.14026</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5030,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5035,7 +5047,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5064,23 +5076,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T62" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U62" t="n">
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>46.14468</v>
+        <v>45.26005</v>
       </c>
       <c r="W62" t="n">
-        <v>-60.44769</v>
+        <v>-63.93614</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5102,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5107,7 +5119,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5145,14 +5157,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>46.13825</v>
+        <v>44.9011</v>
       </c>
       <c r="W63" t="n">
-        <v>-60.45019</v>
+        <v>-65.00793</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5174,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5179,12 +5191,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5198,11 +5210,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5212,23 +5220,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T64" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>45.98426</v>
+        <v>45.27248</v>
       </c>
       <c r="W64" t="n">
-        <v>-60.95151</v>
+        <v>-63.87936</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5246,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5255,7 +5263,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5293,14 +5301,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>45.4857</v>
+        <v>44.89232</v>
       </c>
       <c r="W65" t="n">
-        <v>-62.52535</v>
+        <v>-65.04106</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5318,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5327,12 +5335,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5346,11 +5354,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5360,23 +5364,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.9844</v>
+        <v>46.14468</v>
       </c>
       <c r="W66" t="n">
-        <v>-60.94402</v>
+        <v>-60.44769</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5390,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5403,7 +5407,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5441,14 +5445,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>45.27275</v>
+        <v>46.13825</v>
       </c>
       <c r="W67" t="n">
-        <v>-63.23508</v>
+        <v>-60.45019</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5462,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5475,12 +5479,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5494,7 +5498,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
@@ -5504,23 +5512,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T68" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.82</v>
+        <v>45.98426</v>
       </c>
       <c r="W68" t="n">
-        <v>-63.68532</v>
+        <v>-60.95151</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5538,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5547,12 +5555,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5566,7 +5574,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
@@ -5576,23 +5588,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T69" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.2409</v>
+        <v>45.91475</v>
       </c>
       <c r="W69" t="n">
-        <v>-63.99801</v>
+        <v>-61.23041</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5614,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5619,7 +5631,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5648,23 +5660,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>44.43925</v>
+        <v>45.25157</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.78243999999999</v>
+        <v>-62.11656</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5686,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5691,12 +5703,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5710,11 +5722,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5733,14 +5741,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.91475</v>
+        <v>45.73558</v>
       </c>
       <c r="W71" t="n">
-        <v>-61.23041</v>
+        <v>-62.16591</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5758,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5767,12 +5775,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5786,16 +5794,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5813,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>44.83208</v>
+        <v>45.27275</v>
       </c>
       <c r="W72" t="n">
-        <v>-65.14026</v>
+        <v>-63.23508</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5957,14 +5957,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.73558</v>
+        <v>45.4857</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.16591</v>
+        <v>-62.52535</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.25157</v>
+        <v>45.82</v>
       </c>
       <c r="W75" t="n">
-        <v>-62.11656</v>
+        <v>-63.68532</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -6181,10 +6181,10 @@
         <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.2982</v>
+        <v>46.29595</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.94257</v>
+        <v>-60.9372</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6257,14 +6257,14 @@
         <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.29595</v>
+        <v>46.44638</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.9372</v>
+        <v>-60.57242</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6333,14 +6333,14 @@
         <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.44219</v>
+        <v>46.51873</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.58706</v>
+        <v>-60.64496</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6409,14 +6409,14 @@
         <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.51529</v>
+        <v>46.45026</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.64417</v>
+        <v>-60.5768</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6485,14 +6485,14 @@
         <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.51553</v>
+        <v>46.44219</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.64503</v>
+        <v>-60.58706</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6561,14 +6561,14 @@
         <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.51814</v>
+        <v>46.44885</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.655</v>
+        <v>-60.58676</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6637,14 +6637,14 @@
         <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>44.6087</v>
+        <v>46.44952</v>
       </c>
       <c r="W83" t="n">
-        <v>-65.6011</v>
+        <v>-60.57801</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>44.6151</v>
+        <v>46.4638</v>
       </c>
       <c r="W84" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.57034</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>44.62709</v>
+        <v>46.44956</v>
       </c>
       <c r="W85" t="n">
-        <v>-65.56032</v>
+        <v>-60.57775</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6865,14 +6865,14 @@
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>45.40126</v>
+        <v>46.51478</v>
       </c>
       <c r="W86" t="n">
-        <v>-61.45511</v>
+        <v>-60.64575</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6941,14 +6941,14 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>45.39942</v>
+        <v>46.51529</v>
       </c>
       <c r="W87" t="n">
-        <v>-61.45755</v>
+        <v>-60.64417</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7017,10 +7017,10 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.51873</v>
+        <v>46.51553</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.64496</v>
+        <v>-60.64503</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.29966</v>
+        <v>46.51814</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.94836</v>
+        <v>-60.655</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.44885</v>
+        <v>45.40126</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.58676</v>
+        <v>-61.45511</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.44956</v>
+        <v>46.2982</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.57775</v>
+        <v>-60.94257</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.51478</v>
+        <v>46.29966</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.64575</v>
+        <v>-60.94836</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.44952</v>
+        <v>44.62709</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.57801</v>
+        <v>-65.56032</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>46.4638</v>
+        <v>44.6087</v>
       </c>
       <c r="W94" t="n">
-        <v>-60.57034</v>
+        <v>-65.6011</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>46.44638</v>
+        <v>44.6151</v>
       </c>
       <c r="W95" t="n">
-        <v>-60.57242</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>46.45026</v>
+        <v>45.39942</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.5768</v>
+        <v>-61.45755</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7701,10 +7701,10 @@
         <v>25</v>
       </c>
       <c r="V97" t="n">
-        <v>44.68634</v>
+        <v>44.69007</v>
       </c>
       <c r="W97" t="n">
-        <v>-63.97235</v>
+        <v>-63.97154</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
         <v>25</v>
       </c>
       <c r="V98" t="n">
-        <v>44.69021</v>
+        <v>44.68634</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97107</v>
+        <v>-63.97235</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69007</v>
+        <v>44.69021</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97154</v>
+        <v>-63.97107</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7996,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>46.8323</v>
+        <v>44.48487</v>
       </c>
       <c r="W101" t="n">
-        <v>-60.6939</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8072,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T102" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U102" t="n">
         <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>44.48487</v>
+        <v>46.8323</v>
       </c>
       <c r="W102" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.6939</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>45.76567</v>
+        <v>46.36255</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.56882</v>
+        <v>-60.59174</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.36255</v>
+        <v>46.19179</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.59174</v>
+        <v>-60.57356</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8385,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>46.19179</v>
+        <v>45.77335</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.57356</v>
+        <v>-60.56515</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8461,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>46.38378</v>
+        <v>45.78604</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.80809</v>
+        <v>-60.56073</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>45.77335</v>
+        <v>45.76567</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56515</v>
+        <v>-60.56882</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8613,14 +8613,14 @@
         <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>45.77589</v>
+        <v>46.38378</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.56156</v>
+        <v>-60.80809</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8765,10 @@
         <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>45.78604</v>
+        <v>45.77589</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56073</v>
+        <v>-60.56156</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -8917,10 +8917,10 @@
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>46.13397</v>
+        <v>46.12356</v>
       </c>
       <c r="W113" t="n">
-        <v>-60.92758</v>
+        <v>-60.91944</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -8993,14 +8993,14 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.13658</v>
+        <v>46.17933</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.91312</v>
+        <v>-60.84528</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I115" t="b">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9060,23 +9060,23 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T115" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U115" t="n">
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.5331</v>
+        <v>46.13897</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.79089</v>
+        <v>-60.9063</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9145,14 +9145,14 @@
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.26487</v>
+        <v>46.13658</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.65547</v>
+        <v>-60.91312</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9221,14 +9221,14 @@
         <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>46.13897</v>
+        <v>46.26487</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.9063</v>
+        <v>-60.65547</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9297,14 +9297,14 @@
         <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>46.17933</v>
+        <v>46.13397</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.84528</v>
+        <v>-60.92758</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,12 +9331,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I119" t="b">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9364,23 +9364,23 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T119" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U119" t="n">
         <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>46.12356</v>
+        <v>46.5331</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.91944</v>
+        <v>-60.79089</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T120" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U120" t="n">
         <v>20</v>
       </c>
       <c r="V120" t="n">
-        <v>44.08614</v>
+        <v>44.82095</v>
       </c>
       <c r="W120" t="n">
-        <v>-65.76729</v>
+        <v>-64.29518</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9820,23 +9820,23 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T125" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U125" t="n">
         <v>20</v>
       </c>
       <c r="V125" t="n">
-        <v>44.82095</v>
+        <v>44.08614</v>
       </c>
       <c r="W125" t="n">
-        <v>-64.29518</v>
+        <v>-65.76729</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9905,10 +9905,10 @@
         <v>19</v>
       </c>
       <c r="V126" t="n">
-        <v>46.42609</v>
+        <v>46.4303</v>
       </c>
       <c r="W126" t="n">
-        <v>-60.94179</v>
+        <v>-60.9406</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         <v>19</v>
       </c>
       <c r="V129" t="n">
-        <v>46.4303</v>
+        <v>46.42609</v>
       </c>
       <c r="W129" t="n">
-        <v>-60.9406</v>
+        <v>-60.94179</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.57026</v>
+        <v>46.56569</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91194</v>
+        <v>-60.91812</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1000,19 +1000,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.56826</v>
+        <v>46.56838</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.90602</v>
+        <v>-60.91763</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1076,23 +1076,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.04734</v>
+        <v>46.56837</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.45799</v>
+        <v>-60.91202</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.56837</v>
+        <v>46.04734</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.91202</v>
+        <v>-60.45799</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1228,23 +1228,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.37314</v>
+        <v>46.57009</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.59907</v>
+        <v>-60.91782</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1380,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.57009</v>
+        <v>46.56826</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.91782</v>
+        <v>-60.90602</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.56838</v>
+        <v>46.57026</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91763</v>
+        <v>-60.91194</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.56569</v>
+        <v>46.37494</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.91812</v>
+        <v>-60.59901</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1617,10 +1617,10 @@
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37494</v>
+        <v>46.37314</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59901</v>
+        <v>-60.59907</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Springhaven Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>P13-008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Pb, Zn, Ag, Cd, Bi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>46.28</v>
+        <v>43.91009</v>
       </c>
       <c r="W18" t="n">
-        <v>-60.56967</v>
+        <v>-65.87437</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Springhaven Pb, Zn, Ag Occurrence</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P13-008</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Cd, Bi</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
+          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1925,14 +1925,14 @@
         <v>39</v>
       </c>
       <c r="V19" t="n">
-        <v>43.91009</v>
+        <v>46.28</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.87437</v>
+        <v>-60.56967</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00366</v>
+        <v>47.00887</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59004</v>
+        <v>-60.59389</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>38</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00887</v>
+        <v>47.00366</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59389</v>
+        <v>-60.59004</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2292,23 +2292,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U24" t="n">
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>45.28773</v>
+        <v>45.92081</v>
       </c>
       <c r="W24" t="n">
-        <v>-63.47906</v>
+        <v>-61.3156</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2364,23 +2364,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.30934</v>
+        <v>45.3433</v>
       </c>
       <c r="W25" t="n">
-        <v>-63.47675</v>
+        <v>-63.53544</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2508,23 +2508,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U27" t="n">
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.24369</v>
+        <v>45.26713</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.44116</v>
+        <v>-63.45492</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2589,14 +2589,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.24778</v>
+        <v>45.16925</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.4519</v>
+        <v>-63.38899</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2661,14 +2661,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.16925</v>
+        <v>45.24778</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.38899</v>
+        <v>-63.4519</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2733,14 +2733,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.20532</v>
+        <v>45.24369</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.41063</v>
+        <v>-63.44116</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.19199</v>
+        <v>45.2282</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.39818</v>
+        <v>-63.41684</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2868,23 +2868,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T32" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.92081</v>
+        <v>45.20532</v>
       </c>
       <c r="W32" t="n">
-        <v>-61.3156</v>
+        <v>-63.41063</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2940,23 +2940,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.26713</v>
+        <v>45.19199</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.45492</v>
+        <v>-63.39818</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3084,23 +3084,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>46.18739</v>
+        <v>45.28773</v>
       </c>
       <c r="W35" t="n">
-        <v>-61.15217</v>
+        <v>-63.47906</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3156,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>45.2282</v>
+        <v>45.30934</v>
       </c>
       <c r="W36" t="n">
-        <v>-63.41684</v>
+        <v>-63.47675</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -3228,19 +3228,19 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U37" t="n">
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>46.21501</v>
+        <v>46.18739</v>
       </c>
       <c r="W37" t="n">
-        <v>-61.11267</v>
+        <v>-61.15217</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3309,14 +3309,14 @@
         <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>45.3433</v>
+        <v>46.21501</v>
       </c>
       <c r="W38" t="n">
-        <v>-63.53544</v>
+        <v>-61.11267</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
         <v>34</v>
       </c>
       <c r="V39" t="n">
-        <v>46.24968</v>
+        <v>43.70849</v>
       </c>
       <c r="W39" t="n">
-        <v>-61.04986</v>
+        <v>-66.06631</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>A09-032</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>Sn, Cu, Zn, As</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3461,14 +3461,14 @@
         <v>34</v>
       </c>
       <c r="V40" t="n">
-        <v>43.70849</v>
+        <v>44.60164</v>
       </c>
       <c r="W40" t="n">
-        <v>-66.06631</v>
+        <v>-64.05405</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A09-032</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sn, Cu, Zn, As</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>44.60164</v>
+        <v>46.24968</v>
       </c>
       <c r="W41" t="n">
-        <v>-64.05405</v>
+        <v>-61.04986</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77777</v>
+        <v>45.77979</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.15731</v>
+        <v>-61.1485</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77684</v>
+        <v>45.77981</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.1495</v>
+        <v>-61.14953</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77981</v>
+        <v>45.77777</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.14953</v>
+        <v>-61.15731</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77979</v>
+        <v>45.77684</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1485</v>
+        <v>-61.1495</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3980,23 +3980,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>44.64923</v>
+        <v>45.0448</v>
       </c>
       <c r="W47" t="n">
-        <v>-64.65634</v>
+        <v>-62.16418</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73395</v>
+        <v>44.73589</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91588</v>
+        <v>-62.91248</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4124,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T49" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.43925</v>
+        <v>44.73395</v>
       </c>
       <c r="W49" t="n">
-        <v>-64.78243999999999</v>
+        <v>-62.91588</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4196,23 +4196,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.73589</v>
+        <v>44.64923</v>
       </c>
       <c r="W50" t="n">
-        <v>-62.91248</v>
+        <v>-64.65634</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4258,7 +4258,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4268,23 +4272,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>44.7357</v>
+        <v>46.61843</v>
       </c>
       <c r="W51" t="n">
-        <v>-62.91338</v>
+        <v>-60.52086</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4311,7 +4315,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4340,23 +4344,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>45.2409</v>
+        <v>44.9011</v>
       </c>
       <c r="W52" t="n">
-        <v>-63.99801</v>
+        <v>-65.00793</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4383,12 +4387,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4402,11 +4406,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>46.61843</v>
+        <v>45.26005</v>
       </c>
       <c r="W53" t="n">
-        <v>-60.52086</v>
+        <v>-63.93614</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4478,11 +4478,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4492,23 +4488,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.9844</v>
+        <v>45.27248</v>
       </c>
       <c r="W54" t="n">
-        <v>-60.94402</v>
+        <v>-63.87936</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4514,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4535,7 +4531,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4564,23 +4560,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>45.0448</v>
+        <v>44.7357</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.16418</v>
+        <v>-62.91338</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4586,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4607,12 +4603,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4626,16 +4622,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4653,14 +4641,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.83208</v>
+        <v>44.89232</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.14026</v>
+        <v>-65.04106</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5018,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5047,7 +5035,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5076,23 +5064,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>45.26005</v>
+        <v>46.14468</v>
       </c>
       <c r="W62" t="n">
-        <v>-63.93614</v>
+        <v>-60.44769</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5090,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5119,7 +5107,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5157,14 +5145,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>44.9011</v>
+        <v>46.13825</v>
       </c>
       <c r="W63" t="n">
-        <v>-65.00793</v>
+        <v>-60.45019</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5162,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5191,12 +5179,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5210,7 +5198,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5220,23 +5212,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T64" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>45.27248</v>
+        <v>45.98426</v>
       </c>
       <c r="W64" t="n">
-        <v>-63.87936</v>
+        <v>-60.95151</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5238,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5263,7 +5255,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5301,14 +5293,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>44.89232</v>
+        <v>45.4857</v>
       </c>
       <c r="W65" t="n">
-        <v>-65.04106</v>
+        <v>-62.52535</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5310,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5335,12 +5327,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5354,7 +5346,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5364,23 +5360,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>46.14468</v>
+        <v>45.9844</v>
       </c>
       <c r="W66" t="n">
-        <v>-60.44769</v>
+        <v>-60.94402</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5386,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5407,7 +5403,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5445,14 +5441,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>46.13825</v>
+        <v>45.27275</v>
       </c>
       <c r="W67" t="n">
-        <v>-60.45019</v>
+        <v>-63.23508</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5458,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5479,12 +5475,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5498,11 +5494,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
@@ -5512,23 +5504,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.98426</v>
+        <v>45.82</v>
       </c>
       <c r="W68" t="n">
-        <v>-60.95151</v>
+        <v>-63.68532</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5530,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5555,12 +5547,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5574,11 +5566,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
@@ -5588,23 +5576,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T69" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.91475</v>
+        <v>45.2409</v>
       </c>
       <c r="W69" t="n">
-        <v>-61.23041</v>
+        <v>-63.99801</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -5614,12 +5602,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5631,7 +5619,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5660,23 +5648,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>45.25157</v>
+        <v>44.43925</v>
       </c>
       <c r="W70" t="n">
-        <v>-62.11656</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5674,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5703,12 +5691,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5722,7 +5710,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5741,14 +5733,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.73558</v>
+        <v>45.91475</v>
       </c>
       <c r="W71" t="n">
-        <v>-62.16591</v>
+        <v>-61.23041</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5750,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5775,12 +5767,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5794,8 +5786,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5813,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>45.27275</v>
+        <v>44.83208</v>
       </c>
       <c r="W72" t="n">
-        <v>-63.23508</v>
+        <v>-65.14026</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5957,14 +5957,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.4857</v>
+        <v>45.73558</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.52535</v>
+        <v>-62.16591</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T75" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.82</v>
+        <v>45.25157</v>
       </c>
       <c r="W75" t="n">
-        <v>-63.68532</v>
+        <v>-62.11656</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -6181,10 +6181,10 @@
         <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.29595</v>
+        <v>46.2982</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.9372</v>
+        <v>-60.94257</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6257,14 +6257,14 @@
         <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44638</v>
+        <v>46.29595</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.57242</v>
+        <v>-60.9372</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6333,14 +6333,14 @@
         <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.51873</v>
+        <v>46.44219</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.64496</v>
+        <v>-60.58706</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6409,14 +6409,14 @@
         <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.45026</v>
+        <v>46.51529</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.5768</v>
+        <v>-60.64417</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6485,14 +6485,14 @@
         <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.44219</v>
+        <v>46.51553</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.58706</v>
+        <v>-60.64503</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6561,14 +6561,14 @@
         <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.44885</v>
+        <v>46.51814</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.58676</v>
+        <v>-60.655</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6637,14 +6637,14 @@
         <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>46.44952</v>
+        <v>44.6087</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.57801</v>
+        <v>-65.6011</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>46.4638</v>
+        <v>44.6151</v>
       </c>
       <c r="W84" t="n">
-        <v>-60.57034</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>46.44956</v>
+        <v>44.62709</v>
       </c>
       <c r="W85" t="n">
-        <v>-60.57775</v>
+        <v>-65.56032</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6865,14 +6865,14 @@
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>46.51478</v>
+        <v>45.40126</v>
       </c>
       <c r="W86" t="n">
-        <v>-60.64575</v>
+        <v>-61.45511</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6941,14 +6941,14 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>46.51529</v>
+        <v>45.39942</v>
       </c>
       <c r="W87" t="n">
-        <v>-60.64417</v>
+        <v>-61.45755</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7017,10 +7017,10 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.51553</v>
+        <v>46.51873</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.64503</v>
+        <v>-60.64496</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.51814</v>
+        <v>46.29966</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.655</v>
+        <v>-60.94836</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>45.40126</v>
+        <v>46.44885</v>
       </c>
       <c r="W90" t="n">
-        <v>-61.45511</v>
+        <v>-60.58676</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.2982</v>
+        <v>46.44956</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.94257</v>
+        <v>-60.57775</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.29966</v>
+        <v>46.51478</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.94836</v>
+        <v>-60.64575</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>44.62709</v>
+        <v>46.44952</v>
       </c>
       <c r="W93" t="n">
-        <v>-65.56032</v>
+        <v>-60.57801</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>44.6087</v>
+        <v>46.4638</v>
       </c>
       <c r="W94" t="n">
-        <v>-65.6011</v>
+        <v>-60.57034</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>44.6151</v>
+        <v>46.44638</v>
       </c>
       <c r="W95" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.57242</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>45.39942</v>
+        <v>46.45026</v>
       </c>
       <c r="W96" t="n">
-        <v>-61.45755</v>
+        <v>-60.5768</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7701,10 +7701,10 @@
         <v>25</v>
       </c>
       <c r="V97" t="n">
-        <v>44.69007</v>
+        <v>44.68634</v>
       </c>
       <c r="W97" t="n">
-        <v>-63.97154</v>
+        <v>-63.97235</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
         <v>25</v>
       </c>
       <c r="V98" t="n">
-        <v>44.68634</v>
+        <v>44.69021</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97235</v>
+        <v>-63.97107</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69021</v>
+        <v>44.69007</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97107</v>
+        <v>-63.97154</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7996,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T101" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U101" t="n">
         <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>44.48487</v>
+        <v>46.8323</v>
       </c>
       <c r="W101" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.6939</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8072,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T102" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U102" t="n">
         <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>46.8323</v>
+        <v>44.48487</v>
       </c>
       <c r="W102" t="n">
-        <v>-60.6939</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>46.36255</v>
+        <v>45.76567</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.59174</v>
+        <v>-60.56882</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.19179</v>
+        <v>46.36255</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.57356</v>
+        <v>-60.59174</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8385,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>45.77335</v>
+        <v>46.19179</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.56515</v>
+        <v>-60.57356</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8461,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>45.78604</v>
+        <v>46.38378</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.56073</v>
+        <v>-60.80809</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>45.76567</v>
+        <v>45.77335</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56882</v>
+        <v>-60.56515</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8613,14 +8613,14 @@
         <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>46.38378</v>
+        <v>45.77589</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.80809</v>
+        <v>-60.56156</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8765,10 @@
         <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>45.77589</v>
+        <v>45.78604</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56156</v>
+        <v>-60.56073</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -8917,10 +8917,10 @@
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>46.12356</v>
+        <v>46.13397</v>
       </c>
       <c r="W113" t="n">
-        <v>-60.91944</v>
+        <v>-60.92758</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -8993,14 +8993,14 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.17933</v>
+        <v>46.13658</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.84528</v>
+        <v>-60.91312</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I115" t="b">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9060,23 +9060,23 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T115" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U115" t="n">
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.13897</v>
+        <v>46.5331</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.9063</v>
+        <v>-60.79089</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9145,14 +9145,14 @@
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.13658</v>
+        <v>46.26487</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.91312</v>
+        <v>-60.65547</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9221,14 +9221,14 @@
         <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>46.26487</v>
+        <v>46.13897</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.65547</v>
+        <v>-60.9063</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9297,14 +9297,14 @@
         <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>46.13397</v>
+        <v>46.17933</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.92758</v>
+        <v>-60.84528</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,12 +9331,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I119" t="b">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9364,23 +9364,23 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T119" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U119" t="n">
         <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>46.5331</v>
+        <v>46.12356</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.79089</v>
+        <v>-60.91944</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T120" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U120" t="n">
         <v>20</v>
       </c>
       <c r="V120" t="n">
-        <v>44.82095</v>
+        <v>44.08614</v>
       </c>
       <c r="W120" t="n">
-        <v>-64.29518</v>
+        <v>-65.76729</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9820,23 +9820,23 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T125" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U125" t="n">
         <v>20</v>
       </c>
       <c r="V125" t="n">
-        <v>44.08614</v>
+        <v>44.82095</v>
       </c>
       <c r="W125" t="n">
-        <v>-65.76729</v>
+        <v>-64.29518</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9905,10 +9905,10 @@
         <v>19</v>
       </c>
       <c r="V126" t="n">
-        <v>46.4303</v>
+        <v>46.42609</v>
       </c>
       <c r="W126" t="n">
-        <v>-60.9406</v>
+        <v>-60.94179</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         <v>19</v>
       </c>
       <c r="V129" t="n">
-        <v>46.42609</v>
+        <v>46.4303</v>
       </c>
       <c r="W129" t="n">
-        <v>-60.94179</v>
+        <v>-60.9406</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77777</v>
+        <v>45.77684</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.15731</v>
+        <v>-61.1495</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77684</v>
+        <v>45.77777</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1495</v>
+        <v>-61.15731</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,12 +3951,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I47" t="b">
@@ -3970,7 +3970,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
@@ -3980,23 +3984,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V47" t="n">
-        <v>45.0448</v>
+        <v>45.91475</v>
       </c>
       <c r="W47" t="n">
-        <v>-62.16418</v>
+        <v>-61.23041</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4010,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4023,7 +4027,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4052,23 +4056,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T48" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="U48" t="n">
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73589</v>
+        <v>45.0448</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91248</v>
+        <v>-62.16418</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4133,10 +4137,10 @@
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.73395</v>
+        <v>44.73589</v>
       </c>
       <c r="W49" t="n">
-        <v>-62.91588</v>
+        <v>-62.91248</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -4150,12 +4154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4167,7 +4171,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4196,23 +4200,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.64923</v>
+        <v>44.73395</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.65634</v>
+        <v>-62.91588</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4226,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4239,12 +4243,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4258,11 +4262,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4281,14 +4281,14 @@
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>46.61843</v>
+        <v>44.64923</v>
       </c>
       <c r="W51" t="n">
-        <v>-60.52086</v>
+        <v>-64.65634</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4315,12 +4315,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I52" t="b">
@@ -4334,7 +4334,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
@@ -4353,14 +4357,14 @@
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>44.9011</v>
+        <v>46.61843</v>
       </c>
       <c r="W52" t="n">
-        <v>-65.00793</v>
+        <v>-60.52086</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4374,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4387,7 +4391,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4416,23 +4420,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>45.26005</v>
+        <v>44.9011</v>
       </c>
       <c r="W53" t="n">
-        <v>-63.93614</v>
+        <v>-65.00793</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4446,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4488,23 +4492,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.27248</v>
+        <v>45.26005</v>
       </c>
       <c r="W54" t="n">
-        <v>-63.87936</v>
+        <v>-63.93614</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4531,7 +4535,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4560,23 +4564,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T55" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>44.7357</v>
+        <v>45.27248</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.91338</v>
+        <v>-63.87936</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4590,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4632,23 +4636,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U56" t="n">
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.89232</v>
+        <v>44.631</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.04106</v>
+        <v>-63.44222</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4662,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4704,23 +4708,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U57" t="n">
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>44.631</v>
+        <v>44.7357</v>
       </c>
       <c r="W57" t="n">
-        <v>-63.44222</v>
+        <v>-62.91338</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4785,10 +4789,10 @@
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>44.89125</v>
+        <v>44.89232</v>
       </c>
       <c r="W58" t="n">
-        <v>-65.04064</v>
+        <v>-65.04106</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -4857,10 +4861,10 @@
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>44.89109</v>
+        <v>44.89125</v>
       </c>
       <c r="W59" t="n">
-        <v>-65.03443</v>
+        <v>-65.04064</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -4929,10 +4933,10 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>44.88953</v>
+        <v>44.89109</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.04628</v>
+        <v>-65.03443</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -5001,10 +5005,10 @@
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>44.88409</v>
+        <v>44.88953</v>
       </c>
       <c r="W61" t="n">
-        <v>-65.05318</v>
+        <v>-65.04628</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -5018,12 +5022,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5035,7 +5039,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5073,14 +5077,14 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>46.14468</v>
+        <v>44.88409</v>
       </c>
       <c r="W62" t="n">
-        <v>-60.44769</v>
+        <v>-65.05318</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5145,10 +5149,10 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>46.13825</v>
+        <v>46.14468</v>
       </c>
       <c r="W63" t="n">
-        <v>-60.45019</v>
+        <v>-60.44769</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -5162,12 +5166,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5179,12 +5183,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5198,11 +5202,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5212,23 +5212,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T64" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>45.98426</v>
+        <v>46.13825</v>
       </c>
       <c r="W64" t="n">
-        <v>-60.95151</v>
+        <v>-60.45019</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5238,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5255,12 +5255,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I65" t="b">
@@ -5274,7 +5274,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
@@ -5284,23 +5288,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T65" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U65" t="n">
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>45.4857</v>
+        <v>45.98426</v>
       </c>
       <c r="W65" t="n">
-        <v>-62.52535</v>
+        <v>-60.95151</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5314,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5327,12 +5331,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5346,11 +5350,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5360,23 +5360,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.9844</v>
+        <v>45.4857</v>
       </c>
       <c r="W66" t="n">
-        <v>-60.94402</v>
+        <v>-62.52535</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5403,12 +5403,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I67" t="b">
@@ -5422,7 +5422,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
@@ -5432,23 +5436,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T67" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U67" t="n">
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>45.27275</v>
+        <v>45.9844</v>
       </c>
       <c r="W67" t="n">
-        <v>-63.23508</v>
+        <v>-60.94402</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5462,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5475,7 +5479,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5504,23 +5508,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T68" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.82</v>
+        <v>45.27275</v>
       </c>
       <c r="W68" t="n">
-        <v>-63.68532</v>
+        <v>-63.23508</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5534,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5547,7 +5551,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5576,23 +5580,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.2409</v>
+        <v>45.82</v>
       </c>
       <c r="W69" t="n">
-        <v>-63.99801</v>
+        <v>-63.68532</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5606,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5619,7 +5623,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5648,23 +5652,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>44.43925</v>
+        <v>45.2409</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.78243999999999</v>
+        <v>-63.99801</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5678,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5691,12 +5695,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5710,11 +5714,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5724,23 +5724,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T71" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U71" t="n">
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.91475</v>
+        <v>44.43925</v>
       </c>
       <c r="W71" t="n">
-        <v>-61.23041</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5948,23 +5948,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U74" t="n">
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.73558</v>
+        <v>45.25157</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.16591</v>
+        <v>-62.11656</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.25157</v>
+        <v>45.73558</v>
       </c>
       <c r="W75" t="n">
-        <v>-62.11656</v>
+        <v>-62.16591</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6178,17 +6178,17 @@
         <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V77" t="n">
-        <v>46.2982</v>
+        <v>46.44885</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.94257</v>
+        <v>-60.58676</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6254,17 +6254,17 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V78" t="n">
-        <v>46.29595</v>
+        <v>46.44956</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.9372</v>
+        <v>-60.57775</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V79" t="n">
         <v>46.44219</v>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6406,17 +6406,17 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V80" t="n">
-        <v>46.51529</v>
+        <v>46.44638</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.64417</v>
+        <v>-60.57242</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6482,17 +6482,17 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V81" t="n">
-        <v>46.51553</v>
+        <v>46.45026</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.64503</v>
+        <v>-60.5768</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6558,17 +6558,17 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V82" t="n">
-        <v>46.51814</v>
+        <v>46.44952</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.655</v>
+        <v>-60.57801</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6634,17 +6634,17 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V83" t="n">
-        <v>44.6087</v>
+        <v>46.4638</v>
       </c>
       <c r="W83" t="n">
-        <v>-65.6011</v>
+        <v>-60.57034</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>44.6151</v>
+        <v>46.51529</v>
       </c>
       <c r="W84" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.64417</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>44.62709</v>
+        <v>46.51814</v>
       </c>
       <c r="W85" t="n">
-        <v>-65.56032</v>
+        <v>-60.655</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6865,14 +6865,14 @@
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>45.40126</v>
+        <v>44.6087</v>
       </c>
       <c r="W86" t="n">
-        <v>-61.45511</v>
+        <v>-65.6011</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6941,14 +6941,14 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>45.39942</v>
+        <v>46.51553</v>
       </c>
       <c r="W87" t="n">
-        <v>-61.45755</v>
+        <v>-60.64503</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7017,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.51873</v>
+        <v>44.62709</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.64496</v>
+        <v>-65.56032</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.29966</v>
+        <v>45.40126</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.94836</v>
+        <v>-61.45511</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.44885</v>
+        <v>45.39942</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.58676</v>
+        <v>-61.45755</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.44956</v>
+        <v>44.6151</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.57775</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.51478</v>
+        <v>46.29966</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.64575</v>
+        <v>-60.94836</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.44952</v>
+        <v>46.51873</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.57801</v>
+        <v>-60.64496</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>46.4638</v>
+        <v>46.29595</v>
       </c>
       <c r="W94" t="n">
-        <v>-60.57034</v>
+        <v>-60.9372</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>46.44638</v>
+        <v>46.2982</v>
       </c>
       <c r="W95" t="n">
-        <v>-60.57242</v>
+        <v>-60.94257</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>46.45026</v>
+        <v>46.51478</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.5768</v>
+        <v>-60.64575</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.56569</v>
+        <v>46.56826</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91812</v>
+        <v>-60.90602</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         <v>47</v>
       </c>
       <c r="V6" t="n">
-        <v>46.04374</v>
+        <v>46.04734</v>
       </c>
       <c r="W6" t="n">
-        <v>-60.45777</v>
+        <v>-60.45799</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -950,12 +950,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1000,23 +1000,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.56838</v>
+        <v>46.04374</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.91763</v>
+        <v>-60.45777</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1085,14 +1085,14 @@
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.56837</v>
+        <v>46.37494</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.91202</v>
+        <v>-60.59901</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.04734</v>
+        <v>46.57026</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.45799</v>
+        <v>-60.91194</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1228,19 +1228,19 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.57009</v>
+        <v>46.56837</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.91782</v>
+        <v>-60.91202</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1313,14 +1313,14 @@
         <v>47</v>
       </c>
       <c r="V11" t="n">
-        <v>46.56646</v>
+        <v>46.37314</v>
       </c>
       <c r="W11" t="n">
-        <v>-60.90609</v>
+        <v>-60.59907</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1389,10 +1389,10 @@
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.56826</v>
+        <v>46.56646</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.90602</v>
+        <v>-60.90609</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.57026</v>
+        <v>46.57009</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91194</v>
+        <v>-60.91782</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.37494</v>
+        <v>46.56838</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.59901</v>
+        <v>-60.91763</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1608,23 +1608,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37314</v>
+        <v>46.56569</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59907</v>
+        <v>-60.91812</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Springhaven Pb, Zn, Ag Occurrence</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P13-008</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Cd, Bi</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
+          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>43.91009</v>
+        <v>46.28</v>
       </c>
       <c r="W18" t="n">
-        <v>-65.87437</v>
+        <v>-60.56967</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Springhaven Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>P13-008</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Pb, Zn, Ag, Cd, Bi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1925,14 +1925,14 @@
         <v>39</v>
       </c>
       <c r="V19" t="n">
-        <v>46.28</v>
+        <v>43.91009</v>
       </c>
       <c r="W19" t="n">
-        <v>-60.56967</v>
+        <v>-65.87437</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00887</v>
+        <v>47.00366</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59389</v>
+        <v>-60.59004</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>38</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00366</v>
+        <v>47.00887</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59004</v>
+        <v>-60.59389</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,11 +2206,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2229,14 +2225,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>46.27323</v>
+        <v>45.33992</v>
       </c>
       <c r="W23" t="n">
-        <v>-60.69898</v>
+        <v>-63.48499</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2314,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2373,14 +2369,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.3433</v>
+        <v>45.2282</v>
       </c>
       <c r="W25" t="n">
-        <v>-63.53544</v>
+        <v>-63.41684</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2386,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2407,7 +2403,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2445,14 +2441,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.33992</v>
+        <v>45.3433</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.48499</v>
+        <v>-63.53544</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2458,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2508,23 +2504,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.26713</v>
+        <v>45.24369</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.45492</v>
+        <v>-63.44116</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2530,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2589,14 +2585,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.16925</v>
+        <v>45.24778</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.38899</v>
+        <v>-63.4519</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2661,14 +2657,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.24778</v>
+        <v>45.16925</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.4519</v>
+        <v>-63.38899</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2674,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2733,14 +2729,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.24369</v>
+        <v>45.20532</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.44116</v>
+        <v>-63.41063</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2746,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2801,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.2282</v>
+        <v>45.19199</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.41684</v>
+        <v>-63.39818</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2818,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2839,7 +2835,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2868,23 +2864,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T32" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.20532</v>
+        <v>46.09672</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.41063</v>
+        <v>-61.13017</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2890,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2911,7 +2907,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2940,23 +2936,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.19199</v>
+        <v>46.18739</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.39818</v>
+        <v>-61.15217</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2962,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2983,7 +2979,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3012,23 +3008,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>46.09672</v>
+        <v>45.26713</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.13017</v>
+        <v>-63.45492</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3034,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3055,7 +3051,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3093,14 +3089,14 @@
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>45.28773</v>
+        <v>46.21501</v>
       </c>
       <c r="W35" t="n">
-        <v>-63.47906</v>
+        <v>-61.11267</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3106,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3156,23 +3152,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>45.30934</v>
+        <v>45.28773</v>
       </c>
       <c r="W36" t="n">
-        <v>-63.47675</v>
+        <v>-63.47906</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3178,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3199,7 +3195,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3237,14 +3233,14 @@
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>46.18739</v>
+        <v>45.30934</v>
       </c>
       <c r="W37" t="n">
-        <v>-61.15217</v>
+        <v>-63.47675</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3250,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,12 +3267,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3290,7 +3286,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
@@ -3306,17 +3306,17 @@
         <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V38" t="n">
-        <v>46.21501</v>
+        <v>46.24968</v>
       </c>
       <c r="W38" t="n">
-        <v>-61.11267</v>
+        <v>-61.04986</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>46.24968</v>
+        <v>46.27323</v>
       </c>
       <c r="W41" t="n">
-        <v>-61.04986</v>
+        <v>-60.69898</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77979</v>
+        <v>45.77777</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.1485</v>
+        <v>-61.15731</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77981</v>
+        <v>45.77684</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.14953</v>
+        <v>-61.1495</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77684</v>
+        <v>45.77981</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.1495</v>
+        <v>-61.14953</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77777</v>
+        <v>45.77979</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.15731</v>
+        <v>-61.1485</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,12 +3951,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I47" t="b">
@@ -3970,11 +3970,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
@@ -3990,17 +3986,17 @@
         <v>325</v>
       </c>
       <c r="U47" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>45.91475</v>
+        <v>44.64923</v>
       </c>
       <c r="W47" t="n">
-        <v>-61.23041</v>
+        <v>-64.65634</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4006,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4027,7 +4023,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4056,23 +4052,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U48" t="n">
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>45.0448</v>
+        <v>44.73395</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.16418</v>
+        <v>-62.91588</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4128,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T49" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.73589</v>
+        <v>44.43925</v>
       </c>
       <c r="W49" t="n">
-        <v>-62.91248</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -4209,10 +4205,10 @@
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.73395</v>
+        <v>44.73589</v>
       </c>
       <c r="W50" t="n">
-        <v>-62.91588</v>
+        <v>-62.91248</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -4226,12 +4222,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4243,7 +4239,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4272,23 +4268,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>44.64923</v>
+        <v>44.7357</v>
       </c>
       <c r="W51" t="n">
-        <v>-64.65634</v>
+        <v>-62.91338</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4294,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4315,12 +4311,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I52" t="b">
@@ -4334,11 +4330,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
@@ -4348,23 +4340,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>46.61843</v>
+        <v>45.2409</v>
       </c>
       <c r="W52" t="n">
-        <v>-60.52086</v>
+        <v>-63.99801</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4366,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4391,12 +4383,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4410,7 +4402,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4429,14 +4425,14 @@
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>44.9011</v>
+        <v>46.61843</v>
       </c>
       <c r="W53" t="n">
-        <v>-65.00793</v>
+        <v>-60.52086</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4463,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4482,7 +4478,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4492,23 +4492,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T54" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.26005</v>
+        <v>45.9844</v>
       </c>
       <c r="W54" t="n">
-        <v>-63.93614</v>
+        <v>-60.94402</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4564,23 +4564,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T55" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>45.27248</v>
+        <v>45.0448</v>
       </c>
       <c r="W55" t="n">
-        <v>-63.87936</v>
+        <v>-62.16418</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4590,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4626,8 +4626,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4636,23 +4644,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T56" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U56" t="n">
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.631</v>
+        <v>44.83208</v>
       </c>
       <c r="W56" t="n">
-        <v>-63.44222</v>
+        <v>-65.14026</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4670,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4679,7 +4687,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4708,23 +4716,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U57" t="n">
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>44.7357</v>
+        <v>45.4857</v>
       </c>
       <c r="W57" t="n">
-        <v>-62.91338</v>
+        <v>-62.52535</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4742,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4751,7 +4759,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4780,23 +4788,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U58" t="n">
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>44.89232</v>
+        <v>45.26005</v>
       </c>
       <c r="W58" t="n">
-        <v>-65.04106</v>
+        <v>-63.93614</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4814,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4823,7 +4831,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4852,23 +4860,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T59" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U59" t="n">
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>44.89125</v>
+        <v>44.631</v>
       </c>
       <c r="W59" t="n">
-        <v>-65.04064</v>
+        <v>-63.44222</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -4933,10 +4941,10 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>44.89109</v>
+        <v>44.89125</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.03443</v>
+        <v>-65.04064</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -5005,10 +5013,10 @@
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>44.88953</v>
+        <v>44.89109</v>
       </c>
       <c r="W61" t="n">
-        <v>-65.04628</v>
+        <v>-65.03443</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -5077,10 +5085,10 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>44.88409</v>
+        <v>44.88953</v>
       </c>
       <c r="W62" t="n">
-        <v>-65.05318</v>
+        <v>-65.04628</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -5094,12 +5102,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5111,7 +5119,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5149,14 +5157,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>46.14468</v>
+        <v>44.88409</v>
       </c>
       <c r="W63" t="n">
-        <v>-60.44769</v>
+        <v>-65.05318</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5174,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5183,7 +5191,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5221,14 +5229,14 @@
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>46.13825</v>
+        <v>44.9011</v>
       </c>
       <c r="W64" t="n">
-        <v>-60.45019</v>
+        <v>-65.00793</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5246,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5255,12 +5263,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I65" t="b">
@@ -5274,11 +5282,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
@@ -5288,23 +5292,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U65" t="n">
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>45.98426</v>
+        <v>45.27275</v>
       </c>
       <c r="W65" t="n">
-        <v>-60.95151</v>
+        <v>-63.23508</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5314,12 +5318,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Glenbervie Pb Mine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>E07-018</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5331,7 +5335,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5360,23 +5364,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.4857</v>
+        <v>45.28513</v>
       </c>
       <c r="W66" t="n">
-        <v>-62.52535</v>
+        <v>-62.93781</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5390,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5403,12 +5407,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I67" t="b">
@@ -5422,11 +5426,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
@@ -5436,23 +5436,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T67" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U67" t="n">
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>45.9844</v>
+        <v>44.89232</v>
       </c>
       <c r="W67" t="n">
-        <v>-60.94402</v>
+        <v>-65.04106</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5517,14 +5517,14 @@
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.27275</v>
+        <v>46.14468</v>
       </c>
       <c r="W68" t="n">
-        <v>-63.23508</v>
+        <v>-60.44769</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5580,23 +5580,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T69" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.82</v>
+        <v>46.13825</v>
       </c>
       <c r="W69" t="n">
-        <v>-63.68532</v>
+        <v>-60.45019</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5642,7 +5642,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
@@ -5652,23 +5656,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>45.2409</v>
+        <v>45.98426</v>
       </c>
       <c r="W70" t="n">
-        <v>-63.99801</v>
+        <v>-60.95151</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5678,12 +5682,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5695,7 +5699,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5724,23 +5728,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T71" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="U71" t="n">
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>44.43925</v>
+        <v>45.25157</v>
       </c>
       <c r="W71" t="n">
-        <v>-64.78243999999999</v>
+        <v>-62.11656</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5754,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5767,12 +5771,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5786,16 +5790,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5813,14 +5809,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>44.83208</v>
+        <v>45.73558</v>
       </c>
       <c r="W72" t="n">
-        <v>-65.14026</v>
+        <v>-62.16591</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5826,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Glenbervie Pb Mine</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>E07-018</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -5852,7 +5848,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -5866,7 +5862,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
@@ -5876,23 +5876,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>45.28513</v>
+        <v>45.91475</v>
       </c>
       <c r="W73" t="n">
-        <v>-62.93781</v>
+        <v>-61.23041</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5948,23 +5948,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T74" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U74" t="n">
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.25157</v>
+        <v>45.82</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.11656</v>
+        <v>-63.68532</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T75" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.73558</v>
+        <v>45.27248</v>
       </c>
       <c r="W75" t="n">
-        <v>-62.16591</v>
+        <v>-63.87936</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6178,17 +6178,17 @@
         <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.44885</v>
+        <v>46.29595</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.58676</v>
+        <v>-60.9372</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6254,13 +6254,13 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44956</v>
+        <v>46.44638</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.57775</v>
+        <v>-60.57242</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6330,17 +6330,17 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.44219</v>
+        <v>46.51873</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.58706</v>
+        <v>-60.64496</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6406,13 +6406,13 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.44638</v>
+        <v>46.45026</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.57242</v>
+        <v>-60.5768</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -6482,13 +6482,13 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.45026</v>
+        <v>46.44219</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.5768</v>
+        <v>-60.58706</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -6558,13 +6558,13 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.44952</v>
+        <v>46.44885</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.57801</v>
+        <v>-60.58676</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -6634,13 +6634,13 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>46.4638</v>
+        <v>46.44952</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.57034</v>
+        <v>-60.57801</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>46.51529</v>
+        <v>46.4638</v>
       </c>
       <c r="W84" t="n">
-        <v>-60.64417</v>
+        <v>-60.57034</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>46.51814</v>
+        <v>46.44956</v>
       </c>
       <c r="W85" t="n">
-        <v>-60.655</v>
+        <v>-60.57775</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6865,14 +6865,14 @@
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>44.6087</v>
+        <v>46.51478</v>
       </c>
       <c r="W86" t="n">
-        <v>-65.6011</v>
+        <v>-60.64575</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6941,10 +6941,10 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>46.51553</v>
+        <v>46.51529</v>
       </c>
       <c r="W87" t="n">
-        <v>-60.64503</v>
+        <v>-60.64417</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7017,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>44.62709</v>
+        <v>46.51553</v>
       </c>
       <c r="W88" t="n">
-        <v>-65.56032</v>
+        <v>-60.64503</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>45.40126</v>
+        <v>46.51814</v>
       </c>
       <c r="W89" t="n">
-        <v>-61.45511</v>
+        <v>-60.655</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7169,10 +7169,10 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>45.39942</v>
+        <v>45.40126</v>
       </c>
       <c r="W90" t="n">
-        <v>-61.45755</v>
+        <v>-61.45511</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>44.6151</v>
+        <v>46.2982</v>
       </c>
       <c r="W91" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.94257</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.51873</v>
+        <v>44.62709</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.64496</v>
+        <v>-65.56032</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>46.29595</v>
+        <v>44.6087</v>
       </c>
       <c r="W94" t="n">
-        <v>-60.9372</v>
+        <v>-65.6011</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>46.2982</v>
+        <v>44.6151</v>
       </c>
       <c r="W95" t="n">
-        <v>-60.94257</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>46.51478</v>
+        <v>45.39942</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.64575</v>
+        <v>-61.45755</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7701,10 +7701,10 @@
         <v>25</v>
       </c>
       <c r="V97" t="n">
-        <v>44.68634</v>
+        <v>44.69007</v>
       </c>
       <c r="W97" t="n">
-        <v>-63.97235</v>
+        <v>-63.97154</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
         <v>25</v>
       </c>
       <c r="V98" t="n">
-        <v>44.69021</v>
+        <v>44.68634</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97107</v>
+        <v>-63.97235</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69007</v>
+        <v>44.69021</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97154</v>
+        <v>-63.97107</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7996,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>46.8323</v>
+        <v>44.48487</v>
       </c>
       <c r="W101" t="n">
-        <v>-60.6939</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8072,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T102" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U102" t="n">
         <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>44.48487</v>
+        <v>46.8323</v>
       </c>
       <c r="W102" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.6939</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>45.76567</v>
+        <v>46.36255</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.56882</v>
+        <v>-60.59174</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.36255</v>
+        <v>46.19179</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.59174</v>
+        <v>-60.57356</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8385,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>46.19179</v>
+        <v>45.77335</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.57356</v>
+        <v>-60.56515</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8461,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>46.38378</v>
+        <v>45.78604</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.80809</v>
+        <v>-60.56073</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>45.77335</v>
+        <v>45.76567</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56515</v>
+        <v>-60.56882</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8613,14 +8613,14 @@
         <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>45.77589</v>
+        <v>46.38378</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.56156</v>
+        <v>-60.80809</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8765,10 @@
         <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>45.78604</v>
+        <v>45.77589</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56073</v>
+        <v>-60.56156</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -8917,10 +8917,10 @@
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>46.13397</v>
+        <v>46.12356</v>
       </c>
       <c r="W113" t="n">
-        <v>-60.92758</v>
+        <v>-60.91944</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -8993,14 +8993,14 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.13658</v>
+        <v>46.17933</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.91312</v>
+        <v>-60.84528</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I115" t="b">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9060,23 +9060,23 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T115" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U115" t="n">
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.5331</v>
+        <v>46.13897</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.79089</v>
+        <v>-60.9063</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9145,14 +9145,14 @@
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.26487</v>
+        <v>46.13658</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.65547</v>
+        <v>-60.91312</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9221,14 +9221,14 @@
         <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>46.13897</v>
+        <v>46.26487</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.9063</v>
+        <v>-60.65547</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9297,14 +9297,14 @@
         <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>46.17933</v>
+        <v>46.13397</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.84528</v>
+        <v>-60.92758</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,12 +9331,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I119" t="b">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9364,23 +9364,23 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T119" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U119" t="n">
         <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>46.12356</v>
+        <v>46.5331</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.91944</v>
+        <v>-60.79089</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T120" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U120" t="n">
         <v>20</v>
       </c>
       <c r="V120" t="n">
-        <v>44.08614</v>
+        <v>44.82095</v>
       </c>
       <c r="W120" t="n">
-        <v>-65.76729</v>
+        <v>-64.29518</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9820,23 +9820,23 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T125" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U125" t="n">
         <v>20</v>
       </c>
       <c r="V125" t="n">
-        <v>44.82095</v>
+        <v>44.08614</v>
       </c>
       <c r="W125" t="n">
-        <v>-64.29518</v>
+        <v>-65.76729</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9905,10 +9905,10 @@
         <v>19</v>
       </c>
       <c r="V126" t="n">
-        <v>46.42609</v>
+        <v>46.4303</v>
       </c>
       <c r="W126" t="n">
-        <v>-60.94179</v>
+        <v>-60.9406</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         <v>19</v>
       </c>
       <c r="V129" t="n">
-        <v>46.4303</v>
+        <v>46.42609</v>
       </c>
       <c r="W129" t="n">
-        <v>-60.9406</v>
+        <v>-60.94179</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.56826</v>
+        <v>46.56569</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.90602</v>
+        <v>-60.91812</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         <v>47</v>
       </c>
       <c r="V6" t="n">
-        <v>46.04734</v>
+        <v>46.04374</v>
       </c>
       <c r="W6" t="n">
-        <v>-60.45799</v>
+        <v>-60.45777</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -950,12 +950,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1000,23 +1000,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.04374</v>
+        <v>46.56838</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.45777</v>
+        <v>-60.91763</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1085,14 +1085,14 @@
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.37494</v>
+        <v>46.56837</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.59901</v>
+        <v>-60.91202</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.57026</v>
+        <v>46.04734</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.91194</v>
+        <v>-60.45799</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1228,19 +1228,19 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.56837</v>
+        <v>46.57009</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.91202</v>
+        <v>-60.91782</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1313,14 +1313,14 @@
         <v>47</v>
       </c>
       <c r="V11" t="n">
-        <v>46.37314</v>
+        <v>46.56646</v>
       </c>
       <c r="W11" t="n">
-        <v>-60.59907</v>
+        <v>-60.90609</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1389,10 +1389,10 @@
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.56646</v>
+        <v>46.56826</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.90609</v>
+        <v>-60.90602</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.57009</v>
+        <v>46.57026</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91782</v>
+        <v>-60.91194</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.56838</v>
+        <v>46.37494</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.91763</v>
+        <v>-60.59901</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1608,23 +1608,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.56569</v>
+        <v>46.37314</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.91812</v>
+        <v>-60.59907</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Springhaven Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>P13-008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Pb, Zn, Ag, Cd, Bi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>46.28</v>
+        <v>43.91009</v>
       </c>
       <c r="W18" t="n">
-        <v>-60.56967</v>
+        <v>-65.87437</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Springhaven Pb, Zn, Ag Occurrence</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P13-008</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Cd, Bi</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
+          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1925,14 +1925,14 @@
         <v>39</v>
       </c>
       <c r="V19" t="n">
-        <v>43.91009</v>
+        <v>46.28</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.87437</v>
+        <v>-60.56967</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00366</v>
+        <v>47.00887</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59004</v>
+        <v>-60.59389</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>38</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00887</v>
+        <v>47.00366</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59389</v>
+        <v>-60.59004</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,7 +2206,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2225,14 +2229,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>45.33992</v>
+        <v>46.27323</v>
       </c>
       <c r="W23" t="n">
-        <v>-63.48499</v>
+        <v>-60.69898</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -2314,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2369,14 +2373,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.2282</v>
+        <v>45.3433</v>
       </c>
       <c r="W25" t="n">
-        <v>-63.41684</v>
+        <v>-63.53544</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2390,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2403,7 +2407,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2441,14 +2445,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.3433</v>
+        <v>45.33992</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.53544</v>
+        <v>-63.48499</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2504,23 +2508,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U27" t="n">
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.24369</v>
+        <v>45.26713</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.44116</v>
+        <v>-63.45492</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2585,14 +2589,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.24778</v>
+        <v>45.16925</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.4519</v>
+        <v>-63.38899</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2602,12 +2606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2657,14 +2661,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.16925</v>
+        <v>45.24778</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.38899</v>
+        <v>-63.4519</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2729,14 +2733,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.20532</v>
+        <v>45.24369</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.41063</v>
+        <v>-63.44116</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2801,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.19199</v>
+        <v>45.2282</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.39818</v>
+        <v>-63.41684</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2835,7 +2839,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2864,23 +2868,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T32" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>46.09672</v>
+        <v>45.20532</v>
       </c>
       <c r="W32" t="n">
-        <v>-61.13017</v>
+        <v>-63.41063</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2907,7 +2911,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2936,23 +2940,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>46.18739</v>
+        <v>45.19199</v>
       </c>
       <c r="W33" t="n">
-        <v>-61.15217</v>
+        <v>-63.39818</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2966,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2979,7 +2983,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3008,23 +3012,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>45.26713</v>
+        <v>46.09672</v>
       </c>
       <c r="W34" t="n">
-        <v>-63.45492</v>
+        <v>-61.13017</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3034,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3051,7 +3055,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3089,14 +3093,14 @@
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>46.21501</v>
+        <v>45.28773</v>
       </c>
       <c r="W35" t="n">
-        <v>-61.11267</v>
+        <v>-63.47906</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -3106,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3152,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>45.28773</v>
+        <v>45.30934</v>
       </c>
       <c r="W36" t="n">
-        <v>-63.47906</v>
+        <v>-63.47675</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3182,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3195,7 +3199,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3233,14 +3237,14 @@
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>45.30934</v>
+        <v>46.18739</v>
       </c>
       <c r="W37" t="n">
-        <v>-63.47675</v>
+        <v>-61.15217</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3250,12 +3254,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3267,12 +3271,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3286,11 +3290,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
-        </is>
-      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
@@ -3306,17 +3306,17 @@
         <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>46.24968</v>
+        <v>46.21501</v>
       </c>
       <c r="W38" t="n">
-        <v>-61.04986</v>
+        <v>-61.11267</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>46.27323</v>
+        <v>46.24968</v>
       </c>
       <c r="W41" t="n">
-        <v>-60.69898</v>
+        <v>-61.04986</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77777</v>
+        <v>45.77979</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.15731</v>
+        <v>-61.1485</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77684</v>
+        <v>45.77981</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.1495</v>
+        <v>-61.14953</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77981</v>
+        <v>45.77777</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.14953</v>
+        <v>-61.15731</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77979</v>
+        <v>45.77684</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1485</v>
+        <v>-61.1495</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3980,23 +3980,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>44.64923</v>
+        <v>45.0448</v>
       </c>
       <c r="W47" t="n">
-        <v>-64.65634</v>
+        <v>-62.16418</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73395</v>
+        <v>44.73589</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91588</v>
+        <v>-62.91248</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4124,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T49" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.43925</v>
+        <v>44.73395</v>
       </c>
       <c r="W49" t="n">
-        <v>-64.78243999999999</v>
+        <v>-62.91588</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4196,23 +4196,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.73589</v>
+        <v>44.64923</v>
       </c>
       <c r="W50" t="n">
-        <v>-62.91248</v>
+        <v>-64.65634</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4258,7 +4258,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4268,23 +4272,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>44.7357</v>
+        <v>46.61843</v>
       </c>
       <c r="W51" t="n">
-        <v>-62.91338</v>
+        <v>-60.52086</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4311,7 +4315,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4340,23 +4344,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>45.2409</v>
+        <v>44.9011</v>
       </c>
       <c r="W52" t="n">
-        <v>-63.99801</v>
+        <v>-65.00793</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4383,12 +4387,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4402,11 +4406,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>46.61843</v>
+        <v>45.26005</v>
       </c>
       <c r="W53" t="n">
-        <v>-60.52086</v>
+        <v>-63.93614</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4478,11 +4478,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4492,23 +4488,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.9844</v>
+        <v>45.27248</v>
       </c>
       <c r="W54" t="n">
-        <v>-60.94402</v>
+        <v>-63.87936</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4514,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4535,7 +4531,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4564,23 +4560,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>45.0448</v>
+        <v>44.7357</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.16418</v>
+        <v>-62.91338</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4586,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4607,12 +4603,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4626,16 +4622,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4653,14 +4641,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.83208</v>
+        <v>44.89232</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.14026</v>
+        <v>-65.04106</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4658,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4687,7 +4675,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4716,23 +4704,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T57" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U57" t="n">
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>45.4857</v>
+        <v>44.631</v>
       </c>
       <c r="W57" t="n">
-        <v>-62.52535</v>
+        <v>-63.44222</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4730,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4759,7 +4747,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4788,23 +4776,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U58" t="n">
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>45.26005</v>
+        <v>44.89125</v>
       </c>
       <c r="W58" t="n">
-        <v>-63.93614</v>
+        <v>-65.04064</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4802,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4831,7 +4819,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4860,23 +4848,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T59" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U59" t="n">
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>44.631</v>
+        <v>44.89109</v>
       </c>
       <c r="W59" t="n">
-        <v>-63.44222</v>
+        <v>-65.03443</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4941,10 +4929,10 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>44.89125</v>
+        <v>44.88953</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.04064</v>
+        <v>-65.04628</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -5013,10 +5001,10 @@
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>44.89109</v>
+        <v>44.88409</v>
       </c>
       <c r="W61" t="n">
-        <v>-65.03443</v>
+        <v>-65.05318</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -5030,12 +5018,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5047,7 +5035,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5085,14 +5073,14 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>44.88953</v>
+        <v>46.14468</v>
       </c>
       <c r="W62" t="n">
-        <v>-65.04628</v>
+        <v>-60.44769</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5090,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5119,7 +5107,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5157,14 +5145,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>44.88409</v>
+        <v>46.13825</v>
       </c>
       <c r="W63" t="n">
-        <v>-65.05318</v>
+        <v>-60.45019</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5162,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5191,12 +5179,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5210,7 +5198,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5220,23 +5212,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T64" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>44.9011</v>
+        <v>45.98426</v>
       </c>
       <c r="W64" t="n">
-        <v>-65.00793</v>
+        <v>-60.95151</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5238,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5263,7 +5255,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5301,14 +5293,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>45.27275</v>
+        <v>45.4857</v>
       </c>
       <c r="W65" t="n">
-        <v>-63.23508</v>
+        <v>-62.52535</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5310,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Glenbervie Pb Mine</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>E07-018</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5335,12 +5327,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5354,7 +5346,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5364,23 +5360,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T66" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.28513</v>
+        <v>45.9844</v>
       </c>
       <c r="W66" t="n">
-        <v>-62.93781</v>
+        <v>-60.94402</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5386,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5407,7 +5403,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5445,14 +5441,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>44.89232</v>
+        <v>45.27275</v>
       </c>
       <c r="W67" t="n">
-        <v>-65.04106</v>
+        <v>-63.23508</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5458,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5479,7 +5475,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5508,23 +5504,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>46.14468</v>
+        <v>45.82</v>
       </c>
       <c r="W68" t="n">
-        <v>-60.44769</v>
+        <v>-63.68532</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5530,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5551,7 +5547,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5580,23 +5576,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T69" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>46.13825</v>
+        <v>45.2409</v>
       </c>
       <c r="W69" t="n">
-        <v>-60.45019</v>
+        <v>-63.99801</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5602,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5623,12 +5619,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5642,11 +5638,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
@@ -5656,23 +5648,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>45.98426</v>
+        <v>44.43925</v>
       </c>
       <c r="W70" t="n">
-        <v>-60.95151</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5674,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5699,12 +5691,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5718,7 +5710,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5728,23 +5724,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.25157</v>
+        <v>45.91475</v>
       </c>
       <c r="W71" t="n">
-        <v>-62.11656</v>
+        <v>-61.23041</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5750,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5771,12 +5767,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5790,8 +5786,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5809,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>45.73558</v>
+        <v>44.83208</v>
       </c>
       <c r="W72" t="n">
-        <v>-62.16591</v>
+        <v>-65.14026</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5830,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Glenbervie Pb Mine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>E07-018</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -5848,7 +5852,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -5862,11 +5866,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
@@ -5876,23 +5876,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T73" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U73" t="n">
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>45.91475</v>
+        <v>45.28513</v>
       </c>
       <c r="W73" t="n">
-        <v>-61.23041</v>
+        <v>-62.93781</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5948,23 +5948,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T74" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U74" t="n">
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.82</v>
+        <v>45.73558</v>
       </c>
       <c r="W74" t="n">
-        <v>-63.68532</v>
+        <v>-62.16591</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T75" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.27248</v>
+        <v>45.25157</v>
       </c>
       <c r="W75" t="n">
-        <v>-63.87936</v>
+        <v>-62.11656</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -6181,10 +6181,10 @@
         <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.29595</v>
+        <v>46.2982</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.9372</v>
+        <v>-60.94257</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6257,14 +6257,14 @@
         <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44638</v>
+        <v>46.29595</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.57242</v>
+        <v>-60.9372</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6333,14 +6333,14 @@
         <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.51873</v>
+        <v>46.44219</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.64496</v>
+        <v>-60.58706</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6409,14 +6409,14 @@
         <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.45026</v>
+        <v>46.51529</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.5768</v>
+        <v>-60.64417</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6485,14 +6485,14 @@
         <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.44219</v>
+        <v>46.51553</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.58706</v>
+        <v>-60.64503</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6561,14 +6561,14 @@
         <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.44885</v>
+        <v>46.51814</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.58676</v>
+        <v>-60.655</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6637,14 +6637,14 @@
         <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>46.44952</v>
+        <v>44.62709</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.57801</v>
+        <v>-65.56032</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>46.4638</v>
+        <v>44.6151</v>
       </c>
       <c r="W84" t="n">
-        <v>-60.57034</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>46.44956</v>
+        <v>44.6087</v>
       </c>
       <c r="W85" t="n">
-        <v>-60.57775</v>
+        <v>-65.6011</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6856,23 +6856,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T86" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U86" t="n">
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>46.51478</v>
+        <v>45.1087</v>
       </c>
       <c r="W86" t="n">
-        <v>-60.64575</v>
+        <v>-63.09919</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6941,14 +6941,14 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>46.51529</v>
+        <v>45.40126</v>
       </c>
       <c r="W87" t="n">
-        <v>-60.64417</v>
+        <v>-61.45511</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7017,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.51553</v>
+        <v>45.39942</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.64503</v>
+        <v>-61.45755</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7093,10 +7093,10 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.51814</v>
+        <v>46.51873</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.655</v>
+        <v>-60.64496</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>45.40126</v>
+        <v>46.29966</v>
       </c>
       <c r="W90" t="n">
-        <v>-61.45511</v>
+        <v>-60.94836</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.2982</v>
+        <v>46.44885</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.94257</v>
+        <v>-60.58676</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.29966</v>
+        <v>46.44956</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.94836</v>
+        <v>-60.57775</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>44.62709</v>
+        <v>46.51478</v>
       </c>
       <c r="W93" t="n">
-        <v>-65.56032</v>
+        <v>-60.64575</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>44.6087</v>
+        <v>46.44952</v>
       </c>
       <c r="W94" t="n">
-        <v>-65.6011</v>
+        <v>-60.57801</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>44.6151</v>
+        <v>46.4638</v>
       </c>
       <c r="W95" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.57034</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>45.39942</v>
+        <v>46.44638</v>
       </c>
       <c r="W96" t="n">
-        <v>-61.45755</v>
+        <v>-60.57242</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7698,17 +7698,17 @@
         <v>325</v>
       </c>
       <c r="U97" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V97" t="n">
-        <v>44.69007</v>
+        <v>46.45026</v>
       </c>
       <c r="W97" t="n">
-        <v>-63.97154</v>
+        <v>-60.5768</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7853,10 +7853,10 @@
         <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69021</v>
+        <v>44.69007</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97107</v>
+        <v>-63.97154</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -7870,12 +7870,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7920,23 +7920,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T100" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U100" t="n">
         <v>25</v>
       </c>
       <c r="V100" t="n">
-        <v>45.1087</v>
+        <v>44.69021</v>
       </c>
       <c r="W100" t="n">
-        <v>-63.09919</v>
+        <v>-63.97107</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7996,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T101" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U101" t="n">
         <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>44.48487</v>
+        <v>46.8323</v>
       </c>
       <c r="W101" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.6939</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8072,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T102" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U102" t="n">
         <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>46.8323</v>
+        <v>44.48487</v>
       </c>
       <c r="W102" t="n">
-        <v>-60.6939</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>46.36255</v>
+        <v>45.76567</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.59174</v>
+        <v>-60.56882</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.19179</v>
+        <v>46.36255</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.57356</v>
+        <v>-60.59174</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8385,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>45.77335</v>
+        <v>46.19179</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.56515</v>
+        <v>-60.57356</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8461,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>45.78604</v>
+        <v>46.38378</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.56073</v>
+        <v>-60.80809</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>45.76567</v>
+        <v>45.77335</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56882</v>
+        <v>-60.56515</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8613,14 +8613,14 @@
         <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>46.38378</v>
+        <v>45.77589</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.80809</v>
+        <v>-60.56156</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8765,10 @@
         <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>45.77589</v>
+        <v>45.78604</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56156</v>
+        <v>-60.56073</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -8917,10 +8917,10 @@
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>46.12356</v>
+        <v>46.13397</v>
       </c>
       <c r="W113" t="n">
-        <v>-60.91944</v>
+        <v>-60.92758</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -8993,14 +8993,14 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.17933</v>
+        <v>46.13658</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.84528</v>
+        <v>-60.91312</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I115" t="b">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9060,23 +9060,23 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T115" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U115" t="n">
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.13897</v>
+        <v>46.5331</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.9063</v>
+        <v>-60.79089</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9145,14 +9145,14 @@
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.13658</v>
+        <v>46.26487</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.91312</v>
+        <v>-60.65547</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9221,14 +9221,14 @@
         <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>46.26487</v>
+        <v>46.13897</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.65547</v>
+        <v>-60.9063</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9297,14 +9297,14 @@
         <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>46.13397</v>
+        <v>46.17933</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.92758</v>
+        <v>-60.84528</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,12 +9331,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I119" t="b">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9364,23 +9364,23 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T119" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U119" t="n">
         <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>46.5331</v>
+        <v>46.12356</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.79089</v>
+        <v>-60.91944</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T120" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U120" t="n">
         <v>20</v>
       </c>
       <c r="V120" t="n">
-        <v>44.82095</v>
+        <v>44.08614</v>
       </c>
       <c r="W120" t="n">
-        <v>-64.29518</v>
+        <v>-65.76729</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9820,23 +9820,23 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T125" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U125" t="n">
         <v>20</v>
       </c>
       <c r="V125" t="n">
-        <v>44.08614</v>
+        <v>44.82095</v>
       </c>
       <c r="W125" t="n">
-        <v>-65.76729</v>
+        <v>-64.29518</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9905,10 +9905,10 @@
         <v>19</v>
       </c>
       <c r="V126" t="n">
-        <v>46.4303</v>
+        <v>46.42609</v>
       </c>
       <c r="W126" t="n">
-        <v>-60.9406</v>
+        <v>-60.94179</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         <v>19</v>
       </c>
       <c r="V129" t="n">
-        <v>46.42609</v>
+        <v>46.4303</v>
       </c>
       <c r="W129" t="n">
-        <v>-60.94179</v>
+        <v>-60.9406</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -798,12 +798,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -848,23 +848,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.56569</v>
+        <v>46.04734</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91812</v>
+        <v>-60.45799</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1000,23 +1000,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.56838</v>
+        <v>46.37314</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.91763</v>
+        <v>-60.59907</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1085,14 +1085,14 @@
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.56837</v>
+        <v>46.37494</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.91202</v>
+        <v>-60.59901</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.04734</v>
+        <v>46.56826</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.45799</v>
+        <v>-60.90602</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1228,19 +1228,19 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.57009</v>
+        <v>46.57026</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.91782</v>
+        <v>-60.91194</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1313,10 +1313,10 @@
         <v>47</v>
       </c>
       <c r="V11" t="n">
-        <v>46.56646</v>
+        <v>46.56837</v>
       </c>
       <c r="W11" t="n">
-        <v>-60.90609</v>
+        <v>-60.91202</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1380,19 +1380,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U12" t="n">
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.56826</v>
+        <v>46.56838</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.90602</v>
+        <v>-60.91763</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.57026</v>
+        <v>46.56646</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91194</v>
+        <v>-60.90609</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.37494</v>
+        <v>46.57009</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.59901</v>
+        <v>-60.91782</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1608,23 +1608,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37314</v>
+        <v>46.56569</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59907</v>
+        <v>-60.91812</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2292,23 +2292,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>45.92081</v>
+        <v>45.33992</v>
       </c>
       <c r="W24" t="n">
-        <v>-61.3156</v>
+        <v>-63.48499</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2364,23 +2364,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.3433</v>
+        <v>45.92081</v>
       </c>
       <c r="W25" t="n">
-        <v>-63.53544</v>
+        <v>-61.3156</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2445,14 +2445,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.33992</v>
+        <v>45.2282</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.48499</v>
+        <v>-63.41684</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2508,23 +2508,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.26713</v>
+        <v>45.3433</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.45492</v>
+        <v>-63.53544</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2589,14 +2589,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.16925</v>
+        <v>45.24369</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.38899</v>
+        <v>-63.44116</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2733,14 +2733,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.24369</v>
+        <v>45.16925</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.44116</v>
+        <v>-63.38899</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.2282</v>
+        <v>45.20532</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.41684</v>
+        <v>-63.41063</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2877,14 +2877,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.20532</v>
+        <v>45.19199</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.41063</v>
+        <v>-63.39818</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2940,23 +2940,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.19199</v>
+        <v>46.09672</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.39818</v>
+        <v>-61.13017</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3012,19 +3012,19 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T34" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>46.09672</v>
+        <v>46.18739</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.13017</v>
+        <v>-61.15217</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3084,23 +3084,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>45.28773</v>
+        <v>45.26713</v>
       </c>
       <c r="W35" t="n">
-        <v>-63.47906</v>
+        <v>-63.45492</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3156,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>45.30934</v>
+        <v>46.21501</v>
       </c>
       <c r="W36" t="n">
-        <v>-63.47675</v>
+        <v>-61.11267</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3228,23 +3228,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>46.18739</v>
+        <v>45.28773</v>
       </c>
       <c r="W37" t="n">
-        <v>-61.15217</v>
+        <v>-63.47906</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3300,23 +3300,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U38" t="n">
         <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>46.21501</v>
+        <v>45.30934</v>
       </c>
       <c r="W38" t="n">
-        <v>-61.11267</v>
+        <v>-63.47675</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
         <v>34</v>
       </c>
       <c r="V39" t="n">
-        <v>43.70849</v>
+        <v>46.24968</v>
       </c>
       <c r="W39" t="n">
-        <v>-66.06631</v>
+        <v>-61.04986</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A09-032</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sn, Cu, Zn, As</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3461,14 +3461,14 @@
         <v>34</v>
       </c>
       <c r="V40" t="n">
-        <v>44.60164</v>
+        <v>43.70849</v>
       </c>
       <c r="W40" t="n">
-        <v>-64.05405</v>
+        <v>-66.06631</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>A09-032</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Sn, Cu, Zn, As</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>46.24968</v>
+        <v>44.60164</v>
       </c>
       <c r="W41" t="n">
-        <v>-61.04986</v>
+        <v>-64.05405</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77979</v>
+        <v>45.77777</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.1485</v>
+        <v>-61.15731</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77981</v>
+        <v>45.77684</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.14953</v>
+        <v>-61.1495</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77777</v>
+        <v>45.77981</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.15731</v>
+        <v>-61.14953</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77684</v>
+        <v>45.77979</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1495</v>
+        <v>-61.1485</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,12 +3951,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I47" t="b">
@@ -3970,7 +3970,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
@@ -3980,23 +3984,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V47" t="n">
-        <v>45.0448</v>
+        <v>45.91475</v>
       </c>
       <c r="W47" t="n">
-        <v>-62.16418</v>
+        <v>-61.23041</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4010,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4023,7 +4027,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4052,23 +4056,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T48" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U48" t="n">
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73589</v>
+        <v>44.64923</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91248</v>
+        <v>-64.65634</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4167,7 +4171,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4196,23 +4200,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.64923</v>
+        <v>44.73589</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.65634</v>
+        <v>-62.91248</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4226,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4239,12 +4243,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4258,11 +4262,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4272,23 +4272,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>46.61843</v>
+        <v>44.7357</v>
       </c>
       <c r="W51" t="n">
-        <v>-60.52086</v>
+        <v>-62.91338</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4344,23 +4344,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>44.9011</v>
+        <v>45.2409</v>
       </c>
       <c r="W52" t="n">
-        <v>-65.00793</v>
+        <v>-63.99801</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T53" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>45.26005</v>
+        <v>44.43925</v>
       </c>
       <c r="W53" t="n">
-        <v>-63.93614</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4478,7 +4478,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4488,23 +4492,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.27248</v>
+        <v>46.61843</v>
       </c>
       <c r="W54" t="n">
-        <v>-63.87936</v>
+        <v>-60.52086</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4531,12 +4535,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4550,7 +4554,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
@@ -4569,14 +4577,14 @@
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>44.7357</v>
+        <v>45.9844</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.91338</v>
+        <v>-60.94402</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4603,7 +4611,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4632,23 +4640,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T56" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U56" t="n">
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.89232</v>
+        <v>45.0448</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.04106</v>
+        <v>-62.16418</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4666,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4675,12 +4683,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -4694,8 +4702,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>0</v>
@@ -4704,23 +4720,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U57" t="n">
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>44.631</v>
+        <v>44.83208</v>
       </c>
       <c r="W57" t="n">
-        <v>-63.44222</v>
+        <v>-65.14026</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4746,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4747,7 +4763,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4785,14 +4801,14 @@
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>44.89125</v>
+        <v>45.4857</v>
       </c>
       <c r="W58" t="n">
-        <v>-65.04064</v>
+        <v>-62.52535</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -4802,12 +4818,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4819,7 +4835,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4848,23 +4864,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T59" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U59" t="n">
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>44.89109</v>
+        <v>45.26005</v>
       </c>
       <c r="W59" t="n">
-        <v>-65.03443</v>
+        <v>-63.93614</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4890,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4891,7 +4907,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4920,23 +4936,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T60" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U60" t="n">
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>44.88953</v>
+        <v>44.631</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.04628</v>
+        <v>-63.44222</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -5001,10 +5017,10 @@
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>44.88409</v>
+        <v>44.89125</v>
       </c>
       <c r="W61" t="n">
-        <v>-65.05318</v>
+        <v>-65.04064</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -5018,12 +5034,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5035,7 +5051,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5073,14 +5089,14 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>46.14468</v>
+        <v>44.89109</v>
       </c>
       <c r="W62" t="n">
-        <v>-60.44769</v>
+        <v>-65.03443</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5106,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5107,7 +5123,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5145,14 +5161,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>46.13825</v>
+        <v>44.88953</v>
       </c>
       <c r="W63" t="n">
-        <v>-60.45019</v>
+        <v>-65.04628</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5178,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5179,12 +5195,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5198,11 +5214,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5212,23 +5224,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T64" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>45.98426</v>
+        <v>44.88409</v>
       </c>
       <c r="W64" t="n">
-        <v>-60.95151</v>
+        <v>-65.05318</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5250,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5255,7 +5267,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5293,14 +5305,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>45.4857</v>
+        <v>44.9011</v>
       </c>
       <c r="W65" t="n">
-        <v>-62.52535</v>
+        <v>-65.00793</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5322,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5327,12 +5339,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5346,11 +5358,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5360,23 +5368,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.9844</v>
+        <v>45.27275</v>
       </c>
       <c r="W66" t="n">
-        <v>-60.94402</v>
+        <v>-63.23508</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5394,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Glenbervie Pb Mine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>E07-018</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5403,7 +5411,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5432,23 +5440,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T67" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U67" t="n">
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>45.27275</v>
+        <v>45.28513</v>
       </c>
       <c r="W67" t="n">
-        <v>-63.23508</v>
+        <v>-62.93781</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5466,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5475,7 +5483,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5504,23 +5512,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T68" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.82</v>
+        <v>44.89232</v>
       </c>
       <c r="W68" t="n">
-        <v>-63.68532</v>
+        <v>-65.04106</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5538,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5547,7 +5555,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5576,23 +5584,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T69" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.2409</v>
+        <v>46.14468</v>
       </c>
       <c r="W69" t="n">
-        <v>-63.99801</v>
+        <v>-60.44769</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5610,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5619,7 +5627,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5648,23 +5656,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>44.43925</v>
+        <v>46.13825</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.78243999999999</v>
+        <v>-60.45019</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5682,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5691,12 +5699,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5712,7 +5720,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -5724,23 +5732,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T71" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U71" t="n">
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.91475</v>
+        <v>45.98426</v>
       </c>
       <c r="W71" t="n">
-        <v>-61.23041</v>
+        <v>-60.95151</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5758,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5767,12 +5775,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5786,16 +5794,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5813,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>44.83208</v>
+        <v>45.73558</v>
       </c>
       <c r="W72" t="n">
-        <v>-65.14026</v>
+        <v>-62.16591</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Glenbervie Pb Mine</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>E07-018</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5876,23 +5876,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T73" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U73" t="n">
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>45.28513</v>
+        <v>45.25157</v>
       </c>
       <c r="W73" t="n">
-        <v>-62.93781</v>
+        <v>-62.11656</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5948,23 +5948,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U74" t="n">
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.73558</v>
+        <v>45.82</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.16591</v>
+        <v>-63.68532</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T75" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.25157</v>
+        <v>45.27248</v>
       </c>
       <c r="W75" t="n">
-        <v>-62.11656</v>
+        <v>-63.87936</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6178,17 +6178,17 @@
         <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V77" t="n">
-        <v>46.2982</v>
+        <v>46.44885</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.94257</v>
+        <v>-60.58676</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6254,17 +6254,17 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V78" t="n">
-        <v>46.29595</v>
+        <v>46.44638</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.9372</v>
+        <v>-60.57242</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6330,13 +6330,13 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V79" t="n">
-        <v>46.44219</v>
+        <v>46.44952</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.58706</v>
+        <v>-60.57801</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6406,17 +6406,17 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V80" t="n">
-        <v>46.51529</v>
+        <v>46.4638</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.64417</v>
+        <v>-60.57034</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6482,17 +6482,17 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V81" t="n">
-        <v>46.51553</v>
+        <v>46.45026</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.64503</v>
+        <v>-60.5768</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6558,17 +6558,17 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V82" t="n">
-        <v>46.51814</v>
+        <v>46.44956</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.655</v>
+        <v>-60.57775</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6634,17 +6634,17 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V83" t="n">
-        <v>44.62709</v>
+        <v>46.44219</v>
       </c>
       <c r="W83" t="n">
-        <v>-65.56032</v>
+        <v>-60.58706</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>44.6151</v>
+        <v>46.51873</v>
       </c>
       <c r="W84" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.64496</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>44.6087</v>
+        <v>46.29966</v>
       </c>
       <c r="W85" t="n">
-        <v>-65.6011</v>
+        <v>-60.94836</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6941,14 +6941,14 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>45.40126</v>
+        <v>46.51478</v>
       </c>
       <c r="W87" t="n">
-        <v>-61.45511</v>
+        <v>-60.64575</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7017,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>45.39942</v>
+        <v>46.51529</v>
       </c>
       <c r="W88" t="n">
-        <v>-61.45755</v>
+        <v>-60.64417</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7093,10 +7093,10 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.51873</v>
+        <v>46.51553</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.64496</v>
+        <v>-60.64503</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.29966</v>
+        <v>46.51814</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.94836</v>
+        <v>-60.655</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.44885</v>
+        <v>45.40126</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.58676</v>
+        <v>-61.45511</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.44956</v>
+        <v>46.2982</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.57775</v>
+        <v>-60.94257</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.51478</v>
+        <v>46.29595</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.64575</v>
+        <v>-60.9372</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>46.44952</v>
+        <v>44.62709</v>
       </c>
       <c r="W94" t="n">
-        <v>-60.57801</v>
+        <v>-65.56032</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>46.4638</v>
+        <v>44.6087</v>
       </c>
       <c r="W95" t="n">
-        <v>-60.57034</v>
+        <v>-65.6011</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>46.44638</v>
+        <v>44.6151</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.57242</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7701,14 +7701,14 @@
         <v>26</v>
       </c>
       <c r="V97" t="n">
-        <v>46.45026</v>
+        <v>45.39942</v>
       </c>
       <c r="W97" t="n">
-        <v>-60.5768</v>
+        <v>-61.45755</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7777,10 +7777,10 @@
         <v>25</v>
       </c>
       <c r="V98" t="n">
-        <v>44.68634</v>
+        <v>44.69007</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97235</v>
+        <v>-63.97154</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69007</v>
+        <v>44.69021</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97154</v>
+        <v>-63.97107</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -7929,10 +7929,10 @@
         <v>25</v>
       </c>
       <c r="V100" t="n">
-        <v>44.69021</v>
+        <v>44.68634</v>
       </c>
       <c r="W100" t="n">
-        <v>-63.97107</v>
+        <v>-63.97235</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7996,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>46.8323</v>
+        <v>44.48487</v>
       </c>
       <c r="W101" t="n">
-        <v>-60.6939</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8072,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T102" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U102" t="n">
         <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>44.48487</v>
+        <v>46.8323</v>
       </c>
       <c r="W102" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.6939</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>45.76567</v>
+        <v>46.36255</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.56882</v>
+        <v>-60.59174</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.36255</v>
+        <v>46.19179</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.59174</v>
+        <v>-60.57356</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8385,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>46.19179</v>
+        <v>45.77335</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.57356</v>
+        <v>-60.56515</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8461,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>46.38378</v>
+        <v>45.78604</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.80809</v>
+        <v>-60.56073</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>45.77335</v>
+        <v>45.76567</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56515</v>
+        <v>-60.56882</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8613,14 +8613,14 @@
         <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>45.77589</v>
+        <v>46.38378</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.56156</v>
+        <v>-60.80809</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8765,10 @@
         <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>45.78604</v>
+        <v>45.77589</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56073</v>
+        <v>-60.56156</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -8917,10 +8917,10 @@
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>46.13397</v>
+        <v>46.12356</v>
       </c>
       <c r="W113" t="n">
-        <v>-60.92758</v>
+        <v>-60.91944</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -8993,14 +8993,14 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.13658</v>
+        <v>46.17933</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.91312</v>
+        <v>-60.84528</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I115" t="b">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9060,23 +9060,23 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T115" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U115" t="n">
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.5331</v>
+        <v>46.13897</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.79089</v>
+        <v>-60.9063</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9145,14 +9145,14 @@
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.26487</v>
+        <v>46.13658</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.65547</v>
+        <v>-60.91312</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9221,14 +9221,14 @@
         <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>46.13897</v>
+        <v>46.26487</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.9063</v>
+        <v>-60.65547</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9297,14 +9297,14 @@
         <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>46.17933</v>
+        <v>46.13397</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.84528</v>
+        <v>-60.92758</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,12 +9331,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I119" t="b">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9364,23 +9364,23 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T119" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U119" t="n">
         <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>46.12356</v>
+        <v>46.5331</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.91944</v>
+        <v>-60.79089</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T120" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U120" t="n">
         <v>20</v>
       </c>
       <c r="V120" t="n">
-        <v>44.08614</v>
+        <v>44.82095</v>
       </c>
       <c r="W120" t="n">
-        <v>-65.76729</v>
+        <v>-64.29518</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9820,23 +9820,23 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T125" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U125" t="n">
         <v>20</v>
       </c>
       <c r="V125" t="n">
-        <v>44.82095</v>
+        <v>44.08614</v>
       </c>
       <c r="W125" t="n">
-        <v>-64.29518</v>
+        <v>-65.76729</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9905,10 +9905,10 @@
         <v>19</v>
       </c>
       <c r="V126" t="n">
-        <v>46.42609</v>
+        <v>46.4303</v>
       </c>
       <c r="W126" t="n">
-        <v>-60.94179</v>
+        <v>-60.9406</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -10133,10 +10133,10 @@
         <v>19</v>
       </c>
       <c r="V129" t="n">
-        <v>46.4303</v>
+        <v>46.42609</v>
       </c>
       <c r="W129" t="n">
-        <v>-60.9406</v>
+        <v>-60.94179</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,12 +3951,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I47" t="b">
@@ -3970,11 +3970,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
@@ -3990,17 +3986,17 @@
         <v>325</v>
       </c>
       <c r="U47" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>45.91475</v>
+        <v>44.64923</v>
       </c>
       <c r="W47" t="n">
-        <v>-61.23041</v>
+        <v>-64.65634</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4006,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4027,7 +4023,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4056,23 +4052,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U48" t="n">
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.64923</v>
+        <v>44.73395</v>
       </c>
       <c r="W48" t="n">
-        <v>-64.65634</v>
+        <v>-62.91588</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4128,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T49" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.73395</v>
+        <v>44.43925</v>
       </c>
       <c r="W49" t="n">
-        <v>-62.91588</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4387,12 +4383,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4406,7 +4402,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>44.43925</v>
+        <v>46.61843</v>
       </c>
       <c r="W53" t="n">
-        <v>-64.78243999999999</v>
+        <v>-60.52086</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -4492,23 +4492,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T54" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>46.61843</v>
+        <v>45.9844</v>
       </c>
       <c r="W54" t="n">
-        <v>-60.52086</v>
+        <v>-60.94402</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4554,11 +4554,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
@@ -4568,23 +4564,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T55" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>45.9844</v>
+        <v>45.0448</v>
       </c>
       <c r="W55" t="n">
-        <v>-60.94402</v>
+        <v>-62.16418</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4590,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4611,12 +4607,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4630,8 +4626,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4640,23 +4644,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T56" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U56" t="n">
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>45.0448</v>
+        <v>44.83208</v>
       </c>
       <c r="W56" t="n">
-        <v>-62.16418</v>
+        <v>-65.14026</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4670,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4683,12 +4687,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -4702,16 +4706,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>0</v>
@@ -4729,14 +4725,14 @@
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>44.83208</v>
+        <v>45.4857</v>
       </c>
       <c r="W57" t="n">
-        <v>-65.14026</v>
+        <v>-62.52535</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4742,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4763,7 +4759,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4792,23 +4788,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U58" t="n">
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>45.4857</v>
+        <v>45.26005</v>
       </c>
       <c r="W58" t="n">
-        <v>-62.52535</v>
+        <v>-63.93614</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4814,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4835,7 +4831,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4864,23 +4860,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T59" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U59" t="n">
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>45.26005</v>
+        <v>44.631</v>
       </c>
       <c r="W59" t="n">
-        <v>-63.93614</v>
+        <v>-63.44222</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4886,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4907,7 +4903,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4936,23 +4932,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T60" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U60" t="n">
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>44.631</v>
+        <v>44.89125</v>
       </c>
       <c r="W60" t="n">
-        <v>-63.44222</v>
+        <v>-65.04064</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5017,10 +5013,10 @@
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>44.89125</v>
+        <v>44.89109</v>
       </c>
       <c r="W61" t="n">
-        <v>-65.04064</v>
+        <v>-65.03443</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -5089,10 +5085,10 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>44.89109</v>
+        <v>44.88953</v>
       </c>
       <c r="W62" t="n">
-        <v>-65.03443</v>
+        <v>-65.04628</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -5161,10 +5157,10 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>44.88953</v>
+        <v>44.88409</v>
       </c>
       <c r="W63" t="n">
-        <v>-65.04628</v>
+        <v>-65.05318</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -5233,10 +5229,10 @@
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>44.88409</v>
+        <v>44.9011</v>
       </c>
       <c r="W64" t="n">
-        <v>-65.05318</v>
+        <v>-65.00793</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -5250,12 +5246,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5267,7 +5263,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5305,14 +5301,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>44.9011</v>
+        <v>45.27275</v>
       </c>
       <c r="W65" t="n">
-        <v>-65.00793</v>
+        <v>-63.23508</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5318,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Glenbervie Pb Mine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>E07-018</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5339,7 +5335,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5368,23 +5364,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.27275</v>
+        <v>45.28513</v>
       </c>
       <c r="W66" t="n">
-        <v>-63.23508</v>
+        <v>-62.93781</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5390,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Glenbervie Pb Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E07-018</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5411,7 +5407,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5440,23 +5436,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T67" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U67" t="n">
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>45.28513</v>
+        <v>44.89232</v>
       </c>
       <c r="W67" t="n">
-        <v>-62.93781</v>
+        <v>-65.04106</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5462,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5483,7 +5479,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5521,14 +5517,14 @@
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>44.89232</v>
+        <v>46.14468</v>
       </c>
       <c r="W68" t="n">
-        <v>-65.04106</v>
+        <v>-60.44769</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5593,10 +5589,10 @@
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>46.14468</v>
+        <v>46.13825</v>
       </c>
       <c r="W69" t="n">
-        <v>-60.44769</v>
+        <v>-60.45019</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -5610,12 +5606,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5627,12 +5623,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5646,7 +5642,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
@@ -5656,23 +5656,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T70" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>46.13825</v>
+        <v>45.98426</v>
       </c>
       <c r="W70" t="n">
-        <v>-60.45019</v>
+        <v>-60.95151</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5682,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5718,11 +5718,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5741,14 +5737,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.98426</v>
+        <v>45.25157</v>
       </c>
       <c r="W71" t="n">
-        <v>-60.95151</v>
+        <v>-62.11656</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5826,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -5847,12 +5843,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -5866,7 +5862,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
@@ -5876,23 +5876,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>45.25157</v>
+        <v>45.91475</v>
       </c>
       <c r="W73" t="n">
-        <v>-62.11656</v>
+        <v>-61.23041</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6178,17 +6178,17 @@
         <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.44885</v>
+        <v>46.29595</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.58676</v>
+        <v>-60.9372</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V78" t="n">
         <v>46.44638</v>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6330,17 +6330,17 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.44952</v>
+        <v>46.51873</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.57801</v>
+        <v>-60.64496</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6406,13 +6406,13 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.4638</v>
+        <v>46.45026</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.57034</v>
+        <v>-60.5768</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -6482,13 +6482,13 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.45026</v>
+        <v>46.44219</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.5768</v>
+        <v>-60.58706</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -6558,13 +6558,13 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.44956</v>
+        <v>46.44885</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.57775</v>
+        <v>-60.58676</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -6634,13 +6634,13 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>46.44219</v>
+        <v>46.44952</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.58706</v>
+        <v>-60.57801</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>46.51873</v>
+        <v>46.4638</v>
       </c>
       <c r="W84" t="n">
-        <v>-60.64496</v>
+        <v>-60.57034</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>46.29966</v>
+        <v>46.44956</v>
       </c>
       <c r="W85" t="n">
-        <v>-60.94836</v>
+        <v>-60.57775</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7397,10 +7397,10 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.29595</v>
+        <v>46.29966</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.9372</v>
+        <v>-60.94836</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X129"/>
+  <dimension ref="A1:X125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -629,10 +629,10 @@
         <v>48</v>
       </c>
       <c r="V2" t="n">
-        <v>46.24705</v>
+        <v>46.24531</v>
       </c>
       <c r="W2" t="n">
-        <v>-60.89558</v>
+        <v>-60.89421</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24531</v>
+        <v>46.24705</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89421</v>
+        <v>-60.89558</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -798,12 +798,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -848,23 +848,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.04734</v>
+        <v>46.56569</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.45799</v>
+        <v>-60.91812</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -891,7 +891,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -924,23 +924,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U6" t="n">
         <v>47</v>
       </c>
       <c r="V6" t="n">
-        <v>46.04374</v>
+        <v>46.56838</v>
       </c>
       <c r="W6" t="n">
-        <v>-60.45777</v>
+        <v>-60.91763</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1000,23 +1000,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.37314</v>
+        <v>46.57009</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.59907</v>
+        <v>-60.91782</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1076,23 +1076,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U8" t="n">
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.37494</v>
+        <v>46.04374</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.59901</v>
+        <v>-60.45777</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.56826</v>
+        <v>46.04734</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.90602</v>
+        <v>-60.45799</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1228,23 +1228,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.57026</v>
+        <v>46.37314</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.91194</v>
+        <v>-60.59907</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1313,10 +1313,10 @@
         <v>47</v>
       </c>
       <c r="V11" t="n">
-        <v>46.56837</v>
+        <v>46.56646</v>
       </c>
       <c r="W11" t="n">
-        <v>-60.91202</v>
+        <v>-60.90609</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1380,19 +1380,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.56838</v>
+        <v>46.56826</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.91763</v>
+        <v>-60.90602</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.56646</v>
+        <v>46.57026</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.90609</v>
+        <v>-60.91194</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1532,19 +1532,19 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.57009</v>
+        <v>46.56837</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.91782</v>
+        <v>-60.91202</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1608,23 +1608,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.56569</v>
+        <v>46.37494</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.91812</v>
+        <v>-60.59901</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Meat Cove Zn Deposit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>N02-002</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Zn, Mg, Cd, Ge, Ga, Pb, Cu</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Zn 50%, Au 0.04 g/t, Cu 0.0075%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1922,17 +1922,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V19" t="n">
-        <v>46.28</v>
+        <v>47.00887</v>
       </c>
       <c r="W19" t="n">
-        <v>-60.56967</v>
+        <v>-60.59389</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=N02-002</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00887</v>
+        <v>47.00366</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59389</v>
+        <v>-60.59004</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Meat Cove Zn Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>N02-002</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zn, Mg, Cd, Ge, Ga, Pb, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2130,11 +2130,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Zn 50%, Au 0.04 g/t, Cu 0.0075%</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
@@ -2150,17 +2146,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00366</v>
+        <v>45.19199</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59004</v>
+        <v>-63.39818</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=N02-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2183,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,11 +2202,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2220,23 +2212,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U23" t="n">
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>46.27323</v>
+        <v>45.92081</v>
       </c>
       <c r="W23" t="n">
-        <v>-60.69898</v>
+        <v>-61.3156</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2238,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2263,7 +2255,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2301,14 +2293,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>45.33992</v>
+        <v>45.16925</v>
       </c>
       <c r="W24" t="n">
-        <v>-63.48499</v>
+        <v>-63.38899</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2310,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2335,7 +2327,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2364,23 +2356,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.92081</v>
+        <v>45.20532</v>
       </c>
       <c r="W25" t="n">
-        <v>-61.3156</v>
+        <v>-63.41063</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2382,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2445,14 +2437,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.2282</v>
+        <v>45.3433</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.41684</v>
+        <v>-63.53544</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2454,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2517,14 +2509,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.3433</v>
+        <v>45.28773</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.53544</v>
+        <v>-63.47906</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2526,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2580,23 +2572,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.24369</v>
+        <v>45.26713</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.44116</v>
+        <v>-63.45492</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2623,7 +2615,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2661,14 +2653,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.24778</v>
+        <v>45.33992</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.4519</v>
+        <v>-63.48499</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2670,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2724,23 +2716,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.16925</v>
+        <v>45.30934</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.38899</v>
+        <v>-63.47675</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2742,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2797,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.20532</v>
+        <v>45.24369</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.41063</v>
+        <v>-63.44116</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2814,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2877,14 +2869,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.19199</v>
+        <v>45.24778</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.39818</v>
+        <v>-63.4519</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2886,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2911,7 +2903,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2940,23 +2932,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>46.09672</v>
+        <v>45.2282</v>
       </c>
       <c r="W33" t="n">
-        <v>-61.13017</v>
+        <v>-63.41684</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -3012,19 +3004,19 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>46.18739</v>
+        <v>46.09672</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.15217</v>
+        <v>-61.13017</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -3038,12 +3030,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3055,7 +3047,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3084,23 +3076,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>45.26713</v>
+        <v>46.18739</v>
       </c>
       <c r="W35" t="n">
-        <v>-63.45492</v>
+        <v>-61.15217</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3174,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3199,12 +3191,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3218,7 +3210,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Sb 0.801%, Ag 220.00 g/t, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
@@ -3234,17 +3230,17 @@
         <v>325</v>
       </c>
       <c r="U37" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V37" t="n">
-        <v>45.28773</v>
+        <v>46.28</v>
       </c>
       <c r="W37" t="n">
-        <v>-63.47906</v>
+        <v>-60.56967</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3250,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,12 +3267,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3290,7 +3286,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
@@ -3300,23 +3300,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T38" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V38" t="n">
-        <v>45.30934</v>
+        <v>46.24968</v>
       </c>
       <c r="W38" t="n">
-        <v>-63.47675</v>
+        <v>-61.04986</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
         <v>34</v>
       </c>
       <c r="V39" t="n">
-        <v>46.24968</v>
+        <v>43.70849</v>
       </c>
       <c r="W39" t="n">
-        <v>-61.04986</v>
+        <v>-66.06631</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>A09-032</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>Sn, Cu, Zn, As</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3461,14 +3461,14 @@
         <v>34</v>
       </c>
       <c r="V40" t="n">
-        <v>43.70849</v>
+        <v>44.60164</v>
       </c>
       <c r="W40" t="n">
-        <v>-66.06631</v>
+        <v>-64.05405</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A09-032</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sn, Cu, Zn, As</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>44.60164</v>
+        <v>46.27323</v>
       </c>
       <c r="W41" t="n">
-        <v>-64.05405</v>
+        <v>-60.69898</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77981</v>
+        <v>45.77979</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.14953</v>
+        <v>-61.1485</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77979</v>
+        <v>45.77981</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1485</v>
+        <v>-61.14953</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3980,23 +3980,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>44.64923</v>
+        <v>45.0448</v>
       </c>
       <c r="W47" t="n">
-        <v>-64.65634</v>
+        <v>-62.16418</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4006,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -4042,7 +4042,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
@@ -4052,23 +4056,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T48" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U48" t="n">
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73395</v>
+        <v>46.61843</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91588</v>
+        <v>-60.52086</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4082,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4095,7 +4099,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4124,23 +4128,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.43925</v>
+        <v>44.64923</v>
       </c>
       <c r="W49" t="n">
-        <v>-64.78243999999999</v>
+        <v>-64.65634</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4205,10 +4209,10 @@
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.73589</v>
+        <v>44.73395</v>
       </c>
       <c r="W50" t="n">
-        <v>-62.91248</v>
+        <v>-62.91588</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -4277,10 +4281,10 @@
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>44.7357</v>
+        <v>44.73589</v>
       </c>
       <c r="W51" t="n">
-        <v>-62.91338</v>
+        <v>-62.91248</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -4294,12 +4298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4311,7 +4315,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4340,23 +4344,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>45.2409</v>
+        <v>46.14468</v>
       </c>
       <c r="W52" t="n">
-        <v>-63.99801</v>
+        <v>-60.44769</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4383,12 +4387,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4402,11 +4406,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4425,14 +4425,14 @@
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>46.61843</v>
+        <v>46.13825</v>
       </c>
       <c r="W53" t="n">
-        <v>-60.52086</v>
+        <v>-60.45019</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -4501,10 +4501,10 @@
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.9844</v>
+        <v>45.98426</v>
       </c>
       <c r="W54" t="n">
-        <v>-60.94402</v>
+        <v>-60.95151</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -4518,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4554,7 +4554,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
@@ -4564,23 +4568,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>45.0448</v>
+        <v>45.9844</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.16418</v>
+        <v>-60.94402</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4607,12 +4611,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4626,16 +4630,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4644,23 +4640,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U56" t="n">
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.83208</v>
+        <v>44.631</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.14026</v>
+        <v>-63.44222</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4666,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4687,12 +4683,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -4706,7 +4702,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
@@ -4725,14 +4725,14 @@
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>45.4857</v>
+        <v>45.91475</v>
       </c>
       <c r="W57" t="n">
-        <v>-62.52535</v>
+        <v>-61.23041</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4788,23 +4788,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T58" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U58" t="n">
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>45.26005</v>
+        <v>44.7357</v>
       </c>
       <c r="W58" t="n">
-        <v>-63.93614</v>
+        <v>-62.91338</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4860,23 +4860,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T59" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U59" t="n">
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>44.631</v>
+        <v>44.9011</v>
       </c>
       <c r="W59" t="n">
-        <v>-63.44222</v>
+        <v>-65.00793</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4941,10 +4941,10 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>44.89125</v>
+        <v>44.89232</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.04064</v>
+        <v>-65.04106</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -4958,12 +4958,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5004,23 +5004,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T61" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U61" t="n">
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>44.89109</v>
+        <v>45.26005</v>
       </c>
       <c r="W61" t="n">
-        <v>-65.03443</v>
+        <v>-63.93614</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5076,23 +5076,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T62" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U62" t="n">
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>44.88953</v>
+        <v>45.27248</v>
       </c>
       <c r="W62" t="n">
-        <v>-65.04628</v>
+        <v>-63.87936</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5102,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5157,14 +5157,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>44.88409</v>
+        <v>45.27275</v>
       </c>
       <c r="W63" t="n">
-        <v>-65.05318</v>
+        <v>-63.23508</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5229,10 +5229,10 @@
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>44.9011</v>
+        <v>44.88409</v>
       </c>
       <c r="W64" t="n">
-        <v>-65.00793</v>
+        <v>-65.05318</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -5246,12 +5246,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5301,14 +5301,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>45.27275</v>
+        <v>44.89125</v>
       </c>
       <c r="W65" t="n">
-        <v>-63.23508</v>
+        <v>-65.04064</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Glenbervie Pb Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>E07-018</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5364,23 +5364,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.28513</v>
+        <v>44.89109</v>
       </c>
       <c r="W66" t="n">
-        <v>-62.93781</v>
+        <v>-65.03443</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5436,23 +5436,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U67" t="n">
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>44.89232</v>
+        <v>44.43925</v>
       </c>
       <c r="W67" t="n">
-        <v>-65.04106</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5498,8 +5498,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>0</v>
@@ -5517,14 +5525,14 @@
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>46.14468</v>
+        <v>44.83208</v>
       </c>
       <c r="W68" t="n">
-        <v>-60.44769</v>
+        <v>-65.14026</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5542,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5551,7 +5559,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5589,14 +5597,14 @@
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>46.13825</v>
+        <v>44.88953</v>
       </c>
       <c r="W69" t="n">
-        <v>-60.45019</v>
+        <v>-65.04628</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5614,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5623,12 +5631,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -5642,11 +5650,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
@@ -5656,23 +5660,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>45.98426</v>
+        <v>45.2409</v>
       </c>
       <c r="W70" t="n">
-        <v>-60.95151</v>
+        <v>-63.99801</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -5826,12 +5830,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -5843,12 +5847,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -5862,11 +5866,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
@@ -5885,14 +5885,14 @@
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>45.91475</v>
+        <v>45.4857</v>
       </c>
       <c r="W73" t="n">
-        <v>-61.23041</v>
+        <v>-62.52535</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Glenbervie Pb Mine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>E07-018</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5948,23 +5948,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T74" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U74" t="n">
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.82</v>
+        <v>45.28513</v>
       </c>
       <c r="W74" t="n">
-        <v>-63.68532</v>
+        <v>-62.93781</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Meaghers Grant As Prospect</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>D14-002</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,12 +5991,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -6010,7 +6010,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Au 1.18 g/t, Ag 1.00 g/t, W 0.0002%</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
@@ -6020,23 +6024,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U75" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V75" t="n">
-        <v>45.27248</v>
+        <v>44.90921</v>
       </c>
       <c r="W75" t="n">
-        <v>-63.87936</v>
+        <v>-63.22057</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-002</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6050,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Meaghers Grant As Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>D14-002</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -6063,12 +6067,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I76" t="b">
@@ -6084,7 +6088,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 1.18 g/t, Ag 1.00 g/t, W 0.0002%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -6102,17 +6106,17 @@
         <v>325</v>
       </c>
       <c r="U76" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V76" t="n">
-        <v>44.90921</v>
+        <v>46.44956</v>
       </c>
       <c r="W76" t="n">
-        <v>-63.22057</v>
+        <v>-60.57775</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6126,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6139,7 +6143,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6160,7 +6164,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6181,14 +6185,14 @@
         <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.29595</v>
+        <v>46.51873</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.9372</v>
+        <v>-60.64496</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6219,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6240,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6257,14 +6261,14 @@
         <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44638</v>
+        <v>46.51529</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.57242</v>
+        <v>-60.64417</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6333,10 +6337,10 @@
         <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.51873</v>
+        <v>46.51478</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.64496</v>
+        <v>-60.64575</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -6350,12 +6354,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6371,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6392,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6409,14 +6413,14 @@
         <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.45026</v>
+        <v>44.6087</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.5768</v>
+        <v>-65.6011</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6430,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6447,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6468,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6485,14 +6489,14 @@
         <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.44219</v>
+        <v>44.6151</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.58706</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6506,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6523,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6544,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6561,14 +6565,14 @@
         <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.44885</v>
+        <v>44.62709</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.58676</v>
+        <v>-65.56032</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6582,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,7 +6599,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6616,7 +6620,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6628,23 +6632,23 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T83" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U83" t="n">
         <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>46.44952</v>
+        <v>45.1087</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.57801</v>
+        <v>-63.09919</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6658,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6675,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6696,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6717,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>46.4638</v>
+        <v>45.39942</v>
       </c>
       <c r="W84" t="n">
-        <v>-60.57034</v>
+        <v>-61.45755</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6734,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6751,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6772,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6793,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>46.44956</v>
+        <v>45.40126</v>
       </c>
       <c r="W85" t="n">
-        <v>-60.57775</v>
+        <v>-61.45511</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6810,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6827,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6848,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6856,23 +6860,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T86" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U86" t="n">
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>45.1087</v>
+        <v>46.51814</v>
       </c>
       <c r="W86" t="n">
-        <v>-63.09919</v>
+        <v>-60.655</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6941,10 +6945,10 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>46.51478</v>
+        <v>46.51553</v>
       </c>
       <c r="W87" t="n">
-        <v>-60.64575</v>
+        <v>-60.64503</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -6958,12 +6962,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6979,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +7000,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7021,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.51529</v>
+        <v>46.44952</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.64417</v>
+        <v>-60.57801</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7038,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,12 +7055,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7072,7 +7076,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7097,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.51553</v>
+        <v>46.4638</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.64503</v>
+        <v>-60.57034</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7114,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7131,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7152,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7173,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.51814</v>
+        <v>46.44638</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.655</v>
+        <v>-60.57242</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7190,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7207,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7228,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7249,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>45.40126</v>
+        <v>46.45026</v>
       </c>
       <c r="W91" t="n">
-        <v>-61.45511</v>
+        <v>-60.5768</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7266,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,12 +7283,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -7300,7 +7304,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7325,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.2982</v>
+        <v>46.44885</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.94257</v>
+        <v>-60.58676</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7342,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7359,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7380,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7401,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.29966</v>
+        <v>46.44219</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.94836</v>
+        <v>-60.58706</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7418,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7435,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7456,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7470,17 +7474,17 @@
         <v>325</v>
       </c>
       <c r="U94" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V94" t="n">
-        <v>44.62709</v>
+        <v>44.68634</v>
       </c>
       <c r="W94" t="n">
-        <v>-65.56032</v>
+        <v>-63.97235</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7494,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7511,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7532,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7546,17 +7550,17 @@
         <v>325</v>
       </c>
       <c r="U95" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V95" t="n">
-        <v>44.6087</v>
+        <v>44.69007</v>
       </c>
       <c r="W95" t="n">
-        <v>-65.6011</v>
+        <v>-63.97154</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7570,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7587,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7608,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7622,17 +7626,17 @@
         <v>325</v>
       </c>
       <c r="U96" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V96" t="n">
-        <v>44.6151</v>
+        <v>44.69021</v>
       </c>
       <c r="W96" t="n">
-        <v>-65.58083999999999</v>
+        <v>-63.97107</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7642,12 +7646,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,12 +7663,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7680,7 +7684,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7692,23 +7696,23 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T97" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U97" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V97" t="n">
-        <v>45.39942</v>
+        <v>46.8323</v>
       </c>
       <c r="W97" t="n">
-        <v>-61.45755</v>
+        <v>-60.6939</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7722,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7735,7 +7739,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7756,7 +7760,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -7774,17 +7778,17 @@
         <v>325</v>
       </c>
       <c r="U98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V98" t="n">
-        <v>44.69007</v>
+        <v>44.48487</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97154</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7798,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -7811,7 +7815,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7832,7 +7836,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -7850,17 +7854,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69021</v>
+        <v>45.78604</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97107</v>
+        <v>-60.56073</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -7870,12 +7874,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7887,12 +7891,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -7908,7 +7912,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7926,17 +7930,17 @@
         <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V100" t="n">
-        <v>44.68634</v>
+        <v>46.38378</v>
       </c>
       <c r="W100" t="n">
-        <v>-63.97235</v>
+        <v>-60.80809</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7950,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7967,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7988,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -8002,17 +8006,17 @@
         <v>325</v>
       </c>
       <c r="U101" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V101" t="n">
-        <v>44.48487</v>
+        <v>46.36255</v>
       </c>
       <c r="W101" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.59174</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8026,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8043,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8064,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8076,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T102" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U102" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V102" t="n">
-        <v>46.8323</v>
+        <v>46.19179</v>
       </c>
       <c r="W102" t="n">
-        <v>-60.6939</v>
+        <v>-60.57356</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8102,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8119,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8140,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8161,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>46.36255</v>
+        <v>46.18983</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.59174</v>
+        <v>-60.57015</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8178,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -8191,7 +8195,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8212,7 +8216,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -8233,14 +8237,14 @@
         <v>22</v>
       </c>
       <c r="V104" t="n">
-        <v>46.18983</v>
+        <v>45.77335</v>
       </c>
       <c r="W104" t="n">
-        <v>-60.57015</v>
+        <v>-60.56515</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8254,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8271,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8292,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8313,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.19179</v>
+        <v>45.77827</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.57356</v>
+        <v>-60.55927</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8385,10 +8389,10 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>45.77335</v>
+        <v>45.76567</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.56515</v>
+        <v>-60.56882</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
@@ -8461,10 +8465,10 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>45.78604</v>
+        <v>45.77589</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.56073</v>
+        <v>-60.56156</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
@@ -8478,12 +8482,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8495,7 +8499,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8516,7 +8520,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -8534,17 +8538,17 @@
         <v>325</v>
       </c>
       <c r="U108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V108" t="n">
-        <v>45.76567</v>
+        <v>46.17933</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56882</v>
+        <v>-60.84528</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8558,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8575,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8596,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8604,23 +8608,23 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T109" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U109" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V109" t="n">
-        <v>46.38378</v>
+        <v>46.5331</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.80809</v>
+        <v>-60.79089</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8634,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>The Three Sisters (Lake O'Law)  Au, W, As Occurrence</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-050</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -8647,7 +8651,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Au, W, As, Cu</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8668,7 +8672,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Au 0.63 g/t, Ag 0.80 g/t, Cd 0.00131%, Co 0.0038%, Cr 0.0144%</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -8686,17 +8690,17 @@
         <v>325</v>
       </c>
       <c r="U110" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V110" t="n">
-        <v>45.77827</v>
+        <v>46.28434</v>
       </c>
       <c r="W110" t="n">
-        <v>-60.55927</v>
+        <v>-60.95243</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-050</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8710,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8723,7 +8727,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8744,7 +8748,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -8762,17 +8766,17 @@
         <v>325</v>
       </c>
       <c r="U111" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V111" t="n">
-        <v>45.77589</v>
+        <v>46.13897</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56156</v>
+        <v>-60.9063</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -8782,12 +8786,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The Three Sisters (Lake O'Law)  Au, W, As Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>K07-050</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8799,7 +8803,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Au, W, As, Cu</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8820,7 +8824,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Au 0.63 g/t, Ag 0.80 g/t, Cd 0.00131%, Co 0.0038%, Cr 0.0144%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -8841,14 +8845,14 @@
         <v>21</v>
       </c>
       <c r="V112" t="n">
-        <v>46.28434</v>
+        <v>46.13397</v>
       </c>
       <c r="W112" t="n">
-        <v>-60.95243</v>
+        <v>-60.92758</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-050</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -8917,10 +8921,10 @@
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>46.12356</v>
+        <v>46.13658</v>
       </c>
       <c r="W113" t="n">
-        <v>-60.91944</v>
+        <v>-60.91312</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
@@ -8934,12 +8938,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8951,7 +8955,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8972,7 +8976,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -8993,14 +8997,14 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.17933</v>
+        <v>46.26487</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.84528</v>
+        <v>-60.65547</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9069,10 +9073,10 @@
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.13897</v>
+        <v>46.12356</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.9063</v>
+        <v>-60.91944</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
@@ -9086,12 +9090,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,7 +9107,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9124,7 +9128,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9136,23 +9140,23 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T116" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U116" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V116" t="n">
-        <v>46.13658</v>
+        <v>44.08614</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.91312</v>
+        <v>-65.76729</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9166,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Shaw Lakes Cu, Pb Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>F15-016</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9183,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9204,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Cu 0.213%, Pb 0.328%, Ag 1.10 g/t, Bi 0.0006%, Cd 0.00016%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9218,17 +9222,17 @@
         <v>325</v>
       </c>
       <c r="U117" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V117" t="n">
-        <v>46.26487</v>
+        <v>45.76921</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.65547</v>
+        <v>-60.55671</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-016</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9242,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Cape Saint Mary Stibnite Occurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9259,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Sb, As, Ni, Cu, Ag</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9280,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9288,23 +9292,23 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T118" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U118" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V118" t="n">
-        <v>46.13397</v>
+        <v>44.13698</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.92758</v>
+        <v>-66.19927</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9318,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>French Village Lake Zn, As Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>F16-038</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,12 +9335,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Zn, As, Cu, Cd</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I119" t="b">
@@ -9352,7 +9356,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Zn 0.966%, Ag 1.20 g/t, Au 0.02 g/t, Bi 0.0018%, Cd 0.00352%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9364,23 +9368,23 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T119" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V119" t="n">
-        <v>46.5331</v>
+        <v>45.90959</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.79089</v>
+        <v>-60.27694</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-038</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9394,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>Cape Saint Mary Stibnite Occurrence</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,7 +9411,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>Sb, As, Ni, Cu, Ag</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9428,7 +9432,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9444,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T120" t="n">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="U120" t="n">
         <v>20</v>
       </c>
       <c r="V120" t="n">
-        <v>44.82095</v>
+        <v>44.115</v>
       </c>
       <c r="W120" t="n">
-        <v>-64.29518</v>
+        <v>-66.19658</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9470,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>French Village Lake Zn, As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>F16-038</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9483,7 +9487,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Zn, As, Cu, Cd</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9504,7 +9508,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Zn 0.966%, Ag 1.20 g/t, Au 0.02 g/t, Bi 0.0018%, Cd 0.00352%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -9516,23 +9520,23 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T121" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U121" t="n">
         <v>20</v>
       </c>
       <c r="V121" t="n">
-        <v>45.90959</v>
+        <v>44.82095</v>
       </c>
       <c r="W121" t="n">
-        <v>-60.27694</v>
+        <v>-64.29518</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-038</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9542,12 +9546,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cape Saint Mary Stibnite Occurrence</t>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B01-010</t>
+          <t>K07-019</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9559,7 +9563,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sb, As, Ni, Cu, Ag</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9580,7 +9584,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -9592,23 +9596,23 @@
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T122" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U122" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V122" t="n">
-        <v>44.13698</v>
+        <v>46.4303</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.19927</v>
+        <v>-60.9406</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9622,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shaw Lakes Cu, Pb Occurrence</t>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>F15-016</t>
+          <t>K07-019</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9656,7 +9660,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Pb 0.328%, Ag 1.10 g/t, Bi 0.0006%, Cd 0.00016%</t>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -9674,17 +9678,17 @@
         <v>325</v>
       </c>
       <c r="U123" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V123" t="n">
-        <v>45.76921</v>
+        <v>46.42609</v>
       </c>
       <c r="W123" t="n">
-        <v>-60.55671</v>
+        <v>-60.94179</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>
       </c>
     </row>
@@ -9694,12 +9698,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cape Saint Mary Stibnite Occurrence</t>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B01-010</t>
+          <t>K07-019</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9711,7 +9715,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sb, As, Ni, Cu, Ag</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9732,7 +9736,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -9744,23 +9748,23 @@
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T124" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U124" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V124" t="n">
-        <v>44.115</v>
+        <v>46.42607</v>
       </c>
       <c r="W124" t="n">
-        <v>-66.19658</v>
+        <v>-60.94075</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9774,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>K07-019</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9787,7 +9791,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9808,7 +9812,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9820,325 +9824,21 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T125" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U125" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V125" t="n">
-        <v>44.08614</v>
+        <v>46.42622</v>
       </c>
       <c r="W125" t="n">
-        <v>-65.76729</v>
+        <v>-60.93906</v>
       </c>
       <c r="X125" t="inlineStr">
-        <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>K07-019</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I126" t="b">
-        <v>1</v>
-      </c>
-      <c r="J126" t="b">
-        <v>0</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="n">
-        <v>13</v>
-      </c>
-      <c r="T126" t="n">
-        <v>325</v>
-      </c>
-      <c r="U126" t="n">
-        <v>19</v>
-      </c>
-      <c r="V126" t="n">
-        <v>46.4303</v>
-      </c>
-      <c r="W126" t="n">
-        <v>-60.9406</v>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>K07-019</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I127" t="b">
-        <v>1</v>
-      </c>
-      <c r="J127" t="b">
-        <v>0</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="n">
-        <v>13</v>
-      </c>
-      <c r="T127" t="n">
-        <v>325</v>
-      </c>
-      <c r="U127" t="n">
-        <v>19</v>
-      </c>
-      <c r="V127" t="n">
-        <v>46.42622</v>
-      </c>
-      <c r="W127" t="n">
-        <v>-60.93906</v>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>K07-019</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I128" t="b">
-        <v>1</v>
-      </c>
-      <c r="J128" t="b">
-        <v>0</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="n">
-        <v>13</v>
-      </c>
-      <c r="T128" t="n">
-        <v>325</v>
-      </c>
-      <c r="U128" t="n">
-        <v>19</v>
-      </c>
-      <c r="V128" t="n">
-        <v>46.42607</v>
-      </c>
-      <c r="W128" t="n">
-        <v>-60.94075</v>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>K07-019</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I129" t="b">
-        <v>1</v>
-      </c>
-      <c r="J129" t="b">
-        <v>0</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="n">
-        <v>13</v>
-      </c>
-      <c r="T129" t="n">
-        <v>325</v>
-      </c>
-      <c r="U129" t="n">
-        <v>19</v>
-      </c>
-      <c r="V129" t="n">
-        <v>46.42609</v>
-      </c>
-      <c r="W129" t="n">
-        <v>-60.94179</v>
-      </c>
-      <c r="X129" t="inlineStr">
         <is>
           <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X125"/>
+  <dimension ref="A1:X129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -629,10 +629,10 @@
         <v>48</v>
       </c>
       <c r="V2" t="n">
-        <v>46.24531</v>
+        <v>46.24705</v>
       </c>
       <c r="W2" t="n">
-        <v>-60.89421</v>
+        <v>-60.89558</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24705</v>
+        <v>46.24541</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89558</v>
+        <v>-60.89447</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -874,12 +874,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -891,7 +891,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -924,23 +924,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U6" t="n">
         <v>47</v>
       </c>
       <c r="V6" t="n">
-        <v>46.56838</v>
+        <v>46.04374</v>
       </c>
       <c r="W6" t="n">
-        <v>-60.91763</v>
+        <v>-60.45777</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1000,19 +1000,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.57009</v>
+        <v>46.56838</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.91782</v>
+        <v>-60.91763</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1076,23 +1076,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.04374</v>
+        <v>46.56837</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.45777</v>
+        <v>-60.91202</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1228,23 +1228,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.37314</v>
+        <v>46.57009</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.59907</v>
+        <v>-60.91782</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1541,14 +1541,14 @@
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.56837</v>
+        <v>46.37494</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.91202</v>
+        <v>-60.59901</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1617,10 +1617,10 @@
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37494</v>
+        <v>46.37314</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59901</v>
+        <v>-60.59907</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Meat Cove Zn Deposit</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>N02-002</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Zn, Mg, Cd, Ge, Ga, Pb, Cu</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Zn 50%, Au 0.04 g/t, Cu 0.0075%</t>
+          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1922,17 +1922,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V19" t="n">
-        <v>47.00887</v>
+        <v>46.28</v>
       </c>
       <c r="W19" t="n">
-        <v>-60.59389</v>
+        <v>-60.56967</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=N02-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00366</v>
+        <v>47.00887</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59004</v>
+        <v>-60.59389</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Meat Cove Zn Deposit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>N02-002</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Zn, Mg, Cd, Ge, Ga, Pb, Cu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2130,7 +2130,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Zn 50%, Au 0.04 g/t, Cu 0.0075%</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
@@ -2146,17 +2150,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="V22" t="n">
-        <v>45.19199</v>
+        <v>47.00366</v>
       </c>
       <c r="W22" t="n">
-        <v>-63.39818</v>
+        <v>-60.59004</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=N02-002</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2183,12 +2187,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2202,7 +2206,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2212,23 +2220,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>45.92081</v>
+        <v>46.27323</v>
       </c>
       <c r="W23" t="n">
-        <v>-61.3156</v>
+        <v>-60.69898</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -2238,12 +2246,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2255,7 +2263,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2284,23 +2292,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U24" t="n">
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>45.16925</v>
+        <v>45.92081</v>
       </c>
       <c r="W24" t="n">
-        <v>-63.38899</v>
+        <v>-61.3156</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2310,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2365,14 +2373,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.20532</v>
+        <v>45.3433</v>
       </c>
       <c r="W25" t="n">
-        <v>-63.41063</v>
+        <v>-63.53544</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2390,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2399,7 +2407,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2437,14 +2445,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.3433</v>
+        <v>45.33992</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.53544</v>
+        <v>-63.48499</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2500,23 +2508,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U27" t="n">
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.28773</v>
+        <v>45.26713</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.47906</v>
+        <v>-63.45492</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2572,23 +2580,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.26713</v>
+        <v>45.16925</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.45492</v>
+        <v>-63.38899</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2615,7 +2623,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2653,14 +2661,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.33992</v>
+        <v>45.24778</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.48499</v>
+        <v>-63.4519</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2716,23 +2724,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.30934</v>
+        <v>45.24369</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.47675</v>
+        <v>-63.44116</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2797,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.24369</v>
+        <v>45.2282</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.44116</v>
+        <v>-63.41684</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2869,14 +2877,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.24778</v>
+        <v>45.20532</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.4519</v>
+        <v>-63.41063</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2886,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2941,14 +2949,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.2282</v>
+        <v>45.19199</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.41684</v>
+        <v>-63.39818</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3047,7 +3055,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3076,23 +3084,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>46.18739</v>
+        <v>45.28773</v>
       </c>
       <c r="W35" t="n">
-        <v>-61.15217</v>
+        <v>-63.47906</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3119,7 +3127,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3148,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>46.21501</v>
+        <v>45.30934</v>
       </c>
       <c r="W36" t="n">
-        <v>-61.11267</v>
+        <v>-63.47675</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -3174,12 +3182,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3191,12 +3199,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3210,11 +3218,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Sb 0.801%, Ag 220.00 g/t, Cu 2%, Co 0.0015%, Cr 0.018%</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
@@ -3224,23 +3228,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U37" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>46.28</v>
+        <v>46.18739</v>
       </c>
       <c r="W37" t="n">
-        <v>-60.56967</v>
+        <v>-61.15217</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3250,12 +3254,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3267,12 +3271,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3286,11 +3290,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
-        </is>
-      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
@@ -3306,17 +3306,17 @@
         <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>46.24968</v>
+        <v>46.21501</v>
       </c>
       <c r="W38" t="n">
-        <v>-61.04986</v>
+        <v>-61.11267</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>46.27323</v>
+        <v>46.24968</v>
       </c>
       <c r="W41" t="n">
-        <v>-60.69898</v>
+        <v>-61.04986</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77777</v>
+        <v>45.77979</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.15731</v>
+        <v>-61.1485</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77684</v>
+        <v>45.77981</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.1495</v>
+        <v>-61.14953</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77979</v>
+        <v>45.77777</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.1485</v>
+        <v>-61.15731</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77981</v>
+        <v>45.77684</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.14953</v>
+        <v>-61.1495</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3980,10 +3980,10 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
@@ -4006,12 +4006,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -4042,11 +4042,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
@@ -4056,23 +4052,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U48" t="n">
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>46.61843</v>
+        <v>44.73589</v>
       </c>
       <c r="W48" t="n">
-        <v>-60.52086</v>
+        <v>-62.91248</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4099,7 +4095,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4128,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T49" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.64923</v>
+        <v>44.73395</v>
       </c>
       <c r="W49" t="n">
-        <v>-64.65634</v>
+        <v>-62.91588</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4150,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4171,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4200,23 +4196,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.73395</v>
+        <v>44.64923</v>
       </c>
       <c r="W50" t="n">
-        <v>-62.91588</v>
+        <v>-64.65634</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4222,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4243,12 +4239,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4262,7 +4258,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4272,23 +4272,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>44.73589</v>
+        <v>46.61843</v>
       </c>
       <c r="W51" t="n">
-        <v>-62.91248</v>
+        <v>-60.52086</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4353,14 +4353,14 @@
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>46.14468</v>
+        <v>44.9011</v>
       </c>
       <c r="W52" t="n">
-        <v>-60.44769</v>
+        <v>-65.00793</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>46.13825</v>
+        <v>45.26005</v>
       </c>
       <c r="W53" t="n">
-        <v>-60.45019</v>
+        <v>-63.93614</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4478,11 +4478,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4492,23 +4488,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.98426</v>
+        <v>45.27248</v>
       </c>
       <c r="W54" t="n">
-        <v>-60.95151</v>
+        <v>-63.87936</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4514,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4535,12 +4531,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4554,11 +4550,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
@@ -4577,14 +4569,14 @@
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>45.9844</v>
+        <v>44.7357</v>
       </c>
       <c r="W55" t="n">
-        <v>-60.94402</v>
+        <v>-62.91338</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4586,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4611,7 +4603,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4640,23 +4632,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T56" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U56" t="n">
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.631</v>
+        <v>44.89232</v>
       </c>
       <c r="W56" t="n">
-        <v>-63.44222</v>
+        <v>-65.04106</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4658,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4683,12 +4675,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -4702,11 +4694,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
@@ -4716,23 +4704,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T57" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U57" t="n">
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>45.91475</v>
+        <v>44.631</v>
       </c>
       <c r="W57" t="n">
-        <v>-61.23041</v>
+        <v>-63.44222</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4730,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4759,7 +4747,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4788,23 +4776,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U58" t="n">
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>44.7357</v>
+        <v>44.89125</v>
       </c>
       <c r="W58" t="n">
-        <v>-62.91338</v>
+        <v>-65.04064</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4869,10 +4857,10 @@
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>44.9011</v>
+        <v>44.89109</v>
       </c>
       <c r="W59" t="n">
-        <v>-65.00793</v>
+        <v>-65.03443</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -4941,10 +4929,10 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>44.89232</v>
+        <v>44.88953</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.04106</v>
+        <v>-65.04628</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -4958,12 +4946,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4975,7 +4963,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5004,23 +4992,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T61" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U61" t="n">
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>45.26005</v>
+        <v>44.88409</v>
       </c>
       <c r="W61" t="n">
-        <v>-63.93614</v>
+        <v>-65.05318</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5018,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5047,7 +5035,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5076,23 +5064,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>45.27248</v>
+        <v>46.14468</v>
       </c>
       <c r="W62" t="n">
-        <v>-63.87936</v>
+        <v>-60.44769</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5090,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5119,7 +5107,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5157,14 +5145,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>45.27275</v>
+        <v>46.13825</v>
       </c>
       <c r="W63" t="n">
-        <v>-63.23508</v>
+        <v>-60.45019</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5162,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5191,12 +5179,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5210,7 +5198,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5220,23 +5212,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T64" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>44.88409</v>
+        <v>45.98426</v>
       </c>
       <c r="W64" t="n">
-        <v>-65.05318</v>
+        <v>-60.95151</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5238,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5263,7 +5255,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5301,14 +5293,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>44.89125</v>
+        <v>45.4857</v>
       </c>
       <c r="W65" t="n">
-        <v>-65.04064</v>
+        <v>-62.52535</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5310,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5335,12 +5327,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5354,7 +5346,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5364,23 +5360,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>44.89109</v>
+        <v>45.9844</v>
       </c>
       <c r="W66" t="n">
-        <v>-65.03443</v>
+        <v>-60.94402</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5386,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5407,7 +5403,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5436,23 +5432,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T67" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U67" t="n">
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>44.43925</v>
+        <v>45.27275</v>
       </c>
       <c r="W67" t="n">
-        <v>-64.78243999999999</v>
+        <v>-63.23508</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5458,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5479,12 +5475,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5498,16 +5494,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>0</v>
@@ -5516,23 +5504,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>44.83208</v>
+        <v>45.82</v>
       </c>
       <c r="W68" t="n">
-        <v>-65.14026</v>
+        <v>-63.68532</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5530,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5559,7 +5547,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5588,23 +5576,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T69" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>44.88953</v>
+        <v>45.2409</v>
       </c>
       <c r="W69" t="n">
-        <v>-65.04628</v>
+        <v>-63.99801</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -5614,12 +5602,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5631,7 +5619,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5660,23 +5648,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>45.2409</v>
+        <v>44.43925</v>
       </c>
       <c r="W70" t="n">
-        <v>-63.99801</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5674,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5703,12 +5691,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5722,7 +5710,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5732,23 +5724,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U71" t="n">
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.25157</v>
+        <v>45.91475</v>
       </c>
       <c r="W71" t="n">
-        <v>-62.11656</v>
+        <v>-61.23041</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5750,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5775,12 +5767,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5794,8 +5786,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5813,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>45.73558</v>
+        <v>44.83208</v>
       </c>
       <c r="W72" t="n">
-        <v>-62.16591</v>
+        <v>-65.14026</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Glenbervie Pb Mine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>E07-018</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5876,23 +5876,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T73" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U73" t="n">
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>45.4857</v>
+        <v>45.28513</v>
       </c>
       <c r="W73" t="n">
-        <v>-62.52535</v>
+        <v>-62.93781</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Glenbervie Pb Mine</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E07-018</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5948,23 +5948,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T74" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U74" t="n">
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.28513</v>
+        <v>45.73558</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.93781</v>
+        <v>-62.16591</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Meaghers Grant As Prospect</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>D14-002</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,12 +5991,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -6010,11 +6010,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Au 1.18 g/t, Ag 1.00 g/t, W 0.0002%</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
@@ -6024,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T75" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U75" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>44.90921</v>
+        <v>45.25157</v>
       </c>
       <c r="W75" t="n">
-        <v>-63.22057</v>
+        <v>-62.11656</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -6050,12 +6046,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Meaghers Grant As Prospect</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>D14-002</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -6067,12 +6063,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I76" t="b">
@@ -6088,7 +6084,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Au 1.18 g/t, Ag 1.00 g/t, W 0.0002%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -6106,17 +6102,17 @@
         <v>325</v>
       </c>
       <c r="U76" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V76" t="n">
-        <v>46.44956</v>
+        <v>44.90921</v>
       </c>
       <c r="W76" t="n">
-        <v>-60.57775</v>
+        <v>-63.22057</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-002</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6122,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6143,7 +6139,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6164,7 +6160,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6185,14 +6181,14 @@
         <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.51873</v>
+        <v>46.29595</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.64496</v>
+        <v>-60.9372</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6198,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6219,12 +6215,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6240,7 +6236,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6261,14 +6257,14 @@
         <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.51529</v>
+        <v>46.44219</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.64417</v>
+        <v>-60.58706</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6278,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6295,7 +6291,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6316,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6337,14 +6333,14 @@
         <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.51478</v>
+        <v>46.2982</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.64575</v>
+        <v>-60.94257</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6354,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6371,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6392,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6413,14 +6409,14 @@
         <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>44.6087</v>
+        <v>46.51873</v>
       </c>
       <c r="W80" t="n">
-        <v>-65.6011</v>
+        <v>-60.64496</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6430,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6447,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6468,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6489,14 +6485,14 @@
         <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>44.6151</v>
+        <v>46.51529</v>
       </c>
       <c r="W81" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.64417</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6506,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6523,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6544,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6565,14 +6561,14 @@
         <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>44.62709</v>
+        <v>46.51553</v>
       </c>
       <c r="W82" t="n">
-        <v>-65.56032</v>
+        <v>-60.64503</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6599,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6620,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6632,23 +6628,23 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T83" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U83" t="n">
         <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>45.1087</v>
+        <v>46.51814</v>
       </c>
       <c r="W83" t="n">
-        <v>-63.09919</v>
+        <v>-60.655</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6696,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6717,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>45.39942</v>
+        <v>44.62709</v>
       </c>
       <c r="W84" t="n">
-        <v>-61.45755</v>
+        <v>-65.56032</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6772,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6793,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>45.40126</v>
+        <v>44.6151</v>
       </c>
       <c r="W85" t="n">
-        <v>-61.45511</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6810,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6827,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6848,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6869,14 +6865,14 @@
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>46.51814</v>
+        <v>44.6087</v>
       </c>
       <c r="W86" t="n">
-        <v>-60.655</v>
+        <v>-65.6011</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6903,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6924,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6936,23 +6932,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U87" t="n">
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>46.51553</v>
+        <v>45.1087</v>
       </c>
       <c r="W87" t="n">
-        <v>-60.64503</v>
+        <v>-63.09919</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -6962,12 +6958,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6979,12 +6975,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -7000,7 +6996,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7021,14 +7017,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.44952</v>
+        <v>45.40126</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.57801</v>
+        <v>-61.45511</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7038,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7055,12 +7051,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7076,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7097,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.4638</v>
+        <v>45.39942</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.57034</v>
+        <v>-61.45755</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7114,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7131,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7152,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7173,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.44638</v>
+        <v>46.29966</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.57242</v>
+        <v>-60.94836</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7249,10 +7245,10 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.45026</v>
+        <v>46.44885</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.5768</v>
+        <v>-60.58676</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -7325,10 +7321,10 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.44885</v>
+        <v>46.44956</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.58676</v>
+        <v>-60.57775</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -7342,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7359,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7380,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7401,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.44219</v>
+        <v>46.51478</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.58706</v>
+        <v>-60.64575</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7418,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7435,7 +7431,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7456,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7474,17 +7470,17 @@
         <v>325</v>
       </c>
       <c r="U94" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>44.68634</v>
+        <v>46.44952</v>
       </c>
       <c r="W94" t="n">
-        <v>-63.97235</v>
+        <v>-60.57801</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7494,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7511,7 +7507,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7532,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7550,17 +7546,17 @@
         <v>325</v>
       </c>
       <c r="U95" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>44.69007</v>
+        <v>46.4638</v>
       </c>
       <c r="W95" t="n">
-        <v>-63.97154</v>
+        <v>-60.57034</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7570,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7587,7 +7583,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7608,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7626,17 +7622,17 @@
         <v>325</v>
       </c>
       <c r="U96" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>44.69021</v>
+        <v>46.44638</v>
       </c>
       <c r="W96" t="n">
-        <v>-63.97107</v>
+        <v>-60.57242</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7646,12 +7642,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7663,7 +7659,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7684,7 +7680,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7696,23 +7692,23 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T97" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U97" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V97" t="n">
-        <v>46.8323</v>
+        <v>46.45026</v>
       </c>
       <c r="W97" t="n">
-        <v>-60.6939</v>
+        <v>-60.5768</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7718,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7739,7 +7735,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7760,7 +7756,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -7778,17 +7774,17 @@
         <v>325</v>
       </c>
       <c r="U98" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V98" t="n">
-        <v>44.48487</v>
+        <v>44.68634</v>
       </c>
       <c r="W98" t="n">
-        <v>-65.96890999999999</v>
+        <v>-63.97235</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7798,12 +7794,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -7815,7 +7811,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7836,7 +7832,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -7854,17 +7850,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>45.78604</v>
+        <v>44.69007</v>
       </c>
       <c r="W99" t="n">
-        <v>-60.56073</v>
+        <v>-63.97154</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7874,12 +7870,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7891,12 +7887,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -7912,7 +7908,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7930,17 +7926,17 @@
         <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="V100" t="n">
-        <v>46.38378</v>
+        <v>44.69021</v>
       </c>
       <c r="W100" t="n">
-        <v>-60.80809</v>
+        <v>-63.97107</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7950,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7967,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7988,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -8000,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T101" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U101" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>46.36255</v>
+        <v>46.8323</v>
       </c>
       <c r="W101" t="n">
-        <v>-60.59174</v>
+        <v>-60.6939</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8026,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8043,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8064,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8082,17 +8078,17 @@
         <v>325</v>
       </c>
       <c r="U102" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>46.19179</v>
+        <v>44.48487</v>
       </c>
       <c r="W102" t="n">
-        <v>-60.57356</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8102,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8119,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8140,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8161,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>46.18983</v>
+        <v>45.76567</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.57015</v>
+        <v>-60.56882</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8174,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -8195,7 +8191,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8216,7 +8212,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -8237,14 +8233,14 @@
         <v>22</v>
       </c>
       <c r="V104" t="n">
-        <v>45.77335</v>
+        <v>46.18983</v>
       </c>
       <c r="W104" t="n">
-        <v>-60.56515</v>
+        <v>-60.57015</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8271,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8292,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8313,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>45.77827</v>
+        <v>46.36255</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.55927</v>
+        <v>-60.59174</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8330,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8347,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8368,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8389,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>45.76567</v>
+        <v>46.19179</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.56882</v>
+        <v>-60.57356</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8423,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8444,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8465,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>45.77589</v>
+        <v>46.38378</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.56156</v>
+        <v>-60.80809</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8482,12 +8478,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8499,7 +8495,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8520,7 +8516,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -8538,17 +8534,17 @@
         <v>325</v>
       </c>
       <c r="U108" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>46.17933</v>
+        <v>45.77335</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.84528</v>
+        <v>-60.56515</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8558,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8575,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8596,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8608,23 +8604,23 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T109" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U109" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>46.5331</v>
+        <v>45.77589</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.79089</v>
+        <v>-60.56156</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8630,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The Three Sisters (Lake O'Law)  Au, W, As Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>K07-050</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -8651,7 +8647,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Au, W, As, Cu</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8672,7 +8668,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Au 0.63 g/t, Ag 0.80 g/t, Cd 0.00131%, Co 0.0038%, Cr 0.0144%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -8690,17 +8686,17 @@
         <v>325</v>
       </c>
       <c r="U110" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V110" t="n">
-        <v>46.28434</v>
+        <v>45.77827</v>
       </c>
       <c r="W110" t="n">
-        <v>-60.95243</v>
+        <v>-60.55927</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-050</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8710,12 +8706,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8727,7 +8723,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8748,7 +8744,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -8766,17 +8762,17 @@
         <v>325</v>
       </c>
       <c r="U111" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>46.13897</v>
+        <v>45.78604</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.9063</v>
+        <v>-60.56073</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8786,12 +8782,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>The Three Sisters (Lake O'Law)  Au, W, As Occurrence</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K07-050</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8803,7 +8799,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, W, As, Cu</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8824,7 +8820,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.63 g/t, Ag 0.80 g/t, Cd 0.00131%, Co 0.0038%, Cr 0.0144%</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -8845,14 +8841,14 @@
         <v>21</v>
       </c>
       <c r="V112" t="n">
-        <v>46.13397</v>
+        <v>46.28434</v>
       </c>
       <c r="W112" t="n">
-        <v>-60.92758</v>
+        <v>-60.95243</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-050</t>
         </is>
       </c>
     </row>
@@ -8921,10 +8917,10 @@
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>46.13658</v>
+        <v>46.13397</v>
       </c>
       <c r="W113" t="n">
-        <v>-60.91312</v>
+        <v>-60.92758</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
@@ -8938,12 +8934,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8955,7 +8951,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8976,7 +8972,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -8997,14 +8993,14 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.26487</v>
+        <v>46.13658</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.65547</v>
+        <v>-60.91312</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9031,12 +9027,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I115" t="b">
@@ -9052,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9064,23 +9060,23 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T115" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U115" t="n">
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.12356</v>
+        <v>46.5331</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.91944</v>
+        <v>-60.79089</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9090,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9107,7 +9103,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9128,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9140,23 +9136,23 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T116" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U116" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>44.08614</v>
+        <v>46.26487</v>
       </c>
       <c r="W116" t="n">
-        <v>-65.76729</v>
+        <v>-60.65547</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9166,12 +9162,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shaw Lakes Cu, Pb Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>F15-016</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9183,7 +9179,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9204,7 +9200,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Pb 0.328%, Ag 1.10 g/t, Bi 0.0006%, Cd 0.00016%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9222,17 +9218,17 @@
         <v>325</v>
       </c>
       <c r="U117" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>45.76921</v>
+        <v>46.13897</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.55671</v>
+        <v>-60.9063</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9242,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cape Saint Mary Stibnite Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B01-010</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9259,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sb, As, Ni, Cu, Ag</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9280,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9292,23 +9288,23 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T118" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U118" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>44.13698</v>
+        <v>46.17933</v>
       </c>
       <c r="W118" t="n">
-        <v>-66.19927</v>
+        <v>-60.84528</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9318,12 +9314,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>French Village Lake Zn, As Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>F16-038</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9335,7 +9331,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Zn, As, Cu, Cd</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9356,7 +9352,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Zn 0.966%, Ag 1.20 g/t, Au 0.02 g/t, Bi 0.0018%, Cd 0.00352%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9374,17 +9370,17 @@
         <v>325</v>
       </c>
       <c r="U119" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>45.90959</v>
+        <v>46.12356</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.27694</v>
+        <v>-60.91944</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-038</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9394,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cape Saint Mary Stibnite Occurrence</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B01-010</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9411,7 +9407,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sb, As, Ni, Cu, Ag</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9432,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9444,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T120" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="U120" t="n">
         <v>20</v>
       </c>
       <c r="V120" t="n">
-        <v>44.115</v>
+        <v>44.08614</v>
       </c>
       <c r="W120" t="n">
-        <v>-66.19658</v>
+        <v>-65.76729</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9470,12 +9466,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>French Village Lake Zn, As Occurrence</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>F16-038</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9487,7 +9483,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>Zn, As, Cu, Cd</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9508,7 +9504,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Zn 0.966%, Ag 1.20 g/t, Au 0.02 g/t, Bi 0.0018%, Cd 0.00352%</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -9520,23 +9516,23 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T121" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U121" t="n">
         <v>20</v>
       </c>
       <c r="V121" t="n">
-        <v>44.82095</v>
+        <v>45.90959</v>
       </c>
       <c r="W121" t="n">
-        <v>-64.29518</v>
+        <v>-60.27694</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-038</t>
         </is>
       </c>
     </row>
@@ -9546,12 +9542,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+          <t>Cape Saint Mary Stibnite Occurrence</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>K07-019</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9563,7 +9559,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Sb, As, Ni, Cu, Ag</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9584,7 +9580,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -9596,23 +9592,23 @@
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T122" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U122" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V122" t="n">
-        <v>46.4303</v>
+        <v>44.13698</v>
       </c>
       <c r="W122" t="n">
-        <v>-60.9406</v>
+        <v>-66.19927</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
         </is>
       </c>
     </row>
@@ -9622,12 +9618,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+          <t>Shaw Lakes Cu, Pb Occurrence</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>K07-019</t>
+          <t>F15-016</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9660,7 +9656,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+          <t>Cu 0.213%, Pb 0.328%, Ag 1.10 g/t, Bi 0.0006%, Cd 0.00016%</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -9678,17 +9674,17 @@
         <v>325</v>
       </c>
       <c r="U123" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V123" t="n">
-        <v>46.42609</v>
+        <v>45.76921</v>
       </c>
       <c r="W123" t="n">
-        <v>-60.94179</v>
+        <v>-60.55671</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-016</t>
         </is>
       </c>
     </row>
@@ -9698,12 +9694,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+          <t>Cape Saint Mary Stibnite Occurrence</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>K07-019</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9715,7 +9711,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Sb, As, Ni, Cu, Ag</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9736,7 +9732,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -9748,23 +9744,23 @@
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T124" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U124" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V124" t="n">
-        <v>46.42607</v>
+        <v>44.115</v>
       </c>
       <c r="W124" t="n">
-        <v>-60.94075</v>
+        <v>-66.19658</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
         </is>
       </c>
     </row>
@@ -9774,12 +9770,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>K07-019</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9791,7 +9787,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9812,7 +9808,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9824,21 +9820,325 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
+        <v>7</v>
+      </c>
+      <c r="T125" t="n">
+        <v>175</v>
+      </c>
+      <c r="U125" t="n">
+        <v>20</v>
+      </c>
+      <c r="V125" t="n">
+        <v>44.82095</v>
+      </c>
+      <c r="W125" t="n">
+        <v>-64.29518</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>K07-019</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Cu, Pb, Zn</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Occurrence</t>
+        </is>
+      </c>
+      <c r="I126" t="b">
+        <v>1</v>
+      </c>
+      <c r="J126" t="b">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="n">
         <v>13</v>
       </c>
-      <c r="T125" t="n">
+      <c r="T126" t="n">
         <v>325</v>
       </c>
-      <c r="U125" t="n">
+      <c r="U126" t="n">
         <v>19</v>
       </c>
-      <c r="V125" t="n">
+      <c r="V126" t="n">
+        <v>46.42609</v>
+      </c>
+      <c r="W126" t="n">
+        <v>-60.94179</v>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>K07-019</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cu, Pb, Zn</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Occurrence</t>
+        </is>
+      </c>
+      <c r="I127" t="b">
+        <v>1</v>
+      </c>
+      <c r="J127" t="b">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="n">
+        <v>13</v>
+      </c>
+      <c r="T127" t="n">
+        <v>325</v>
+      </c>
+      <c r="U127" t="n">
+        <v>19</v>
+      </c>
+      <c r="V127" t="n">
         <v>46.42622</v>
       </c>
-      <c r="W125" t="n">
+      <c r="W127" t="n">
         <v>-60.93906</v>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>K07-019</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Cu, Pb, Zn</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Occurrence</t>
+        </is>
+      </c>
+      <c r="I128" t="b">
+        <v>1</v>
+      </c>
+      <c r="J128" t="b">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="n">
+        <v>13</v>
+      </c>
+      <c r="T128" t="n">
+        <v>325</v>
+      </c>
+      <c r="U128" t="n">
+        <v>19</v>
+      </c>
+      <c r="V128" t="n">
+        <v>46.42607</v>
+      </c>
+      <c r="W128" t="n">
+        <v>-60.94075</v>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>K07-019</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Cu, Pb, Zn</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Occurrence</t>
+        </is>
+      </c>
+      <c r="I129" t="b">
+        <v>1</v>
+      </c>
+      <c r="J129" t="b">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="n">
+        <v>13</v>
+      </c>
+      <c r="T129" t="n">
+        <v>325</v>
+      </c>
+      <c r="U129" t="n">
+        <v>19</v>
+      </c>
+      <c r="V129" t="n">
+        <v>46.4303</v>
+      </c>
+      <c r="W129" t="n">
+        <v>-60.9406</v>
+      </c>
+      <c r="X129" t="inlineStr">
         <is>
           <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,11 +2206,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2229,14 +2225,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>46.27323</v>
+        <v>45.16925</v>
       </c>
       <c r="W23" t="n">
-        <v>-60.69898</v>
+        <v>-63.38899</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2242,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2263,12 +2259,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2282,7 +2278,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
@@ -2292,23 +2292,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>45.92081</v>
+        <v>46.27323</v>
       </c>
       <c r="W24" t="n">
-        <v>-61.3156</v>
+        <v>-60.69898</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2364,23 +2364,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T25" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.3433</v>
+        <v>45.92081</v>
       </c>
       <c r="W25" t="n">
-        <v>-63.53544</v>
+        <v>-61.3156</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2445,14 +2445,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.33992</v>
+        <v>45.3433</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.48499</v>
+        <v>-63.53544</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2508,23 +2508,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.26713</v>
+        <v>45.33992</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.45492</v>
+        <v>-63.48499</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2580,23 +2580,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.16925</v>
+        <v>45.26713</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.38899</v>
+        <v>-63.45492</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2661,14 +2661,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.24778</v>
+        <v>45.28773</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.4519</v>
+        <v>-63.47906</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2724,23 +2724,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.24369</v>
+        <v>45.30934</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.44116</v>
+        <v>-63.47675</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.2282</v>
+        <v>45.24778</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.41684</v>
+        <v>-63.4519</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2877,14 +2877,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.20532</v>
+        <v>45.24369</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.41063</v>
+        <v>-63.44116</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2949,14 +2949,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.19199</v>
+        <v>45.2282</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.39818</v>
+        <v>-63.41684</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3012,23 +3012,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>46.09672</v>
+        <v>45.20532</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.13017</v>
+        <v>-63.41063</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3093,14 +3093,14 @@
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>45.28773</v>
+        <v>45.19199</v>
       </c>
       <c r="W35" t="n">
-        <v>-63.47906</v>
+        <v>-63.39818</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3156,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T36" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>45.30934</v>
+        <v>46.09672</v>
       </c>
       <c r="W36" t="n">
-        <v>-63.47675</v>
+        <v>-61.13017</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A09-032</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sn, Cu, Zn, As</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3461,14 +3461,14 @@
         <v>34</v>
       </c>
       <c r="V40" t="n">
-        <v>44.60164</v>
+        <v>46.24968</v>
       </c>
       <c r="W40" t="n">
-        <v>-64.05405</v>
+        <v>-61.04986</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>A09-032</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Sn, Cu, Zn, As</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>46.24968</v>
+        <v>44.60241</v>
       </c>
       <c r="W41" t="n">
-        <v>-61.04986</v>
+        <v>-64.0553</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
         </is>
       </c>
     </row>
@@ -3613,10 +3613,10 @@
         <v>34</v>
       </c>
       <c r="V42" t="n">
-        <v>44.60241</v>
+        <v>44.60164</v>
       </c>
       <c r="W42" t="n">
-        <v>-64.0553</v>
+        <v>-64.05405</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6178,17 +6178,17 @@
         <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V77" t="n">
-        <v>46.29595</v>
+        <v>46.44956</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.9372</v>
+        <v>-60.57775</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V78" t="n">
         <v>46.44219</v>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6330,17 +6330,17 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V79" t="n">
-        <v>46.2982</v>
+        <v>46.44885</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.94257</v>
+        <v>-60.58676</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6406,17 +6406,17 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V80" t="n">
-        <v>46.51873</v>
+        <v>46.44952</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.64496</v>
+        <v>-60.57801</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6482,17 +6482,17 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V81" t="n">
-        <v>46.51529</v>
+        <v>46.44638</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.64417</v>
+        <v>-60.57242</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6558,17 +6558,17 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V82" t="n">
-        <v>46.51553</v>
+        <v>46.4638</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.64503</v>
+        <v>-60.57034</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6634,17 +6634,17 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V83" t="n">
-        <v>46.51814</v>
+        <v>46.45026</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.655</v>
+        <v>-60.5768</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>44.62709</v>
+        <v>46.29966</v>
       </c>
       <c r="W84" t="n">
-        <v>-65.56032</v>
+        <v>-60.94836</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>44.6151</v>
+        <v>46.51873</v>
       </c>
       <c r="W85" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.64496</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6865,14 +6865,14 @@
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>44.6087</v>
+        <v>46.51529</v>
       </c>
       <c r="W86" t="n">
-        <v>-65.6011</v>
+        <v>-60.64417</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6932,23 +6932,23 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T87" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U87" t="n">
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>45.1087</v>
+        <v>46.51553</v>
       </c>
       <c r="W87" t="n">
-        <v>-63.09919</v>
+        <v>-60.64503</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7017,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>45.40126</v>
+        <v>46.51814</v>
       </c>
       <c r="W88" t="n">
-        <v>-61.45511</v>
+        <v>-60.655</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>45.39942</v>
+        <v>44.62709</v>
       </c>
       <c r="W89" t="n">
-        <v>-61.45755</v>
+        <v>-65.56032</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.29966</v>
+        <v>44.6151</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.94836</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.44885</v>
+        <v>44.6087</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.58676</v>
+        <v>-65.6011</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7312,23 +7312,23 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T92" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U92" t="n">
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.44956</v>
+        <v>45.1087</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.57775</v>
+        <v>-63.09919</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.51478</v>
+        <v>45.40126</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.64575</v>
+        <v>-61.45511</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>46.44952</v>
+        <v>45.39942</v>
       </c>
       <c r="W94" t="n">
-        <v>-60.57801</v>
+        <v>-61.45755</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>46.4638</v>
+        <v>46.29595</v>
       </c>
       <c r="W95" t="n">
-        <v>-60.57034</v>
+        <v>-60.9372</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>46.44638</v>
+        <v>46.2982</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.57242</v>
+        <v>-60.94257</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7701,14 +7701,14 @@
         <v>26</v>
       </c>
       <c r="V97" t="n">
-        <v>46.45026</v>
+        <v>46.51478</v>
       </c>
       <c r="W97" t="n">
-        <v>-60.5768</v>
+        <v>-60.64575</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X129"/>
+  <dimension ref="A1:X130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.56569</v>
+        <v>46.57026</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91812</v>
+        <v>-60.91194</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1000,19 +1000,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.56838</v>
+        <v>46.56826</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.91763</v>
+        <v>-60.90602</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1076,23 +1076,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U8" t="n">
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.56837</v>
+        <v>46.04734</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.91202</v>
+        <v>-60.45799</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.04734</v>
+        <v>46.56837</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.45799</v>
+        <v>-60.91202</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1228,23 +1228,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.57009</v>
+        <v>46.37314</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.91782</v>
+        <v>-60.59907</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1380,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U12" t="n">
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.56826</v>
+        <v>46.57009</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.90602</v>
+        <v>-60.91782</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.57026</v>
+        <v>46.56838</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91194</v>
+        <v>-60.91763</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.37494</v>
+        <v>46.56569</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.59901</v>
+        <v>-60.91812</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1617,10 +1617,10 @@
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37314</v>
+        <v>46.37494</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59907</v>
+        <v>-60.59901</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Springhaven Pb, Zn, Ag Occurrence</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P13-008</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Cd, Bi</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
+          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>43.91009</v>
+        <v>46.28</v>
       </c>
       <c r="W18" t="n">
-        <v>-65.87437</v>
+        <v>-60.56967</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Springhaven Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>P13-008</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Pb, Zn, Ag, Cd, Bi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1925,14 +1925,14 @@
         <v>39</v>
       </c>
       <c r="V19" t="n">
-        <v>46.28</v>
+        <v>43.91009</v>
       </c>
       <c r="W19" t="n">
-        <v>-60.56967</v>
+        <v>-65.87437</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00887</v>
+        <v>47.00366</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59389</v>
+        <v>-60.59004</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>38</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00366</v>
+        <v>47.00887</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59004</v>
+        <v>-60.59389</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,7 +2206,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2225,14 +2229,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>45.16925</v>
+        <v>46.27323</v>
       </c>
       <c r="W23" t="n">
-        <v>-63.38899</v>
+        <v>-60.69898</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2246,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2259,12 +2263,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2278,11 +2282,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
@@ -2301,14 +2301,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>46.27323</v>
+        <v>45.28773</v>
       </c>
       <c r="W24" t="n">
-        <v>-60.69898</v>
+        <v>-63.47906</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2364,23 +2364,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.92081</v>
+        <v>45.30934</v>
       </c>
       <c r="W25" t="n">
-        <v>-61.3156</v>
+        <v>-63.47675</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2445,14 +2445,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.3433</v>
+        <v>45.33992</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.53544</v>
+        <v>-63.48499</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2517,14 +2517,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.33992</v>
+        <v>45.24369</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.48499</v>
+        <v>-63.44116</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2580,23 +2580,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.26713</v>
+        <v>45.24778</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.45492</v>
+        <v>-63.4519</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2661,14 +2661,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.28773</v>
+        <v>45.16925</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.47906</v>
+        <v>-63.38899</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2724,23 +2724,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.30934</v>
+        <v>45.20532</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.47675</v>
+        <v>-63.41063</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.24778</v>
+        <v>45.19199</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.4519</v>
+        <v>-63.39818</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2868,23 +2868,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.24369</v>
+        <v>45.92081</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.44116</v>
+        <v>-61.3156</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2940,23 +2940,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.2282</v>
+        <v>45.26713</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.41684</v>
+        <v>-63.45492</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3012,23 +3012,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>45.20532</v>
+        <v>46.09672</v>
       </c>
       <c r="W34" t="n">
-        <v>-63.41063</v>
+        <v>-61.13017</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3084,23 +3084,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>45.19199</v>
+        <v>46.18739</v>
       </c>
       <c r="W35" t="n">
-        <v>-63.39818</v>
+        <v>-61.15217</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3156,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>46.09672</v>
+        <v>45.2282</v>
       </c>
       <c r="W36" t="n">
-        <v>-61.13017</v>
+        <v>-63.41684</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -3228,19 +3228,19 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>46.18739</v>
+        <v>46.21501</v>
       </c>
       <c r="W37" t="n">
-        <v>-61.15217</v>
+        <v>-61.11267</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3309,14 +3309,14 @@
         <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>46.21501</v>
+        <v>45.3433</v>
       </c>
       <c r="W38" t="n">
-        <v>-61.11267</v>
+        <v>-63.53544</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>A09-032</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>Sn, Cu, Zn, As</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
         <v>34</v>
       </c>
       <c r="V39" t="n">
-        <v>43.70849</v>
+        <v>44.60241</v>
       </c>
       <c r="W39" t="n">
-        <v>-66.06631</v>
+        <v>-64.0553</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A09-032</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sn, Cu, Zn, As</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>44.60241</v>
+        <v>43.70849</v>
       </c>
       <c r="W41" t="n">
-        <v>-64.0553</v>
+        <v>-66.06631</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77979</v>
+        <v>45.77777</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.1485</v>
+        <v>-61.15731</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77981</v>
+        <v>45.77684</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.14953</v>
+        <v>-61.1495</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77777</v>
+        <v>45.77981</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.15731</v>
+        <v>-61.14953</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77684</v>
+        <v>45.77979</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1495</v>
+        <v>-61.1485</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3980,23 +3980,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>45.0448</v>
+        <v>44.64923</v>
       </c>
       <c r="W47" t="n">
-        <v>-62.16418</v>
+        <v>-64.65634</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73589</v>
+        <v>44.73395</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91248</v>
+        <v>-62.91588</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4124,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T49" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.73395</v>
+        <v>44.43925</v>
       </c>
       <c r="W49" t="n">
-        <v>-62.91588</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4196,23 +4196,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.64923</v>
+        <v>44.73589</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.65634</v>
+        <v>-62.91248</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4258,11 +4258,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4272,23 +4268,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>46.61843</v>
+        <v>44.7357</v>
       </c>
       <c r="W51" t="n">
-        <v>-60.52086</v>
+        <v>-62.91338</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4294,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4315,7 +4311,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4344,23 +4340,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>44.9011</v>
+        <v>45.2409</v>
       </c>
       <c r="W52" t="n">
-        <v>-65.00793</v>
+        <v>-63.99801</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4387,12 +4383,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4406,7 +4402,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>45.26005</v>
+        <v>46.61843</v>
       </c>
       <c r="W53" t="n">
-        <v>-63.93614</v>
+        <v>-60.52086</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4478,7 +4478,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4488,23 +4492,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.27248</v>
+        <v>45.9844</v>
       </c>
       <c r="W54" t="n">
-        <v>-63.87936</v>
+        <v>-60.94402</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4531,7 +4535,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4560,23 +4564,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T55" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>44.7357</v>
+        <v>45.0448</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.91338</v>
+        <v>-62.16418</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4590,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4603,12 +4607,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4622,8 +4626,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4641,14 +4653,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.89232</v>
+        <v>44.83208</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.04106</v>
+        <v>-65.14026</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5030,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5035,7 +5047,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5064,23 +5076,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T62" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U62" t="n">
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>46.14468</v>
+        <v>45.26005</v>
       </c>
       <c r="W62" t="n">
-        <v>-60.44769</v>
+        <v>-63.93614</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5102,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5107,7 +5119,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5145,14 +5157,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>46.13825</v>
+        <v>44.9011</v>
       </c>
       <c r="W63" t="n">
-        <v>-60.45019</v>
+        <v>-65.00793</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5174,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5179,12 +5191,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5198,11 +5210,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5212,23 +5220,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T64" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>45.98426</v>
+        <v>45.27248</v>
       </c>
       <c r="W64" t="n">
-        <v>-60.95151</v>
+        <v>-63.87936</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5246,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5255,7 +5263,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5293,14 +5301,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>45.4857</v>
+        <v>44.89232</v>
       </c>
       <c r="W65" t="n">
-        <v>-62.52535</v>
+        <v>-65.04106</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5318,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5327,12 +5335,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5346,11 +5354,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5360,23 +5364,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.9844</v>
+        <v>46.14468</v>
       </c>
       <c r="W66" t="n">
-        <v>-60.94402</v>
+        <v>-60.44769</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5390,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5403,7 +5407,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5441,14 +5445,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>45.27275</v>
+        <v>46.13825</v>
       </c>
       <c r="W67" t="n">
-        <v>-63.23508</v>
+        <v>-60.45019</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5462,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5475,12 +5479,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5494,7 +5498,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
@@ -5504,23 +5512,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T68" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.82</v>
+        <v>45.98426</v>
       </c>
       <c r="W68" t="n">
-        <v>-63.68532</v>
+        <v>-60.95151</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5538,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5547,12 +5555,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5566,7 +5574,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
@@ -5576,23 +5588,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T69" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.2409</v>
+        <v>45.91475</v>
       </c>
       <c r="W69" t="n">
-        <v>-63.99801</v>
+        <v>-61.23041</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5614,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5619,7 +5631,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5648,23 +5660,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>44.43925</v>
+        <v>45.25157</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.78243999999999</v>
+        <v>-62.11656</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5686,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5691,12 +5703,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5710,11 +5722,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5733,14 +5741,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.91475</v>
+        <v>45.73558</v>
       </c>
       <c r="W71" t="n">
-        <v>-61.23041</v>
+        <v>-62.16591</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5758,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5767,12 +5775,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5786,16 +5794,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5813,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>44.83208</v>
+        <v>45.27275</v>
       </c>
       <c r="W72" t="n">
-        <v>-65.14026</v>
+        <v>-63.23508</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5957,14 +5957,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.73558</v>
+        <v>45.4857</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.16591</v>
+        <v>-62.52535</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.25157</v>
+        <v>45.82</v>
       </c>
       <c r="W75" t="n">
-        <v>-62.11656</v>
+        <v>-63.68532</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -6181,10 +6181,10 @@
         <v>27</v>
       </c>
       <c r="V77" t="n">
-        <v>46.44956</v>
+        <v>46.44885</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.57775</v>
+        <v>-60.58676</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         <v>27</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44219</v>
+        <v>46.44638</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.58706</v>
+        <v>-60.57242</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -6333,10 +6333,10 @@
         <v>27</v>
       </c>
       <c r="V79" t="n">
-        <v>46.44885</v>
+        <v>46.4638</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.58676</v>
+        <v>-60.57034</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -6485,10 +6485,10 @@
         <v>27</v>
       </c>
       <c r="V81" t="n">
-        <v>46.44638</v>
+        <v>46.45026</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.57242</v>
+        <v>-60.5768</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
         <v>27</v>
       </c>
       <c r="V82" t="n">
-        <v>46.4638</v>
+        <v>46.44956</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.57034</v>
+        <v>-60.57775</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -6637,10 +6637,10 @@
         <v>27</v>
       </c>
       <c r="V83" t="n">
-        <v>46.45026</v>
+        <v>46.44219</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.5768</v>
+        <v>-60.58706</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6856,23 +6856,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T86" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U86" t="n">
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>46.51529</v>
+        <v>45.1087</v>
       </c>
       <c r="W86" t="n">
-        <v>-60.64417</v>
+        <v>-63.09919</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -6941,10 +6941,10 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>46.51553</v>
+        <v>46.51478</v>
       </c>
       <c r="W87" t="n">
-        <v>-60.64503</v>
+        <v>-60.64575</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -7017,10 +7017,10 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.51814</v>
+        <v>46.51529</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.655</v>
+        <v>-60.64417</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>44.62709</v>
+        <v>46.51553</v>
       </c>
       <c r="W89" t="n">
-        <v>-65.56032</v>
+        <v>-60.64503</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>44.6151</v>
+        <v>46.51814</v>
       </c>
       <c r="W90" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.655</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>44.6087</v>
+        <v>45.40126</v>
       </c>
       <c r="W91" t="n">
-        <v>-65.6011</v>
+        <v>-61.45511</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7312,23 +7312,23 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T92" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U92" t="n">
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>45.1087</v>
+        <v>46.2982</v>
       </c>
       <c r="W92" t="n">
-        <v>-63.09919</v>
+        <v>-60.94257</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>45.40126</v>
+        <v>46.29595</v>
       </c>
       <c r="W93" t="n">
-        <v>-61.45511</v>
+        <v>-60.9372</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>45.39942</v>
+        <v>44.62709</v>
       </c>
       <c r="W94" t="n">
-        <v>-61.45755</v>
+        <v>-65.56032</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>46.29595</v>
+        <v>44.6087</v>
       </c>
       <c r="W95" t="n">
-        <v>-60.9372</v>
+        <v>-65.6011</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>46.2982</v>
+        <v>44.6151</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.94257</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7701,14 +7701,14 @@
         <v>26</v>
       </c>
       <c r="V97" t="n">
-        <v>46.51478</v>
+        <v>45.39942</v>
       </c>
       <c r="W97" t="n">
-        <v>-60.64575</v>
+        <v>-61.45755</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7777,10 +7777,10 @@
         <v>25</v>
       </c>
       <c r="V98" t="n">
-        <v>44.68634</v>
+        <v>44.69007</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97235</v>
+        <v>-63.97154</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69007</v>
+        <v>44.69021</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97154</v>
+        <v>-63.97107</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -7929,10 +7929,10 @@
         <v>25</v>
       </c>
       <c r="V100" t="n">
-        <v>44.69021</v>
+        <v>44.68634</v>
       </c>
       <c r="W100" t="n">
-        <v>-63.97107</v>
+        <v>-63.97235</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7996,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>46.8323</v>
+        <v>44.48487</v>
       </c>
       <c r="W101" t="n">
-        <v>-60.6939</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8072,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T102" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U102" t="n">
         <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>44.48487</v>
+        <v>46.8323</v>
       </c>
       <c r="W102" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.6939</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>45.76567</v>
+        <v>46.36255</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.56882</v>
+        <v>-60.59174</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.36255</v>
+        <v>46.19179</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.59174</v>
+        <v>-60.57356</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8385,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>46.19179</v>
+        <v>45.77335</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.57356</v>
+        <v>-60.56515</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8461,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>46.38378</v>
+        <v>45.78604</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.80809</v>
+        <v>-60.56073</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>45.77335</v>
+        <v>45.76567</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56515</v>
+        <v>-60.56882</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8613,14 +8613,14 @@
         <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>45.77589</v>
+        <v>46.38378</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.56156</v>
+        <v>-60.80809</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8765,10 @@
         <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>45.78604</v>
+        <v>45.77589</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56073</v>
+        <v>-60.56156</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -8858,12 +8858,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Upper Mount Thom Cu, Zn, Ni, Ag Occurrence</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>E10-033</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Cu, Zn, Ni, Ag, Cd, Fe</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Cu 0.124%, Ni 0.0967%, Co 0.0231%, Zn 0.306%, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -8908,23 +8908,23 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T113" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U113" t="n">
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>46.13397</v>
+        <v>45.51103</v>
       </c>
       <c r="W113" t="n">
-        <v>-60.92758</v>
+        <v>-62.96642</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E10-033</t>
         </is>
       </c>
     </row>
@@ -8993,10 +8993,10 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.13658</v>
+        <v>46.12356</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.91312</v>
+        <v>-60.91944</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I115" t="b">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9060,23 +9060,23 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T115" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U115" t="n">
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.5331</v>
+        <v>46.17933</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.79089</v>
+        <v>-60.84528</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9145,14 +9145,14 @@
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.26487</v>
+        <v>46.13897</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.65547</v>
+        <v>-60.9063</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9221,10 +9221,10 @@
         <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>46.13897</v>
+        <v>46.13658</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.9063</v>
+        <v>-60.91312</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9297,14 +9297,14 @@
         <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>46.17933</v>
+        <v>46.26487</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.84528</v>
+        <v>-60.65547</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9373,10 +9373,10 @@
         <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>46.12356</v>
+        <v>46.13397</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.91944</v>
+        <v>-60.92758</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I120" t="b">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T120" t="n">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="U120" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V120" t="n">
-        <v>44.08614</v>
+        <v>46.5331</v>
       </c>
       <c r="W120" t="n">
-        <v>-65.76729</v>
+        <v>-60.79089</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>French Village Lake Zn, As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>F16-038</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Zn, As, Cu, Cd</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Zn 0.966%, Ag 1.20 g/t, Au 0.02 g/t, Bi 0.0018%, Cd 0.00352%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -9516,23 +9516,23 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T121" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U121" t="n">
         <v>20</v>
       </c>
       <c r="V121" t="n">
-        <v>45.90959</v>
+        <v>44.82095</v>
       </c>
       <c r="W121" t="n">
-        <v>-60.27694</v>
+        <v>-64.29518</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-038</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cape Saint Mary Stibnite Occurrence</t>
+          <t>French Village Lake Zn, As Occurrence</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B01-010</t>
+          <t>F16-038</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sb, As, Ni, Cu, Ag</t>
+          <t>Zn, As, Cu, Cd</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
+          <t>Zn 0.966%, Ag 1.20 g/t, Au 0.02 g/t, Bi 0.0018%, Cd 0.00352%</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -9592,23 +9592,23 @@
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T122" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U122" t="n">
         <v>20</v>
       </c>
       <c r="V122" t="n">
-        <v>44.13698</v>
+        <v>45.90959</v>
       </c>
       <c r="W122" t="n">
-        <v>-66.19927</v>
+        <v>-60.27694</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-038</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shaw Lakes Cu, Pb Occurrence</t>
+          <t>Cape Saint Mary Stibnite Occurrence</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>F15-016</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>Sb, As, Ni, Cu, Ag</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Pb 0.328%, Ag 1.10 g/t, Bi 0.0006%, Cd 0.00016%</t>
+          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -9668,23 +9668,23 @@
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T123" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U123" t="n">
         <v>20</v>
       </c>
       <c r="V123" t="n">
-        <v>45.76921</v>
+        <v>44.13698</v>
       </c>
       <c r="W123" t="n">
-        <v>-60.55671</v>
+        <v>-66.19927</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
         </is>
       </c>
     </row>
@@ -9694,12 +9694,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cape Saint Mary Stibnite Occurrence</t>
+          <t>Shaw Lakes Cu, Pb Occurrence</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B01-010</t>
+          <t>F15-016</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sb, As, Ni, Cu, Ag</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
+          <t>Cu 0.213%, Pb 0.328%, Ag 1.10 g/t, Bi 0.0006%, Cd 0.00016%</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -9744,23 +9744,23 @@
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T124" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U124" t="n">
         <v>20</v>
       </c>
       <c r="V124" t="n">
-        <v>44.115</v>
+        <v>45.76921</v>
       </c>
       <c r="W124" t="n">
-        <v>-66.19658</v>
+        <v>-60.55671</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-016</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>Cape Saint Mary Stibnite Occurrence</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>Sb, As, Ni, Cu, Ag</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9820,23 +9820,23 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T125" t="n">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="U125" t="n">
         <v>20</v>
       </c>
       <c r="V125" t="n">
-        <v>44.82095</v>
+        <v>44.115</v>
       </c>
       <c r="W125" t="n">
-        <v>-64.29518</v>
+        <v>-66.19658</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
         </is>
       </c>
     </row>
@@ -9846,12 +9846,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>K07-019</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -9896,23 +9896,23 @@
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T126" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U126" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V126" t="n">
-        <v>46.42609</v>
+        <v>44.08614</v>
       </c>
       <c r="W126" t="n">
-        <v>-60.94179</v>
+        <v>-65.76729</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9981,10 +9981,10 @@
         <v>19</v>
       </c>
       <c r="V127" t="n">
-        <v>46.42622</v>
+        <v>46.4303</v>
       </c>
       <c r="W127" t="n">
-        <v>-60.93906</v>
+        <v>-60.9406</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
@@ -10057,10 +10057,10 @@
         <v>19</v>
       </c>
       <c r="V128" t="n">
-        <v>46.42607</v>
+        <v>46.42622</v>
       </c>
       <c r="W128" t="n">
-        <v>-60.94075</v>
+        <v>-60.93906</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
@@ -10133,12 +10133,88 @@
         <v>19</v>
       </c>
       <c r="V129" t="n">
-        <v>46.4303</v>
+        <v>46.42607</v>
       </c>
       <c r="W129" t="n">
-        <v>-60.9406</v>
+        <v>-60.94075</v>
       </c>
       <c r="X129" t="inlineStr">
+        <is>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>K07-019</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Cu, Pb, Zn</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Occurrence</t>
+        </is>
+      </c>
+      <c r="I130" t="b">
+        <v>1</v>
+      </c>
+      <c r="J130" t="b">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="n">
+        <v>13</v>
+      </c>
+      <c r="T130" t="n">
+        <v>325</v>
+      </c>
+      <c r="U130" t="n">
+        <v>19</v>
+      </c>
+      <c r="V130" t="n">
+        <v>46.42609</v>
+      </c>
+      <c r="W130" t="n">
+        <v>-60.94179</v>
+      </c>
+      <c r="X130" t="inlineStr">
         <is>
           <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.57026</v>
+        <v>46.56569</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91194</v>
+        <v>-60.91812</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1000,19 +1000,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.56826</v>
+        <v>46.56838</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.90602</v>
+        <v>-60.91763</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1076,23 +1076,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.04734</v>
+        <v>46.56837</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.45799</v>
+        <v>-60.91202</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.56837</v>
+        <v>46.04734</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.91202</v>
+        <v>-60.45799</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1228,23 +1228,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.37314</v>
+        <v>46.57009</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.59907</v>
+        <v>-60.91782</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1380,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.57009</v>
+        <v>46.56826</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.91782</v>
+        <v>-60.90602</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.56838</v>
+        <v>46.57026</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91763</v>
+        <v>-60.91194</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.56569</v>
+        <v>46.37494</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.91812</v>
+        <v>-60.59901</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1617,10 +1617,10 @@
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37494</v>
+        <v>46.37314</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59901</v>
+        <v>-60.59907</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Springhaven Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>P13-008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Pb, Zn, Ag, Cd, Bi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>46.28</v>
+        <v>43.91009</v>
       </c>
       <c r="W18" t="n">
-        <v>-60.56967</v>
+        <v>-65.87437</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Springhaven Pb, Zn, Ag Occurrence</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P13-008</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Cd, Bi</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
+          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1925,14 +1925,14 @@
         <v>39</v>
       </c>
       <c r="V19" t="n">
-        <v>43.91009</v>
+        <v>46.28</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.87437</v>
+        <v>-60.56967</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00366</v>
+        <v>47.00887</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59004</v>
+        <v>-60.59389</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>38</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00887</v>
+        <v>47.00366</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59389</v>
+        <v>-60.59004</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,11 +2206,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2229,14 +2225,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>46.27323</v>
+        <v>45.16925</v>
       </c>
       <c r="W23" t="n">
-        <v>-60.69898</v>
+        <v>-63.38899</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2242,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2263,12 +2259,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2282,7 +2278,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
@@ -2301,14 +2301,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>45.28773</v>
+        <v>46.27323</v>
       </c>
       <c r="W24" t="n">
-        <v>-63.47906</v>
+        <v>-60.69898</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2364,23 +2364,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T25" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.30934</v>
+        <v>45.92081</v>
       </c>
       <c r="W25" t="n">
-        <v>-63.47675</v>
+        <v>-61.3156</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2445,14 +2445,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.33992</v>
+        <v>45.3433</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.48499</v>
+        <v>-63.53544</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2517,14 +2517,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.24369</v>
+        <v>45.33992</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.44116</v>
+        <v>-63.48499</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2580,23 +2580,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.24778</v>
+        <v>45.26713</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.4519</v>
+        <v>-63.45492</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2661,14 +2661,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.16925</v>
+        <v>45.28773</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.38899</v>
+        <v>-63.47906</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2724,23 +2724,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.20532</v>
+        <v>45.30934</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.41063</v>
+        <v>-63.47675</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.19199</v>
+        <v>45.24778</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.39818</v>
+        <v>-63.4519</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2868,23 +2868,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T32" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.92081</v>
+        <v>45.24369</v>
       </c>
       <c r="W32" t="n">
-        <v>-61.3156</v>
+        <v>-63.44116</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2940,23 +2940,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.26713</v>
+        <v>45.2282</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.45492</v>
+        <v>-63.41684</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3012,23 +3012,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>46.09672</v>
+        <v>45.20532</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.13017</v>
+        <v>-63.41063</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3084,23 +3084,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>46.18739</v>
+        <v>45.19199</v>
       </c>
       <c r="W35" t="n">
-        <v>-61.15217</v>
+        <v>-63.39818</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3156,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T36" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>45.2282</v>
+        <v>46.09672</v>
       </c>
       <c r="W36" t="n">
-        <v>-63.41684</v>
+        <v>-61.13017</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3228,19 +3228,19 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U37" t="n">
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>46.21501</v>
+        <v>46.18739</v>
       </c>
       <c r="W37" t="n">
-        <v>-61.11267</v>
+        <v>-61.15217</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3309,14 +3309,14 @@
         <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>45.3433</v>
+        <v>46.21501</v>
       </c>
       <c r="W38" t="n">
-        <v>-63.53544</v>
+        <v>-61.11267</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A09-032</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sn, Cu, Zn, As</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
         <v>34</v>
       </c>
       <c r="V39" t="n">
-        <v>44.60241</v>
+        <v>43.70849</v>
       </c>
       <c r="W39" t="n">
-        <v>-64.0553</v>
+        <v>-66.06631</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>A09-032</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>Sn, Cu, Zn, As</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>43.70849</v>
+        <v>44.60241</v>
       </c>
       <c r="W41" t="n">
-        <v>-66.06631</v>
+        <v>-64.0553</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77777</v>
+        <v>45.77979</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.15731</v>
+        <v>-61.1485</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77684</v>
+        <v>45.77981</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.1495</v>
+        <v>-61.14953</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77981</v>
+        <v>45.77777</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.14953</v>
+        <v>-61.15731</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77979</v>
+        <v>45.77684</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1485</v>
+        <v>-61.1495</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3980,23 +3980,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>44.64923</v>
+        <v>45.0448</v>
       </c>
       <c r="W47" t="n">
-        <v>-64.65634</v>
+        <v>-62.16418</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73395</v>
+        <v>44.73589</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91588</v>
+        <v>-62.91248</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4124,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T49" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.43925</v>
+        <v>44.73395</v>
       </c>
       <c r="W49" t="n">
-        <v>-64.78243999999999</v>
+        <v>-62.91588</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4196,23 +4196,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.73589</v>
+        <v>44.64923</v>
       </c>
       <c r="W50" t="n">
-        <v>-62.91248</v>
+        <v>-64.65634</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4258,7 +4258,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4268,23 +4272,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>44.7357</v>
+        <v>46.61843</v>
       </c>
       <c r="W51" t="n">
-        <v>-62.91338</v>
+        <v>-60.52086</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4311,7 +4315,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4340,23 +4344,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>45.2409</v>
+        <v>44.9011</v>
       </c>
       <c r="W52" t="n">
-        <v>-63.99801</v>
+        <v>-65.00793</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4383,12 +4387,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4402,11 +4406,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>46.61843</v>
+        <v>45.26005</v>
       </c>
       <c r="W53" t="n">
-        <v>-60.52086</v>
+        <v>-63.93614</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4478,11 +4478,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4492,23 +4488,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.9844</v>
+        <v>45.27248</v>
       </c>
       <c r="W54" t="n">
-        <v>-60.94402</v>
+        <v>-63.87936</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4514,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4535,7 +4531,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4564,23 +4560,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>45.0448</v>
+        <v>44.7357</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.16418</v>
+        <v>-62.91338</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4586,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4607,12 +4603,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4626,16 +4622,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4653,14 +4641,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.83208</v>
+        <v>44.89232</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.14026</v>
+        <v>-65.04106</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5018,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5047,7 +5035,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5076,23 +5064,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T62" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U62" t="n">
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>45.26005</v>
+        <v>46.14468</v>
       </c>
       <c r="W62" t="n">
-        <v>-63.93614</v>
+        <v>-60.44769</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5090,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5119,7 +5107,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5157,14 +5145,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>44.9011</v>
+        <v>46.13825</v>
       </c>
       <c r="W63" t="n">
-        <v>-65.00793</v>
+        <v>-60.45019</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5162,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5191,12 +5179,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5210,7 +5198,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5220,23 +5212,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T64" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>45.27248</v>
+        <v>45.98426</v>
       </c>
       <c r="W64" t="n">
-        <v>-63.87936</v>
+        <v>-60.95151</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5238,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5263,7 +5255,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5301,14 +5293,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>44.89232</v>
+        <v>45.4857</v>
       </c>
       <c r="W65" t="n">
-        <v>-65.04106</v>
+        <v>-62.52535</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5310,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5335,12 +5327,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5354,7 +5346,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5364,23 +5360,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T66" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>46.14468</v>
+        <v>45.9844</v>
       </c>
       <c r="W66" t="n">
-        <v>-60.44769</v>
+        <v>-60.94402</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5386,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5407,7 +5403,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5445,14 +5441,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>46.13825</v>
+        <v>45.27275</v>
       </c>
       <c r="W67" t="n">
-        <v>-60.45019</v>
+        <v>-63.23508</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5458,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5479,12 +5475,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5498,11 +5494,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
@@ -5512,23 +5504,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.98426</v>
+        <v>45.82</v>
       </c>
       <c r="W68" t="n">
-        <v>-60.95151</v>
+        <v>-63.68532</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5530,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5555,12 +5547,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5574,11 +5566,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
@@ -5588,23 +5576,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T69" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.91475</v>
+        <v>45.2409</v>
       </c>
       <c r="W69" t="n">
-        <v>-61.23041</v>
+        <v>-63.99801</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -5614,12 +5602,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5631,7 +5619,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5660,23 +5648,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>45.25157</v>
+        <v>44.43925</v>
       </c>
       <c r="W70" t="n">
-        <v>-62.11656</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5674,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5703,12 +5691,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5722,7 +5710,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5741,14 +5733,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.73558</v>
+        <v>45.91475</v>
       </c>
       <c r="W71" t="n">
-        <v>-62.16591</v>
+        <v>-61.23041</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5750,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5775,12 +5767,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5794,8 +5786,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5813,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>45.27275</v>
+        <v>44.83208</v>
       </c>
       <c r="W72" t="n">
-        <v>-63.23508</v>
+        <v>-65.14026</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5957,14 +5957,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.4857</v>
+        <v>45.73558</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.52535</v>
+        <v>-62.16591</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T75" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.82</v>
+        <v>45.25157</v>
       </c>
       <c r="W75" t="n">
-        <v>-63.68532</v>
+        <v>-62.11656</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6178,17 +6178,17 @@
         <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.44885</v>
+        <v>46.29595</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.58676</v>
+        <v>-60.9372</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6254,13 +6254,13 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44638</v>
+        <v>46.44219</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.57242</v>
+        <v>-60.58706</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6330,17 +6330,17 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.4638</v>
+        <v>46.2982</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.57034</v>
+        <v>-60.94257</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6406,17 +6406,17 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.44952</v>
+        <v>46.51873</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.57801</v>
+        <v>-60.64496</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6482,17 +6482,17 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.45026</v>
+        <v>46.51529</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.5768</v>
+        <v>-60.64417</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6558,17 +6558,17 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.44956</v>
+        <v>46.51553</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.57775</v>
+        <v>-60.64503</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6634,17 +6634,17 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>46.44219</v>
+        <v>46.51814</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.58706</v>
+        <v>-60.655</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>46.29966</v>
+        <v>44.6087</v>
       </c>
       <c r="W84" t="n">
-        <v>-60.94836</v>
+        <v>-65.6011</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>46.51873</v>
+        <v>44.6151</v>
       </c>
       <c r="W85" t="n">
-        <v>-60.64496</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6856,23 +6856,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T86" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U86" t="n">
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>45.1087</v>
+        <v>44.62709</v>
       </c>
       <c r="W86" t="n">
-        <v>-63.09919</v>
+        <v>-65.56032</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6941,14 +6941,14 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>46.51478</v>
+        <v>45.40126</v>
       </c>
       <c r="W87" t="n">
-        <v>-60.64575</v>
+        <v>-61.45511</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7017,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.51529</v>
+        <v>45.39942</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.64417</v>
+        <v>-61.45755</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.51553</v>
+        <v>46.29966</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.64503</v>
+        <v>-60.94836</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.51814</v>
+        <v>46.44885</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.655</v>
+        <v>-60.58676</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>45.40126</v>
+        <v>46.44956</v>
       </c>
       <c r="W91" t="n">
-        <v>-61.45511</v>
+        <v>-60.57775</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.2982</v>
+        <v>46.51478</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.94257</v>
+        <v>-60.64575</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.29595</v>
+        <v>46.44952</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.9372</v>
+        <v>-60.57801</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>44.62709</v>
+        <v>46.4638</v>
       </c>
       <c r="W94" t="n">
-        <v>-65.56032</v>
+        <v>-60.57034</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>44.6087</v>
+        <v>46.44638</v>
       </c>
       <c r="W95" t="n">
-        <v>-65.6011</v>
+        <v>-60.57242</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>44.6151</v>
+        <v>46.45026</v>
       </c>
       <c r="W96" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.5768</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I97" t="b">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7698,17 +7698,17 @@
         <v>325</v>
       </c>
       <c r="U97" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V97" t="n">
-        <v>45.39942</v>
+        <v>44.68634</v>
       </c>
       <c r="W97" t="n">
-        <v>-61.45755</v>
+        <v>-63.97235</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7777,10 +7777,10 @@
         <v>25</v>
       </c>
       <c r="V98" t="n">
-        <v>44.69007</v>
+        <v>44.69021</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97154</v>
+        <v>-63.97107</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69021</v>
+        <v>44.69007</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97107</v>
+        <v>-63.97154</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -7870,12 +7870,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7920,23 +7920,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U100" t="n">
         <v>25</v>
       </c>
       <c r="V100" t="n">
-        <v>44.68634</v>
+        <v>45.1087</v>
       </c>
       <c r="W100" t="n">
-        <v>-63.97235</v>
+        <v>-63.09919</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7996,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T101" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U101" t="n">
         <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>44.48487</v>
+        <v>46.8323</v>
       </c>
       <c r="W101" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.6939</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8072,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T102" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U102" t="n">
         <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>46.8323</v>
+        <v>44.48487</v>
       </c>
       <c r="W102" t="n">
-        <v>-60.6939</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>46.36255</v>
+        <v>45.76567</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.59174</v>
+        <v>-60.56882</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.19179</v>
+        <v>46.36255</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.57356</v>
+        <v>-60.59174</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8385,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>45.77335</v>
+        <v>46.19179</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.56515</v>
+        <v>-60.57356</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8461,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>45.78604</v>
+        <v>46.38378</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.56073</v>
+        <v>-60.80809</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>45.76567</v>
+        <v>45.77335</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56882</v>
+        <v>-60.56515</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8613,14 +8613,14 @@
         <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>46.38378</v>
+        <v>45.77589</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.80809</v>
+        <v>-60.56156</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8765,10 @@
         <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>45.77589</v>
+        <v>45.78604</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56156</v>
+        <v>-60.56073</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -8993,10 +8993,10 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.12356</v>
+        <v>46.13397</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.91944</v>
+        <v>-60.92758</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9069,14 +9069,14 @@
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.17933</v>
+        <v>46.13658</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.84528</v>
+        <v>-60.91312</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,12 +9103,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I116" t="b">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9136,23 +9136,23 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T116" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U116" t="n">
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.13897</v>
+        <v>46.5331</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.9063</v>
+        <v>-60.79089</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9221,14 +9221,14 @@
         <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>46.13658</v>
+        <v>46.26487</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.91312</v>
+        <v>-60.65547</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9297,14 +9297,14 @@
         <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>46.26487</v>
+        <v>46.13897</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.65547</v>
+        <v>-60.9063</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9373,14 +9373,14 @@
         <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>46.13397</v>
+        <v>46.17933</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.92758</v>
+        <v>-60.84528</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I120" t="b">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T120" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U120" t="n">
         <v>21</v>
       </c>
       <c r="V120" t="n">
-        <v>46.5331</v>
+        <v>46.12356</v>
       </c>
       <c r="W120" t="n">
-        <v>-60.79089</v>
+        <v>-60.91944</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -9516,23 +9516,23 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T121" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U121" t="n">
         <v>20</v>
       </c>
       <c r="V121" t="n">
-        <v>44.82095</v>
+        <v>44.08614</v>
       </c>
       <c r="W121" t="n">
-        <v>-64.29518</v>
+        <v>-65.76729</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9846,12 +9846,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -9896,23 +9896,23 @@
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T126" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U126" t="n">
         <v>20</v>
       </c>
       <c r="V126" t="n">
-        <v>44.08614</v>
+        <v>44.82095</v>
       </c>
       <c r="W126" t="n">
-        <v>-65.76729</v>
+        <v>-64.29518</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9981,10 +9981,10 @@
         <v>19</v>
       </c>
       <c r="V127" t="n">
-        <v>46.4303</v>
+        <v>46.42609</v>
       </c>
       <c r="W127" t="n">
-        <v>-60.9406</v>
+        <v>-60.94179</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
@@ -10209,10 +10209,10 @@
         <v>19</v>
       </c>
       <c r="V130" t="n">
-        <v>46.42609</v>
+        <v>46.4303</v>
       </c>
       <c r="W130" t="n">
-        <v>-60.94179</v>
+        <v>-60.9406</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -6181,10 +6181,10 @@
         <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.29595</v>
+        <v>46.2982</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.9372</v>
+        <v>-60.94257</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6257,14 +6257,14 @@
         <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44219</v>
+        <v>46.29595</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.58706</v>
+        <v>-60.9372</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6333,14 +6333,14 @@
         <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.2982</v>
+        <v>46.44219</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.94257</v>
+        <v>-60.58706</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6409,10 +6409,10 @@
         <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.51873</v>
+        <v>46.51529</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.64496</v>
+        <v>-60.64417</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -6485,10 +6485,10 @@
         <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.51529</v>
+        <v>46.51553</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.64417</v>
+        <v>-60.64503</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
         <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.51553</v>
+        <v>46.51814</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.64503</v>
+        <v>-60.655</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6637,14 +6637,14 @@
         <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>46.51814</v>
+        <v>44.62709</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.655</v>
+        <v>-65.56032</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6713,10 +6713,10 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>44.6087</v>
+        <v>44.6151</v>
       </c>
       <c r="W84" t="n">
-        <v>-65.6011</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -6789,10 +6789,10 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>44.6151</v>
+        <v>44.6087</v>
       </c>
       <c r="W85" t="n">
-        <v>-65.58083999999999</v>
+        <v>-65.6011</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6856,23 +6856,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T86" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U86" t="n">
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>44.62709</v>
+        <v>45.1087</v>
       </c>
       <c r="W86" t="n">
-        <v>-65.56032</v>
+        <v>-63.09919</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7093,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.29966</v>
+        <v>46.51873</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.94836</v>
+        <v>-60.64496</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.44885</v>
+        <v>46.29966</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.58676</v>
+        <v>-60.94836</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7245,10 +7245,10 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.44956</v>
+        <v>46.44885</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.57775</v>
+        <v>-60.58676</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.51478</v>
+        <v>46.44956</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.64575</v>
+        <v>-60.57775</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.44952</v>
+        <v>46.51478</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.57801</v>
+        <v>-60.64575</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7473,10 +7473,10 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>46.4638</v>
+        <v>46.44952</v>
       </c>
       <c r="W94" t="n">
-        <v>-60.57034</v>
+        <v>-60.57801</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -7549,10 +7549,10 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>46.44638</v>
+        <v>46.4638</v>
       </c>
       <c r="W95" t="n">
-        <v>-60.57242</v>
+        <v>-60.57034</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -7625,10 +7625,10 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>46.45026</v>
+        <v>46.44638</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.5768</v>
+        <v>-60.57242</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7698,17 +7698,17 @@
         <v>325</v>
       </c>
       <c r="U97" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V97" t="n">
-        <v>44.68634</v>
+        <v>46.45026</v>
       </c>
       <c r="W97" t="n">
-        <v>-63.97235</v>
+        <v>-60.5768</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7777,10 +7777,10 @@
         <v>25</v>
       </c>
       <c r="V98" t="n">
-        <v>44.69021</v>
+        <v>44.68634</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97107</v>
+        <v>-63.97235</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -7870,12 +7870,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7920,23 +7920,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T100" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U100" t="n">
         <v>25</v>
       </c>
       <c r="V100" t="n">
-        <v>45.1087</v>
+        <v>44.69021</v>
       </c>
       <c r="W100" t="n">
-        <v>-63.09919</v>
+        <v>-63.97107</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24541</v>
+        <v>46.24531</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89447</v>
+        <v>-60.89421</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.56569</v>
+        <v>46.57026</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91812</v>
+        <v>-60.91194</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1000,19 +1000,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.56838</v>
+        <v>46.56826</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.91763</v>
+        <v>-60.90602</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1076,23 +1076,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U8" t="n">
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.56837</v>
+        <v>46.04734</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.91202</v>
+        <v>-60.45799</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.04734</v>
+        <v>46.56837</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.45799</v>
+        <v>-60.91202</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1228,23 +1228,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.57009</v>
+        <v>46.37314</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.91782</v>
+        <v>-60.59907</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1380,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U12" t="n">
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.56826</v>
+        <v>46.57009</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.90602</v>
+        <v>-60.91782</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.57026</v>
+        <v>46.56838</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91194</v>
+        <v>-60.91763</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.37494</v>
+        <v>46.56569</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.59901</v>
+        <v>-60.91812</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1617,10 +1617,10 @@
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37314</v>
+        <v>46.37494</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59907</v>
+        <v>-60.59901</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Springhaven Pb, Zn, Ag Occurrence</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P13-008</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Cd, Bi</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
+          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>43.91009</v>
+        <v>46.28</v>
       </c>
       <c r="W18" t="n">
-        <v>-65.87437</v>
+        <v>-60.56967</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Springhaven Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>P13-008</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Pb, Zn, Ag, Cd, Bi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1925,14 +1925,14 @@
         <v>39</v>
       </c>
       <c r="V19" t="n">
-        <v>46.28</v>
+        <v>43.91009</v>
       </c>
       <c r="W19" t="n">
-        <v>-60.56967</v>
+        <v>-65.87437</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00887</v>
+        <v>47.00366</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59389</v>
+        <v>-60.59004</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         <v>38</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00366</v>
+        <v>47.00887</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59004</v>
+        <v>-60.59389</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,7 +2206,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2225,14 +2229,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>45.16925</v>
+        <v>46.27323</v>
       </c>
       <c r="W23" t="n">
-        <v>-63.38899</v>
+        <v>-60.69898</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2246,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2259,12 +2263,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2278,11 +2282,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
@@ -2301,14 +2301,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>46.27323</v>
+        <v>45.28773</v>
       </c>
       <c r="W24" t="n">
-        <v>-60.69898</v>
+        <v>-63.47906</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2364,23 +2364,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.92081</v>
+        <v>45.30934</v>
       </c>
       <c r="W25" t="n">
-        <v>-61.3156</v>
+        <v>-63.47675</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2445,14 +2445,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.3433</v>
+        <v>45.33992</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.53544</v>
+        <v>-63.48499</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2517,14 +2517,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.33992</v>
+        <v>45.24369</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.48499</v>
+        <v>-63.44116</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2580,23 +2580,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.26713</v>
+        <v>45.24778</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.45492</v>
+        <v>-63.4519</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2661,14 +2661,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.28773</v>
+        <v>45.16925</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.47906</v>
+        <v>-63.38899</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2724,23 +2724,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.30934</v>
+        <v>45.20532</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.47675</v>
+        <v>-63.41063</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2805,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.24778</v>
+        <v>45.19199</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.4519</v>
+        <v>-63.39818</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2868,23 +2868,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.24369</v>
+        <v>45.92081</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.44116</v>
+        <v>-61.3156</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2940,23 +2940,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T33" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.2282</v>
+        <v>45.26713</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.41684</v>
+        <v>-63.45492</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3012,23 +3012,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>45.20532</v>
+        <v>46.09672</v>
       </c>
       <c r="W34" t="n">
-        <v>-63.41063</v>
+        <v>-61.13017</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3084,23 +3084,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>45.19199</v>
+        <v>46.18739</v>
       </c>
       <c r="W35" t="n">
-        <v>-63.39818</v>
+        <v>-61.15217</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3156,23 +3156,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U36" t="n">
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>46.09672</v>
+        <v>45.2282</v>
       </c>
       <c r="W36" t="n">
-        <v>-61.13017</v>
+        <v>-63.41684</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -3228,19 +3228,19 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>46.18739</v>
+        <v>46.21501</v>
       </c>
       <c r="W37" t="n">
-        <v>-61.15217</v>
+        <v>-61.11267</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3309,14 +3309,14 @@
         <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>46.21501</v>
+        <v>45.3433</v>
       </c>
       <c r="W38" t="n">
-        <v>-61.11267</v>
+        <v>-63.53544</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
         <v>34</v>
       </c>
       <c r="V39" t="n">
-        <v>43.70849</v>
+        <v>46.24968</v>
       </c>
       <c r="W39" t="n">
-        <v>-66.06631</v>
+        <v>-61.04986</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3461,14 +3461,14 @@
         <v>34</v>
       </c>
       <c r="V40" t="n">
-        <v>46.24968</v>
+        <v>43.70849</v>
       </c>
       <c r="W40" t="n">
-        <v>-61.04986</v>
+        <v>-66.06631</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -3537,10 +3537,10 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>44.60241</v>
+        <v>44.60164</v>
       </c>
       <c r="W41" t="n">
-        <v>-64.0553</v>
+        <v>-64.05405</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         <v>34</v>
       </c>
       <c r="V42" t="n">
-        <v>44.60164</v>
+        <v>44.60241</v>
       </c>
       <c r="W42" t="n">
-        <v>-64.05405</v>
+        <v>-64.0553</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -3689,10 +3689,10 @@
         <v>33</v>
       </c>
       <c r="V43" t="n">
-        <v>45.77979</v>
+        <v>45.77777</v>
       </c>
       <c r="W43" t="n">
-        <v>-61.1485</v>
+        <v>-61.15731</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         <v>33</v>
       </c>
       <c r="V44" t="n">
-        <v>45.77981</v>
+        <v>45.77684</v>
       </c>
       <c r="W44" t="n">
-        <v>-61.14953</v>
+        <v>-61.1495</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77777</v>
+        <v>45.77981</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.15731</v>
+        <v>-61.14953</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77684</v>
+        <v>45.77979</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1495</v>
+        <v>-61.1485</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3980,23 +3980,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>45.0448</v>
+        <v>44.64923</v>
       </c>
       <c r="W47" t="n">
-        <v>-62.16418</v>
+        <v>-64.65634</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73589</v>
+        <v>44.73395</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91248</v>
+        <v>-62.91588</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4124,23 +4124,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T49" t="n">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.73395</v>
+        <v>44.43925</v>
       </c>
       <c r="W49" t="n">
-        <v>-62.91588</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4196,23 +4196,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U50" t="n">
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.64923</v>
+        <v>44.73589</v>
       </c>
       <c r="W50" t="n">
-        <v>-64.65634</v>
+        <v>-62.91248</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4258,11 +4258,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -4272,23 +4268,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T51" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U51" t="n">
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>46.61843</v>
+        <v>44.7357</v>
       </c>
       <c r="W51" t="n">
-        <v>-60.52086</v>
+        <v>-62.91338</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4294,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4315,7 +4311,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4344,23 +4340,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>44.9011</v>
+        <v>45.2409</v>
       </c>
       <c r="W52" t="n">
-        <v>-65.00793</v>
+        <v>-63.99801</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4387,12 +4383,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4406,7 +4402,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4416,23 +4416,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>45.26005</v>
+        <v>46.61843</v>
       </c>
       <c r="W53" t="n">
-        <v>-63.93614</v>
+        <v>-60.52086</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4442,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4459,12 +4459,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4478,7 +4478,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
@@ -4488,23 +4492,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T54" t="n">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="U54" t="n">
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.27248</v>
+        <v>45.9844</v>
       </c>
       <c r="W54" t="n">
-        <v>-63.87936</v>
+        <v>-60.94402</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4531,7 +4535,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4560,23 +4564,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T55" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>44.7357</v>
+        <v>45.0448</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.91338</v>
+        <v>-62.16418</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4590,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4603,12 +4607,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4622,8 +4626,16 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4641,14 +4653,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.89232</v>
+        <v>44.83208</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.04106</v>
+        <v>-65.14026</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5030,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5035,7 +5047,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5064,23 +5076,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T62" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U62" t="n">
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>46.14468</v>
+        <v>45.26005</v>
       </c>
       <c r="W62" t="n">
-        <v>-60.44769</v>
+        <v>-63.93614</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5102,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5107,7 +5119,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5145,14 +5157,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>46.13825</v>
+        <v>44.9011</v>
       </c>
       <c r="W63" t="n">
-        <v>-60.45019</v>
+        <v>-65.00793</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5174,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5179,12 +5191,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -5198,11 +5210,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
@@ -5212,23 +5220,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T64" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>45.98426</v>
+        <v>45.27248</v>
       </c>
       <c r="W64" t="n">
-        <v>-60.95151</v>
+        <v>-63.87936</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5246,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5255,7 +5263,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5293,14 +5301,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>45.4857</v>
+        <v>44.89232</v>
       </c>
       <c r="W65" t="n">
-        <v>-62.52535</v>
+        <v>-65.04106</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5318,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5327,12 +5335,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5346,11 +5354,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
@@ -5360,23 +5364,23 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T66" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U66" t="n">
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>45.9844</v>
+        <v>46.14468</v>
       </c>
       <c r="W66" t="n">
-        <v>-60.94402</v>
+        <v>-60.44769</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5390,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5403,7 +5407,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5441,14 +5445,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>45.27275</v>
+        <v>46.13825</v>
       </c>
       <c r="W67" t="n">
-        <v>-63.23508</v>
+        <v>-60.45019</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5462,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5475,12 +5479,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5494,7 +5498,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
@@ -5504,23 +5512,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T68" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.82</v>
+        <v>45.98426</v>
       </c>
       <c r="W68" t="n">
-        <v>-63.68532</v>
+        <v>-60.95151</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5538,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5547,12 +5555,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5566,7 +5574,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
@@ -5576,23 +5588,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T69" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U69" t="n">
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.2409</v>
+        <v>45.91475</v>
       </c>
       <c r="W69" t="n">
-        <v>-63.99801</v>
+        <v>-61.23041</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5614,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5619,7 +5631,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5648,23 +5660,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>44.43925</v>
+        <v>45.25157</v>
       </c>
       <c r="W70" t="n">
-        <v>-64.78243999999999</v>
+        <v>-62.11656</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5686,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5691,12 +5703,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -5710,11 +5722,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
@@ -5733,14 +5741,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.91475</v>
+        <v>45.73558</v>
       </c>
       <c r="W71" t="n">
-        <v>-61.23041</v>
+        <v>-62.16591</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5758,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5767,12 +5775,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5786,16 +5794,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>0</v>
@@ -5813,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>44.83208</v>
+        <v>45.27275</v>
       </c>
       <c r="W72" t="n">
-        <v>-65.14026</v>
+        <v>-63.23508</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5957,14 +5957,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.73558</v>
+        <v>45.4857</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.16591</v>
+        <v>-62.52535</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>E13-001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Cu, Ag, U</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6020,23 +6020,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U75" t="n">
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>45.25157</v>
+        <v>45.82</v>
       </c>
       <c r="W75" t="n">
-        <v>-62.11656</v>
+        <v>-63.68532</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
         </is>
       </c>
     </row>
@@ -6181,10 +6181,10 @@
         <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.2982</v>
+        <v>46.29595</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.94257</v>
+        <v>-60.9372</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6215,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6257,14 +6257,14 @@
         <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.29595</v>
+        <v>46.44638</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.9372</v>
+        <v>-60.57242</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I79" t="b">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6333,14 +6333,14 @@
         <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.44219</v>
+        <v>46.51873</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.58706</v>
+        <v>-60.64496</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6409,14 +6409,14 @@
         <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.51529</v>
+        <v>46.45026</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.64417</v>
+        <v>-60.5768</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6485,14 +6485,14 @@
         <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.51553</v>
+        <v>46.44219</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.64503</v>
+        <v>-60.58706</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6561,14 +6561,14 @@
         <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.51814</v>
+        <v>46.44885</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.655</v>
+        <v>-60.58676</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6637,14 +6637,14 @@
         <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>44.62709</v>
+        <v>46.44952</v>
       </c>
       <c r="W83" t="n">
-        <v>-65.56032</v>
+        <v>-60.57801</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>44.6151</v>
+        <v>46.4638</v>
       </c>
       <c r="W84" t="n">
-        <v>-65.58083999999999</v>
+        <v>-60.57034</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6789,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>44.6087</v>
+        <v>46.44956</v>
       </c>
       <c r="W85" t="n">
-        <v>-65.6011</v>
+        <v>-60.57775</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6856,23 +6856,23 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T86" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U86" t="n">
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>45.1087</v>
+        <v>46.51478</v>
       </c>
       <c r="W86" t="n">
-        <v>-63.09919</v>
+        <v>-60.64575</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6941,14 +6941,14 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>45.40126</v>
+        <v>46.51529</v>
       </c>
       <c r="W87" t="n">
-        <v>-61.45511</v>
+        <v>-60.64417</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7017,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>45.39942</v>
+        <v>46.51553</v>
       </c>
       <c r="W88" t="n">
-        <v>-61.45755</v>
+        <v>-60.64503</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -7093,10 +7093,10 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.51873</v>
+        <v>46.51814</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.64496</v>
+        <v>-60.655</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7127,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7169,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>46.29966</v>
+        <v>45.40126</v>
       </c>
       <c r="W90" t="n">
-        <v>-60.94836</v>
+        <v>-61.45511</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7186,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7245,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.44885</v>
+        <v>46.2982</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.58676</v>
+        <v>-60.94257</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ryan Brook  Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K07-049</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7321,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.44956</v>
+        <v>46.29966</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.57775</v>
+        <v>-60.94836</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7355,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7397,14 +7397,14 @@
         <v>26</v>
       </c>
       <c r="V93" t="n">
-        <v>46.51478</v>
+        <v>44.62709</v>
       </c>
       <c r="W93" t="n">
-        <v>-60.64575</v>
+        <v>-65.56032</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7473,14 +7473,14 @@
         <v>26</v>
       </c>
       <c r="V94" t="n">
-        <v>46.44952</v>
+        <v>44.6087</v>
       </c>
       <c r="W94" t="n">
-        <v>-60.57801</v>
+        <v>-65.6011</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7549,14 +7549,14 @@
         <v>26</v>
       </c>
       <c r="V95" t="n">
-        <v>46.4638</v>
+        <v>44.6151</v>
       </c>
       <c r="W95" t="n">
-        <v>-60.57034</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7625,14 +7625,14 @@
         <v>26</v>
       </c>
       <c r="V96" t="n">
-        <v>46.44638</v>
+        <v>45.39942</v>
       </c>
       <c r="W96" t="n">
-        <v>-60.57242</v>
+        <v>-61.45755</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7698,17 +7698,17 @@
         <v>325</v>
       </c>
       <c r="U97" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V97" t="n">
-        <v>46.45026</v>
+        <v>44.69007</v>
       </c>
       <c r="W97" t="n">
-        <v>-60.5768</v>
+        <v>-63.97154</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7853,10 +7853,10 @@
         <v>25</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69007</v>
+        <v>44.69021</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97154</v>
+        <v>-63.97107</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -7870,12 +7870,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7920,23 +7920,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U100" t="n">
         <v>25</v>
       </c>
       <c r="V100" t="n">
-        <v>44.69021</v>
+        <v>45.1087</v>
       </c>
       <c r="W100" t="n">
-        <v>-63.97107</v>
+        <v>-63.09919</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7996,23 +7996,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>24</v>
       </c>
       <c r="V101" t="n">
-        <v>46.8323</v>
+        <v>44.48487</v>
       </c>
       <c r="W101" t="n">
-        <v>-60.6939</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8072,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T102" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U102" t="n">
         <v>24</v>
       </c>
       <c r="V102" t="n">
-        <v>44.48487</v>
+        <v>46.8323</v>
       </c>
       <c r="W102" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.6939</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8098,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8157,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>45.76567</v>
+        <v>46.36255</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.56882</v>
+        <v>-60.59174</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8309,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.36255</v>
+        <v>46.19179</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.59174</v>
+        <v>-60.57356</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8326,12 +8326,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8385,14 +8385,14 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>46.19179</v>
+        <v>45.77335</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.57356</v>
+        <v>-60.56515</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I107" t="b">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8461,14 +8461,14 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>46.38378</v>
+        <v>45.78604</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.80809</v>
+        <v>-60.56073</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="V108" t="n">
-        <v>45.77335</v>
+        <v>45.76567</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56515</v>
+        <v>-60.56882</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8613,14 +8613,14 @@
         <v>22</v>
       </c>
       <c r="V109" t="n">
-        <v>45.77589</v>
+        <v>46.38378</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.56156</v>
+        <v>-60.80809</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -8765,10 +8765,10 @@
         <v>22</v>
       </c>
       <c r="V111" t="n">
-        <v>45.78604</v>
+        <v>45.77589</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56073</v>
+        <v>-60.56156</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
@@ -8993,10 +8993,10 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.13397</v>
+        <v>46.12356</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.92758</v>
+        <v>-60.91944</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9069,14 +9069,14 @@
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.13658</v>
+        <v>46.17933</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.91312</v>
+        <v>-60.84528</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9103,12 +9103,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I116" t="b">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -9136,23 +9136,23 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T116" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U116" t="n">
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.5331</v>
+        <v>46.13897</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.79089</v>
+        <v>-60.9063</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9221,14 +9221,14 @@
         <v>21</v>
       </c>
       <c r="V117" t="n">
-        <v>46.26487</v>
+        <v>46.13658</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.65547</v>
+        <v>-60.91312</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9297,14 +9297,14 @@
         <v>21</v>
       </c>
       <c r="V118" t="n">
-        <v>46.13897</v>
+        <v>46.26487</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.9063</v>
+        <v>-60.65547</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9373,14 +9373,14 @@
         <v>21</v>
       </c>
       <c r="V119" t="n">
-        <v>46.17933</v>
+        <v>46.13397</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.84528</v>
+        <v>-60.92758</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I120" t="b">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9440,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T120" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U120" t="n">
         <v>21</v>
       </c>
       <c r="V120" t="n">
-        <v>46.12356</v>
+        <v>46.5331</v>
       </c>
       <c r="W120" t="n">
-        <v>-60.91944</v>
+        <v>-60.79089</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -9516,23 +9516,23 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T121" t="n">
-        <v>275</v>
+        <v>175</v>
       </c>
       <c r="U121" t="n">
         <v>20</v>
       </c>
       <c r="V121" t="n">
-        <v>44.08614</v>
+        <v>44.82095</v>
       </c>
       <c r="W121" t="n">
-        <v>-65.76729</v>
+        <v>-64.29518</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9846,12 +9846,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -9896,23 +9896,23 @@
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T126" t="n">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="U126" t="n">
         <v>20</v>
       </c>
       <c r="V126" t="n">
-        <v>44.82095</v>
+        <v>44.08614</v>
       </c>
       <c r="W126" t="n">
-        <v>-64.29518</v>
+        <v>-65.76729</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9981,10 +9981,10 @@
         <v>19</v>
       </c>
       <c r="V127" t="n">
-        <v>46.42609</v>
+        <v>46.4303</v>
       </c>
       <c r="W127" t="n">
-        <v>-60.94179</v>
+        <v>-60.9406</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
@@ -10209,10 +10209,10 @@
         <v>19</v>
       </c>
       <c r="V130" t="n">
-        <v>46.4303</v>
+        <v>46.42609</v>
       </c>
       <c r="W130" t="n">
-        <v>-60.9406</v>
+        <v>-60.94179</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X130"/>
+  <dimension ref="A1:X126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -629,10 +629,10 @@
         <v>48</v>
       </c>
       <c r="V2" t="n">
-        <v>46.24705</v>
+        <v>46.24531</v>
       </c>
       <c r="W2" t="n">
-        <v>-60.89558</v>
+        <v>-60.89421</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24531</v>
+        <v>46.24705</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89421</v>
+        <v>-60.89558</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.57026</v>
+        <v>46.56569</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91194</v>
+        <v>-60.91812</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -874,12 +874,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -891,7 +891,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -924,23 +924,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U6" t="n">
         <v>47</v>
       </c>
       <c r="V6" t="n">
-        <v>46.04374</v>
+        <v>46.56838</v>
       </c>
       <c r="W6" t="n">
-        <v>-60.45777</v>
+        <v>-60.91763</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1000,19 +1000,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.56826</v>
+        <v>46.57009</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.90602</v>
+        <v>-60.91782</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1085,10 +1085,10 @@
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.04734</v>
+        <v>46.04374</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.45799</v>
+        <v>-60.45777</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.56837</v>
+        <v>46.04734</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.91202</v>
+        <v>-60.45799</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1380,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.57009</v>
+        <v>46.56826</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.91782</v>
+        <v>-60.90602</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.56838</v>
+        <v>46.57026</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91763</v>
+        <v>-60.91194</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1532,19 +1532,19 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.56569</v>
+        <v>46.56837</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.91812</v>
+        <v>-60.91202</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
+          <t>Springhaven Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K07-001</t>
+          <t>P13-008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pb, Cu, Sb, Zn</t>
+          <t>Pb, Zn, Ag, Cd, Bi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ag 220.00 g/t, Sb 0.801%, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1849,14 +1849,14 @@
         <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>46.28</v>
+        <v>43.91009</v>
       </c>
       <c r="W18" t="n">
-        <v>-60.56967</v>
+        <v>-65.87437</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Springhaven Pb, Zn, Ag Occurrence</t>
+          <t>Meat Cove Zn Deposit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P13-008</t>
+          <t>N02-002</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Cd, Bi</t>
+          <t>Zn, Mg, Cd, Ge, Ga, Pb, Cu</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ag 340.00 g/t, Pb 16.8%, Zn 0.938%, Bi 0.0544%, Cd 0.0844%</t>
+          <t>Zn 50%, Au 0.04 g/t, Cu 0.0075%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1922,17 +1922,17 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V19" t="n">
-        <v>43.91009</v>
+        <v>47.00887</v>
       </c>
       <c r="W19" t="n">
-        <v>-65.87437</v>
+        <v>-60.59389</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=P13-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=N02-002</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Meat Cove Zn Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>N02-002</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zn, Mg, Cd, Ge, Ga, Pb, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2130,11 +2130,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Zn 50%, Au 0.04 g/t, Cu 0.0075%</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
@@ -2150,17 +2146,17 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>47.00887</v>
+        <v>45.19199</v>
       </c>
       <c r="W22" t="n">
-        <v>-60.59389</v>
+        <v>-63.39818</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=N02-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2187,12 +2183,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2206,11 +2202,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -2220,23 +2212,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U23" t="n">
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>46.27323</v>
+        <v>45.92081</v>
       </c>
       <c r="W23" t="n">
-        <v>-60.69898</v>
+        <v>-61.3156</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2238,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2301,14 +2293,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>45.28773</v>
+        <v>45.16925</v>
       </c>
       <c r="W24" t="n">
-        <v>-63.47906</v>
+        <v>-63.38899</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2310,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Shubenacadie River Ti Sands - Bar 9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>E03-097</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2364,23 +2356,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U25" t="n">
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>45.30934</v>
+        <v>45.20532</v>
       </c>
       <c r="W25" t="n">
-        <v>-63.47675</v>
+        <v>-63.41063</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2382,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2407,7 +2399,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2445,14 +2437,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.33992</v>
+        <v>45.3433</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.48499</v>
+        <v>-63.53544</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2454,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2517,14 +2509,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.24369</v>
+        <v>45.28773</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.44116</v>
+        <v>-63.47906</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2526,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2580,23 +2572,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.24778</v>
+        <v>45.26713</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.4519</v>
+        <v>-63.45492</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2623,7 +2615,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2661,14 +2653,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.16925</v>
+        <v>45.33992</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.38899</v>
+        <v>-63.48499</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2670,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 9</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E03-097</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2724,23 +2716,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T30" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.20532</v>
+        <v>45.30934</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.41063</v>
+        <v>-63.47675</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-097</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2742,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2805,14 +2797,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.19199</v>
+        <v>45.24369</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.39818</v>
+        <v>-63.44116</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2814,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2839,7 +2831,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2868,23 +2860,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T32" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.92081</v>
+        <v>45.24778</v>
       </c>
       <c r="W32" t="n">
-        <v>-61.3156</v>
+        <v>-63.4519</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2886,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2940,23 +2932,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U33" t="n">
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.26713</v>
+        <v>45.2282</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.45492</v>
+        <v>-63.41684</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3102,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3127,7 +3119,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3165,14 +3157,14 @@
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>45.2282</v>
+        <v>46.21501</v>
       </c>
       <c r="W36" t="n">
-        <v>-63.41684</v>
+        <v>-61.11267</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3174,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Price Point Cu, Sb, Zn, Pb, Ag Occurrence</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>K07-001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3199,12 +3191,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Pb, Cu, Sb, Zn</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3218,7 +3210,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Sb 0.801%, Ag 220.00 g/t, Cu 2%, Co 0.0015%, Cr 0.018%</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
@@ -3234,17 +3230,17 @@
         <v>325</v>
       </c>
       <c r="U37" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V37" t="n">
-        <v>46.21501</v>
+        <v>46.28</v>
       </c>
       <c r="W37" t="n">
-        <v>-61.11267</v>
+        <v>-60.56967</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-001</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3250,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>K06-008</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3271,12 +3267,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>W, Cu, Ag, Au</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3290,7 +3286,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
@@ -3306,17 +3306,17 @@
         <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V38" t="n">
-        <v>45.3433</v>
+        <v>46.24968</v>
       </c>
       <c r="W38" t="n">
-        <v>-63.53544</v>
+        <v>-61.04986</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Murphy Brook W, Cu, Ag, Au Occurrence</t>
+          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>K06-008</t>
+          <t>O09-002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>W, Cu, Ag, Au</t>
+          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>W 0.231%, Ag 33.90 g/t, Au 0.30 g/t, Te 0.0024%, Cr 0.046%</t>
+          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
         <v>34</v>
       </c>
       <c r="V39" t="n">
-        <v>46.24968</v>
+        <v>43.70849</v>
       </c>
       <c r="W39" t="n">
-        <v>-61.04986</v>
+        <v>-66.06631</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K06-008</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pinkney Point Cu, Mo, W, Sn, As Occurrence</t>
+          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>O09-002</t>
+          <t>A09-032</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cu, Mo, As, Sn, W, Be, F, Ag, Bi</t>
+          <t>Sn, Cu, Zn, As</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>W 0.993%, Sn 0.0562%, Cu 0.123%, Ag 1.90 g/t, Be 0.00063%</t>
+          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3461,14 +3461,14 @@
         <v>34</v>
       </c>
       <c r="V40" t="n">
-        <v>43.70849</v>
+        <v>44.60164</v>
       </c>
       <c r="W40" t="n">
-        <v>-66.06631</v>
+        <v>-64.05405</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=O09-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fox Point Sn-Cu-Ag-Zn-As Occurrence</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A09-032</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sn, Cu, Zn, As</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sn 71%, Cu 2.28%, Ag 29.40 g/t, Bi 0.0394%, Zn 0.34%</t>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3537,14 +3537,14 @@
         <v>34</v>
       </c>
       <c r="V41" t="n">
-        <v>44.60164</v>
+        <v>46.27323</v>
       </c>
       <c r="W41" t="n">
-        <v>-64.05405</v>
+        <v>-60.69898</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A09-032</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -3841,10 +3841,10 @@
         <v>33</v>
       </c>
       <c r="V45" t="n">
-        <v>45.77981</v>
+        <v>45.77979</v>
       </c>
       <c r="W45" t="n">
-        <v>-61.14953</v>
+        <v>-61.1485</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         <v>33</v>
       </c>
       <c r="V46" t="n">
-        <v>45.77979</v>
+        <v>45.77981</v>
       </c>
       <c r="W46" t="n">
-        <v>-61.1485</v>
+        <v>-61.14953</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Whetstone Lake Quarry</t>
+          <t>Miller Lake Au District</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A10-029</t>
+          <t>E01-003</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Siltstone, Whetstone</t>
+          <t>Au, As, Zn, Pb</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3980,23 +3980,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U47" t="n">
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>44.64923</v>
+        <v>45.0448</v>
       </c>
       <c r="W47" t="n">
-        <v>-64.65634</v>
+        <v>-62.16418</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4006,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clam Harbour Gold Mine</t>
+          <t>Ingonish River Cu, Fe Occurrence</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>D10-001</t>
+          <t>K10-001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -4042,7 +4042,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
@@ -4052,23 +4056,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T48" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U48" t="n">
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>44.73395</v>
+        <v>46.61843</v>
       </c>
       <c r="W48" t="n">
-        <v>-62.91588</v>
+        <v>-60.52086</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4082,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pleasant River Barrens Au District</t>
+          <t>Whetstone Lake Quarry</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A07-005</t>
+          <t>A10-029</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4095,7 +4099,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Siltstone, Whetstone</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4124,23 +4128,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U49" t="n">
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>44.43925</v>
+        <v>44.64923</v>
       </c>
       <c r="W49" t="n">
-        <v>-64.78243999999999</v>
+        <v>-64.65634</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-029</t>
         </is>
       </c>
     </row>
@@ -4205,10 +4209,10 @@
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>44.73589</v>
+        <v>44.73395</v>
       </c>
       <c r="W50" t="n">
-        <v>-62.91248</v>
+        <v>-62.91588</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -4277,10 +4281,10 @@
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>44.7357</v>
+        <v>44.73589</v>
       </c>
       <c r="W51" t="n">
-        <v>-62.91338</v>
+        <v>-62.91248</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -4294,12 +4298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Whale Creek Manganese Mine</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>E04-015</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4311,7 +4315,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4340,23 +4344,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U52" t="n">
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>45.2409</v>
+        <v>46.14468</v>
       </c>
       <c r="W52" t="n">
-        <v>-63.99801</v>
+        <v>-60.44769</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ingonish River Cu, Fe Occurrence</t>
+          <t>Ingraham Mine Ba, Fe Occurrence</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K10-001</t>
+          <t>K01-012</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4383,12 +4387,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Ba, Fe</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4402,11 +4406,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Co 0.0026%, Cr 0.003%, Cu 0.0352%, Ga 0.002%</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
@@ -4425,14 +4425,14 @@
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>46.61843</v>
+        <v>46.13825</v>
       </c>
       <c r="W53" t="n">
-        <v>-60.52086</v>
+        <v>-60.45019</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
         </is>
       </c>
     </row>
@@ -4501,10 +4501,10 @@
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>45.9844</v>
+        <v>45.98426</v>
       </c>
       <c r="W54" t="n">
-        <v>-60.94402</v>
+        <v>-60.95151</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -4518,12 +4518,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Miller Lake Au District</t>
+          <t>Jubilee Zn, Pb Deposit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E01-003</t>
+          <t>F15-007</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Au, As, Zn, Pb</t>
+          <t>Zn, Pb, Cu, Ba</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4554,7 +4554,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
@@ -4564,23 +4568,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U55" t="n">
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>45.0448</v>
+        <v>45.9844</v>
       </c>
       <c r="W55" t="n">
-        <v>-62.16418</v>
+        <v>-60.94402</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E01-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Barteaux Brook Occurrence</t>
+          <t>Cow Bay Au District</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A14-022</t>
+          <t>D11-001</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4607,12 +4611,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4626,16 +4630,8 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>drill-tested</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0</v>
@@ -4644,23 +4640,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U56" t="n">
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>44.83208</v>
+        <v>44.631</v>
       </c>
       <c r="W56" t="n">
-        <v>-65.14026</v>
+        <v>-63.44222</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4666,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cow Bay Au District</t>
+          <t>Glencoe Road Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D11-001</t>
+          <t>F14-046</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4687,12 +4683,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -4706,7 +4702,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
@@ -4716,23 +4716,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U57" t="n">
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>44.631</v>
+        <v>45.91475</v>
       </c>
       <c r="W57" t="n">
-        <v>-63.44222</v>
+        <v>-61.23041</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D11-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Clam Harbour Gold Mine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>D10-001</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4788,23 +4788,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T58" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U58" t="n">
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>44.89125</v>
+        <v>44.7357</v>
       </c>
       <c r="W58" t="n">
-        <v>-65.04064</v>
+        <v>-62.91338</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D10-001</t>
         </is>
       </c>
     </row>
@@ -4869,10 +4869,10 @@
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>44.89109</v>
+        <v>44.9011</v>
       </c>
       <c r="W59" t="n">
-        <v>-65.03443</v>
+        <v>-65.00793</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>44.88953</v>
+        <v>44.89232</v>
       </c>
       <c r="W60" t="n">
-        <v>-65.04628</v>
+        <v>-65.04106</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -4958,12 +4958,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Wheadon Property Mn Occurrence</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E05-021</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5004,23 +5004,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T61" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U61" t="n">
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>44.88409</v>
+        <v>45.26005</v>
       </c>
       <c r="W61" t="n">
-        <v>-65.05318</v>
+        <v>-63.93614</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wheadon Property Mn Occurrence</t>
+          <t>Tennycape Estuary Mn Occurrence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>E05-021</t>
+          <t>E05-018</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -5076,23 +5076,23 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U62" t="n">
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>45.26005</v>
+        <v>45.27248</v>
       </c>
       <c r="W62" t="n">
-        <v>-63.93614</v>
+        <v>-63.87936</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-021</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5102,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
+          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A14-003</t>
+          <t>E06-004</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fe, Mn</t>
+          <t>Fe, Ba</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5157,14 +5157,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>44.9011</v>
+        <v>45.27275</v>
       </c>
       <c r="W63" t="n">
-        <v>-65.00793</v>
+        <v>-63.23508</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tennycape Estuary Mn Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>E05-018</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5220,23 +5220,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T64" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U64" t="n">
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>45.27248</v>
+        <v>44.88409</v>
       </c>
       <c r="W64" t="n">
-        <v>-63.87936</v>
+        <v>-65.05318</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5301,10 +5301,10 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>44.89232</v>
+        <v>44.89125</v>
       </c>
       <c r="W65" t="n">
-        <v>-65.04106</v>
+        <v>-65.04064</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5373,14 +5373,14 @@
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>46.14468</v>
+        <v>44.89109</v>
       </c>
       <c r="W66" t="n">
-        <v>-60.44769</v>
+        <v>-65.03443</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ingraham Mine Ba, Fe Occurrence</t>
+          <t>Pleasant River Barrens Au District</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>K01-012</t>
+          <t>A07-005</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ba, Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5436,23 +5436,23 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U67" t="n">
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>46.13825</v>
+        <v>44.43925</v>
       </c>
       <c r="W67" t="n">
-        <v>-60.45019</v>
+        <v>-64.78243999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-012</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A07-005</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jubilee Zn, Pb Deposit</t>
+          <t>Barteaux Brook Occurrence</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>F15-007</t>
+          <t>A14-022</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Zn, Pb, Cu, Ba</t>
+          <t>Cu, Mo, Zn, Bi, Au, Ag</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -5500,10 +5500,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Zn 1.34%, Pb 1%, Te 0.0016%, Ag 1.30 g/t, Cd 0.0162%</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>Co 0.0828%, Zn 0.757%, Ag 0.63 g/t, Cu 0.00025%, Pb 0.00222%</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>drill-tested</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>0</v>
@@ -5512,23 +5516,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T68" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U68" t="n">
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>45.98426</v>
+        <v>44.83208</v>
       </c>
       <c r="W68" t="n">
-        <v>-60.95151</v>
+        <v>-65.14026</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-022</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5542,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Glencoe Road Pb, Zn Occurrence</t>
+          <t>Nictaux-Torbrook Fe, Mn Deposits</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>F14-046</t>
+          <t>A14-003</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5555,12 +5559,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe, Mn</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -5574,11 +5578,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Au 3.00 g/t, Ga 0.0034%, Te 0.0018%, Ag 0.30 g/t, Cd 0.00058%</t>
-        </is>
-      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
@@ -5597,14 +5597,14 @@
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>45.91475</v>
+        <v>44.88953</v>
       </c>
       <c r="W69" t="n">
-        <v>-61.23041</v>
+        <v>-65.04628</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A14-003</t>
         </is>
       </c>
     </row>
@@ -5614,12 +5614,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hirschfield Pb Prospect</t>
+          <t>Whale Creek Manganese Mine</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>E08-020</t>
+          <t>E04-015</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pb, Ag</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5660,23 +5660,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U70" t="n">
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>45.25157</v>
+        <v>45.2409</v>
       </c>
       <c r="W70" t="n">
-        <v>-62.11656</v>
+        <v>-63.99801</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E04-015</t>
         </is>
       </c>
     </row>
@@ -5686,12 +5686,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arisaig Brook</t>
+          <t>Hirschfield Pb Prospect</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>E09-017</t>
+          <t>E08-020</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Ag</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5732,23 +5732,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T71" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U71" t="n">
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>45.73558</v>
+        <v>45.25157</v>
       </c>
       <c r="W71" t="n">
-        <v>-62.16591</v>
+        <v>-62.11656</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E08-020</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5758,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chambers and Pearson Fe Deposits (Brookfield Fe Mines)</t>
+          <t>Arisaig Brook</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>E06-004</t>
+          <t>E09-017</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fe, Ba</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5813,14 +5813,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>45.27275</v>
+        <v>45.73558</v>
       </c>
       <c r="W72" t="n">
-        <v>-63.23508</v>
+        <v>-62.16591</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E09-017</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Glenbervie Pb Mine</t>
+          <t>Websters Iron Mine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>E07-018</t>
+          <t>E07-007</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pb, Zn</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5876,23 +5876,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T73" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U73" t="n">
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>45.28513</v>
+        <v>45.4857</v>
       </c>
       <c r="W73" t="n">
-        <v>-62.93781</v>
+        <v>-62.52535</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
         </is>
       </c>
     </row>
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Websters Iron Mine</t>
+          <t>Glenbervie Pb Mine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E07-007</t>
+          <t>E07-018</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Pb, Zn</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5948,23 +5948,23 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T74" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U74" t="n">
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>45.4857</v>
+        <v>45.28513</v>
       </c>
       <c r="W74" t="n">
-        <v>-62.52535</v>
+        <v>-62.93781</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-018</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chisholm Brook Cu Mine (W. A. McPherson's Mine)</t>
+          <t>Meaghers Grant As Prospect</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E13-001</t>
+          <t>D14-002</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5991,12 +5991,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cu, Ag, U</t>
+          <t>As, Au</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -6010,7 +6010,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Au 1.18 g/t, Ag 1.00 g/t, W 0.0002%</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="n">
@@ -6020,23 +6024,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U75" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V75" t="n">
-        <v>45.82</v>
+        <v>44.90921</v>
       </c>
       <c r="W75" t="n">
-        <v>-63.68532</v>
+        <v>-63.22057</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E13-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-002</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6050,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Meaghers Grant As Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>D14-002</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -6063,12 +6067,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>As, Au</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I76" t="b">
@@ -6084,7 +6088,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Au 1.18 g/t, Ag 1.00 g/t, W 0.0002%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -6102,17 +6106,17 @@
         <v>325</v>
       </c>
       <c r="U76" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V76" t="n">
-        <v>44.90921</v>
+        <v>46.44956</v>
       </c>
       <c r="W76" t="n">
-        <v>-63.22057</v>
+        <v>-60.57775</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D14-002</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6122,12 +6126,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6139,7 +6143,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6160,7 +6164,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6181,14 +6185,14 @@
         <v>26</v>
       </c>
       <c r="V77" t="n">
-        <v>46.29595</v>
+        <v>46.51873</v>
       </c>
       <c r="W77" t="n">
-        <v>-60.9372</v>
+        <v>-60.64496</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6215,12 +6219,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -6236,7 +6240,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6257,14 +6261,14 @@
         <v>26</v>
       </c>
       <c r="V78" t="n">
-        <v>46.44638</v>
+        <v>46.51529</v>
       </c>
       <c r="W78" t="n">
-        <v>-60.57242</v>
+        <v>-60.64417</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6333,10 +6337,10 @@
         <v>26</v>
       </c>
       <c r="V79" t="n">
-        <v>46.51873</v>
+        <v>46.51478</v>
       </c>
       <c r="W79" t="n">
-        <v>-60.64496</v>
+        <v>-60.64575</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -6350,12 +6354,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6367,12 +6371,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6388,7 +6392,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6409,14 +6413,14 @@
         <v>26</v>
       </c>
       <c r="V80" t="n">
-        <v>46.45026</v>
+        <v>44.6087</v>
       </c>
       <c r="W80" t="n">
-        <v>-60.5768</v>
+        <v>-65.6011</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6430,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6443,12 +6447,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6464,7 +6468,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6485,14 +6489,14 @@
         <v>26</v>
       </c>
       <c r="V81" t="n">
-        <v>46.44219</v>
+        <v>44.62709</v>
       </c>
       <c r="W81" t="n">
-        <v>-60.58706</v>
+        <v>-65.56032</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6506,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Clementsport Fe Deposits</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>A12-010</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6519,12 +6523,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I82" t="b">
@@ -6540,7 +6544,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6561,14 +6565,14 @@
         <v>26</v>
       </c>
       <c r="V82" t="n">
-        <v>46.44885</v>
+        <v>44.6151</v>
       </c>
       <c r="W82" t="n">
-        <v>-60.58676</v>
+        <v>-65.58083999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
         </is>
       </c>
     </row>
@@ -6578,12 +6582,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6595,12 +6599,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I83" t="b">
@@ -6616,7 +6620,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6637,14 +6641,14 @@
         <v>26</v>
       </c>
       <c r="V83" t="n">
-        <v>46.44952</v>
+        <v>45.39942</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.57801</v>
+        <v>-61.45755</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6658,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>South Manchester Fe Mine (Callahan Mine)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>F06-004</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6671,12 +6675,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I84" t="b">
@@ -6692,7 +6696,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6713,14 +6717,14 @@
         <v>26</v>
       </c>
       <c r="V84" t="n">
-        <v>46.4638</v>
+        <v>45.40126</v>
       </c>
       <c r="W84" t="n">
-        <v>-60.57034</v>
+        <v>-61.45511</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6734,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>McMillan Brook Skarn</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-009</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6747,12 +6751,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Cu, As, Mo, W, Sn, F</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I85" t="b">
@@ -6768,7 +6772,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6789,14 +6793,14 @@
         <v>26</v>
       </c>
       <c r="V85" t="n">
-        <v>46.44956</v>
+        <v>46.51814</v>
       </c>
       <c r="W85" t="n">
-        <v>-60.57775</v>
+        <v>-60.655</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
         </is>
       </c>
     </row>
@@ -6865,10 +6869,10 @@
         <v>26</v>
       </c>
       <c r="V86" t="n">
-        <v>46.51478</v>
+        <v>46.51553</v>
       </c>
       <c r="W86" t="n">
-        <v>-60.64575</v>
+        <v>-60.64503</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -6882,12 +6886,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6899,12 +6903,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I87" t="b">
@@ -6920,7 +6924,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6941,14 +6945,14 @@
         <v>26</v>
       </c>
       <c r="V87" t="n">
-        <v>46.51529</v>
+        <v>46.44952</v>
       </c>
       <c r="W87" t="n">
-        <v>-60.64417</v>
+        <v>-60.57801</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -6958,12 +6962,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6975,12 +6979,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6996,7 +7000,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -7017,14 +7021,14 @@
         <v>26</v>
       </c>
       <c r="V88" t="n">
-        <v>46.51553</v>
+        <v>46.4638</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.64503</v>
+        <v>-60.57034</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7038,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>McMillan Brook Skarn</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K10-009</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7051,12 +7055,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cu, As, Mo, W, Sn, F</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7072,7 +7076,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Ag 0.60 g/t, Au 0.01 g/t, Be 0.0003%, Bi 2e-05%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -7093,14 +7097,14 @@
         <v>26</v>
       </c>
       <c r="V89" t="n">
-        <v>46.51814</v>
+        <v>46.44638</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.655</v>
+        <v>-60.57242</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7114,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -7127,12 +7131,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -7148,7 +7152,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7169,14 +7173,14 @@
         <v>26</v>
       </c>
       <c r="V90" t="n">
-        <v>45.40126</v>
+        <v>46.45026</v>
       </c>
       <c r="W90" t="n">
-        <v>-61.45511</v>
+        <v>-60.5768</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7186,12 +7190,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -7203,12 +7207,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -7224,7 +7228,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7245,14 +7249,14 @@
         <v>26</v>
       </c>
       <c r="V91" t="n">
-        <v>46.2982</v>
+        <v>46.44885</v>
       </c>
       <c r="W91" t="n">
-        <v>-60.94257</v>
+        <v>-60.58676</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7266,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ryan Brook  Pb, Zn Occurrence</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>K07-049</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7279,12 +7283,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu, Fe, Ag, Mo</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -7300,7 +7304,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Ag 13.80 g/t, Cd 2e-06%, Co 0.0015%, Cr 0.0076%, Cu 0.0047%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7321,14 +7325,14 @@
         <v>26</v>
       </c>
       <c r="V92" t="n">
-        <v>46.29966</v>
+        <v>46.44219</v>
       </c>
       <c r="W92" t="n">
-        <v>-60.94836</v>
+        <v>-60.58706</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-049</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7342,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7355,12 +7359,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -7376,7 +7380,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7394,17 +7398,17 @@
         <v>325</v>
       </c>
       <c r="U93" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V93" t="n">
-        <v>44.62709</v>
+        <v>44.68634</v>
       </c>
       <c r="W93" t="n">
-        <v>-65.56032</v>
+        <v>-63.97235</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7418,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7431,12 +7435,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7452,7 +7456,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7470,17 +7474,17 @@
         <v>325</v>
       </c>
       <c r="U94" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V94" t="n">
-        <v>44.6087</v>
+        <v>44.69021</v>
       </c>
       <c r="W94" t="n">
-        <v>-65.6011</v>
+        <v>-63.97107</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7494,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Clementsport Fe Deposits</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A12-010</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7507,12 +7511,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7528,7 +7532,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ag 0.10 g/t, Co 0.0041%, Cu 0.0017%, Ni 0.0073%, Pb 0.01%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7546,17 +7550,17 @@
         <v>325</v>
       </c>
       <c r="U95" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V95" t="n">
-        <v>44.6151</v>
+        <v>44.69007</v>
       </c>
       <c r="W95" t="n">
-        <v>-65.58083999999999</v>
+        <v>-63.97154</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A12-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7570,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>South Manchester Fe Mine (Callahan Mine)</t>
+          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>F06-004</t>
+          <t>E03-092</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7583,12 +7587,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Cu, Ag</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Past Producer</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I96" t="b">
@@ -7604,7 +7608,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Ag 2.00 g/t, Au 0.04 g/t, Be 0.00015%, Cd 2.3e-05%, Co 0.0006%</t>
+          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7616,23 +7620,23 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T96" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U96" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V96" t="n">
-        <v>45.39942</v>
+        <v>45.1087</v>
       </c>
       <c r="W96" t="n">
-        <v>-61.45755</v>
+        <v>-63.09919</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F06-004</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
         </is>
       </c>
     </row>
@@ -7642,12 +7646,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7659,7 +7663,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7680,7 +7684,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7692,23 +7696,23 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T97" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U97" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V97" t="n">
-        <v>44.69007</v>
+        <v>46.8323</v>
       </c>
       <c r="W97" t="n">
-        <v>-63.97154</v>
+        <v>-60.6939</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7722,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7735,7 +7739,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7756,7 +7760,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -7774,17 +7778,17 @@
         <v>325</v>
       </c>
       <c r="U98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V98" t="n">
-        <v>44.68634</v>
+        <v>44.48487</v>
       </c>
       <c r="W98" t="n">
-        <v>-63.97235</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7798,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -7811,7 +7815,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7832,7 +7836,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -7850,17 +7854,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V99" t="n">
-        <v>44.69021</v>
+        <v>45.78604</v>
       </c>
       <c r="W99" t="n">
-        <v>-63.97107</v>
+        <v>-60.56073</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -7870,12 +7874,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Millen Mountain Cu Occurrence (Branch Road)</t>
+          <t>West Branch North River Ag-Bi Occurrence</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>E03-092</t>
+          <t>K07-088</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7887,12 +7891,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cu, Ag</t>
+          <t>Ag, Bi</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -7908,7 +7912,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Cu 1.63%, Ag 3.10 g/t, Au 0.00 g/t, Cd 2e-05%, Co 0.001%</t>
+          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7920,23 +7924,23 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T100" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V100" t="n">
-        <v>45.1087</v>
+        <v>46.38378</v>
       </c>
       <c r="W100" t="n">
-        <v>-63.09919</v>
+        <v>-60.80809</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-092</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7950,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>Barachois River Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>K07-053</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7963,7 +7967,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Cu, Mo, Fe</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7984,7 +7988,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -8002,17 +8006,17 @@
         <v>325</v>
       </c>
       <c r="U101" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V101" t="n">
-        <v>44.48487</v>
+        <v>46.36255</v>
       </c>
       <c r="W101" t="n">
-        <v>-65.96890999999999</v>
+        <v>-60.59174</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8026,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8039,7 +8043,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8060,7 +8064,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8072,23 +8076,23 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T102" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U102" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V102" t="n">
-        <v>46.8323</v>
+        <v>46.19179</v>
       </c>
       <c r="W102" t="n">
-        <v>-60.6939</v>
+        <v>-60.57356</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8102,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Barachois River Cu, Mo Occurrence</t>
+          <t>Beinn Scalpie Cu Occurrence</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>K07-053</t>
+          <t>K02-006</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8115,7 +8119,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cu, Mo, Fe</t>
+          <t>Cu, Fe</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8136,7 +8140,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Cu 0.655%, Mo 0.0531%, Co 0.0015%, Cr 0.0009%, Ni 0.0002%</t>
+          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8157,14 +8161,14 @@
         <v>22</v>
       </c>
       <c r="V103" t="n">
-        <v>46.36255</v>
+        <v>46.18983</v>
       </c>
       <c r="W103" t="n">
-        <v>-60.59174</v>
+        <v>-60.57015</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-053</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8178,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -8191,7 +8195,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8212,7 +8216,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -8233,14 +8237,14 @@
         <v>22</v>
       </c>
       <c r="V104" t="n">
-        <v>46.18983</v>
+        <v>45.77335</v>
       </c>
       <c r="W104" t="n">
-        <v>-60.57015</v>
+        <v>-60.56515</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8254,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Beinn Scalpie Cu Occurrence</t>
+          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>K02-006</t>
+          <t>F15-022</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8267,7 +8271,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cu, Fe</t>
+          <t>Pb, Zn, Sr, Ba</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8288,7 +8292,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Cu 0.817%, Cr 0.046%, Sb 3e-05%, Sc 0.00075%, Ag 1.00 g/t</t>
+          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8309,14 +8313,14 @@
         <v>22</v>
       </c>
       <c r="V105" t="n">
-        <v>46.19179</v>
+        <v>45.77827</v>
       </c>
       <c r="W105" t="n">
-        <v>-60.57356</v>
+        <v>-60.55927</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
         </is>
       </c>
     </row>
@@ -8385,10 +8389,10 @@
         <v>22</v>
       </c>
       <c r="V106" t="n">
-        <v>45.77335</v>
+        <v>45.76567</v>
       </c>
       <c r="W106" t="n">
-        <v>-60.56515</v>
+        <v>-60.56882</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
@@ -8461,10 +8465,10 @@
         <v>22</v>
       </c>
       <c r="V107" t="n">
-        <v>45.78604</v>
+        <v>45.77589</v>
       </c>
       <c r="W107" t="n">
-        <v>-60.56073</v>
+        <v>-60.56156</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
@@ -8478,12 +8482,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K02-046</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8495,7 +8499,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Pb, Zn, As, Au</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8516,7 +8520,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -8534,17 +8538,17 @@
         <v>325</v>
       </c>
       <c r="U108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V108" t="n">
-        <v>45.76567</v>
+        <v>46.17933</v>
       </c>
       <c r="W108" t="n">
-        <v>-60.56882</v>
+        <v>-60.84528</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8558,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>West Branch North River Ag-Bi Occurrence</t>
+          <t>Conneach Brook Road North Au Occurrence</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>K07-088</t>
+          <t>K10-090</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8571,12 +8575,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ag, Bi</t>
+          <t>Au, Fe</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8592,7 +8596,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Ag 46.60 g/t, Bi 0.0779%, Au 0.02 g/t, Cd 6e-05%, Co 0.00029%</t>
+          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8604,23 +8608,23 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T109" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U109" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V109" t="n">
-        <v>46.38378</v>
+        <v>46.5331</v>
       </c>
       <c r="W109" t="n">
-        <v>-60.80809</v>
+        <v>-60.79089</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-088</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8634,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>Upper Mount Thom Cu, Zn, Ni, Ag Occurrence</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>E10-033</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -8647,7 +8651,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Cu, Zn, Ni, Ag, Cd, Fe</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8668,7 +8672,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Cu 0.124%, Ni 0.0967%, Co 0.0231%, Zn 0.306%, Ag 5.50 g/t</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -8680,23 +8684,23 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T110" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U110" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V110" t="n">
-        <v>45.77827</v>
+        <v>45.51103</v>
       </c>
       <c r="W110" t="n">
-        <v>-60.55927</v>
+        <v>-62.96642</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E10-033</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8710,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Loch Lomond Lake Pb, Zn, Sr, Ba Occurrence</t>
+          <t>The Three Sisters (Lake O'Law)  Au, W, As Occurrence</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>F15-022</t>
+          <t>K07-050</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8723,7 +8727,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pb, Zn, Sr, Ba</t>
+          <t>Au, W, As, Cu</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8744,7 +8748,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Ag 26.30 g/t, Zn 0.937%, Pb 1%, Te 0.002%, Bi 0.001%</t>
+          <t>Au 0.63 g/t, Ag 0.80 g/t, Cd 0.00131%, Co 0.0038%, Cr 0.0144%</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -8762,17 +8766,17 @@
         <v>325</v>
       </c>
       <c r="U111" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V111" t="n">
-        <v>45.77589</v>
+        <v>46.28434</v>
       </c>
       <c r="W111" t="n">
-        <v>-60.56156</v>
+        <v>-60.95243</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-022</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-050</t>
         </is>
       </c>
     </row>
@@ -8782,12 +8786,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The Three Sisters (Lake O'Law)  Au, W, As Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>K07-050</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8799,7 +8803,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Au, W, As, Cu</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8820,7 +8824,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Au 0.63 g/t, Ag 0.80 g/t, Cd 0.00131%, Co 0.0038%, Cr 0.0144%</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -8841,14 +8845,14 @@
         <v>21</v>
       </c>
       <c r="V112" t="n">
-        <v>46.28434</v>
+        <v>46.13897</v>
       </c>
       <c r="W112" t="n">
-        <v>-60.95243</v>
+        <v>-60.9063</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-050</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -8858,12 +8862,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Upper Mount Thom Cu, Zn, Ni, Ag Occurrence</t>
+          <t>Yankee Line Road Ba, Pb Occurrence</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>E10-033</t>
+          <t>K02-014</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8875,7 +8879,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cu, Zn, Ni, Ag, Cd, Fe</t>
+          <t>Ba, Cu, Sr, F, Pb</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8896,7 +8900,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Cu 0.124%, Ni 0.0967%, Co 0.0231%, Zn 0.306%, Ag 5.50 g/t</t>
+          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -8908,23 +8912,23 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T113" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U113" t="n">
         <v>21</v>
       </c>
       <c r="V113" t="n">
-        <v>45.51103</v>
+        <v>46.13397</v>
       </c>
       <c r="W113" t="n">
-        <v>-62.96642</v>
+        <v>-60.92758</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E10-033</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
         </is>
       </c>
     </row>
@@ -8993,10 +8997,10 @@
         <v>21</v>
       </c>
       <c r="V114" t="n">
-        <v>46.12356</v>
+        <v>46.13658</v>
       </c>
       <c r="W114" t="n">
-        <v>-60.91944</v>
+        <v>-60.91312</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -9010,12 +9014,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Crowdis Mountain Pb-Zn Ocurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>K02-046</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9027,7 +9031,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pb, Zn, As, Au</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9048,7 +9052,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Au 0.44 g/t, Co 0.0016%, Cr 0.0051%, Cu 0.0039%, Ga 0.001%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -9069,14 +9073,14 @@
         <v>21</v>
       </c>
       <c r="V115" t="n">
-        <v>46.17933</v>
+        <v>46.26487</v>
       </c>
       <c r="W115" t="n">
-        <v>-60.84528</v>
+        <v>-60.65547</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-046</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
@@ -9145,10 +9149,10 @@
         <v>21</v>
       </c>
       <c r="V116" t="n">
-        <v>46.13897</v>
+        <v>46.12356</v>
       </c>
       <c r="W116" t="n">
-        <v>-60.9063</v>
+        <v>-60.91944</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
@@ -9162,12 +9166,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>East Kemptville As Occurrence</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>A04-027</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9179,7 +9183,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>As</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9200,7 +9204,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9212,23 +9216,23 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T117" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U117" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V117" t="n">
-        <v>46.13658</v>
+        <v>44.08614</v>
       </c>
       <c r="W117" t="n">
-        <v>-60.91312</v>
+        <v>-65.76729</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9242,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Shaw Lakes Cu, Pb Occurrence</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>F15-016</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9255,7 +9259,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9276,7 +9280,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Cu 0.213%, Pb 0.328%, Ag 1.10 g/t, Bi 0.0006%, Cd 0.00016%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9294,17 +9298,17 @@
         <v>325</v>
       </c>
       <c r="U118" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V118" t="n">
-        <v>46.26487</v>
+        <v>45.76921</v>
       </c>
       <c r="W118" t="n">
-        <v>-60.65547</v>
+        <v>-60.55671</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-016</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9318,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Yankee Line Road Ba, Pb Occurrence</t>
+          <t>Cape Saint Mary Stibnite Occurrence</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>K02-014</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9331,7 +9335,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ba, Cu, Sr, F, Pb</t>
+          <t>Sb, As, Ni, Cu, Ag</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9352,7 +9356,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Ag 35.00 g/t, Rb 0.0035%, Sb 7e-05%, Sc 0.00048%, U 0.00075%</t>
+          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9364,23 +9368,23 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T119" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V119" t="n">
-        <v>46.13397</v>
+        <v>44.13698</v>
       </c>
       <c r="W119" t="n">
-        <v>-60.92758</v>
+        <v>-66.19927</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K02-014</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9394,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Conneach Brook Road North Au Occurrence</t>
+          <t>French Village Lake Zn, As Occurrence</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>K10-090</t>
+          <t>F16-038</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9407,12 +9411,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Au, Fe</t>
+          <t>Zn, As, Cu, Cd</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I120" t="b">
@@ -9428,7 +9432,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Au 0.65 g/t, Be 0.0002%, Bi 5e-05%, Co 0.00159%, Cu 0.00376%</t>
+          <t>Zn 0.966%, Ag 1.20 g/t, Au 0.02 g/t, Bi 0.0018%, Cd 0.00352%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9440,23 +9444,23 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T120" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U120" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V120" t="n">
-        <v>46.5331</v>
+        <v>45.90959</v>
       </c>
       <c r="W120" t="n">
-        <v>-60.79089</v>
+        <v>-60.27694</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-090</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-038</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9470,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Leminster Molybdenum</t>
+          <t>Cape Saint Mary Stibnite Occurrence</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>A16-009</t>
+          <t>B01-010</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9483,7 +9487,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>As, Fe, Mo, Bi</t>
+          <t>Sb, As, Ni, Cu, Ag</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9504,7 +9508,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
+          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -9516,23 +9520,23 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T121" t="n">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="U121" t="n">
         <v>20</v>
       </c>
       <c r="V121" t="n">
-        <v>44.82095</v>
+        <v>44.115</v>
       </c>
       <c r="W121" t="n">
-        <v>-64.29518</v>
+        <v>-66.19658</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
         </is>
       </c>
     </row>
@@ -9542,12 +9546,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>French Village Lake Zn, As Occurrence</t>
+          <t>Leminster Molybdenum</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>F16-038</t>
+          <t>A16-009</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9559,7 +9563,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Zn, As, Cu, Cd</t>
+          <t>As, Fe, Mo, Bi</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9580,7 +9584,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Zn 0.966%, Ag 1.20 g/t, Au 0.02 g/t, Bi 0.0018%, Cd 0.00352%</t>
+          <t>Mo 0.0961%, Bi 0.0174%, Cr 0.00715%, Cu 0.00145%, Nb 0.00051%</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -9592,23 +9596,23 @@
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T122" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U122" t="n">
         <v>20</v>
       </c>
       <c r="V122" t="n">
-        <v>45.90959</v>
+        <v>44.82095</v>
       </c>
       <c r="W122" t="n">
-        <v>-60.27694</v>
+        <v>-64.29518</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-038</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-009</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9622,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cape Saint Mary Stibnite Occurrence</t>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B01-010</t>
+          <t>K07-019</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9635,7 +9639,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sb, As, Ni, Cu, Ag</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9656,7 +9660,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -9668,23 +9672,23 @@
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T123" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U123" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V123" t="n">
-        <v>44.13698</v>
+        <v>46.4303</v>
       </c>
       <c r="W123" t="n">
-        <v>-66.19927</v>
+        <v>-60.9406</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>
       </c>
     </row>
@@ -9694,12 +9698,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shaw Lakes Cu, Pb Occurrence</t>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>F15-016</t>
+          <t>K07-019</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9732,7 +9736,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Cu 0.213%, Pb 0.328%, Ag 1.10 g/t, Bi 0.0006%, Cd 0.00016%</t>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -9750,17 +9754,17 @@
         <v>325</v>
       </c>
       <c r="U124" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V124" t="n">
-        <v>45.76921</v>
+        <v>46.42609</v>
       </c>
       <c r="W124" t="n">
-        <v>-60.55671</v>
+        <v>-60.94179</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9774,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cape Saint Mary Stibnite Occurrence</t>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B01-010</t>
+          <t>K07-019</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9787,7 +9791,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sb, As, Ni, Cu, Ag</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9808,7 +9812,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Cu 0.25%, Ni 0.0542%, Co 0.018%</t>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9820,23 +9824,23 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T125" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U125" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V125" t="n">
-        <v>44.115</v>
+        <v>46.42607</v>
       </c>
       <c r="W125" t="n">
-        <v>-66.19658</v>
+        <v>-60.94075</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=B01-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>
       </c>
     </row>
@@ -9846,12 +9850,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>East Kemptville As Occurrence</t>
+          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>A04-027</t>
+          <t>K07-019</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9863,7 +9867,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>As</t>
+          <t>Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9884,7 +9888,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Au 0.35 g/t, Ag 0.60 g/t, Cd 8e-06%, Cu 0.0046%, Pb 0.0051%</t>
+          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -9896,325 +9900,21 @@
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T126" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U126" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V126" t="n">
-        <v>44.08614</v>
+        <v>46.42622</v>
       </c>
       <c r="W126" t="n">
-        <v>-65.76729</v>
+        <v>-60.93906</v>
       </c>
       <c r="X126" t="inlineStr">
-        <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A04-027</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>K07-019</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I127" t="b">
-        <v>1</v>
-      </c>
-      <c r="J127" t="b">
-        <v>0</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="n">
-        <v>13</v>
-      </c>
-      <c r="T127" t="n">
-        <v>325</v>
-      </c>
-      <c r="U127" t="n">
-        <v>19</v>
-      </c>
-      <c r="V127" t="n">
-        <v>46.4303</v>
-      </c>
-      <c r="W127" t="n">
-        <v>-60.9406</v>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>K07-019</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I128" t="b">
-        <v>1</v>
-      </c>
-      <c r="J128" t="b">
-        <v>0</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="n">
-        <v>13</v>
-      </c>
-      <c r="T128" t="n">
-        <v>325</v>
-      </c>
-      <c r="U128" t="n">
-        <v>19</v>
-      </c>
-      <c r="V128" t="n">
-        <v>46.42622</v>
-      </c>
-      <c r="W128" t="n">
-        <v>-60.93906</v>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>K07-019</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I129" t="b">
-        <v>1</v>
-      </c>
-      <c r="J129" t="b">
-        <v>0</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="n">
-        <v>13</v>
-      </c>
-      <c r="T129" t="n">
-        <v>325</v>
-      </c>
-      <c r="U129" t="n">
-        <v>19</v>
-      </c>
-      <c r="V129" t="n">
-        <v>46.42607</v>
-      </c>
-      <c r="W129" t="n">
-        <v>-60.94075</v>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Sugarloaf Mountain Cu, Pb, Zn Occurrence</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>K07-019</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Cu, Pb, Zn</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Occurrence</t>
-        </is>
-      </c>
-      <c r="I130" t="b">
-        <v>1</v>
-      </c>
-      <c r="J130" t="b">
-        <v>0</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>Zn 0.696%, Pb 0.697%, Cd 0.00113%, Co 0.002%, Cr 0.0118%</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="n">
-        <v>13</v>
-      </c>
-      <c r="T130" t="n">
-        <v>325</v>
-      </c>
-      <c r="U130" t="n">
-        <v>19</v>
-      </c>
-      <c r="V130" t="n">
-        <v>46.42609</v>
-      </c>
-      <c r="W130" t="n">
-        <v>-60.94179</v>
-      </c>
-      <c r="X130" t="inlineStr">
         <is>
           <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-019</t>
         </is>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -629,10 +629,10 @@
         <v>48</v>
       </c>
       <c r="V2" t="n">
-        <v>46.24531</v>
+        <v>46.24541</v>
       </c>
       <c r="W2" t="n">
-        <v>-60.89421</v>
+        <v>-60.89447</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>46.24705</v>
+        <v>46.24531</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.89558</v>
+        <v>-60.89421</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.24541</v>
+        <v>46.24705</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.89447</v>
+        <v>-60.89558</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>47</v>
       </c>
       <c r="V5" t="n">
-        <v>46.56569</v>
+        <v>46.56826</v>
       </c>
       <c r="W5" t="n">
-        <v>-60.91812</v>
+        <v>-60.90602</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -924,19 +924,19 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>47</v>
       </c>
       <c r="V6" t="n">
-        <v>46.56838</v>
+        <v>46.56646</v>
       </c>
       <c r="W6" t="n">
-        <v>-60.91763</v>
+        <v>-60.90609</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1000,19 +1000,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
         <v>47</v>
       </c>
       <c r="V7" t="n">
-        <v>46.57009</v>
+        <v>46.56838</v>
       </c>
       <c r="W7" t="n">
-        <v>-60.91782</v>
+        <v>-60.91763</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1085,10 +1085,10 @@
         <v>47</v>
       </c>
       <c r="V8" t="n">
-        <v>46.04374</v>
+        <v>46.04734</v>
       </c>
       <c r="W8" t="n">
-        <v>-60.45777</v>
+        <v>-60.45799</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K01-016</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Cu, Pb, Zn</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1152,23 +1152,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U9" t="n">
         <v>47</v>
       </c>
       <c r="V9" t="n">
-        <v>46.04734</v>
+        <v>46.57009</v>
       </c>
       <c r="W9" t="n">
-        <v>-60.45799</v>
+        <v>-60.91782</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K10-045</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Cu, Pb, Zn, As, Au, Ag</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1228,23 +1228,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
         <v>47</v>
       </c>
       <c r="V10" t="n">
-        <v>46.37314</v>
+        <v>46.56569</v>
       </c>
       <c r="W10" t="n">
-        <v>-60.59907</v>
+        <v>-60.91812</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
         </is>
       </c>
     </row>
@@ -1304,19 +1304,19 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
         <v>47</v>
       </c>
       <c r="V11" t="n">
-        <v>46.56646</v>
+        <v>46.57026</v>
       </c>
       <c r="W11" t="n">
-        <v>-60.90609</v>
+        <v>-60.91194</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         <v>47</v>
       </c>
       <c r="V12" t="n">
-        <v>46.56826</v>
+        <v>46.56837</v>
       </c>
       <c r="W12" t="n">
-        <v>-60.90602</v>
+        <v>-60.91202</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1456,23 +1456,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>47</v>
       </c>
       <c r="V13" t="n">
-        <v>46.57026</v>
+        <v>46.37494</v>
       </c>
       <c r="W13" t="n">
-        <v>-60.91194</v>
+        <v>-60.59901</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jim Campbells Barren  Au, Cu, Pb, Zn, As Prospects</t>
+          <t>Barachois River  Au,  Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>K10-045</t>
+          <t>K07-030</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cu, Pb, Zn, As, Au, Ag</t>
+          <t>Au, Ag, Te, Cu, Pb</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Au 10.00 g/t, Cu 1.07%, Ag 50.00 g/t, Bi 0.0808%, Zn 0.348%</t>
+          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1541,14 +1541,14 @@
         <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>46.56837</v>
+        <v>46.37314</v>
       </c>
       <c r="W14" t="n">
-        <v>-60.91202</v>
+        <v>-60.59907</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-045</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Barachois River  Au,  Ag, Te Occurrence</t>
+          <t>Rear Boisdale (McAdams Lake)  Ag, As, Au, Cu, Fe, Pb, Zn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K07-030</t>
+          <t>K01-016</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Au, Ag, Te, Cu, Pb</t>
+          <t>Ag, As, Au, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Au 16.70 g/t, Te 0.0315%, Ag 27.80 g/t, Bi 0.0029%, Co 0.0035%</t>
+          <t>Au 408.00 g/t, Ag 50.00 g/t, Zn 2%, Pb 1%, Cd 0.0505%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1608,23 +1608,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U15" t="n">
         <v>47</v>
       </c>
       <c r="V15" t="n">
-        <v>46.37494</v>
+        <v>46.04374</v>
       </c>
       <c r="W15" t="n">
-        <v>-60.59901</v>
+        <v>-60.45777</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-030</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K01-016</t>
         </is>
       </c>
     </row>
@@ -2001,10 +2001,10 @@
         <v>38</v>
       </c>
       <c r="V20" t="n">
-        <v>47.00366</v>
+        <v>47.00545</v>
       </c>
       <c r="W20" t="n">
-        <v>-60.59004</v>
+        <v>-60.58996</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2077,10 +2077,10 @@
         <v>38</v>
       </c>
       <c r="V21" t="n">
-        <v>47.00545</v>
+        <v>47.00366</v>
       </c>
       <c r="W21" t="n">
-        <v>-60.58996</v>
+        <v>-60.59004</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 10</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>E03-098</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2140,23 +2140,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U22" t="n">
         <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>45.19199</v>
+        <v>46.09672</v>
       </c>
       <c r="W22" t="n">
-        <v>-63.39818</v>
+        <v>-61.13017</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2212,23 +2212,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>45.92081</v>
+        <v>46.21501</v>
       </c>
       <c r="W23" t="n">
-        <v>-61.3156</v>
+        <v>-61.11267</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 11</t>
+          <t>Shubenacadie River Ti Sands - Bar 7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E03-099</t>
+          <t>E03-095</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2293,14 +2293,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>45.16925</v>
+        <v>45.24369</v>
       </c>
       <c r="W24" t="n">
-        <v>-63.38899</v>
+        <v>-63.44116</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 1</t>
+          <t>Shubenacadie River Ti Sands - Bar 10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>E05-068</t>
+          <t>E03-098</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2437,14 +2437,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>45.3433</v>
+        <v>45.19199</v>
       </c>
       <c r="W26" t="n">
-        <v>-63.53544</v>
+        <v>-63.39818</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-098</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 4</t>
+          <t>Shubenacadie River Ti Sands - Bar 11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>E06-071</t>
+          <t>E03-099</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2509,14 +2509,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>45.28773</v>
+        <v>45.16925</v>
       </c>
       <c r="W27" t="n">
-        <v>-63.47906</v>
+        <v>-63.38899</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-099</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 5</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>E06-072</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ti, Fe, Zr, Garnet</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2572,23 +2572,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T28" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U28" t="n">
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>45.26713</v>
+        <v>45.92081</v>
       </c>
       <c r="W28" t="n">
-        <v>-63.45492</v>
+        <v>-61.3156</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 2</t>
+          <t>Shubenacadie River Ti Sands - Bar 8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>E06-069</t>
+          <t>E03-096</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ti, Zr, Fe, Garnet</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2653,14 +2653,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>45.33992</v>
+        <v>45.2282</v>
       </c>
       <c r="W29" t="n">
-        <v>-63.48499</v>
+        <v>-63.41684</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-069</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 3</t>
+          <t>Shubenacadie River Ti Sands - Bar 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>E06-070</t>
+          <t>E05-068</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2716,23 +2716,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U30" t="n">
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>45.30934</v>
+        <v>45.3433</v>
       </c>
       <c r="W30" t="n">
-        <v>-63.47675</v>
+        <v>-63.53544</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E05-068</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 7</t>
+          <t>Shubenacadie River Ti Sands - Bar 4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>E03-095</t>
+          <t>E06-071</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2797,14 +2797,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>45.24369</v>
+        <v>45.28773</v>
       </c>
       <c r="W31" t="n">
-        <v>-63.44116</v>
+        <v>-63.47906</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-095</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-071</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 6</t>
+          <t>Shubenacadie River Ti Sands - Bar 5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>E03-094</t>
+          <t>E06-072</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2860,23 +2860,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U32" t="n">
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>45.24778</v>
+        <v>45.26713</v>
       </c>
       <c r="W32" t="n">
-        <v>-63.4519</v>
+        <v>-63.45492</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-072</t>
         </is>
       </c>
     </row>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shubenacadie River Ti Sands - Bar 8</t>
+          <t>Shubenacadie River Ti Sands - Bar 6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>E03-096</t>
+          <t>E03-094</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2941,14 +2941,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>45.2282</v>
+        <v>45.24778</v>
       </c>
       <c r="W33" t="n">
-        <v>-63.41684</v>
+        <v>-63.4519</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-096</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E03-094</t>
         </is>
       </c>
     </row>
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-070</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Fe, Zr, Garnet</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3004,23 +3004,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T34" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>46.09672</v>
+        <v>45.30934</v>
       </c>
       <c r="W34" t="n">
-        <v>-61.13017</v>
+        <v>-63.47675</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E06-070</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Shubenacadie River Ti Sands - Bar 2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>E06-069</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Ti, Zr, Fe, Garnet</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3076,23 +3076,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U35" t="n">
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>46.18739</v>
+        <v>45.33992</v>
       </c>
       <c r="W35" t="n">
-        <v>-61.15217</v>
+        <v>-63.48499</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/